--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G13">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G34">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G51">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G54">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G61">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G74">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="Q82">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA82">
         <v>1.85</v>
       </c>
       <c r="AB82">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC82">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>3.09</v>
+        <v>4</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA83">
         <v>1.85</v>
       </c>
       <c r="AB83">
+        <v>1.89</v>
+      </c>
+      <c r="AC83">
+        <v>3.08</v>
+      </c>
+      <c r="AD83">
+        <v>1.36</v>
+      </c>
+      <c r="AE83">
+        <v>1.08</v>
+      </c>
+      <c r="AF83">
+        <v>1.79</v>
+      </c>
+      <c r="AG83">
+        <v>2</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.3</v>
+      </c>
+      <c r="AK83">
         <v>1.95</v>
-      </c>
-      <c r="AC83">
-        <v>0</v>
-      </c>
-      <c r="AD83">
-        <v>0</v>
-      </c>
-      <c r="AE83">
-        <v>0</v>
-      </c>
-      <c r="AF83">
-        <v>0</v>
-      </c>
-      <c r="AG83">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>0</v>
-      </c>
-      <c r="AK83">
-        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G105">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G124">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G149">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G41">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G106">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G129">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G134">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G141">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G124">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU154"/>
+  <dimension ref="A1:AU156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-04 13:15:00</t>
+          <t>2026-09-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-04 13:30:00</t>
+          <t>2026-09-04 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-04 14:00:00</t>
+          <t>2026-09-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-04 14:30:00</t>
+          <t>2026-09-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-04 15:00:00</t>
+          <t>2026-09-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G69">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G70">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G76">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G78">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G79">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G81">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G82">
@@ -13671,17 +13671,17 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N82">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="Q83">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA83">
         <v>1.85</v>
       </c>
       <c r="AB83">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC83">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84">
@@ -13997,68 +13997,68 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G86">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G136">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G149">
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-09-04 21:30:00</t>
+          <t>2026-09-04 21:00:00</t>
         </is>
       </c>
     </row>
@@ -24875,27 +24875,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G151">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-09-04 21:30:00</t>
+          <t>2026-09-04 21:00:00</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G152">
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G153">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-09-04 22:30:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -25364,156 +25364,482 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154">
+        <v>0</v>
+      </c>
+      <c r="U154">
+        <v>0</v>
+      </c>
+      <c r="V154">
+        <v>0</v>
+      </c>
+      <c r="W154">
+        <v>0</v>
+      </c>
+      <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154">
+        <v>0</v>
+      </c>
+      <c r="Z154">
+        <v>0</v>
+      </c>
+      <c r="AA154">
+        <v>0</v>
+      </c>
+      <c r="AB154">
+        <v>0</v>
+      </c>
+      <c r="AC154">
+        <v>0</v>
+      </c>
+      <c r="AD154">
+        <v>0</v>
+      </c>
+      <c r="AE154">
+        <v>0</v>
+      </c>
+      <c r="AF154">
+        <v>0</v>
+      </c>
+      <c r="AG154">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
+        <v>0</v>
+      </c>
+      <c r="AK154">
+        <v>0</v>
+      </c>
+      <c r="AL154">
+        <v>0</v>
+      </c>
+      <c r="AM154">
+        <v>-1</v>
+      </c>
+      <c r="AN154">
+        <v>-1</v>
+      </c>
+      <c r="AO154">
+        <v>-1</v>
+      </c>
+      <c r="AP154">
+        <v>-1</v>
+      </c>
+      <c r="AQ154">
+        <v>0</v>
+      </c>
+      <c r="AR154">
+        <v>0</v>
+      </c>
+      <c r="AS154">
+        <v>0</v>
+      </c>
+      <c r="AT154">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <v>0</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155">
+        <v>0</v>
+      </c>
+      <c r="U155">
+        <v>0</v>
+      </c>
+      <c r="V155">
+        <v>0</v>
+      </c>
+      <c r="W155">
+        <v>0</v>
+      </c>
+      <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155">
+        <v>0</v>
+      </c>
+      <c r="Z155">
+        <v>0</v>
+      </c>
+      <c r="AA155">
+        <v>0</v>
+      </c>
+      <c r="AB155">
+        <v>0</v>
+      </c>
+      <c r="AC155">
+        <v>0</v>
+      </c>
+      <c r="AD155">
+        <v>0</v>
+      </c>
+      <c r="AE155">
+        <v>0</v>
+      </c>
+      <c r="AF155">
+        <v>0</v>
+      </c>
+      <c r="AG155">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
+        <v>0</v>
+      </c>
+      <c r="AK155">
+        <v>0</v>
+      </c>
+      <c r="AL155">
+        <v>0</v>
+      </c>
+      <c r="AM155">
+        <v>-1</v>
+      </c>
+      <c r="AN155">
+        <v>-1</v>
+      </c>
+      <c r="AO155">
+        <v>-1</v>
+      </c>
+      <c r="AP155">
+        <v>-1</v>
+      </c>
+      <c r="AQ155">
+        <v>0</v>
+      </c>
+      <c r="AR155">
+        <v>0</v>
+      </c>
+      <c r="AS155">
+        <v>0</v>
+      </c>
+      <c r="AT155">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="inlineStr">
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>0</v>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154">
-        <v>0</v>
-      </c>
-      <c r="U154">
-        <v>0</v>
-      </c>
-      <c r="V154">
-        <v>0</v>
-      </c>
-      <c r="W154">
-        <v>0</v>
-      </c>
-      <c r="X154">
-        <v>0</v>
-      </c>
-      <c r="Y154">
-        <v>0</v>
-      </c>
-      <c r="Z154">
-        <v>0</v>
-      </c>
-      <c r="AA154">
-        <v>0</v>
-      </c>
-      <c r="AB154">
-        <v>0</v>
-      </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-      <c r="AK154">
-        <v>0</v>
-      </c>
-      <c r="AL154">
-        <v>0</v>
-      </c>
-      <c r="AM154">
-        <v>-1</v>
-      </c>
-      <c r="AN154">
-        <v>-1</v>
-      </c>
-      <c r="AO154">
-        <v>-1</v>
-      </c>
-      <c r="AP154">
-        <v>-1</v>
-      </c>
-      <c r="AQ154">
-        <v>0</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
-        <v>0</v>
-      </c>
-      <c r="AT154">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <v>0</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156">
+        <v>0</v>
+      </c>
+      <c r="U156">
+        <v>0</v>
+      </c>
+      <c r="V156">
+        <v>0</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="X156">
+        <v>0</v>
+      </c>
+      <c r="Y156">
+        <v>0</v>
+      </c>
+      <c r="Z156">
+        <v>0</v>
+      </c>
+      <c r="AA156">
+        <v>0</v>
+      </c>
+      <c r="AB156">
+        <v>0</v>
+      </c>
+      <c r="AC156">
+        <v>0</v>
+      </c>
+      <c r="AD156">
+        <v>0</v>
+      </c>
+      <c r="AE156">
+        <v>0</v>
+      </c>
+      <c r="AF156">
+        <v>0</v>
+      </c>
+      <c r="AG156">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>0</v>
+      </c>
+      <c r="AK156">
+        <v>0</v>
+      </c>
+      <c r="AL156">
+        <v>0</v>
+      </c>
+      <c r="AM156">
+        <v>-1</v>
+      </c>
+      <c r="AN156">
+        <v>-1</v>
+      </c>
+      <c r="AO156">
+        <v>-1</v>
+      </c>
+      <c r="AP156">
+        <v>-1</v>
+      </c>
+      <c r="AQ156">
+        <v>0</v>
+      </c>
+      <c r="AR156">
+        <v>0</v>
+      </c>
+      <c r="AS156">
+        <v>0</v>
+      </c>
+      <c r="AT156">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G143">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G24">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU156"/>
+  <dimension ref="A1:AU152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-04 07:30:00</t>
+          <t>2026-09-04 07:00:00</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bình Phước</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-04 08:00:00</t>
+          <t>2026-09-04 07:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pattani</t>
+          <t>Bình Phước</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-04 09:00:00</t>
+          <t>2026-09-04 08:00:00</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Pattani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G7">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-04 09:15:00</t>
+          <t>2026-09-04 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:00</t>
+          <t>2026-09-04 09:15:00</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kelantan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Kelantan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-04 10:45:00</t>
+          <t>2026-09-04 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-04 11:00:00</t>
+          <t>2026-09-04 10:45:00</t>
         </is>
       </c>
     </row>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-04 12:15:00</t>
+          <t>2026-09-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-04 13:00:00</t>
+          <t>2026-09-04 11:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-04 13:00:00</t>
+          <t>2026-09-04 12:15:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-04 13:15:00</t>
+          <t>2026-09-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-04 13:15:00</t>
+          <t>2026-09-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-04 13:30:00</t>
+          <t>2026-09-04 13:15:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-04 13:30:00</t>
+          <t>2026-09-04 13:15:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G32">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-04 14:00:00</t>
+          <t>2026-09-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-04 14:00:00</t>
+          <t>2026-09-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-04 14:00:00</t>
+          <t>2026-09-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40">
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-04 14:30:00</t>
+          <t>2026-09-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-04 14:30:00</t>
+          <t>2026-09-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-04 14:30:00</t>
+          <t>2026-09-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-04 15:00:00</t>
+          <t>2026-09-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-04 15:00:00</t>
+          <t>2026-09-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-04 15:00:00</t>
+          <t>2026-09-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G59">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G66">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G70">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,27 +11998,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12324,27 +12324,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,22 +12818,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G77">
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G80">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G81">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G82">
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G83">
@@ -13834,17 +13834,17 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N83">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N85">
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,17 +14486,17 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,68 +14649,68 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="Q90">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T90">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U90">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V90">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z90">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA90">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC90">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD90">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG90">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK90">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-04 17:00:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,27 +15095,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,27 +16725,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,27 +24386,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G148">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24549,27 +24549,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G149">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24712,27 +24712,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G150">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24875,27 +24875,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G151">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G152">
@@ -25188,658 +25188,6 @@
         <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>0</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153">
-        <v>0</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>0</v>
-      </c>
-      <c r="Z153">
-        <v>0</v>
-      </c>
-      <c r="AA153">
-        <v>0</v>
-      </c>
-      <c r="AB153">
-        <v>0</v>
-      </c>
-      <c r="AC153">
-        <v>0</v>
-      </c>
-      <c r="AD153">
-        <v>0</v>
-      </c>
-      <c r="AE153">
-        <v>0</v>
-      </c>
-      <c r="AF153">
-        <v>0</v>
-      </c>
-      <c r="AG153">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>0</v>
-      </c>
-      <c r="AK153">
-        <v>0</v>
-      </c>
-      <c r="AL153">
-        <v>0</v>
-      </c>
-      <c r="AM153">
-        <v>-1</v>
-      </c>
-      <c r="AN153">
-        <v>-1</v>
-      </c>
-      <c r="AO153">
-        <v>-1</v>
-      </c>
-      <c r="AP153">
-        <v>-1</v>
-      </c>
-      <c r="AQ153">
-        <v>0</v>
-      </c>
-      <c r="AR153">
-        <v>0</v>
-      </c>
-      <c r="AS153">
-        <v>0</v>
-      </c>
-      <c r="AT153">
-        <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>0</v>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154">
-        <v>0</v>
-      </c>
-      <c r="U154">
-        <v>0</v>
-      </c>
-      <c r="V154">
-        <v>0</v>
-      </c>
-      <c r="W154">
-        <v>0</v>
-      </c>
-      <c r="X154">
-        <v>0</v>
-      </c>
-      <c r="Y154">
-        <v>0</v>
-      </c>
-      <c r="Z154">
-        <v>0</v>
-      </c>
-      <c r="AA154">
-        <v>0</v>
-      </c>
-      <c r="AB154">
-        <v>0</v>
-      </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-      <c r="AK154">
-        <v>0</v>
-      </c>
-      <c r="AL154">
-        <v>0</v>
-      </c>
-      <c r="AM154">
-        <v>-1</v>
-      </c>
-      <c r="AN154">
-        <v>-1</v>
-      </c>
-      <c r="AO154">
-        <v>-1</v>
-      </c>
-      <c r="AP154">
-        <v>-1</v>
-      </c>
-      <c r="AQ154">
-        <v>0</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
-        <v>0</v>
-      </c>
-      <c r="AT154">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>0</v>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155">
-        <v>0</v>
-      </c>
-      <c r="U155">
-        <v>0</v>
-      </c>
-      <c r="V155">
-        <v>0</v>
-      </c>
-      <c r="W155">
-        <v>0</v>
-      </c>
-      <c r="X155">
-        <v>0</v>
-      </c>
-      <c r="Y155">
-        <v>0</v>
-      </c>
-      <c r="Z155">
-        <v>0</v>
-      </c>
-      <c r="AA155">
-        <v>0</v>
-      </c>
-      <c r="AB155">
-        <v>0</v>
-      </c>
-      <c r="AC155">
-        <v>0</v>
-      </c>
-      <c r="AD155">
-        <v>0</v>
-      </c>
-      <c r="AE155">
-        <v>0</v>
-      </c>
-      <c r="AF155">
-        <v>0</v>
-      </c>
-      <c r="AG155">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>0</v>
-      </c>
-      <c r="AK155">
-        <v>0</v>
-      </c>
-      <c r="AL155">
-        <v>0</v>
-      </c>
-      <c r="AM155">
-        <v>-1</v>
-      </c>
-      <c r="AN155">
-        <v>-1</v>
-      </c>
-      <c r="AO155">
-        <v>-1</v>
-      </c>
-      <c r="AP155">
-        <v>-1</v>
-      </c>
-      <c r="AQ155">
-        <v>0</v>
-      </c>
-      <c r="AR155">
-        <v>0</v>
-      </c>
-      <c r="AS155">
-        <v>0</v>
-      </c>
-      <c r="AT155">
-        <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>0</v>
-      </c>
-      <c r="R156">
-        <v>0</v>
-      </c>
-      <c r="S156">
-        <v>0</v>
-      </c>
-      <c r="T156">
-        <v>0</v>
-      </c>
-      <c r="U156">
-        <v>0</v>
-      </c>
-      <c r="V156">
-        <v>0</v>
-      </c>
-      <c r="W156">
-        <v>0</v>
-      </c>
-      <c r="X156">
-        <v>0</v>
-      </c>
-      <c r="Y156">
-        <v>0</v>
-      </c>
-      <c r="Z156">
-        <v>0</v>
-      </c>
-      <c r="AA156">
-        <v>0</v>
-      </c>
-      <c r="AB156">
-        <v>0</v>
-      </c>
-      <c r="AC156">
-        <v>0</v>
-      </c>
-      <c r="AD156">
-        <v>0</v>
-      </c>
-      <c r="AE156">
-        <v>0</v>
-      </c>
-      <c r="AF156">
-        <v>0</v>
-      </c>
-      <c r="AG156">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>0</v>
-      </c>
-      <c r="AK156">
-        <v>0</v>
-      </c>
-      <c r="AL156">
-        <v>0</v>
-      </c>
-      <c r="AM156">
-        <v>-1</v>
-      </c>
-      <c r="AN156">
-        <v>-1</v>
-      </c>
-      <c r="AO156">
-        <v>-1</v>
-      </c>
-      <c r="AP156">
-        <v>-1</v>
-      </c>
-      <c r="AQ156">
-        <v>0</v>
-      </c>
-      <c r="AR156">
-        <v>0</v>
-      </c>
-      <c r="AS156">
-        <v>0</v>
-      </c>
-      <c r="AT156">
-        <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU152"/>
+  <dimension ref="A1:AU147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G38">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G55">
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G74">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G84">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G86">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,17 +14486,17 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N87">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="O88">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="Q88">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S88">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T88">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U88">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V88">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z88">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA88">
         <v>1.85</v>
       </c>
       <c r="AB88">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC88">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK88">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,68 +14812,68 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G95">
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S96">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T96">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U96">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V96">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y96">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z96">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD96">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG96">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK96">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-09-04 17:00:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G99">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G142">
@@ -23571,27 +23571,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23734,27 +23734,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23897,27 +23897,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,27 +24060,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G146">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -24223,27 +24223,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G147">
@@ -24373,821 +24373,6 @@
         <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>0</v>
-      </c>
-      <c r="R148">
-        <v>0</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-      <c r="U148">
-        <v>0</v>
-      </c>
-      <c r="V148">
-        <v>0</v>
-      </c>
-      <c r="W148">
-        <v>0</v>
-      </c>
-      <c r="X148">
-        <v>0</v>
-      </c>
-      <c r="Y148">
-        <v>0</v>
-      </c>
-      <c r="Z148">
-        <v>0</v>
-      </c>
-      <c r="AA148">
-        <v>0</v>
-      </c>
-      <c r="AB148">
-        <v>0</v>
-      </c>
-      <c r="AC148">
-        <v>0</v>
-      </c>
-      <c r="AD148">
-        <v>0</v>
-      </c>
-      <c r="AE148">
-        <v>0</v>
-      </c>
-      <c r="AF148">
-        <v>0</v>
-      </c>
-      <c r="AG148">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>0</v>
-      </c>
-      <c r="AK148">
-        <v>0</v>
-      </c>
-      <c r="AL148">
-        <v>0</v>
-      </c>
-      <c r="AM148">
-        <v>-1</v>
-      </c>
-      <c r="AN148">
-        <v>-1</v>
-      </c>
-      <c r="AO148">
-        <v>-1</v>
-      </c>
-      <c r="AP148">
-        <v>-1</v>
-      </c>
-      <c r="AQ148">
-        <v>0</v>
-      </c>
-      <c r="AR148">
-        <v>0</v>
-      </c>
-      <c r="AS148">
-        <v>0</v>
-      </c>
-      <c r="AT148">
-        <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>0</v>
-      </c>
-      <c r="R149">
-        <v>0</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149">
-        <v>0</v>
-      </c>
-      <c r="U149">
-        <v>0</v>
-      </c>
-      <c r="V149">
-        <v>0</v>
-      </c>
-      <c r="W149">
-        <v>0</v>
-      </c>
-      <c r="X149">
-        <v>0</v>
-      </c>
-      <c r="Y149">
-        <v>0</v>
-      </c>
-      <c r="Z149">
-        <v>0</v>
-      </c>
-      <c r="AA149">
-        <v>0</v>
-      </c>
-      <c r="AB149">
-        <v>0</v>
-      </c>
-      <c r="AC149">
-        <v>0</v>
-      </c>
-      <c r="AD149">
-        <v>0</v>
-      </c>
-      <c r="AE149">
-        <v>0</v>
-      </c>
-      <c r="AF149">
-        <v>0</v>
-      </c>
-      <c r="AG149">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>0</v>
-      </c>
-      <c r="AK149">
-        <v>0</v>
-      </c>
-      <c r="AL149">
-        <v>0</v>
-      </c>
-      <c r="AM149">
-        <v>-1</v>
-      </c>
-      <c r="AN149">
-        <v>-1</v>
-      </c>
-      <c r="AO149">
-        <v>-1</v>
-      </c>
-      <c r="AP149">
-        <v>-1</v>
-      </c>
-      <c r="AQ149">
-        <v>0</v>
-      </c>
-      <c r="AR149">
-        <v>0</v>
-      </c>
-      <c r="AS149">
-        <v>0</v>
-      </c>
-      <c r="AT149">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-      <c r="U150">
-        <v>0</v>
-      </c>
-      <c r="V150">
-        <v>0</v>
-      </c>
-      <c r="W150">
-        <v>0</v>
-      </c>
-      <c r="X150">
-        <v>0</v>
-      </c>
-      <c r="Y150">
-        <v>0</v>
-      </c>
-      <c r="Z150">
-        <v>0</v>
-      </c>
-      <c r="AA150">
-        <v>0</v>
-      </c>
-      <c r="AB150">
-        <v>0</v>
-      </c>
-      <c r="AC150">
-        <v>0</v>
-      </c>
-      <c r="AD150">
-        <v>0</v>
-      </c>
-      <c r="AE150">
-        <v>0</v>
-      </c>
-      <c r="AF150">
-        <v>0</v>
-      </c>
-      <c r="AG150">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-      <c r="AK150">
-        <v>0</v>
-      </c>
-      <c r="AL150">
-        <v>0</v>
-      </c>
-      <c r="AM150">
-        <v>-1</v>
-      </c>
-      <c r="AN150">
-        <v>-1</v>
-      </c>
-      <c r="AO150">
-        <v>-1</v>
-      </c>
-      <c r="AP150">
-        <v>-1</v>
-      </c>
-      <c r="AQ150">
-        <v>0</v>
-      </c>
-      <c r="AR150">
-        <v>0</v>
-      </c>
-      <c r="AS150">
-        <v>0</v>
-      </c>
-      <c r="AT150">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
-        <v>0</v>
-      </c>
-      <c r="U151">
-        <v>0</v>
-      </c>
-      <c r="V151">
-        <v>0</v>
-      </c>
-      <c r="W151">
-        <v>0</v>
-      </c>
-      <c r="X151">
-        <v>0</v>
-      </c>
-      <c r="Y151">
-        <v>0</v>
-      </c>
-      <c r="Z151">
-        <v>0</v>
-      </c>
-      <c r="AA151">
-        <v>0</v>
-      </c>
-      <c r="AB151">
-        <v>0</v>
-      </c>
-      <c r="AC151">
-        <v>0</v>
-      </c>
-      <c r="AD151">
-        <v>0</v>
-      </c>
-      <c r="AE151">
-        <v>0</v>
-      </c>
-      <c r="AF151">
-        <v>0</v>
-      </c>
-      <c r="AG151">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-      <c r="AK151">
-        <v>0</v>
-      </c>
-      <c r="AL151">
-        <v>0</v>
-      </c>
-      <c r="AM151">
-        <v>-1</v>
-      </c>
-      <c r="AN151">
-        <v>-1</v>
-      </c>
-      <c r="AO151">
-        <v>-1</v>
-      </c>
-      <c r="AP151">
-        <v>-1</v>
-      </c>
-      <c r="AQ151">
-        <v>0</v>
-      </c>
-      <c r="AR151">
-        <v>0</v>
-      </c>
-      <c r="AS151">
-        <v>0</v>
-      </c>
-      <c r="AT151">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>0</v>
-      </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="T152">
-        <v>0</v>
-      </c>
-      <c r="U152">
-        <v>0</v>
-      </c>
-      <c r="V152">
-        <v>0</v>
-      </c>
-      <c r="W152">
-        <v>0</v>
-      </c>
-      <c r="X152">
-        <v>0</v>
-      </c>
-      <c r="Y152">
-        <v>0</v>
-      </c>
-      <c r="Z152">
-        <v>0</v>
-      </c>
-      <c r="AA152">
-        <v>0</v>
-      </c>
-      <c r="AB152">
-        <v>0</v>
-      </c>
-      <c r="AC152">
-        <v>0</v>
-      </c>
-      <c r="AD152">
-        <v>0</v>
-      </c>
-      <c r="AE152">
-        <v>0</v>
-      </c>
-      <c r="AF152">
-        <v>0</v>
-      </c>
-      <c r="AG152">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>0</v>
-      </c>
-      <c r="AK152">
-        <v>0</v>
-      </c>
-      <c r="AL152">
-        <v>0</v>
-      </c>
-      <c r="AM152">
-        <v>-1</v>
-      </c>
-      <c r="AN152">
-        <v>-1</v>
-      </c>
-      <c r="AO152">
-        <v>-1</v>
-      </c>
-      <c r="AP152">
-        <v>-1</v>
-      </c>
-      <c r="AQ152">
-        <v>0</v>
-      </c>
-      <c r="AR152">
-        <v>0</v>
-      </c>
-      <c r="AS152">
-        <v>0</v>
-      </c>
-      <c r="AT152">
-        <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G26">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G47">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G55">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G65">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G68">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G80">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU147"/>
+  <dimension ref="A1:AU143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G134">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G138">
@@ -22919,27 +22919,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G139">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23082,27 +23082,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G140">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23245,27 +23245,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G143">
@@ -23721,658 +23721,6 @@
         <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>0</v>
-      </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144">
-        <v>0</v>
-      </c>
-      <c r="U144">
-        <v>0</v>
-      </c>
-      <c r="V144">
-        <v>0</v>
-      </c>
-      <c r="W144">
-        <v>0</v>
-      </c>
-      <c r="X144">
-        <v>0</v>
-      </c>
-      <c r="Y144">
-        <v>0</v>
-      </c>
-      <c r="Z144">
-        <v>0</v>
-      </c>
-      <c r="AA144">
-        <v>0</v>
-      </c>
-      <c r="AB144">
-        <v>0</v>
-      </c>
-      <c r="AC144">
-        <v>0</v>
-      </c>
-      <c r="AD144">
-        <v>0</v>
-      </c>
-      <c r="AE144">
-        <v>0</v>
-      </c>
-      <c r="AF144">
-        <v>0</v>
-      </c>
-      <c r="AG144">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>0</v>
-      </c>
-      <c r="AK144">
-        <v>0</v>
-      </c>
-      <c r="AL144">
-        <v>0</v>
-      </c>
-      <c r="AM144">
-        <v>-1</v>
-      </c>
-      <c r="AN144">
-        <v>-1</v>
-      </c>
-      <c r="AO144">
-        <v>-1</v>
-      </c>
-      <c r="AP144">
-        <v>-1</v>
-      </c>
-      <c r="AQ144">
-        <v>0</v>
-      </c>
-      <c r="AR144">
-        <v>0</v>
-      </c>
-      <c r="AS144">
-        <v>0</v>
-      </c>
-      <c r="AT144">
-        <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>0</v>
-      </c>
-      <c r="R145">
-        <v>0</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-      <c r="U145">
-        <v>0</v>
-      </c>
-      <c r="V145">
-        <v>0</v>
-      </c>
-      <c r="W145">
-        <v>0</v>
-      </c>
-      <c r="X145">
-        <v>0</v>
-      </c>
-      <c r="Y145">
-        <v>0</v>
-      </c>
-      <c r="Z145">
-        <v>0</v>
-      </c>
-      <c r="AA145">
-        <v>0</v>
-      </c>
-      <c r="AB145">
-        <v>0</v>
-      </c>
-      <c r="AC145">
-        <v>0</v>
-      </c>
-      <c r="AD145">
-        <v>0</v>
-      </c>
-      <c r="AE145">
-        <v>0</v>
-      </c>
-      <c r="AF145">
-        <v>0</v>
-      </c>
-      <c r="AG145">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>0</v>
-      </c>
-      <c r="AK145">
-        <v>0</v>
-      </c>
-      <c r="AL145">
-        <v>0</v>
-      </c>
-      <c r="AM145">
-        <v>-1</v>
-      </c>
-      <c r="AN145">
-        <v>-1</v>
-      </c>
-      <c r="AO145">
-        <v>-1</v>
-      </c>
-      <c r="AP145">
-        <v>-1</v>
-      </c>
-      <c r="AQ145">
-        <v>0</v>
-      </c>
-      <c r="AR145">
-        <v>0</v>
-      </c>
-      <c r="AS145">
-        <v>0</v>
-      </c>
-      <c r="AT145">
-        <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
-      <c r="V146">
-        <v>0</v>
-      </c>
-      <c r="W146">
-        <v>0</v>
-      </c>
-      <c r="X146">
-        <v>0</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="Z146">
-        <v>0</v>
-      </c>
-      <c r="AA146">
-        <v>0</v>
-      </c>
-      <c r="AB146">
-        <v>0</v>
-      </c>
-      <c r="AC146">
-        <v>0</v>
-      </c>
-      <c r="AD146">
-        <v>0</v>
-      </c>
-      <c r="AE146">
-        <v>0</v>
-      </c>
-      <c r="AF146">
-        <v>0</v>
-      </c>
-      <c r="AG146">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-      <c r="AK146">
-        <v>0</v>
-      </c>
-      <c r="AL146">
-        <v>0</v>
-      </c>
-      <c r="AM146">
-        <v>-1</v>
-      </c>
-      <c r="AN146">
-        <v>-1</v>
-      </c>
-      <c r="AO146">
-        <v>-1</v>
-      </c>
-      <c r="AP146">
-        <v>-1</v>
-      </c>
-      <c r="AQ146">
-        <v>0</v>
-      </c>
-      <c r="AR146">
-        <v>0</v>
-      </c>
-      <c r="AS146">
-        <v>0</v>
-      </c>
-      <c r="AT146">
-        <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
-      </c>
-      <c r="R147">
-        <v>0</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147">
-        <v>0</v>
-      </c>
-      <c r="U147">
-        <v>0</v>
-      </c>
-      <c r="V147">
-        <v>0</v>
-      </c>
-      <c r="W147">
-        <v>0</v>
-      </c>
-      <c r="X147">
-        <v>0</v>
-      </c>
-      <c r="Y147">
-        <v>0</v>
-      </c>
-      <c r="Z147">
-        <v>0</v>
-      </c>
-      <c r="AA147">
-        <v>0</v>
-      </c>
-      <c r="AB147">
-        <v>0</v>
-      </c>
-      <c r="AC147">
-        <v>0</v>
-      </c>
-      <c r="AD147">
-        <v>0</v>
-      </c>
-      <c r="AE147">
-        <v>0</v>
-      </c>
-      <c r="AF147">
-        <v>0</v>
-      </c>
-      <c r="AG147">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>0</v>
-      </c>
-      <c r="AK147">
-        <v>0</v>
-      </c>
-      <c r="AL147">
-        <v>0</v>
-      </c>
-      <c r="AM147">
-        <v>-1</v>
-      </c>
-      <c r="AN147">
-        <v>-1</v>
-      </c>
-      <c r="AO147">
-        <v>-1</v>
-      </c>
-      <c r="AP147">
-        <v>-1</v>
-      </c>
-      <c r="AQ147">
-        <v>0</v>
-      </c>
-      <c r="AR147">
-        <v>0</v>
-      </c>
-      <c r="AS147">
-        <v>0</v>
-      </c>
-      <c r="AT147">
-        <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU143"/>
+  <dimension ref="A1:AU130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G125">
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G130">
@@ -21602,2125 +21602,6 @@
         <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-      <c r="U142">
-        <v>0</v>
-      </c>
-      <c r="V142">
-        <v>0</v>
-      </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>0</v>
-      </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142">
-        <v>0</v>
-      </c>
-      <c r="AB142">
-        <v>0</v>
-      </c>
-      <c r="AC142">
-        <v>0</v>
-      </c>
-      <c r="AD142">
-        <v>0</v>
-      </c>
-      <c r="AE142">
-        <v>0</v>
-      </c>
-      <c r="AF142">
-        <v>0</v>
-      </c>
-      <c r="AG142">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>0</v>
-      </c>
-      <c r="AK142">
-        <v>0</v>
-      </c>
-      <c r="AL142">
-        <v>0</v>
-      </c>
-      <c r="AM142">
-        <v>-1</v>
-      </c>
-      <c r="AN142">
-        <v>-1</v>
-      </c>
-      <c r="AO142">
-        <v>-1</v>
-      </c>
-      <c r="AP142">
-        <v>-1</v>
-      </c>
-      <c r="AQ142">
-        <v>0</v>
-      </c>
-      <c r="AR142">
-        <v>0</v>
-      </c>
-      <c r="AS142">
-        <v>0</v>
-      </c>
-      <c r="AT142">
-        <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-      <c r="U143">
-        <v>0</v>
-      </c>
-      <c r="V143">
-        <v>0</v>
-      </c>
-      <c r="W143">
-        <v>0</v>
-      </c>
-      <c r="X143">
-        <v>0</v>
-      </c>
-      <c r="Y143">
-        <v>0</v>
-      </c>
-      <c r="Z143">
-        <v>0</v>
-      </c>
-      <c r="AA143">
-        <v>0</v>
-      </c>
-      <c r="AB143">
-        <v>0</v>
-      </c>
-      <c r="AC143">
-        <v>0</v>
-      </c>
-      <c r="AD143">
-        <v>0</v>
-      </c>
-      <c r="AE143">
-        <v>0</v>
-      </c>
-      <c r="AF143">
-        <v>0</v>
-      </c>
-      <c r="AG143">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>0</v>
-      </c>
-      <c r="AK143">
-        <v>0</v>
-      </c>
-      <c r="AL143">
-        <v>0</v>
-      </c>
-      <c r="AM143">
-        <v>-1</v>
-      </c>
-      <c r="AN143">
-        <v>-1</v>
-      </c>
-      <c r="AO143">
-        <v>-1</v>
-      </c>
-      <c r="AP143">
-        <v>-1</v>
-      </c>
-      <c r="AQ143">
-        <v>0</v>
-      </c>
-      <c r="AR143">
-        <v>0</v>
-      </c>
-      <c r="AS143">
-        <v>0</v>
-      </c>
-      <c r="AT143">
-        <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU130"/>
+  <dimension ref="A1:AU126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-04 14:30:00</t>
+          <t>2026-09-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-04 15:00:00</t>
+          <t>2026-09-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G65">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-09-04 15:15:00</t>
+          <t>2026-09-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G70">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-09-04 15:30:00</t>
+          <t>2026-09-04 15:15:00</t>
         </is>
       </c>
     </row>
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G75">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-09-04 15:45:00</t>
+          <t>2026-09-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G86">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N86">
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,68 +14812,68 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N89">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK89">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G90">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,68 +15138,68 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G92">
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G96">
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S97">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T97">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U97">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V97">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y97">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z97">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB97">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD97">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE97">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF97">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG97">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK97">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-09-04 17:00:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G100">
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G121">
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G126">
@@ -20950,658 +20950,6 @@
         <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G117">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G117">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -6536,31 +6536,31 @@
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -7025,31 +7025,31 @@
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -7176,10 +7176,10 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -7188,31 +7188,31 @@
         <v>0</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -14988,34 +14988,34 @@
         <v>3.09</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA90">
         <v>1.85</v>
@@ -15024,19 +15024,19 @@
         <v>1.95</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL90">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU126"/>
+  <dimension ref="A1:AU123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-09-04 21:30:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G123">
@@ -20461,495 +20461,6 @@
         <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
-      <c r="U125">
-        <v>0</v>
-      </c>
-      <c r="V125">
-        <v>0</v>
-      </c>
-      <c r="W125">
-        <v>0</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>0</v>
-      </c>
-      <c r="Z125">
-        <v>0</v>
-      </c>
-      <c r="AA125">
-        <v>0</v>
-      </c>
-      <c r="AB125">
-        <v>0</v>
-      </c>
-      <c r="AC125">
-        <v>0</v>
-      </c>
-      <c r="AD125">
-        <v>0</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>0</v>
-      </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-      <c r="AK125">
-        <v>0</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
-        <v>0</v>
-      </c>
-      <c r="AB126">
-        <v>0</v>
-      </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10448,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -11088,10 +11088,10 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -11100,31 +11100,31 @@
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -11251,10 +11251,10 @@
         <v>0</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -11263,31 +11263,31 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,10 +11402,10 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -11426,31 +11426,31 @@
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE68">
         <v>0</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>3.16</v>
+        <v>2.71</v>
       </c>
       <c r="P28">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="Q28">
+        <v>3.08</v>
+      </c>
+      <c r="R28">
+        <v>1.91</v>
+      </c>
+      <c r="S28">
+        <v>1.37</v>
+      </c>
+      <c r="T28">
+        <v>2.7</v>
+      </c>
+      <c r="U28">
         <v>3.1</v>
-      </c>
-      <c r="R28">
-        <v>2.02</v>
-      </c>
-      <c r="S28">
-        <v>1.45</v>
-      </c>
-      <c r="T28">
-        <v>2.53</v>
-      </c>
-      <c r="U28">
-        <v>3.2</v>
       </c>
       <c r="V28">
         <v>1.3</v>
@@ -4903,19 +4903,19 @@
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
         <v>1.35</v>
       </c>
       <c r="Z28">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA28">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB28">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
         <v>4.4</v>
@@ -4924,13 +4924,13 @@
         <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG28">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.14</v>
@@ -8625,77 +8625,77 @@
         <v>2.26</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="Q51">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V51">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="AA51">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
+        <v>2.95</v>
+      </c>
+      <c r="AD51">
+        <v>1.37</v>
+      </c>
+      <c r="AE51">
+        <v>1.08</v>
+      </c>
+      <c r="AF51">
+        <v>1.66</v>
+      </c>
+      <c r="AG51">
+        <v>2.09</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.22</v>
+      </c>
+      <c r="AK51">
         <v>1.8</v>
-      </c>
-      <c r="AC51">
-        <v>3.3</v>
-      </c>
-      <c r="AD51">
-        <v>1.19</v>
-      </c>
-      <c r="AE51">
-        <v>1.02</v>
-      </c>
-      <c r="AF51">
-        <v>1.83</v>
-      </c>
-      <c r="AG51">
-        <v>1.87</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.25</v>
-      </c>
-      <c r="AK51">
-        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10448,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O63">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P63">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q63">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="R63">
         <v>2.38</v>
@@ -10602,7 +10602,7 @@
         <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W63">
         <v>1.16</v>
@@ -10611,47 +10611,47 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA63">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB63">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AC63">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AD63">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE63">
+        <v>1.25</v>
+      </c>
+      <c r="AF63">
+        <v>1.42</v>
+      </c>
+      <c r="AG63">
+        <v>2.65</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.26</v>
       </c>
-      <c r="AF63">
-        <v>1.43</v>
-      </c>
-      <c r="AG63">
-        <v>2.7</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.25</v>
-      </c>
       <c r="AK63">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="O64">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="Q64">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="R64">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U64">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="V64">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA64">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AB64">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="AC64">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD64">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AG64">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="O65">
         <v>4.8</v>
       </c>
       <c r="P65">
-        <v>5.4</v>
+        <v>6.25</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q67">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="R67">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
         <v>2.35</v>
@@ -11257,31 +11257,31 @@
         <v>1.5</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AB67">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AC67">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AD67">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE67">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
         <v>1.53</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,22 +11396,22 @@
         <v>2.65</v>
       </c>
       <c r="O68">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q68">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="R68">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
         <v>2.16</v>
@@ -11420,10 +11420,10 @@
         <v>1.58</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
         <v>1.13</v>
@@ -11441,16 +11441,16 @@
         <v>2.32</v>
       </c>
       <c r="AD68">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AE68">
         <v>1.19</v>
       </c>
       <c r="AF68">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG68">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,10 +11559,10 @@
         <v>1.55</v>
       </c>
       <c r="O69">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P69">
-        <v>4.96</v>
+        <v>4.75</v>
       </c>
       <c r="Q69">
         <v>1.96</v>
@@ -11571,49 +11571,49 @@
         <v>2.63</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U69">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="V69">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA69">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB69">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AC69">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD69">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE69">
         <v>1.21</v>
       </c>
       <c r="AF69">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG69">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O73">
+        <v>3</v>
+      </c>
+      <c r="P73">
+        <v>3.25</v>
+      </c>
+      <c r="Q73">
+        <v>2.63</v>
+      </c>
+      <c r="R73">
         <v>2.1</v>
       </c>
-      <c r="P73">
-        <v>3.9</v>
-      </c>
-      <c r="Q73">
-        <v>2.6</v>
-      </c>
-      <c r="R73">
-        <v>2.03</v>
-      </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T73">
         <v>2.69</v>
       </c>
       <c r="U73">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="V73">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W73">
         <v>1.05</v>
@@ -12241,31 +12241,31 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z73">
         <v>3.05</v>
       </c>
       <c r="AA73">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB73">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC73">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD73">
         <v>1.22</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG73">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK73">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,65 +13512,65 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q81">
-        <v>4.04</v>
+        <v>2.95</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U81">
-        <v>2.22</v>
+        <v>2.79</v>
       </c>
       <c r="V81">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="AA81">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB81">
+        <v>2.12</v>
+      </c>
+      <c r="AC81">
+        <v>2.43</v>
+      </c>
+      <c r="AD81">
+        <v>1.44</v>
+      </c>
+      <c r="AE81">
+        <v>1.08</v>
+      </c>
+      <c r="AF81">
+        <v>1.65</v>
+      </c>
+      <c r="AG81">
         <v>2.33</v>
       </c>
-      <c r="AC81">
-        <v>2.63</v>
-      </c>
-      <c r="AD81">
-        <v>1.57</v>
-      </c>
-      <c r="AE81">
-        <v>1.19</v>
-      </c>
-      <c r="AF81">
-        <v>1.46</v>
-      </c>
-      <c r="AG81">
-        <v>2.5</v>
-      </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AK81">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,10 +13684,10 @@
         <v>2.13</v>
       </c>
       <c r="Q82">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
         <v>1.28</v>
@@ -13696,40 +13696,40 @@
         <v>3.15</v>
       </c>
       <c r="U82">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="V82">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z82">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="AA82">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB82">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC82">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AD82">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE82">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
+        <v>1.25</v>
+      </c>
+      <c r="AK82">
         <v>1.22</v>
-      </c>
-      <c r="AK82">
-        <v>1.31</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q83">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="R83">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="U83">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA83">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AB83">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="AC83">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF83">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AG83">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,22 +14010,22 @@
         <v>1.72</v>
       </c>
       <c r="Q84">
-        <v>4.73</v>
+        <v>4.33</v>
       </c>
       <c r="R84">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S84">
         <v>1.32</v>
       </c>
       <c r="T84">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="U84">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W84">
         <v>1.11</v>
@@ -14034,31 +14034,31 @@
         <v>1.05</v>
       </c>
       <c r="Y84">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z84">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA84">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB84">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC84">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD84">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE84">
         <v>1.14</v>
       </c>
       <c r="AF84">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG84">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q85">
-        <v>5.95</v>
+        <v>4.54</v>
       </c>
       <c r="R85">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="S85">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="T85">
         <v>2.36</v>
       </c>
       <c r="U85">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V85">
         <v>1.3</v>
@@ -14194,34 +14194,34 @@
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z85">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA85">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB85">
         <v>1.61</v>
       </c>
       <c r="AC85">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD85">
         <v>1.18</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF85">
         <v>2.09</v>
       </c>
       <c r="AG85">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AK85">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="N96">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O96">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P96">
         <v>1.5</v>
@@ -15969,19 +15969,19 @@
         <v>5</v>
       </c>
       <c r="R96">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="S96">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T96">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U96">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V96">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W96">
         <v>1.18</v>
@@ -15993,28 +15993,28 @@
         <v>1.08</v>
       </c>
       <c r="Z96">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA96">
+        <v>1.36</v>
+      </c>
+      <c r="AB96">
+        <v>2.88</v>
+      </c>
+      <c r="AC96">
+        <v>1.95</v>
+      </c>
+      <c r="AD96">
+        <v>1.73</v>
+      </c>
+      <c r="AE96">
+        <v>1.33</v>
+      </c>
+      <c r="AF96">
         <v>1.5</v>
       </c>
-      <c r="AB96">
-        <v>2.62</v>
-      </c>
-      <c r="AC96">
-        <v>2</v>
-      </c>
-      <c r="AD96">
-        <v>1.69</v>
-      </c>
-      <c r="AE96">
-        <v>1.3</v>
-      </c>
-      <c r="AF96">
-        <v>1.52</v>
-      </c>
       <c r="AG96">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>2.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
         <v>2.95</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G124">
@@ -21345,55 +21345,55 @@
         <v>0</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X129">
         <v>0</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL129">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,46 +6503,46 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O38">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q38">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R38">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U38">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z38">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB38">
         <v>2.1</v>
@@ -6554,13 +6554,13 @@
         <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG38">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK38">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,37 +6666,37 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q39">
         <v>2.02</v>
       </c>
       <c r="R39">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U39">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.11</v>
@@ -6711,7 +6711,7 @@
         <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
         <v>1.6</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,58 +6829,58 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q40">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="U40">
         <v>2.05</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA40">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AB40">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC40">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD40">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF40">
         <v>1.37</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>5</v>
       </c>
       <c r="P42">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q42">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="R42">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U42">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V42">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA42">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AC42">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD42">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.14</v>
       </c>
       <c r="AK42">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="O43">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P43">
-        <v>3.52</v>
+        <v>2.98</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="R43">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>4.7</v>
+        <v>5.15</v>
       </c>
       <c r="AA43">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="AC43">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG43">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O65">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P65">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q65">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R65">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="S65">
         <v>1.17</v>
       </c>
       <c r="T65">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U65">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V65">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W65">
         <v>1.22</v>
@@ -10937,31 +10937,31 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z65">
-        <v>6.95</v>
+        <v>6.45</v>
       </c>
       <c r="AA65">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AB65">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC65">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AD65">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE65">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="O66">
+        <v>3.6</v>
+      </c>
+      <c r="P66">
+        <v>2.25</v>
+      </c>
+      <c r="Q66">
+        <v>3.39</v>
+      </c>
+      <c r="R66">
+        <v>2.55</v>
+      </c>
+      <c r="S66">
+        <v>1.22</v>
+      </c>
+      <c r="T66">
+        <v>3.6</v>
+      </c>
+      <c r="U66">
+        <v>2.16</v>
+      </c>
+      <c r="V66">
+        <v>1.58</v>
+      </c>
+      <c r="W66">
+        <v>1.13</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.13</v>
+      </c>
+      <c r="Z66">
         <v>5</v>
       </c>
-      <c r="P66">
-        <v>5.75</v>
-      </c>
-      <c r="Q66">
-        <v>1.82</v>
-      </c>
-      <c r="R66">
-        <v>2.68</v>
-      </c>
-      <c r="S66">
-        <v>1.17</v>
-      </c>
-      <c r="T66">
-        <v>4.15</v>
-      </c>
-      <c r="U66">
-        <v>1.91</v>
-      </c>
-      <c r="V66">
-        <v>1.86</v>
-      </c>
-      <c r="W66">
-        <v>1.22</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.05</v>
-      </c>
-      <c r="Z66">
-        <v>6.45</v>
-      </c>
       <c r="AA66">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AB66">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC66">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AD66">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="AE66">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG66">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2.71</v>
+        <v>1.38</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.65</v>
+        <v>1.39</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P68">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="Q68">
-        <v>3.39</v>
+        <v>1.81</v>
       </c>
       <c r="R68">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="S68">
+        <v>1.17</v>
+      </c>
+      <c r="T68">
+        <v>4.1</v>
+      </c>
+      <c r="U68">
+        <v>1.89</v>
+      </c>
+      <c r="V68">
+        <v>1.84</v>
+      </c>
+      <c r="W68">
         <v>1.22</v>
       </c>
-      <c r="T68">
-        <v>3.6</v>
-      </c>
-      <c r="U68">
-        <v>2.16</v>
-      </c>
-      <c r="V68">
-        <v>1.58</v>
-      </c>
-      <c r="W68">
-        <v>1.13</v>
-      </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z68">
-        <v>5</v>
+        <v>6.95</v>
       </c>
       <c r="AA68">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AB68">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="AC68">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="AD68">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="AE68">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AF68">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AG68">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>1.38</v>
+        <v>2.85</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q70">
         <v>2.45</v>
@@ -11734,22 +11734,22 @@
         <v>2.25</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U70">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="V70">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
         <v>1.17</v>
@@ -11758,22 +11758,22 @@
         <v>3.75</v>
       </c>
       <c r="AA70">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC70">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD70">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
         <v>2.1</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q76">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="R76">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="S76">
         <v>1.65</v>
@@ -12718,22 +12718,22 @@
         <v>2.1</v>
       </c>
       <c r="U76">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="V76">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W76">
         <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y76">
         <v>1.6</v>
       </c>
       <c r="Z76">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AA76">
         <v>2.74</v>
@@ -12745,13 +12745,13 @@
         <v>5.45</v>
       </c>
       <c r="AD76">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE76">
         <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG76">
         <v>1.53</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK76">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O78">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="Q78">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U78">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z78">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA78">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AB78">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC78">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AD78">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE78">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG78">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AK78">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O81">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P81">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="Q81">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="R81">
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T81">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U81">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="V81">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB81">
         <v>2.12</v>
       </c>
       <c r="AC81">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD81">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE81">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
+        <v>2.6</v>
+      </c>
+      <c r="O82">
+        <v>3.3</v>
+      </c>
+      <c r="P82">
+        <v>2.45</v>
+      </c>
+      <c r="Q82">
         <v>2.95</v>
-      </c>
-      <c r="O82">
-        <v>3.55</v>
-      </c>
-      <c r="P82">
-        <v>2.13</v>
-      </c>
-      <c r="Q82">
-        <v>3.66</v>
       </c>
       <c r="R82">
         <v>2.3</v>
       </c>
       <c r="S82">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T82">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U82">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="V82">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA82">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB82">
         <v>2.12</v>
       </c>
       <c r="AC82">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD82">
+        <v>1.44</v>
+      </c>
+      <c r="AE82">
+        <v>1.08</v>
+      </c>
+      <c r="AF82">
+        <v>1.65</v>
+      </c>
+      <c r="AG82">
+        <v>2.33</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
         <v>1.41</v>
       </c>
-      <c r="AE82">
-        <v>1.13</v>
-      </c>
-      <c r="AF82">
-        <v>1.53</v>
-      </c>
-      <c r="AG82">
-        <v>2.3</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.25</v>
-      </c>
       <c r="AK82">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14499,71 +14499,71 @@
         <v>1.57</v>
       </c>
       <c r="Q87">
-        <v>4.06</v>
+        <v>5</v>
       </c>
       <c r="R87">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U87">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V87">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z87">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA87">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB87">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC87">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD87">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE87">
+        <v>1.21</v>
+      </c>
+      <c r="AF87">
+        <v>1.56</v>
+      </c>
+      <c r="AG87">
+        <v>2.3</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
+        <v>1.23</v>
+      </c>
+      <c r="AK87">
         <v>1.19</v>
-      </c>
-      <c r="AF87">
-        <v>1.57</v>
-      </c>
-      <c r="AG87">
-        <v>2.28</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>2.3</v>
-      </c>
-      <c r="AK87">
-        <v>1.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15305,16 +15305,16 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="Q92">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R92">
         <v>2.15</v>
@@ -15329,7 +15329,7 @@
         <v>2.62</v>
       </c>
       <c r="V92">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
         <v>1.06</v>
@@ -15347,7 +15347,7 @@
         <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC92">
         <v>2.94</v>
@@ -15359,7 +15359,7 @@
         <v>1.09</v>
       </c>
       <c r="AF92">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
         <v>2.11</v>
@@ -15477,13 +15477,13 @@
         <v>4</v>
       </c>
       <c r="Q93">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
         <v>2.77</v>
@@ -15495,10 +15495,10 @@
         <v>1.43</v>
       </c>
       <c r="W93">
+        <v>1.1</v>
+      </c>
+      <c r="X93">
         <v>1.05</v>
-      </c>
-      <c r="X93">
-        <v>1</v>
       </c>
       <c r="Y93">
         <v>1.25</v>
@@ -15513,13 +15513,13 @@
         <v>1.89</v>
       </c>
       <c r="AC93">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
         <v>1.79</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK93">
         <v>1.95</v>
@@ -15631,37 +15631,37 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="O94">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="P94">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q94">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="R94">
         <v>2.63</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U94">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V94">
         <v>1.7</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
         <v>1.09</v>
@@ -15670,25 +15670,25 @@
         <v>6.1</v>
       </c>
       <c r="AA94">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AB94">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AC94">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD94">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE94">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF94">
         <v>1.42</v>
       </c>
       <c r="AG94">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17270,16 +17270,16 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R104">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="S104">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T104">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="U104">
         <v>3.75</v>
@@ -17288,10 +17288,10 @@
         <v>1.23</v>
       </c>
       <c r="W104">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y104">
         <v>1.52</v>
@@ -17315,7 +17315,7 @@
         <v>1.01</v>
       </c>
       <c r="AF104">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AG104">
         <v>1.54</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK104">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="V35">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z35">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA35">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AB35">
+        <v>2.48</v>
+      </c>
+      <c r="AC35">
+        <v>2.14</v>
+      </c>
+      <c r="AD35">
+        <v>1.68</v>
+      </c>
+      <c r="AE35">
+        <v>1.24</v>
+      </c>
+      <c r="AF35">
+        <v>1.5</v>
+      </c>
+      <c r="AG35">
+        <v>2.4</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.16</v>
+      </c>
+      <c r="AK35">
         <v>2.21</v>
-      </c>
-      <c r="AC35">
-        <v>2.45</v>
-      </c>
-      <c r="AD35">
-        <v>1.44</v>
-      </c>
-      <c r="AE35">
-        <v>1.21</v>
-      </c>
-      <c r="AF35">
-        <v>1.52</v>
-      </c>
-      <c r="AG35">
-        <v>2.37</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.26</v>
-      </c>
-      <c r="AK35">
-        <v>1.68</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q36">
-        <v>2.13</v>
+        <v>2.64</v>
       </c>
       <c r="R36">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
+        <v>1.29</v>
+      </c>
+      <c r="T36">
+        <v>3.3</v>
+      </c>
+      <c r="U36">
+        <v>2.39</v>
+      </c>
+      <c r="V36">
+        <v>1.51</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.15</v>
+      </c>
+      <c r="Z36">
+        <v>4.25</v>
+      </c>
+      <c r="AA36">
+        <v>1.64</v>
+      </c>
+      <c r="AB36">
+        <v>2.21</v>
+      </c>
+      <c r="AC36">
+        <v>2.45</v>
+      </c>
+      <c r="AD36">
+        <v>1.44</v>
+      </c>
+      <c r="AE36">
+        <v>1.21</v>
+      </c>
+      <c r="AF36">
+        <v>1.52</v>
+      </c>
+      <c r="AG36">
+        <v>2.37</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.26</v>
       </c>
-      <c r="T36">
-        <v>3.34</v>
-      </c>
-      <c r="U36">
-        <v>2.18</v>
-      </c>
-      <c r="V36">
-        <v>1.64</v>
-      </c>
-      <c r="W36">
-        <v>1.14</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.1</v>
-      </c>
-      <c r="Z36">
-        <v>5.1</v>
-      </c>
-      <c r="AA36">
-        <v>1.43</v>
-      </c>
-      <c r="AB36">
-        <v>2.48</v>
-      </c>
-      <c r="AC36">
-        <v>2.14</v>
-      </c>
-      <c r="AD36">
+      <c r="AK36">
         <v>1.68</v>
-      </c>
-      <c r="AE36">
-        <v>1.24</v>
-      </c>
-      <c r="AF36">
-        <v>1.5</v>
-      </c>
-      <c r="AG36">
-        <v>2.4</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.16</v>
-      </c>
-      <c r="AK36">
-        <v>2.21</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.75</v>
+        <v>1.69</v>
       </c>
       <c r="O55">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>2.4</v>
+        <v>4.16</v>
       </c>
       <c r="Q55">
-        <v>3.7</v>
+        <v>2.32</v>
       </c>
       <c r="R55">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="T55">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="U55">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="V55">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="Z55">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="AA55">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AB55">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC55">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="AD55">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AE55">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF55">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG55">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK55">
-        <v>1.38</v>
+        <v>2.08</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.69</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P56">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q56">
-        <v>2.32</v>
+        <v>3.7</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="S56">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U56">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V56">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W56">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="Z56">
-        <v>3.6</v>
+        <v>2.69</v>
       </c>
       <c r="AA56">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AB56">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AC56">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="AD56">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE56">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG56">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK56">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="O57">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P57">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="Q57">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="R57">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U57">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V57">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W57">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA57">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB57">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC57">
         <v>3.6</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="Q58">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S58">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T58">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V58">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z58">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AA58">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB58">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC58">
         <v>3.6</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P67">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q67">
-        <v>3.18</v>
+        <v>1.96</v>
       </c>
       <c r="R67">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U67">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="V67">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W67">
+        <v>1.13</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
         <v>1.1</v>
       </c>
-      <c r="X67">
-        <v>1.03</v>
-      </c>
-      <c r="Y67">
-        <v>1.14</v>
-      </c>
       <c r="Z67">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AC67">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD67">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE67">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
         <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="O68">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>6.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q68">
-        <v>1.81</v>
+        <v>3.18</v>
       </c>
       <c r="R68">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>6.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA68">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="AB68">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC68">
-        <v>1.78</v>
+        <v>2.33</v>
       </c>
       <c r="AD68">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="AE68">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>2.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="O69">
+        <v>4.8</v>
+      </c>
+      <c r="P69">
+        <v>6.25</v>
+      </c>
+      <c r="Q69">
+        <v>1.81</v>
+      </c>
+      <c r="R69">
+        <v>2.62</v>
+      </c>
+      <c r="S69">
+        <v>1.17</v>
+      </c>
+      <c r="T69">
         <v>4.1</v>
       </c>
-      <c r="P69">
-        <v>4.75</v>
-      </c>
-      <c r="Q69">
-        <v>1.96</v>
-      </c>
-      <c r="R69">
-        <v>2.63</v>
-      </c>
-      <c r="S69">
+      <c r="U69">
+        <v>1.89</v>
+      </c>
+      <c r="V69">
+        <v>1.84</v>
+      </c>
+      <c r="W69">
         <v>1.22</v>
       </c>
-      <c r="T69">
-        <v>3.58</v>
-      </c>
-      <c r="U69">
-        <v>2.19</v>
-      </c>
-      <c r="V69">
-        <v>1.62</v>
-      </c>
-      <c r="W69">
-        <v>1.13</v>
-      </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z69">
-        <v>5</v>
+        <v>6.95</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AB69">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC69">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="AD69">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AE69">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AF69">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG69">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK69">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="O76">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="P76">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -12770,7 +12770,7 @@
         <v>1.34</v>
       </c>
       <c r="AK76">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O80">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="Q80">
         <v>3.04</v>
@@ -13385,13 +13385,13 @@
         <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AA80">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB80">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC80">
         <v>3.58</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
+        <v>2.6</v>
+      </c>
+      <c r="O81">
+        <v>3.3</v>
+      </c>
+      <c r="P81">
+        <v>2.45</v>
+      </c>
+      <c r="Q81">
         <v>2.95</v>
-      </c>
-      <c r="O81">
-        <v>3.55</v>
-      </c>
-      <c r="P81">
-        <v>2.13</v>
-      </c>
-      <c r="Q81">
-        <v>3.66</v>
       </c>
       <c r="R81">
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U81">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="V81">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA81">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB81">
         <v>2.12</v>
       </c>
       <c r="AC81">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD81">
+        <v>1.44</v>
+      </c>
+      <c r="AE81">
+        <v>1.08</v>
+      </c>
+      <c r="AF81">
+        <v>1.65</v>
+      </c>
+      <c r="AG81">
+        <v>2.33</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.41</v>
       </c>
-      <c r="AE81">
-        <v>1.13</v>
-      </c>
-      <c r="AF81">
-        <v>1.53</v>
-      </c>
-      <c r="AG81">
-        <v>2.3</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.25</v>
-      </c>
       <c r="AK81">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
+        <v>1.87</v>
+      </c>
+      <c r="Q82">
+        <v>3.26</v>
+      </c>
+      <c r="R82">
         <v>2.45</v>
       </c>
-      <c r="Q82">
-        <v>2.95</v>
-      </c>
-      <c r="R82">
-        <v>2.3</v>
-      </c>
       <c r="S82">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U82">
-        <v>2.79</v>
+        <v>2.25</v>
       </c>
       <c r="V82">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z82">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA82">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="AC82">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD82">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE82">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG82">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P83">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>3.26</v>
+        <v>3.66</v>
       </c>
       <c r="R83">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T83">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U83">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V83">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA83">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB83">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="AC83">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD83">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE83">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF83">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
         <v>1.22</v>
@@ -16624,19 +16624,19 @@
         <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T100">
+        <v>2.8</v>
+      </c>
+      <c r="U100">
         <v>2.7</v>
       </c>
-      <c r="U100">
-        <v>2.9</v>
-      </c>
       <c r="V100">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W100">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
         <v>1.02</v>
@@ -16663,10 +16663,10 @@
         <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG100">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O106">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P106">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q106">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2274,25 +2274,25 @@
         <v>1.13</v>
       </c>
       <c r="Q12">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="R12">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="S12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T12">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V12">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,28 +2301,28 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
         <v>2.62</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE12">
         <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AG12">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2763,46 +2763,46 @@
         <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
         <v>2.42</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AB15">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AC15">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
         <v>1.15</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="Q19">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
         <v>2.23</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U19">
         <v>2.31</v>
@@ -3433,34 +3433,34 @@
         <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AC19">
         <v>2.58</v>
       </c>
       <c r="AD19">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
         <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
         <v>2.36</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O28">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="P28">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="Q28">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="R28">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="T28">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="U28">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V28">
         <v>1.3</v>
       </c>
       <c r="W28">
+        <v>1.01</v>
+      </c>
+      <c r="X28">
         <v>1.06</v>
       </c>
-      <c r="X28">
-        <v>1.05</v>
-      </c>
       <c r="Y28">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA28">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC28">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
         <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>2.89</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5220,10 +5220,10 @@
         <v>4.15</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V30">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W30">
         <v>1.15</v>
@@ -5238,10 +5238,10 @@
         <v>6.05</v>
       </c>
       <c r="AA30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB30">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AC30">
         <v>1.99</v>
@@ -5272,7 +5272,7 @@
         <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="O32">
         <v>3.75</v>
       </c>
       <c r="P32">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q32">
         <v>6.7</v>
@@ -5540,7 +5540,7 @@
         <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T32">
         <v>2.65</v>
@@ -5561,7 +5561,7 @@
         <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="AA32">
         <v>2.15</v>
@@ -5570,7 +5570,7 @@
         <v>1.72</v>
       </c>
       <c r="AC32">
-        <v>3.6</v>
+        <v>3.79</v>
       </c>
       <c r="AD32">
         <v>1.23</v>
@@ -5860,16 +5860,16 @@
         <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U34">
         <v>2.44</v>
@@ -5884,13 +5884,13 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA34">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
         <v>2.06</v>
@@ -5899,7 +5899,7 @@
         <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE34">
         <v>1.11</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="U35">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="V35">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA35">
+        <v>1.66</v>
+      </c>
+      <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.48</v>
+      </c>
+      <c r="AD35">
         <v>1.43</v>
       </c>
-      <c r="AB35">
-        <v>2.48</v>
-      </c>
-      <c r="AC35">
-        <v>2.14</v>
-      </c>
-      <c r="AD35">
-        <v>1.68</v>
-      </c>
       <c r="AE35">
+        <v>1.2</v>
+      </c>
+      <c r="AF35">
+        <v>1.52</v>
+      </c>
+      <c r="AG35">
+        <v>2.37</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.24</v>
       </c>
-      <c r="AF35">
-        <v>1.5</v>
-      </c>
-      <c r="AG35">
-        <v>2.4</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.16</v>
-      </c>
       <c r="AK35">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U36">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="V36">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>4.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA36">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AB36">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AC36">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q37">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="R37">
         <v>2.38</v>
@@ -6361,10 +6361,10 @@
         <v>3.34</v>
       </c>
       <c r="U37">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V37">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -6379,16 +6379,16 @@
         <v>4.55</v>
       </c>
       <c r="AA37">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE37">
         <v>1.18</v>
@@ -6397,7 +6397,7 @@
         <v>1.54</v>
       </c>
       <c r="AG37">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="AK37">
         <v>1.23</v>
@@ -7001,55 +7001,55 @@
         <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U41">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V41">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA41">
         <v>1.43</v>
       </c>
       <c r="AB41">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="AC41">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AD41">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE41">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AG41">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>1.47</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q44">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="R44">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="S44">
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U44">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V44">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7517,28 +7517,28 @@
         <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA44">
+        <v>1.56</v>
+      </c>
+      <c r="AB44">
+        <v>2.43</v>
+      </c>
+      <c r="AC44">
+        <v>2.35</v>
+      </c>
+      <c r="AD44">
+        <v>1.6</v>
+      </c>
+      <c r="AE44">
+        <v>1.19</v>
+      </c>
+      <c r="AF44">
         <v>1.5</v>
       </c>
-      <c r="AB44">
-        <v>2.5</v>
-      </c>
-      <c r="AC44">
-        <v>2.25</v>
-      </c>
-      <c r="AD44">
-        <v>1.61</v>
-      </c>
-      <c r="AE44">
-        <v>1.23</v>
-      </c>
-      <c r="AF44">
-        <v>1.47</v>
-      </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="Q51">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
         <v>1.34</v>
@@ -8655,22 +8655,22 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
         <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10273,13 +10273,13 @@
         <v>2.66</v>
       </c>
       <c r="U61">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="V61">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10294,7 +10294,7 @@
         <v>1.93</v>
       </c>
       <c r="AB61">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC61">
         <v>3.2</v>
@@ -10306,10 +10306,10 @@
         <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG61">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10578,55 +10578,55 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="P63">
         <v>3.9</v>
       </c>
       <c r="Q63">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="R63">
         <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W63">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AC63">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AD63">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
         <v>1.25</v>
@@ -10635,7 +10635,7 @@
         <v>1.42</v>
       </c>
       <c r="AG63">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="Q64">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S64">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U64">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V64">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10786,19 +10786,19 @@
         <v>2.66</v>
       </c>
       <c r="AC64">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD64">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE64">
         <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AG64">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,16 +10907,16 @@
         <v>1.4</v>
       </c>
       <c r="O65">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P65">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R65">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="S65">
         <v>1.17</v>
@@ -10925,10 +10925,10 @@
         <v>4.15</v>
       </c>
       <c r="U65">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V65">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W65">
         <v>1.22</v>
@@ -10946,13 +10946,13 @@
         <v>1.28</v>
       </c>
       <c r="AB65">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="AC65">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AD65">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AE65">
         <v>1.4</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
         <v>2.25</v>
       </c>
       <c r="Q66">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="R66">
         <v>2.55</v>
@@ -11091,7 +11091,7 @@
         <v>2.16</v>
       </c>
       <c r="V66">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W66">
         <v>1.13</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA66">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AB66">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AC66">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AD66">
         <v>1.66</v>
       </c>
       <c r="AE66">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,16 +11233,16 @@
         <v>1.55</v>
       </c>
       <c r="O67">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q67">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="R67">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="S67">
         <v>1.22</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB67">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC67">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AD67">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE67">
         <v>1.21</v>
       </c>
       <c r="AF67">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG67">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="R68">
         <v>2.17</v>
@@ -11414,16 +11414,16 @@
         <v>3.6</v>
       </c>
       <c r="U68">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
         <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.14</v>
@@ -11447,10 +11447,10 @@
         <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,31 +11556,31 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="O69">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P69">
-        <v>6.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q69">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R69">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S69">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T69">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U69">
+        <v>1.83</v>
+      </c>
+      <c r="V69">
         <v>1.89</v>
-      </c>
-      <c r="V69">
-        <v>1.84</v>
       </c>
       <c r="W69">
         <v>1.22</v>
@@ -11589,31 +11589,31 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z69">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="AA69">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AB69">
         <v>3.5</v>
       </c>
       <c r="AC69">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AD69">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AE69">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF69">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,13 +11722,13 @@
         <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q70">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="R70">
         <v>2.25</v>
@@ -11749,34 +11749,34 @@
         <v>1.12</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z70">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AC70">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD70">
+        <v>1.43</v>
+      </c>
+      <c r="AE70">
+        <v>1.14</v>
+      </c>
+      <c r="AF70">
         <v>1.51</v>
       </c>
-      <c r="AE70">
-        <v>1.15</v>
-      </c>
-      <c r="AF70">
-        <v>1.5</v>
-      </c>
       <c r="AG70">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="O73">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q73">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S73">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T73">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="U73">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="V73">
         <v>1.34</v>
       </c>
       <c r="W73">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="AA73">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB73">
         <v>1.71</v>
       </c>
       <c r="AC73">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD73">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG73">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK73">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O74">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
         <v>6.5</v>
       </c>
       <c r="Q74">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R74">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="S74">
         <v>1.31</v>
       </c>
       <c r="T74">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="U74">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V74">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z74">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="AA74">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB74">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC74">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD74">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE74">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG74">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK74">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12866,7 +12866,7 @@
         <v>3.3</v>
       </c>
       <c r="P77">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
         <v>2.27</v>
@@ -12878,40 +12878,40 @@
         <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA77">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB77">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC77">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AD77">
         <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
         <v>1.9</v>
@@ -13192,22 +13192,22 @@
         <v>4.8</v>
       </c>
       <c r="P79">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="Q79">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R79">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="S79">
         <v>1.21</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U79">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="V79">
         <v>1.83</v>
@@ -13222,28 +13222,28 @@
         <v>1.07</v>
       </c>
       <c r="Z79">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA79">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AB79">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AC79">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AD79">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AE79">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF79">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG79">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK79">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13373,10 +13373,10 @@
         <v>2.96</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13385,10 +13385,10 @@
         <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="AA80">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB80">
         <v>1.69</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O81">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P81">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="Q81">
-        <v>2.95</v>
+        <v>3.66</v>
       </c>
       <c r="R81">
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T81">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U81">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="V81">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB81">
         <v>2.12</v>
       </c>
       <c r="AC81">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD81">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE81">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
+        <v>2.6</v>
+      </c>
+      <c r="O83">
+        <v>3.3</v>
+      </c>
+      <c r="P83">
+        <v>2.45</v>
+      </c>
+      <c r="Q83">
         <v>2.95</v>
-      </c>
-      <c r="O83">
-        <v>3.55</v>
-      </c>
-      <c r="P83">
-        <v>2.13</v>
-      </c>
-      <c r="Q83">
-        <v>3.66</v>
       </c>
       <c r="R83">
         <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U83">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="V83">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA83">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB83">
         <v>2.12</v>
       </c>
       <c r="AC83">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD83">
+        <v>1.44</v>
+      </c>
+      <c r="AE83">
+        <v>1.08</v>
+      </c>
+      <c r="AF83">
+        <v>1.65</v>
+      </c>
+      <c r="AG83">
+        <v>2.33</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.41</v>
       </c>
-      <c r="AE83">
-        <v>1.13</v>
-      </c>
-      <c r="AF83">
-        <v>1.53</v>
-      </c>
-      <c r="AG83">
-        <v>2.3</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.25</v>
-      </c>
       <c r="AK83">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14167,25 +14167,25 @@
         <v>5</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>4.54</v>
+        <v>5.9</v>
       </c>
       <c r="R85">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S85">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="T85">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U85">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="V85">
         <v>1.3</v>
@@ -14197,31 +14197,31 @@
         <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z85">
         <v>2.7</v>
       </c>
       <c r="AA85">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AB85">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC85">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD85">
         <v>1.18</v>
       </c>
       <c r="AE85">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF85">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG85">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>2.03</v>
+        <v>1.37</v>
       </c>
       <c r="AK85">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="O86">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="P86">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,19 +14490,19 @@
         </is>
       </c>
       <c r="N87">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O87">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P87">
         <v>1.57</v>
       </c>
       <c r="Q87">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R87">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
         <v>1.25</v>
@@ -14511,43 +14511,43 @@
         <v>3.84</v>
       </c>
       <c r="U87">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="V87">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W87">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z87">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA87">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB87">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AC87">
         <v>2.33</v>
       </c>
       <c r="AD87">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE87">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF87">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG87">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="AK87">
         <v>1.19</v>
@@ -14653,22 +14653,22 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O88">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q88">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T88">
         <v>3.6</v>
@@ -14683,7 +14683,7 @@
         <v>1.14</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
         <v>1.14</v>
@@ -14692,19 +14692,19 @@
         <v>3.95</v>
       </c>
       <c r="AA88">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB88">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="AC88">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD88">
         <v>1.54</v>
       </c>
       <c r="AE88">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
         <v>1.55</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O96">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P96">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Q96">
-        <v>5</v>
+        <v>4.53</v>
       </c>
       <c r="R96">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="S96">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U96">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V96">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA96">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB96">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AC96">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AD96">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE96">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF96">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG96">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16446,34 +16446,34 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O99">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="P99">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q99">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R99">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="S99">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T99">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U99">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V99">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16482,28 +16482,28 @@
         <v>1.13</v>
       </c>
       <c r="Z99">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="AA99">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB99">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC99">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD99">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE99">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF99">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AG99">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK99">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17282,10 +17282,10 @@
         <v>2.27</v>
       </c>
       <c r="U104">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V104">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W104">
         <v>1.04</v>
@@ -17294,25 +17294,25 @@
         <v>1.07</v>
       </c>
       <c r="Y104">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z104">
         <v>2.4</v>
       </c>
       <c r="AA104">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AB104">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC104">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="AD104">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE104">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
         <v>2.33</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
         <v>1.95</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O108">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
         <v>2.8</v>
       </c>
       <c r="Q108">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="R108">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="S108">
         <v>1.47</v>
@@ -17934,10 +17934,10 @@
         <v>2.5</v>
       </c>
       <c r="U108">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
         <v>1.05</v>
@@ -17946,31 +17946,31 @@
         <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Z108">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AA108">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="AB108">
         <v>1.6</v>
       </c>
       <c r="AC108">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD108">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AG108">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK108">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20204,16 +20204,16 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U122">
         <v>0</v>
@@ -20228,31 +20228,31 @@
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE122">
         <v>0</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20367,10 +20367,10 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S123">
         <v>0</v>
@@ -20379,10 +20379,10 @@
         <v>0</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W123">
         <v>0</v>
@@ -20391,31 +20391,31 @@
         <v>0</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE123">
         <v>0</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21019,55 +21019,55 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="R127">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S127">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T127">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U127">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="V127">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z127">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA127">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB127">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AC127">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="AD127">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF127">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AG127">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AL127">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU129"/>
+  <dimension ref="A1:AU121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,52 +973,52 @@
         <v>4.68</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="AA4">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="AK4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,28 +1133,28 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>4.72</v>
+        <v>4.76</v>
       </c>
       <c r="R5">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="S5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.14</v>
@@ -1163,7 +1163,7 @@
         <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB5">
         <v>2.27</v>
@@ -1178,10 +1178,10 @@
         <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG5">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>1.13</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="R35">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S35">
+        <v>1.25</v>
+      </c>
+      <c r="T35">
+        <v>3.42</v>
+      </c>
+      <c r="U35">
+        <v>2.14</v>
+      </c>
+      <c r="V35">
+        <v>1.66</v>
+      </c>
+      <c r="W35">
+        <v>1.15</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.09</v>
+      </c>
+      <c r="Z35">
+        <v>5.3</v>
+      </c>
+      <c r="AA35">
+        <v>1.41</v>
+      </c>
+      <c r="AB35">
+        <v>2.5</v>
+      </c>
+      <c r="AC35">
+        <v>2.08</v>
+      </c>
+      <c r="AD35">
+        <v>1.65</v>
+      </c>
+      <c r="AE35">
         <v>1.3</v>
       </c>
-      <c r="T35">
-        <v>3.22</v>
-      </c>
-      <c r="U35">
-        <v>2.39</v>
-      </c>
-      <c r="V35">
-        <v>1.51</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.18</v>
-      </c>
-      <c r="Z35">
-        <v>4.33</v>
-      </c>
-      <c r="AA35">
-        <v>1.66</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.48</v>
-      </c>
-      <c r="AD35">
-        <v>1.43</v>
-      </c>
-      <c r="AE35">
-        <v>1.2</v>
-      </c>
       <c r="AF35">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG35">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q36">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="R36">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="U36">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="V36">
+        <v>1.51</v>
+      </c>
+      <c r="W36">
+        <v>1.08</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.18</v>
+      </c>
+      <c r="Z36">
+        <v>4.33</v>
+      </c>
+      <c r="AA36">
         <v>1.66</v>
       </c>
-      <c r="W36">
-        <v>1.15</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.09</v>
-      </c>
-      <c r="Z36">
-        <v>5.3</v>
-      </c>
-      <c r="AA36">
-        <v>1.41</v>
-      </c>
       <c r="AB36">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O38">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P38">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q38">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
         <v>3.25</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="V38">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA38">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC38">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="AD38">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE38">
         <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG38">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,22 +6675,22 @@
         <v>5.4</v>
       </c>
       <c r="Q39">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S39">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.35</v>
       </c>
       <c r="U39">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W39">
         <v>1.09</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA39">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AC39">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD39">
+        <v>1.55</v>
+      </c>
+      <c r="AE39">
+        <v>1.2</v>
+      </c>
+      <c r="AF39">
         <v>1.6</v>
       </c>
-      <c r="AE39">
-        <v>1.22</v>
-      </c>
-      <c r="AF39">
-        <v>1.5</v>
-      </c>
       <c r="AG39">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="O40">
         <v>3.55</v>
       </c>
       <c r="P40">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="Q40">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R40">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
         <v>1.23</v>
@@ -6850,10 +6850,10 @@
         <v>3.52</v>
       </c>
       <c r="U40">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W40">
         <v>1.13</v>
@@ -6865,25 +6865,25 @@
         <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA40">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB40">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD40">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG40">
         <v>2.7</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="O42">
         <v>5</v>
       </c>
       <c r="P42">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q42">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="R42">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="S42">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="U42">
         <v>2.05</v>
       </c>
       <c r="V42">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W42">
         <v>1.17</v>
@@ -7197,10 +7197,10 @@
         <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AC42">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD42">
         <v>1.8</v>
@@ -7212,7 +7212,7 @@
         <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="Q43">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R43">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="U43">
         <v>2.21</v>
@@ -7351,31 +7351,31 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>5.15</v>
+        <v>5.38</v>
       </c>
       <c r="AA43">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AB43">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AC43">
         <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF43">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
         <v>1.67</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="Q54">
         <v>3.76</v>
@@ -9129,16 +9129,16 @@
         <v>1.43</v>
       </c>
       <c r="T54">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U54">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="V54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9147,10 +9147,10 @@
         <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB54">
         <v>1.76</v>
@@ -9165,10 +9165,10 @@
         <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,25 +9274,25 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O55">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q55">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S55">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="U55">
         <v>2.65</v>
@@ -9307,19 +9307,19 @@
         <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="AA55">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AB55">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC55">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD55">
         <v>1.33</v>
@@ -9328,10 +9328,10 @@
         <v>1.09</v>
       </c>
       <c r="AF55">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG55">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="P56">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q56">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="R56">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="S56">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T56">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U56">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="V56">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.28</v>
+      </c>
+      <c r="Z56">
+        <v>3.12</v>
+      </c>
+      <c r="AA56">
+        <v>2.14</v>
+      </c>
+      <c r="AB56">
+        <v>1.55</v>
+      </c>
+      <c r="AC56">
+        <v>3.78</v>
+      </c>
+      <c r="AD56">
+        <v>1.25</v>
+      </c>
+      <c r="AE56">
         <v>1.05</v>
       </c>
-      <c r="Y56">
-        <v>1.45</v>
-      </c>
-      <c r="Z56">
-        <v>2.69</v>
-      </c>
-      <c r="AA56">
-        <v>2.3</v>
-      </c>
-      <c r="AB56">
-        <v>1.53</v>
-      </c>
-      <c r="AC56">
-        <v>4.35</v>
-      </c>
-      <c r="AD56">
-        <v>1.15</v>
-      </c>
-      <c r="AE56">
-        <v>1.01</v>
-      </c>
       <c r="AF56">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG56">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
         <v>1.38</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="O57">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="Q57">
-        <v>3.45</v>
+        <v>2.71</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S57">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U57">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V57">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z57">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AA57">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB57">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC57">
         <v>3.6</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AG57">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P58">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="Q58">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="R58">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="S58">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T58">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U58">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
+        <v>1.03</v>
+      </c>
+      <c r="Y58">
+        <v>1.42</v>
+      </c>
+      <c r="Z58">
+        <v>2.82</v>
+      </c>
+      <c r="AA58">
+        <v>2.37</v>
+      </c>
+      <c r="AB58">
+        <v>1.59</v>
+      </c>
+      <c r="AC58">
+        <v>3.98</v>
+      </c>
+      <c r="AD58">
+        <v>1.17</v>
+      </c>
+      <c r="AE58">
         <v>1.02</v>
       </c>
-      <c r="Y58">
-        <v>1.32</v>
-      </c>
-      <c r="Z58">
-        <v>3</v>
-      </c>
-      <c r="AA58">
-        <v>2.2</v>
-      </c>
-      <c r="AB58">
-        <v>1.65</v>
-      </c>
-      <c r="AC58">
-        <v>3.6</v>
-      </c>
-      <c r="AD58">
-        <v>1.23</v>
-      </c>
-      <c r="AE58">
-        <v>1.04</v>
-      </c>
       <c r="AF58">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG58">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O59">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q59">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="R59">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T59">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="U59">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AA59">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB59">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC59">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG59">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q68">
-        <v>3.12</v>
+        <v>1.88</v>
       </c>
       <c r="R68">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T68">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>4.45</v>
+        <v>8</v>
       </c>
       <c r="AA68">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AB68">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="AC68">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="AD68">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AF68">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
+        <v>2.75</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.13</v>
+      </c>
+      <c r="AK68">
         <v>2.5</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.28</v>
-      </c>
-      <c r="AK68">
-        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="O69">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>1.88</v>
+        <v>3.12</v>
       </c>
       <c r="R69">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="S69">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U69">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="V69">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z69">
-        <v>8</v>
+        <v>4.45</v>
       </c>
       <c r="AA69">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AB69">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC69">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="AD69">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AE69">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG69">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12543,16 +12543,16 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R75">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T75">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U75">
         <v>2.66</v>
@@ -12576,7 +12576,7 @@
         <v>1.82</v>
       </c>
       <c r="AB75">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC75">
         <v>3.04</v>
@@ -12591,7 +12591,7 @@
         <v>1.64</v>
       </c>
       <c r="AG75">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK75">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="P76">
         <v>3.4</v>
       </c>
       <c r="Q76">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="R76">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="S76">
         <v>1.65</v>
@@ -12718,16 +12718,16 @@
         <v>2.1</v>
       </c>
       <c r="U76">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="V76">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W76">
         <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y76">
         <v>1.6</v>
@@ -12742,19 +12742,19 @@
         <v>1.35</v>
       </c>
       <c r="AC76">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AD76">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE76">
         <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AG76">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.34</v>
       </c>
       <c r="AK76">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q77">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="R77">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U77">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="AA77">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AC77">
         <v>3.55</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AG77">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,34 +13023,34 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O78">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V78">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W78">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13065,7 +13065,7 @@
         <v>1.65</v>
       </c>
       <c r="AB78">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC78">
         <v>2.65</v>
@@ -13074,13 +13074,13 @@
         <v>1.43</v>
       </c>
       <c r="AE78">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
         <v>1.52</v>
       </c>
       <c r="AG78">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13521,25 +13521,25 @@
         <v>2.13</v>
       </c>
       <c r="Q81">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="R81">
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U81">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V81">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13548,28 +13548,28 @@
         <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA81">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB81">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC81">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AD81">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE81">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG81">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O82">
         <v>3.6</v>
       </c>
       <c r="P82">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q82">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="R82">
         <v>2.45</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
         <v>3.28</v>
       </c>
       <c r="U82">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V82">
         <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB82">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AC82">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD82">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AE82">
         <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AG82">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AK82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>2.45</v>
       </c>
       <c r="Q83">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="V83">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W83">
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z83">
         <v>3.34</v>
       </c>
       <c r="AA83">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AB83">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AC83">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="AD83">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
         <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14022,31 +14022,31 @@
         <v>2.96</v>
       </c>
       <c r="U84">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V84">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z84">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="AA84">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB84">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC84">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AD84">
         <v>1.35</v>
@@ -14055,10 +14055,10 @@
         <v>1.14</v>
       </c>
       <c r="AF84">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG84">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="N85">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O85">
         <v>3.1</v>
@@ -14173,43 +14173,43 @@
         <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="R85">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S85">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T85">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U85">
-        <v>3.48</v>
+        <v>3.15</v>
       </c>
       <c r="V85">
         <v>1.3</v>
       </c>
       <c r="W85">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z85">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA85">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AB85">
         <v>1.62</v>
       </c>
       <c r="AC85">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD85">
         <v>1.18</v>
@@ -14218,10 +14218,10 @@
         <v>1.01</v>
       </c>
       <c r="AF85">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AG85">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.37</v>
+        <v>2.03</v>
       </c>
       <c r="AK85">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC92">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="AD92">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG92">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q93">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
+        <v>1.35</v>
+      </c>
+      <c r="T93">
+        <v>2.94</v>
+      </c>
+      <c r="U93">
+        <v>2.65</v>
+      </c>
+      <c r="V93">
         <v>1.42</v>
       </c>
-      <c r="T93">
-        <v>2.77</v>
-      </c>
-      <c r="U93">
-        <v>2.77</v>
-      </c>
-      <c r="V93">
-        <v>1.43</v>
-      </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA93">
         <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD93">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF93">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK93">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="O94">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="P94">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q94">
         <v>4.45</v>
@@ -15649,43 +15649,43 @@
         <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U94">
         <v>2.14</v>
       </c>
       <c r="V94">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W94">
         <v>1.14</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.09</v>
       </c>
       <c r="Z94">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA94">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB94">
         <v>2.54</v>
       </c>
       <c r="AC94">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD94">
         <v>1.7</v>
       </c>
       <c r="AE94">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF94">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AG94">
         <v>2.47</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK94">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16126,13 +16126,13 @@
         <v>5</v>
       </c>
       <c r="P97">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q97">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R97">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="S97">
         <v>1.23</v>
@@ -16153,22 +16153,22 @@
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA97">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB97">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="AC97">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AD97">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AE97">
         <v>1.27</v>
@@ -17427,46 +17427,46 @@
         <v>2.9</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
+        <v>2.13</v>
+      </c>
+      <c r="Q105">
+        <v>3.58</v>
+      </c>
+      <c r="R105">
         <v>2.2</v>
       </c>
-      <c r="Q105">
-        <v>3.64</v>
-      </c>
-      <c r="R105">
-        <v>2.13</v>
-      </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="V105">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
         <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC105">
         <v>2.92</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="O106">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
         <v>4.75</v>
@@ -17750,52 +17750,52 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O107">
         <v>3.4</v>
       </c>
       <c r="P107">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q107">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="R107">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="S107">
         <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V107">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="AA107">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB107">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC107">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="AD107">
         <v>1.38</v>
@@ -17804,10 +17804,10 @@
         <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG107">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK107">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19715,55 +19715,55 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G121">
@@ -20041,55 +20041,55 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20135,1310 +20135,6 @@
         <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>2.33</v>
-      </c>
-      <c r="R122">
-        <v>2.17</v>
-      </c>
-      <c r="S122">
-        <v>1.35</v>
-      </c>
-      <c r="T122">
-        <v>2.65</v>
-      </c>
-      <c r="U122">
-        <v>0</v>
-      </c>
-      <c r="V122">
-        <v>0</v>
-      </c>
-      <c r="W122">
-        <v>0</v>
-      </c>
-      <c r="X122">
-        <v>0</v>
-      </c>
-      <c r="Y122">
-        <v>1.29</v>
-      </c>
-      <c r="Z122">
-        <v>3.05</v>
-      </c>
-      <c r="AA122">
-        <v>1.93</v>
-      </c>
-      <c r="AB122">
-        <v>1.71</v>
-      </c>
-      <c r="AC122">
-        <v>3.25</v>
-      </c>
-      <c r="AD122">
-        <v>1.26</v>
-      </c>
-      <c r="AE122">
-        <v>0</v>
-      </c>
-      <c r="AF122">
-        <v>1.85</v>
-      </c>
-      <c r="AG122">
-        <v>1.83</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.22</v>
-      </c>
-      <c r="AK122">
-        <v>1.8</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>2.3</v>
-      </c>
-      <c r="R123">
-        <v>2.23</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123">
-        <v>0</v>
-      </c>
-      <c r="U123">
-        <v>2.48</v>
-      </c>
-      <c r="V123">
-        <v>1.41</v>
-      </c>
-      <c r="W123">
-        <v>0</v>
-      </c>
-      <c r="X123">
-        <v>0</v>
-      </c>
-      <c r="Y123">
-        <v>1.24</v>
-      </c>
-      <c r="Z123">
-        <v>3.4</v>
-      </c>
-      <c r="AA123">
-        <v>1.8</v>
-      </c>
-      <c r="AB123">
-        <v>1.83</v>
-      </c>
-      <c r="AC123">
-        <v>2.95</v>
-      </c>
-      <c r="AD123">
-        <v>1.32</v>
-      </c>
-      <c r="AE123">
-        <v>0</v>
-      </c>
-      <c r="AF123">
-        <v>1.72</v>
-      </c>
-      <c r="AG123">
-        <v>1.97</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.21</v>
-      </c>
-      <c r="AK123">
-        <v>1.81</v>
-      </c>
-      <c r="AL123">
-        <v>0</v>
-      </c>
-      <c r="AM123">
-        <v>-1</v>
-      </c>
-      <c r="AN123">
-        <v>-1</v>
-      </c>
-      <c r="AO123">
-        <v>-1</v>
-      </c>
-      <c r="AP123">
-        <v>-1</v>
-      </c>
-      <c r="AQ123">
-        <v>0</v>
-      </c>
-      <c r="AR123">
-        <v>0</v>
-      </c>
-      <c r="AS123">
-        <v>0</v>
-      </c>
-      <c r="AT123">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
-      <c r="U125">
-        <v>0</v>
-      </c>
-      <c r="V125">
-        <v>0</v>
-      </c>
-      <c r="W125">
-        <v>0</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>0</v>
-      </c>
-      <c r="Z125">
-        <v>0</v>
-      </c>
-      <c r="AA125">
-        <v>0</v>
-      </c>
-      <c r="AB125">
-        <v>0</v>
-      </c>
-      <c r="AC125">
-        <v>0</v>
-      </c>
-      <c r="AD125">
-        <v>0</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>0</v>
-      </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-      <c r="AK125">
-        <v>0</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>2.1</v>
-      </c>
-      <c r="O126">
-        <v>3.1</v>
-      </c>
-      <c r="P126">
-        <v>3.2</v>
-      </c>
-      <c r="Q126">
-        <v>2.55</v>
-      </c>
-      <c r="R126">
-        <v>2.1</v>
-      </c>
-      <c r="S126">
-        <v>1.4</v>
-      </c>
-      <c r="T126">
-        <v>2.69</v>
-      </c>
-      <c r="U126">
-        <v>2.85</v>
-      </c>
-      <c r="V126">
-        <v>1.36</v>
-      </c>
-      <c r="W126">
-        <v>1.06</v>
-      </c>
-      <c r="X126">
-        <v>1.05</v>
-      </c>
-      <c r="Y126">
-        <v>1.3</v>
-      </c>
-      <c r="Z126">
-        <v>3.2</v>
-      </c>
-      <c r="AA126">
-        <v>1.95</v>
-      </c>
-      <c r="AB126">
-        <v>1.8</v>
-      </c>
-      <c r="AC126">
-        <v>3.5</v>
-      </c>
-      <c r="AD126">
-        <v>1.28</v>
-      </c>
-      <c r="AE126">
-        <v>1.05</v>
-      </c>
-      <c r="AF126">
-        <v>1.77</v>
-      </c>
-      <c r="AG126">
-        <v>1.97</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.3</v>
-      </c>
-      <c r="AK126">
-        <v>1.64</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>2.08</v>
-      </c>
-      <c r="R127">
-        <v>2.35</v>
-      </c>
-      <c r="S127">
-        <v>1.35</v>
-      </c>
-      <c r="T127">
-        <v>2.88</v>
-      </c>
-      <c r="U127">
-        <v>2.69</v>
-      </c>
-      <c r="V127">
-        <v>1.4</v>
-      </c>
-      <c r="W127">
-        <v>1.05</v>
-      </c>
-      <c r="X127">
-        <v>1.02</v>
-      </c>
-      <c r="Y127">
-        <v>1.24</v>
-      </c>
-      <c r="Z127">
-        <v>3.66</v>
-      </c>
-      <c r="AA127">
-        <v>1.88</v>
-      </c>
-      <c r="AB127">
-        <v>1.93</v>
-      </c>
-      <c r="AC127">
-        <v>3.26</v>
-      </c>
-      <c r="AD127">
-        <v>1.33</v>
-      </c>
-      <c r="AE127">
-        <v>1.11</v>
-      </c>
-      <c r="AF127">
-        <v>1.92</v>
-      </c>
-      <c r="AG127">
-        <v>1.79</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.22</v>
-      </c>
-      <c r="AK127">
-        <v>2.38</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-09-04 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>3.54</v>
-      </c>
-      <c r="R129">
-        <v>2.31</v>
-      </c>
-      <c r="S129">
-        <v>1.27</v>
-      </c>
-      <c r="T129">
-        <v>2.75</v>
-      </c>
-      <c r="U129">
-        <v>2.22</v>
-      </c>
-      <c r="V129">
-        <v>1.57</v>
-      </c>
-      <c r="W129">
-        <v>1.09</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>1.11</v>
-      </c>
-      <c r="Z129">
-        <v>4.6</v>
-      </c>
-      <c r="AA129">
-        <v>1.53</v>
-      </c>
-      <c r="AB129">
-        <v>2.31</v>
-      </c>
-      <c r="AC129">
-        <v>2.3</v>
-      </c>
-      <c r="AD129">
-        <v>1.49</v>
-      </c>
-      <c r="AE129">
-        <v>1.17</v>
-      </c>
-      <c r="AF129">
-        <v>1.36</v>
-      </c>
-      <c r="AG129">
-        <v>2.15</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>1.67</v>
-      </c>
-      <c r="AK129">
-        <v>1.19</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="P56">
+        <v>2.68</v>
+      </c>
+      <c r="Q56">
+        <v>3.26</v>
+      </c>
+      <c r="R56">
+        <v>1.98</v>
+      </c>
+      <c r="S56">
+        <v>1.46</v>
+      </c>
+      <c r="T56">
+        <v>2.53</v>
+      </c>
+      <c r="U56">
+        <v>3.22</v>
+      </c>
+      <c r="V56">
+        <v>1.3</v>
+      </c>
+      <c r="W56">
+        <v>1.02</v>
+      </c>
+      <c r="X56">
+        <v>1.03</v>
+      </c>
+      <c r="Y56">
+        <v>1.42</v>
+      </c>
+      <c r="Z56">
+        <v>2.82</v>
+      </c>
+      <c r="AA56">
         <v>2.37</v>
       </c>
-      <c r="Q56">
-        <v>3.23</v>
-      </c>
-      <c r="R56">
-        <v>1.99</v>
-      </c>
-      <c r="S56">
-        <v>1.43</v>
-      </c>
-      <c r="T56">
-        <v>2.62</v>
-      </c>
-      <c r="U56">
-        <v>2.94</v>
-      </c>
-      <c r="V56">
-        <v>1.35</v>
-      </c>
-      <c r="W56">
-        <v>1.03</v>
-      </c>
-      <c r="X56">
+      <c r="AB56">
+        <v>1.59</v>
+      </c>
+      <c r="AC56">
+        <v>3.98</v>
+      </c>
+      <c r="AD56">
+        <v>1.17</v>
+      </c>
+      <c r="AE56">
         <v>1.02</v>
       </c>
-      <c r="Y56">
-        <v>1.28</v>
-      </c>
-      <c r="Z56">
-        <v>3.12</v>
-      </c>
-      <c r="AA56">
-        <v>2.14</v>
-      </c>
-      <c r="AB56">
-        <v>1.55</v>
-      </c>
-      <c r="AC56">
-        <v>3.78</v>
-      </c>
-      <c r="AD56">
-        <v>1.25</v>
-      </c>
-      <c r="AE56">
-        <v>1.05</v>
-      </c>
       <c r="AF56">
+        <v>1.95</v>
+      </c>
+      <c r="AG56">
         <v>1.75</v>
-      </c>
-      <c r="AG56">
-        <v>1.97</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="O57">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P57">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q57">
-        <v>2.71</v>
+        <v>3.23</v>
       </c>
       <c r="R57">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T57">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U57">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V57">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA57">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB57">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC57">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="Q58">
-        <v>3.26</v>
+        <v>2.71</v>
       </c>
       <c r="R58">
         <v>1.98</v>
       </c>
       <c r="S58">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
         <v>2.53</v>
       </c>
       <c r="U58">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
         <v>1.02</v>
       </c>
-      <c r="X58">
-        <v>1.03</v>
-      </c>
       <c r="Y58">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AA58">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AB58">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AC58">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="AD58">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG58">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="P67">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q67">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="R67">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="S67">
+        <v>1.14</v>
+      </c>
+      <c r="T67">
+        <v>4.5</v>
+      </c>
+      <c r="U67">
+        <v>1.83</v>
+      </c>
+      <c r="V67">
+        <v>1.89</v>
+      </c>
+      <c r="W67">
         <v>1.22</v>
       </c>
-      <c r="T67">
-        <v>3.58</v>
-      </c>
-      <c r="U67">
-        <v>2.19</v>
-      </c>
-      <c r="V67">
-        <v>1.62</v>
-      </c>
-      <c r="W67">
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.05</v>
+      </c>
+      <c r="Z67">
+        <v>8</v>
+      </c>
+      <c r="AA67">
+        <v>1.3</v>
+      </c>
+      <c r="AB67">
+        <v>3.5</v>
+      </c>
+      <c r="AC67">
+        <v>1.72</v>
+      </c>
+      <c r="AD67">
+        <v>2.06</v>
+      </c>
+      <c r="AE67">
+        <v>1.43</v>
+      </c>
+      <c r="AF67">
+        <v>1.4</v>
+      </c>
+      <c r="AG67">
+        <v>2.75</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.13</v>
       </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.14</v>
-      </c>
-      <c r="Z67">
-        <v>5.25</v>
-      </c>
-      <c r="AA67">
-        <v>1.47</v>
-      </c>
-      <c r="AB67">
-        <v>2.55</v>
-      </c>
-      <c r="AC67">
-        <v>2.13</v>
-      </c>
-      <c r="AD67">
-        <v>1.61</v>
-      </c>
-      <c r="AE67">
-        <v>1.21</v>
-      </c>
-      <c r="AF67">
-        <v>1.5</v>
-      </c>
-      <c r="AG67">
-        <v>2.38</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.19</v>
-      </c>
       <c r="AK67">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="O68">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
-        <v>1.88</v>
+        <v>3.12</v>
       </c>
       <c r="R68">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="S68">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>8</v>
+        <v>4.45</v>
       </c>
       <c r="AA68">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AB68">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC68">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="AD68">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AE68">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q69">
-        <v>3.12</v>
+        <v>2.07</v>
       </c>
       <c r="R69">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="S69">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U69">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V69">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W69">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
         <v>1.14</v>
       </c>
       <c r="Z69">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA69">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AB69">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AC69">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="AD69">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AE69">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF69">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>1.46</v>
+        <v>2.27</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -16621,22 +16621,22 @@
         <v>2.04</v>
       </c>
       <c r="R100">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U100">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V100">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W100">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X100">
         <v>1.02</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK100">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G116">

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2769,19 +2769,19 @@
         <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,19 +2793,19 @@
         <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB15">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AC15">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
         <v>1.55</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
         <v>1.83</v>
@@ -5045,25 +5045,25 @@
         <v>2.89</v>
       </c>
       <c r="Q29">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R29">
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
         <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5075,7 +5075,7 @@
         <v>3.42</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
         <v>1.9</v>
@@ -5090,10 +5090,10 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
         <v>1.55</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="U35">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="V35">
+        <v>1.51</v>
+      </c>
+      <c r="W35">
+        <v>1.08</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.18</v>
+      </c>
+      <c r="Z35">
+        <v>4.33</v>
+      </c>
+      <c r="AA35">
         <v>1.66</v>
       </c>
-      <c r="W35">
-        <v>1.15</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.09</v>
-      </c>
-      <c r="Z35">
-        <v>5.3</v>
-      </c>
-      <c r="AA35">
-        <v>1.41</v>
-      </c>
       <c r="AB35">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AD35">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="R36">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S36">
+        <v>1.25</v>
+      </c>
+      <c r="T36">
+        <v>3.42</v>
+      </c>
+      <c r="U36">
+        <v>2.14</v>
+      </c>
+      <c r="V36">
+        <v>1.66</v>
+      </c>
+      <c r="W36">
+        <v>1.15</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.09</v>
+      </c>
+      <c r="Z36">
+        <v>5.3</v>
+      </c>
+      <c r="AA36">
+        <v>1.41</v>
+      </c>
+      <c r="AB36">
+        <v>2.5</v>
+      </c>
+      <c r="AC36">
+        <v>2.08</v>
+      </c>
+      <c r="AD36">
+        <v>1.65</v>
+      </c>
+      <c r="AE36">
         <v>1.3</v>
       </c>
-      <c r="T36">
-        <v>3.22</v>
-      </c>
-      <c r="U36">
-        <v>2.39</v>
-      </c>
-      <c r="V36">
-        <v>1.51</v>
-      </c>
-      <c r="W36">
-        <v>1.08</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.18</v>
-      </c>
-      <c r="Z36">
-        <v>4.33</v>
-      </c>
-      <c r="AA36">
-        <v>1.66</v>
-      </c>
-      <c r="AB36">
-        <v>2.15</v>
-      </c>
-      <c r="AC36">
-        <v>2.48</v>
-      </c>
-      <c r="AD36">
-        <v>1.43</v>
-      </c>
-      <c r="AE36">
-        <v>1.2</v>
-      </c>
       <c r="AF36">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="R66">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
         <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="V66">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>5.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA66">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AB66">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AC66">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AD66">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF66">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG66">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="O67">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q67">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="R67">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="S67">
+        <v>1.22</v>
+      </c>
+      <c r="T67">
+        <v>3.58</v>
+      </c>
+      <c r="U67">
+        <v>2.19</v>
+      </c>
+      <c r="V67">
+        <v>1.62</v>
+      </c>
+      <c r="W67">
+        <v>1.13</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
         <v>1.14</v>
       </c>
-      <c r="T67">
-        <v>4.5</v>
-      </c>
-      <c r="U67">
-        <v>1.83</v>
-      </c>
-      <c r="V67">
-        <v>1.89</v>
-      </c>
-      <c r="W67">
-        <v>1.22</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.05</v>
-      </c>
       <c r="Z67">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB67">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC67">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="AD67">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="AE67">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG67">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q68">
-        <v>3.12</v>
+        <v>1.88</v>
       </c>
       <c r="R68">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T68">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>4.45</v>
+        <v>8</v>
       </c>
       <c r="AA68">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AB68">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="AC68">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="AD68">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="AF68">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
+        <v>2.75</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.13</v>
+      </c>
+      <c r="AK68">
         <v>2.5</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.28</v>
-      </c>
-      <c r="AK68">
-        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,31 +11556,31 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q69">
-        <v>2.07</v>
+        <v>3.34</v>
       </c>
       <c r="R69">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S69">
         <v>1.22</v>
       </c>
       <c r="T69">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U69">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="V69">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W69">
         <v>1.13</v>
@@ -11589,31 +11589,31 @@
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z69">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA69">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB69">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC69">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AD69">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE69">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P82">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="Q82">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
+        <v>1.36</v>
+      </c>
+      <c r="T82">
+        <v>2.88</v>
+      </c>
+      <c r="U82">
+        <v>2.62</v>
+      </c>
+      <c r="V82">
+        <v>1.39</v>
+      </c>
+      <c r="W82">
+        <v>1.06</v>
+      </c>
+      <c r="X82">
+        <v>1.05</v>
+      </c>
+      <c r="Y82">
+        <v>1.24</v>
+      </c>
+      <c r="Z82">
+        <v>3.34</v>
+      </c>
+      <c r="AA82">
+        <v>1.88</v>
+      </c>
+      <c r="AB82">
+        <v>1.95</v>
+      </c>
+      <c r="AC82">
+        <v>3.1</v>
+      </c>
+      <c r="AD82">
+        <v>1.36</v>
+      </c>
+      <c r="AE82">
+        <v>1.12</v>
+      </c>
+      <c r="AF82">
+        <v>1.65</v>
+      </c>
+      <c r="AG82">
+        <v>2.1</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
         <v>1.25</v>
       </c>
-      <c r="T82">
-        <v>3.28</v>
-      </c>
-      <c r="U82">
-        <v>2.22</v>
-      </c>
-      <c r="V82">
-        <v>1.58</v>
-      </c>
-      <c r="W82">
-        <v>1.15</v>
-      </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.17</v>
-      </c>
-      <c r="Z82">
-        <v>4.8</v>
-      </c>
-      <c r="AA82">
-        <v>1.5</v>
-      </c>
-      <c r="AB82">
-        <v>2.33</v>
-      </c>
-      <c r="AC82">
-        <v>2.25</v>
-      </c>
-      <c r="AD82">
-        <v>1.62</v>
-      </c>
-      <c r="AE82">
-        <v>1.19</v>
-      </c>
-      <c r="AF82">
-        <v>1.46</v>
-      </c>
-      <c r="AG82">
-        <v>2.5</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.75</v>
-      </c>
       <c r="AK82">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
+        <v>1.89</v>
+      </c>
+      <c r="Q83">
+        <v>3.4</v>
+      </c>
+      <c r="R83">
         <v>2.45</v>
       </c>
-      <c r="Q83">
-        <v>3</v>
-      </c>
-      <c r="R83">
-        <v>2.1</v>
-      </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U83">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="V83">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z83">
-        <v>3.34</v>
+        <v>4.8</v>
       </c>
       <c r="AA83">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AB83">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AC83">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK83">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q92">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
+        <v>1.35</v>
+      </c>
+      <c r="T92">
+        <v>2.94</v>
+      </c>
+      <c r="U92">
+        <v>2.65</v>
+      </c>
+      <c r="V92">
         <v>1.42</v>
       </c>
-      <c r="T92">
-        <v>2.77</v>
-      </c>
-      <c r="U92">
-        <v>2.77</v>
-      </c>
-      <c r="V92">
-        <v>1.43</v>
-      </c>
       <c r="W92">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z92">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC92">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF92">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK92">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="Q93">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U93">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA93">
         <v>1.85</v>
       </c>
       <c r="AB93">
+        <v>1.89</v>
+      </c>
+      <c r="AC93">
+        <v>3.2</v>
+      </c>
+      <c r="AD93">
+        <v>1.3</v>
+      </c>
+      <c r="AE93">
+        <v>1.11</v>
+      </c>
+      <c r="AF93">
+        <v>1.79</v>
+      </c>
+      <c r="AG93">
+        <v>2</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.2</v>
+      </c>
+      <c r="AK93">
         <v>1.95</v>
-      </c>
-      <c r="AC93">
-        <v>2.94</v>
-      </c>
-      <c r="AD93">
-        <v>1.31</v>
-      </c>
-      <c r="AE93">
-        <v>1.09</v>
-      </c>
-      <c r="AF93">
-        <v>1.67</v>
-      </c>
-      <c r="AG93">
-        <v>2.1</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.35</v>
-      </c>
-      <c r="AK93">
-        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -970,28 +970,28 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>4.68</v>
+        <v>4</v>
       </c>
       <c r="R4">
         <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.17</v>
@@ -1000,13 +1000,13 @@
         <v>3.98</v>
       </c>
       <c r="AA4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC4">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AD4">
         <v>1.36</v>
@@ -1018,7 +1018,7 @@
         <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1142,34 +1142,34 @@
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
         <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
         <v>2.27</v>
       </c>
       <c r="AC5">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD5">
         <v>1.47</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
         <v>1.13</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O12">
-        <v>7.45</v>
+        <v>6.6</v>
       </c>
       <c r="P12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Q12">
         <v>10.1</v>
       </c>
       <c r="R12">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="S12">
         <v>1.17</v>
@@ -2292,7 +2292,7 @@
         <v>1.67</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,28 +2301,28 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB12">
         <v>2.62</v>
       </c>
       <c r="AC12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AD12">
         <v>1.68</v>
       </c>
       <c r="AE12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         <v>2.61</v>
       </c>
       <c r="Q19">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
         <v>3.14</v>
@@ -3433,34 +3433,34 @@
         <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB19">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
         <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG19">
         <v>2.36</v>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,58 +4873,58 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O28">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P28">
         <v>2.87</v>
       </c>
       <c r="Q28">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="S28">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="T28">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U28">
         <v>3.28</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z28">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="AA28">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="AB28">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="AD28">
         <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
         <v>1.9</v>
@@ -4946,7 +4946,7 @@
         <v>1.4</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5223,7 +5223,7 @@
         <v>2.07</v>
       </c>
       <c r="V30">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W30">
         <v>1.15</v>
@@ -5238,10 +5238,10 @@
         <v>6.05</v>
       </c>
       <c r="AA30">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB30">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AC30">
         <v>1.99</v>
@@ -5272,7 +5272,7 @@
         <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,46 +5525,46 @@
         </is>
       </c>
       <c r="N32">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>3.75</v>
       </c>
       <c r="P32">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q32">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V32">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB32">
         <v>1.72</v>
@@ -5573,16 +5573,16 @@
         <v>3.79</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE32">
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AG32">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
-        <v>2.49</v>
+        <v>2.79</v>
       </c>
       <c r="R34">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
         <v>1.29</v>
@@ -5872,34 +5872,34 @@
         <v>3.08</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB34">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC34">
         <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
         <v>1.11</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
         <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="R35">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA35">
+        <v>1.61</v>
+      </c>
+      <c r="AB35">
+        <v>2.25</v>
+      </c>
+      <c r="AC35">
+        <v>2.39</v>
+      </c>
+      <c r="AD35">
+        <v>1.46</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
+        <v>1.5</v>
+      </c>
+      <c r="AG35">
+        <v>2.42</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.26</v>
+      </c>
+      <c r="AK35">
         <v>1.66</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.48</v>
-      </c>
-      <c r="AD35">
-        <v>1.43</v>
-      </c>
-      <c r="AE35">
-        <v>1.2</v>
-      </c>
-      <c r="AF35">
-        <v>1.52</v>
-      </c>
-      <c r="AG35">
-        <v>2.37</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.24</v>
-      </c>
-      <c r="AK35">
-        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="R36">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T36">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
         <v>2.14</v>
@@ -6213,28 +6213,28 @@
         <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
         <v>2.08</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AE36">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
         <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
+        <v>4.4</v>
+      </c>
+      <c r="O37">
         <v>4.2</v>
       </c>
-      <c r="O37">
-        <v>4</v>
-      </c>
       <c r="P37">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q37">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R37">
         <v>2.38</v>
@@ -6361,19 +6361,19 @@
         <v>3.34</v>
       </c>
       <c r="U37">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
         <v>4.55</v>
@@ -6385,19 +6385,19 @@
         <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD37">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>2.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O38">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q38">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="R38">
         <v>2.38</v>
@@ -6521,13 +6521,13 @@
         <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
         <v>1.1</v>
@@ -6539,28 +6539,28 @@
         <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB38">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC38">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AD38">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="O39">
         <v>4.1</v>
       </c>
       <c r="P39">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q39">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R39">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
         <v>1.25</v>
@@ -6687,10 +6687,10 @@
         <v>3.35</v>
       </c>
       <c r="U39">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V39">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.09</v>
@@ -6705,22 +6705,22 @@
         <v>4.6</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AD39">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG39">
         <v>2.13</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="O40">
         <v>3.55</v>
       </c>
       <c r="P40">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="R40">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="S40">
         <v>1.23</v>
@@ -6865,13 +6865,13 @@
         <v>1.09</v>
       </c>
       <c r="Z40">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA40">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB40">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC40">
         <v>2.16</v>
@@ -6880,10 +6880,10 @@
         <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF40">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG40">
         <v>2.7</v>
@@ -7001,10 +7001,10 @@
         <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7025,19 +7025,19 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AB41">
         <v>2.33</v>
       </c>
       <c r="AC41">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="AD41">
         <v>1.51</v>
@@ -7490,52 +7490,52 @@
         <v>3.4</v>
       </c>
       <c r="Q44">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="R44">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W44">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA44">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC44">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD44">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE44">
         <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG44">
         <v>2.44</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
         <v>1.89</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8628,19 +8628,19 @@
         <v>3.3</v>
       </c>
       <c r="P51">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="Q51">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U51">
         <v>2.62</v>
@@ -8652,22 +8652,22 @@
         <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB51">
         <v>1.98</v>
       </c>
       <c r="AC51">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
@@ -8676,10 +8676,10 @@
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG51">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O54">
         <v>3</v>
       </c>
       <c r="P54">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q54">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="R54">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T54">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U54">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W54">
         <v>1.04</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z54">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AA54">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC54">
-        <v>3.92</v>
+        <v>3.38</v>
       </c>
       <c r="AD54">
         <v>1.24</v>
       </c>
       <c r="AE54">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF54">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9280,58 +9280,58 @@
         <v>3.4</v>
       </c>
       <c r="P55">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q55">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="R55">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S55">
         <v>1.35</v>
       </c>
       <c r="T55">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="U55">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W55">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="AA55">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB55">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC55">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AD55">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE55">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="Q56">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="R56">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S56">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T56">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U56">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="V56">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
+        <v>1.03</v>
+      </c>
+      <c r="X56">
         <v>1.02</v>
       </c>
-      <c r="X56">
-        <v>1.03</v>
-      </c>
       <c r="Y56">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="AA56">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC56">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AD56">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG56">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>2.37</v>
+        <v>3.32</v>
       </c>
       <c r="Q57">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="R57">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S57">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T57">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U57">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V57">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="AA57">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AB57">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK57">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q58">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="R58">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
         <v>1.44</v>
       </c>
       <c r="T58">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U58">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB58">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC58">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AD58">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG58">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P59">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
         <v>2.33</v>
@@ -9965,10 +9965,10 @@
         <v>3.75</v>
       </c>
       <c r="AA59">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB59">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC59">
         <v>2.62</v>
@@ -9980,10 +9980,10 @@
         <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R61">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T61">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="U61">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="V61">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
         <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z61">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA61">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC61">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD61">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF61">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG61">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,52 +10415,52 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q62">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="R62">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V62">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
         <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA62">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC62">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD62">
         <v>1.38</v>
@@ -10469,10 +10469,10 @@
         <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AG62">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O63">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P63">
         <v>3.9</v>
       </c>
       <c r="Q63">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R63">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U63">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB63">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AC63">
         <v>2.15</v>
       </c>
       <c r="AD63">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE63">
         <v>1.25</v>
       </c>
       <c r="AF63">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
         <v>2.37</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="R64">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="U64">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V64">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10777,28 +10777,28 @@
         <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA64">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC64">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AD64">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AE64">
         <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG64">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,16 +10907,16 @@
         <v>1.4</v>
       </c>
       <c r="O65">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P65">
         <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R65">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="S65">
         <v>1.17</v>
@@ -10946,22 +10946,22 @@
         <v>1.28</v>
       </c>
       <c r="AB65">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="AC65">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AD65">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AE65">
         <v>1.4</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK65">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,16 +11076,16 @@
         <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="R66">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U66">
         <v>2.32</v>
@@ -11094,7 +11094,7 @@
         <v>1.53</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,28 +11103,28 @@
         <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB66">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC66">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE66">
         <v>1.16</v>
       </c>
       <c r="AF66">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P67">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q67">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="R67">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T67">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="U67">
         <v>2.19</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC67">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AD67">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE67">
         <v>1.21</v>
       </c>
       <c r="AF67">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O68">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="P68">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q68">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R68">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="S68">
         <v>1.14</v>
@@ -11420,19 +11420,19 @@
         <v>1.89</v>
       </c>
       <c r="W68">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z68">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AA68">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AB68">
         <v>3.5</v>
@@ -11447,10 +11447,10 @@
         <v>1.43</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG68">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK68">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P69">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q69">
         <v>3.34</v>
       </c>
       <c r="R69">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="S69">
         <v>1.22</v>
@@ -11577,10 +11577,10 @@
         <v>3.6</v>
       </c>
       <c r="U69">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V69">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W69">
         <v>1.13</v>
@@ -11589,31 +11589,31 @@
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z69">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA69">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB69">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC69">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AD69">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE69">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG69">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
         <v>1.39</v>
@@ -11722,16 +11722,16 @@
         <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
         <v>2.75</v>
       </c>
       <c r="Q70">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S70">
         <v>1.27</v>
@@ -11764,7 +11764,7 @@
         <v>2.17</v>
       </c>
       <c r="AC70">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD70">
         <v>1.43</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12214,25 +12214,25 @@
         <v>3.1</v>
       </c>
       <c r="P73">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q73">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R73">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="S73">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T73">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U73">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="V73">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
         <v>1.02</v>
@@ -12244,16 +12244,16 @@
         <v>1.3</v>
       </c>
       <c r="Z73">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="AA73">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB73">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC73">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AD73">
         <v>1.21</v>
@@ -12262,10 +12262,10 @@
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG73">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK73">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,22 +12374,22 @@
         <v>1.36</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P74">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q74">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R74">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="U74">
         <v>2.53</v>
@@ -12407,16 +12407,16 @@
         <v>1.18</v>
       </c>
       <c r="Z74">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="AA74">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB74">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC74">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AD74">
         <v>1.37</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AK74">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,16 +12543,16 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S75">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U75">
         <v>2.66</v>
@@ -12573,25 +12573,25 @@
         <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB75">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC75">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG75">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T77">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U77">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="V77">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W77">
         <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z77">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC77">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="AD77">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK77">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13038,19 +13038,19 @@
         <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U78">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="V78">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W78">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13068,7 +13068,7 @@
         <v>2.17</v>
       </c>
       <c r="AC78">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="AD78">
         <v>1.43</v>
@@ -13080,7 +13080,7 @@
         <v>1.52</v>
       </c>
       <c r="AG78">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AK78">
         <v>1.52</v>
@@ -13186,19 +13186,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O79">
         <v>4.8</v>
       </c>
       <c r="P79">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q79">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R79">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="S79">
         <v>1.21</v>
@@ -13207,10 +13207,10 @@
         <v>4.2</v>
       </c>
       <c r="U79">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V79">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W79">
         <v>1.22</v>
@@ -13222,44 +13222,44 @@
         <v>1.07</v>
       </c>
       <c r="Z79">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA79">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB79">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="AC79">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AD79">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AE79">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF79">
         <v>1.47</v>
       </c>
       <c r="AG79">
+        <v>2.53</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.21</v>
+      </c>
+      <c r="AK79">
         <v>2.62</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.13</v>
-      </c>
-      <c r="AK79">
-        <v>2.55</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="O80">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P80">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="Q80">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R80">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S80">
         <v>1.39</v>
@@ -13373,10 +13373,10 @@
         <v>2.96</v>
       </c>
       <c r="V80">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13388,25 +13388,25 @@
         <v>2.97</v>
       </c>
       <c r="AA80">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB80">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC80">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD80">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE80">
         <v>1.04</v>
       </c>
       <c r="AF80">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG80">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="Q81">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="V81">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z81">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB81">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD81">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE81">
         <v>1.12</v>
       </c>
       <c r="AF81">
+        <v>1.65</v>
+      </c>
+      <c r="AG81">
+        <v>2.1</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>1.25</v>
+      </c>
+      <c r="AK81">
         <v>1.48</v>
-      </c>
-      <c r="AG81">
-        <v>2.35</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.22</v>
-      </c>
-      <c r="AK81">
-        <v>1.31</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
+        <v>1.89</v>
+      </c>
+      <c r="Q82">
+        <v>3.4</v>
+      </c>
+      <c r="R82">
         <v>2.45</v>
       </c>
-      <c r="Q82">
-        <v>3</v>
-      </c>
-      <c r="R82">
-        <v>2.1</v>
-      </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U82">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="V82">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>3.34</v>
+        <v>4.8</v>
       </c>
       <c r="AA82">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AC82">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD82">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE82">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="AG82">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK82">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P83">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U83">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V83">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W83">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA83">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB83">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="AC83">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="AD83">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE83">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AG83">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q85">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="R85">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S85">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T85">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="U85">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V85">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W85">
         <v>1.03</v>
       </c>
       <c r="X85">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z85">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AA85">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB85">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC85">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD85">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE85">
         <v>1.01</v>
       </c>
       <c r="AF85">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AG85">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>2.03</v>
+        <v>1.37</v>
       </c>
       <c r="AK85">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14330,10 +14330,10 @@
         <v>8.5</v>
       </c>
       <c r="O86">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="P86">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O87">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P87">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q87">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="S87">
         <v>1.25</v>
       </c>
       <c r="T87">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="U87">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="V87">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W87">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA87">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB87">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="AC87">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD87">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AE87">
+        <v>1.24</v>
+      </c>
+      <c r="AF87">
+        <v>1.54</v>
+      </c>
+      <c r="AG87">
+        <v>2.35</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.22</v>
       </c>
-      <c r="AF87">
-        <v>1.55</v>
-      </c>
-      <c r="AG87">
-        <v>2.32</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>2.4</v>
-      </c>
       <c r="AK87">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O88">
         <v>3.65</v>
@@ -14662,10 +14662,10 @@
         <v>3.85</v>
       </c>
       <c r="Q88">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="R88">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
         <v>1.24</v>
@@ -14689,19 +14689,19 @@
         <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA88">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC88">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AD88">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE88">
         <v>1.17</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V92">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
       </c>
       <c r="AB92">
+        <v>1.89</v>
+      </c>
+      <c r="AC92">
+        <v>3.2</v>
+      </c>
+      <c r="AD92">
+        <v>1.3</v>
+      </c>
+      <c r="AE92">
+        <v>1.11</v>
+      </c>
+      <c r="AF92">
+        <v>1.79</v>
+      </c>
+      <c r="AG92">
+        <v>2</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.2</v>
+      </c>
+      <c r="AK92">
         <v>1.95</v>
-      </c>
-      <c r="AC92">
-        <v>2.94</v>
-      </c>
-      <c r="AD92">
-        <v>1.31</v>
-      </c>
-      <c r="AE92">
-        <v>1.09</v>
-      </c>
-      <c r="AF92">
-        <v>1.67</v>
-      </c>
-      <c r="AG92">
-        <v>2.1</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.35</v>
-      </c>
-      <c r="AK92">
-        <v>1.57</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q93">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
+        <v>1.35</v>
+      </c>
+      <c r="T93">
+        <v>2.94</v>
+      </c>
+      <c r="U93">
+        <v>2.65</v>
+      </c>
+      <c r="V93">
         <v>1.42</v>
       </c>
-      <c r="T93">
-        <v>2.77</v>
-      </c>
-      <c r="U93">
-        <v>2.77</v>
-      </c>
-      <c r="V93">
-        <v>1.43</v>
-      </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA93">
         <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD93">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF93">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK93">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O96">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P96">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q96">
-        <v>4.53</v>
+        <v>5.95</v>
       </c>
       <c r="R96">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S96">
         <v>1.22</v>
@@ -15978,13 +15978,13 @@
         <v>4.05</v>
       </c>
       <c r="U96">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="V96">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W96">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,28 +15993,28 @@
         <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="AA96">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB96">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC96">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AD96">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE96">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF96">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.2</v>
       </c>
       <c r="AK96">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O97">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P97">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q97">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="S97">
         <v>1.23</v>
@@ -16162,10 +16162,10 @@
         <v>1.44</v>
       </c>
       <c r="AB97">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC97">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AD97">
         <v>1.81</v>
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
+        <v>1.22</v>
+      </c>
+      <c r="O99">
+        <v>6</v>
+      </c>
+      <c r="P99">
+        <v>15</v>
+      </c>
+      <c r="Q99">
+        <v>1.62</v>
+      </c>
+      <c r="R99">
+        <v>2.51</v>
+      </c>
+      <c r="S99">
+        <v>1.32</v>
+      </c>
+      <c r="T99">
+        <v>3.1</v>
+      </c>
+      <c r="U99">
+        <v>2.38</v>
+      </c>
+      <c r="V99">
+        <v>1.43</v>
+      </c>
+      <c r="W99">
+        <v>1.08</v>
+      </c>
+      <c r="X99">
+        <v>1.03</v>
+      </c>
+      <c r="Y99">
+        <v>1.16</v>
+      </c>
+      <c r="Z99">
+        <v>4.05</v>
+      </c>
+      <c r="AA99">
+        <v>1.62</v>
+      </c>
+      <c r="AB99">
+        <v>2.24</v>
+      </c>
+      <c r="AC99">
+        <v>2.59</v>
+      </c>
+      <c r="AD99">
+        <v>1.48</v>
+      </c>
+      <c r="AE99">
+        <v>1.14</v>
+      </c>
+      <c r="AF99">
+        <v>2.4</v>
+      </c>
+      <c r="AG99">
+        <v>1.51</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.13</v>
       </c>
-      <c r="O99">
-        <v>7.7</v>
-      </c>
-      <c r="P99">
-        <v>20</v>
-      </c>
-      <c r="Q99">
-        <v>1.49</v>
-      </c>
-      <c r="R99">
-        <v>2.85</v>
-      </c>
-      <c r="S99">
-        <v>1.24</v>
-      </c>
-      <c r="T99">
-        <v>3.5</v>
-      </c>
-      <c r="U99">
-        <v>2.31</v>
-      </c>
-      <c r="V99">
-        <v>1.57</v>
-      </c>
-      <c r="W99">
-        <v>1.12</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.13</v>
-      </c>
-      <c r="Z99">
-        <v>4.78</v>
-      </c>
-      <c r="AA99">
-        <v>1.56</v>
-      </c>
-      <c r="AB99">
-        <v>2.43</v>
-      </c>
-      <c r="AC99">
-        <v>2.4</v>
-      </c>
-      <c r="AD99">
-        <v>1.55</v>
-      </c>
-      <c r="AE99">
-        <v>1.17</v>
-      </c>
-      <c r="AF99">
-        <v>2.51</v>
-      </c>
-      <c r="AG99">
-        <v>1.46</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.08</v>
-      </c>
       <c r="AK99">
-        <v>6.1</v>
+        <v>4.68</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16621,22 +16621,22 @@
         <v>2.04</v>
       </c>
       <c r="R100">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T100">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U100">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V100">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W100">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
         <v>1.02</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK100">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17270,19 +17270,19 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="R104">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S104">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T104">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U104">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V104">
         <v>1.22</v>
@@ -17303,22 +17303,22 @@
         <v>2.52</v>
       </c>
       <c r="AB104">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC104">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="AD104">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE104">
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AG104">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O108">
         <v>2.9</v>
@@ -17928,34 +17928,34 @@
         <v>1.89</v>
       </c>
       <c r="S108">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T108">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U108">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V108">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X108">
         <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z108">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AA108">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AB108">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC108">
         <v>4.6</v>
@@ -17964,7 +17964,7 @@
         <v>1.13</v>
       </c>
       <c r="AE108">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF108">
         <v>2.02</v>
@@ -19718,52 +19718,52 @@
         <v>2.08</v>
       </c>
       <c r="R119">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
         <v>1.35</v>
       </c>
       <c r="T119">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U119">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V119">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W119">
         <v>1.05</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z119">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="AA119">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC119">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="AD119">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE119">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF119">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG119">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O21">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="P21">
         <v>2.36</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W35">
+        <v>1.15</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
         <v>1.09</v>
       </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.14</v>
-      </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA35">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q36">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="R36">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
+        <v>1.28</v>
+      </c>
+      <c r="T36">
+        <v>3.3</v>
+      </c>
+      <c r="U36">
+        <v>2.34</v>
+      </c>
+      <c r="V36">
+        <v>1.53</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.14</v>
+      </c>
+      <c r="Z36">
+        <v>4.4</v>
+      </c>
+      <c r="AA36">
+        <v>1.61</v>
+      </c>
+      <c r="AB36">
+        <v>2.25</v>
+      </c>
+      <c r="AC36">
+        <v>2.39</v>
+      </c>
+      <c r="AD36">
+        <v>1.46</v>
+      </c>
+      <c r="AE36">
+        <v>1.15</v>
+      </c>
+      <c r="AF36">
+        <v>1.5</v>
+      </c>
+      <c r="AG36">
+        <v>2.42</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.26</v>
       </c>
-      <c r="T36">
-        <v>3.34</v>
-      </c>
-      <c r="U36">
-        <v>2.14</v>
-      </c>
-      <c r="V36">
+      <c r="AK36">
         <v>1.66</v>
-      </c>
-      <c r="W36">
-        <v>1.15</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.09</v>
-      </c>
-      <c r="Z36">
-        <v>5.25</v>
-      </c>
-      <c r="AA36">
-        <v>1.44</v>
-      </c>
-      <c r="AB36">
-        <v>2.7</v>
-      </c>
-      <c r="AC36">
-        <v>2.08</v>
-      </c>
-      <c r="AD36">
-        <v>1.72</v>
-      </c>
-      <c r="AE36">
-        <v>1.26</v>
-      </c>
-      <c r="AF36">
-        <v>1.49</v>
-      </c>
-      <c r="AG36">
-        <v>2.4</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.23</v>
-      </c>
-      <c r="AK36">
-        <v>2.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="O37">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="P37">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q37">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="V37">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB37">
         <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AD37">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG37">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>4.1</v>
       </c>
       <c r="P39">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q39">
         <v>2.02</v>
@@ -6681,7 +6681,7 @@
         <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T39">
         <v>3.35</v>
@@ -6862,13 +6862,13 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
         <v>5.4</v>
       </c>
       <c r="AA40">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
         <v>2.6</v>
@@ -6877,16 +6877,16 @@
         <v>2.16</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE40">
         <v>1.23</v>
       </c>
       <c r="AF40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG40">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,37 +7155,37 @@
         </is>
       </c>
       <c r="N42">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>5</v>
       </c>
       <c r="P42">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Q42">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R42">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T42">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="U42">
         <v>2.05</v>
       </c>
       <c r="V42">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W42">
         <v>1.17</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.08</v>
@@ -7197,22 +7197,22 @@
         <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="AC42">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD42">
         <v>1.8</v>
       </c>
       <c r="AE42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF42">
         <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,46 +7321,46 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q43">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
         <v>2.21</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>5.38</v>
+        <v>4.95</v>
       </c>
       <c r="AA43">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AC43">
         <v>2.27</v>
@@ -7369,13 +7369,13 @@
         <v>1.65</v>
       </c>
       <c r="AE43">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>2.25</v>
       </c>
       <c r="AA46">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC46">
         <v>5.75</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>7.42</v>
+        <v>7.28</v>
       </c>
       <c r="O52">
-        <v>4.97</v>
+        <v>5.49</v>
       </c>
       <c r="P52">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O53">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
       <c r="P53">
-        <v>10.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O54">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
         <v>2.3</v>
@@ -9150,10 +9150,10 @@
         <v>2.94</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB54">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC54">
         <v>3.38</v>
@@ -9165,10 +9165,10 @@
         <v>1.05</v>
       </c>
       <c r="AF54">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG54">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y55">
         <v>1.22</v>
@@ -9313,19 +9313,19 @@
         <v>3.54</v>
       </c>
       <c r="AA55">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB55">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC55">
-        <v>3.17</v>
+        <v>2.8</v>
       </c>
       <c r="AD55">
         <v>1.34</v>
       </c>
       <c r="AE55">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
         <v>1.74</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P56">
-        <v>2.37</v>
+        <v>2.66</v>
       </c>
       <c r="Q56">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R56">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T56">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U56">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="V56">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z56">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB56">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC56">
-        <v>3.3</v>
+        <v>4.59</v>
       </c>
       <c r="AD56">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE56">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG56">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK56">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>3.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q57">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="R57">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="S57">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T57">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U57">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="V57">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AA57">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB57">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="Q58">
-        <v>3.22</v>
+        <v>2.78</v>
       </c>
       <c r="R58">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T58">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U58">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="V58">
+        <v>1.34</v>
+      </c>
+      <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
         <v>1.3</v>
       </c>
-      <c r="W58">
-        <v>1.02</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.4</v>
-      </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA58">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC58">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="AD58">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF58">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9959,25 +9959,25 @@
         <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z59">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="AA59">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB59">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD59">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
         <v>1.65</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
+        <v>1.57</v>
+      </c>
+      <c r="O66">
+        <v>3.9</v>
+      </c>
+      <c r="P66">
+        <v>4.33</v>
+      </c>
+      <c r="Q66">
+        <v>1.97</v>
+      </c>
+      <c r="R66">
+        <v>2.4</v>
+      </c>
+      <c r="S66">
+        <v>1.23</v>
+      </c>
+      <c r="T66">
+        <v>3.52</v>
+      </c>
+      <c r="U66">
+        <v>2.19</v>
+      </c>
+      <c r="V66">
+        <v>1.62</v>
+      </c>
+      <c r="W66">
+        <v>1.13</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.1</v>
+      </c>
+      <c r="Z66">
+        <v>5</v>
+      </c>
+      <c r="AA66">
+        <v>1.5</v>
+      </c>
+      <c r="AB66">
         <v>2.5</v>
       </c>
-      <c r="O66">
-        <v>3.35</v>
-      </c>
-      <c r="P66">
-        <v>2.5</v>
-      </c>
-      <c r="Q66">
-        <v>3</v>
-      </c>
-      <c r="R66">
-        <v>2.32</v>
-      </c>
-      <c r="S66">
-        <v>1.3</v>
-      </c>
-      <c r="T66">
-        <v>3.16</v>
-      </c>
-      <c r="U66">
-        <v>2.32</v>
-      </c>
-      <c r="V66">
+      <c r="AC66">
+        <v>2.24</v>
+      </c>
+      <c r="AD66">
+        <v>1.62</v>
+      </c>
+      <c r="AE66">
+        <v>1.21</v>
+      </c>
+      <c r="AF66">
         <v>1.53</v>
       </c>
-      <c r="W66">
-        <v>1.09</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.14</v>
-      </c>
-      <c r="Z66">
-        <v>4.4</v>
-      </c>
-      <c r="AA66">
-        <v>1.6</v>
-      </c>
-      <c r="AB66">
-        <v>2.3</v>
-      </c>
-      <c r="AC66">
+      <c r="AG66">
         <v>2.35</v>
       </c>
-      <c r="AD66">
-        <v>1.47</v>
-      </c>
-      <c r="AE66">
-        <v>1.16</v>
-      </c>
-      <c r="AF66">
-        <v>1.48</v>
-      </c>
-      <c r="AG66">
-        <v>2.47</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>1.46</v>
+        <v>2.27</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.57</v>
+        <v>2.81</v>
       </c>
       <c r="O67">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="P67">
-        <v>4.33</v>
+        <v>2.24</v>
       </c>
       <c r="Q67">
-        <v>1.97</v>
+        <v>3.34</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S67">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="V67">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W67">
         <v>1.13</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AA67">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB67">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC67">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AD67">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE67">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF67">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AG67">
-        <v>2.35</v>
+        <v>2.77</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O68">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="S68">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA68">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AB68">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC68">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AD68">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AG68">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>2.64</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,65 +11556,65 @@
         </is>
       </c>
       <c r="N69">
+        <v>1.44</v>
+      </c>
+      <c r="O69">
+        <v>4.5</v>
+      </c>
+      <c r="P69">
+        <v>5</v>
+      </c>
+      <c r="Q69">
+        <v>1.85</v>
+      </c>
+      <c r="R69">
+        <v>2.72</v>
+      </c>
+      <c r="S69">
+        <v>1.14</v>
+      </c>
+      <c r="T69">
+        <v>4.5</v>
+      </c>
+      <c r="U69">
+        <v>1.83</v>
+      </c>
+      <c r="V69">
+        <v>1.89</v>
+      </c>
+      <c r="W69">
+        <v>1.23</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>1.03</v>
+      </c>
+      <c r="Z69">
+        <v>7.4</v>
+      </c>
+      <c r="AA69">
+        <v>1.24</v>
+      </c>
+      <c r="AB69">
+        <v>3.5</v>
+      </c>
+      <c r="AC69">
+        <v>1.72</v>
+      </c>
+      <c r="AD69">
+        <v>2.06</v>
+      </c>
+      <c r="AE69">
+        <v>1.43</v>
+      </c>
+      <c r="AF69">
+        <v>1.38</v>
+      </c>
+      <c r="AG69">
         <v>2.81</v>
       </c>
-      <c r="O69">
-        <v>3.68</v>
-      </c>
-      <c r="P69">
-        <v>2.24</v>
-      </c>
-      <c r="Q69">
-        <v>3.34</v>
-      </c>
-      <c r="R69">
-        <v>2.31</v>
-      </c>
-      <c r="S69">
-        <v>1.22</v>
-      </c>
-      <c r="T69">
-        <v>3.6</v>
-      </c>
-      <c r="U69">
-        <v>2.12</v>
-      </c>
-      <c r="V69">
-        <v>1.65</v>
-      </c>
-      <c r="W69">
-        <v>1.13</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.08</v>
-      </c>
-      <c r="Z69">
-        <v>5.45</v>
-      </c>
-      <c r="AA69">
-        <v>1.41</v>
-      </c>
-      <c r="AB69">
-        <v>2.52</v>
-      </c>
-      <c r="AC69">
-        <v>2.14</v>
-      </c>
-      <c r="AD69">
-        <v>1.67</v>
-      </c>
-      <c r="AE69">
-        <v>1.28</v>
-      </c>
-      <c r="AF69">
-        <v>1.39</v>
-      </c>
-      <c r="AG69">
-        <v>2.77</v>
-      </c>
       <c r="AH69" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12706,10 +12706,10 @@
         <v>3.4</v>
       </c>
       <c r="Q76">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="R76">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="S76">
         <v>1.65</v>
@@ -12733,16 +12733,16 @@
         <v>1.6</v>
       </c>
       <c r="Z76">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AA76">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AB76">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC76">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD76">
         <v>1.08</v>
@@ -12751,10 +12751,10 @@
         <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AG76">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12881,10 +12881,10 @@
         <v>2.65</v>
       </c>
       <c r="U77">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W77">
         <v>1.05</v>
@@ -12933,7 +12933,7 @@
         <v>1.31</v>
       </c>
       <c r="AK77">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13521,19 +13521,19 @@
         <v>2.45</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S81">
         <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U81">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V81">
         <v>1.39</v>
@@ -13542,7 +13542,7 @@
         <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.24</v>
@@ -13551,25 +13551,25 @@
         <v>3.34</v>
       </c>
       <c r="AA81">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB81">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC81">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD81">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE81">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF81">
         <v>1.65</v>
       </c>
       <c r="AG81">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,10 +13684,10 @@
         <v>1.89</v>
       </c>
       <c r="Q82">
-        <v>3.4</v>
+        <v>4.04</v>
       </c>
       <c r="R82">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
         <v>1.25</v>
@@ -13702,19 +13702,19 @@
         <v>1.58</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z82">
         <v>4.8</v>
       </c>
       <c r="AA82">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB82">
         <v>2.33</v>
@@ -13723,7 +13723,7 @@
         <v>2.25</v>
       </c>
       <c r="AD82">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE82">
         <v>1.19</v>
@@ -13732,7 +13732,7 @@
         <v>1.46</v>
       </c>
       <c r="AG82">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,10 +13847,10 @@
         <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S83">
         <v>1.29</v>
@@ -13871,7 +13871,7 @@
         <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z83">
         <v>4.05</v>
@@ -13886,16 +13886,16 @@
         <v>2.68</v>
       </c>
       <c r="AD83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE83">
         <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AG83">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>1.72</v>
       </c>
       <c r="Q84">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="R84">
         <v>2.17</v>
@@ -14022,10 +14022,10 @@
         <v>2.96</v>
       </c>
       <c r="U84">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
         <v>1.06</v>
@@ -14034,31 +14034,31 @@
         <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z84">
         <v>3.72</v>
       </c>
       <c r="AA84">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB84">
         <v>1.98</v>
       </c>
       <c r="AC84">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AD84">
         <v>1.35</v>
       </c>
       <c r="AE84">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF84">
         <v>1.67</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="O87">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P87">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q87">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="R87">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U87">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V87">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W87">
         <v>1.16</v>
@@ -14523,7 +14523,7 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z87">
         <v>5.45</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
         <v>4</v>
@@ -15344,10 +15344,10 @@
         <v>3.3</v>
       </c>
       <c r="AA92">
+        <v>1.95</v>
+      </c>
+      <c r="AB92">
         <v>1.85</v>
-      </c>
-      <c r="AB92">
-        <v>1.89</v>
       </c>
       <c r="AC92">
         <v>3.2</v>
@@ -15507,7 +15507,7 @@
         <v>3.44</v>
       </c>
       <c r="AA93">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB93">
         <v>1.95</v>
@@ -15522,10 +15522,10 @@
         <v>1.09</v>
       </c>
       <c r="AF93">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG93">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK93">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.3</v>
+        <v>4.52</v>
       </c>
       <c r="O94">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="P94">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Q94">
         <v>4.45</v>
       </c>
       <c r="R94">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="S94">
         <v>1.22</v>
       </c>
       <c r="T94">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
         <v>2.14</v>
@@ -15670,19 +15670,19 @@
         <v>5.3</v>
       </c>
       <c r="AA94">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB94">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC94">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD94">
         <v>1.7</v>
       </c>
       <c r="AE94">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF94">
         <v>1.48</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15960,22 +15960,22 @@
         <v>6.5</v>
       </c>
       <c r="O96">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="P96">
         <v>1.4</v>
       </c>
       <c r="Q96">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="R96">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="S96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T96">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="U96">
         <v>2.06</v>
@@ -15984,10 +15984,10 @@
         <v>1.79</v>
       </c>
       <c r="W96">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
         <v>1.07</v>
@@ -16011,10 +16011,10 @@
         <v>1.32</v>
       </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG96">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16455,22 +16455,22 @@
         <v>15</v>
       </c>
       <c r="Q99">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R99">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="S99">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U99">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V99">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W99">
         <v>1.08</v>
@@ -16479,13 +16479,13 @@
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA99">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AB99">
         <v>2.24</v>
@@ -16500,10 +16500,10 @@
         <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AG99">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17270,7 +17270,7 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R104">
         <v>1.86</v>
@@ -17306,7 +17306,7 @@
         <v>1.44</v>
       </c>
       <c r="AC104">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AD104">
         <v>1.1</v>
@@ -17315,10 +17315,10 @@
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AG104">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O105">
         <v>3.25</v>
       </c>
       <c r="P105">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="Q105">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
         <v>1.33</v>
@@ -17445,19 +17445,19 @@
         <v>2.91</v>
       </c>
       <c r="U105">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V105">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
         <v>3.5</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O106">
         <v>3.3</v>
       </c>
       <c r="P106">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="O107">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="P107">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q107">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="R107">
         <v>2.11</v>
       </c>
       <c r="S107">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T107">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U107">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V107">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z107">
         <v>4.03</v>
       </c>
       <c r="AA107">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB107">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC107">
         <v>2.92</v>
       </c>
       <c r="AD107">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE107">
         <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O108">
         <v>2.9</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
         <v>3.26</v>
@@ -17934,7 +17934,7 @@
         <v>2.36</v>
       </c>
       <c r="U108">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V108">
         <v>1.26</v>
@@ -17949,22 +17949,22 @@
         <v>1.43</v>
       </c>
       <c r="Z108">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AA108">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB108">
         <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="AD108">
         <v>1.13</v>
       </c>
       <c r="AE108">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
         <v>2.02</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="O118">
         <v>3.2</v>
@@ -19552,19 +19552,19 @@
         <v>3.1</v>
       </c>
       <c r="Q118">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="U118">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V118">
         <v>1.36</v>
@@ -19585,22 +19585,22 @@
         <v>1.94</v>
       </c>
       <c r="AB118">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC118">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD118">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF118">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG118">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19724,7 +19724,7 @@
         <v>1.35</v>
       </c>
       <c r="T119">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U119">
         <v>2.66</v>
@@ -19748,7 +19748,7 @@
         <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC119">
         <v>2.97</v>
@@ -19760,7 +19760,7 @@
         <v>1.08</v>
       </c>
       <c r="AF119">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG119">
         <v>1.81</v>
@@ -20044,52 +20044,52 @@
         <v>3.56</v>
       </c>
       <c r="R121">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S121">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T121">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U121">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V121">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W121">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X121">
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z121">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA121">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB121">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AC121">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD121">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE121">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF121">
         <v>1.36</v>
       </c>
       <c r="AG121">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK121">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.52</v>
+        <v>2.18</v>
       </c>
       <c r="R24">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>2.79</v>
+        <v>2.31</v>
       </c>
       <c r="V24">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AB24">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q25">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R25">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="U25">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
+        <v>1.06</v>
+      </c>
+      <c r="X25">
+        <v>1.03</v>
+      </c>
+      <c r="Y25">
+        <v>1.18</v>
+      </c>
+      <c r="Z25">
+        <v>3.84</v>
+      </c>
+      <c r="AA25">
+        <v>1.75</v>
+      </c>
+      <c r="AB25">
+        <v>2.05</v>
+      </c>
+      <c r="AC25">
+        <v>2.74</v>
+      </c>
+      <c r="AD25">
+        <v>1.35</v>
+      </c>
+      <c r="AE25">
         <v>1.1</v>
       </c>
-      <c r="X25">
-        <v>1.02</v>
-      </c>
-      <c r="Y25">
-        <v>1.16</v>
-      </c>
-      <c r="Z25">
-        <v>4.2</v>
-      </c>
-      <c r="AA25">
-        <v>1.59</v>
-      </c>
-      <c r="AB25">
-        <v>2.25</v>
-      </c>
-      <c r="AC25">
-        <v>2.38</v>
-      </c>
-      <c r="AD25">
-        <v>1.46</v>
-      </c>
-      <c r="AE25">
-        <v>1.16</v>
-      </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
         <v>2.32</v>
       </c>
       <c r="R26">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="S26">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="T26">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="U26">
+        <v>2.15</v>
+      </c>
+      <c r="V26">
+        <v>1.61</v>
+      </c>
+      <c r="W26">
+        <v>1.13</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
+        <v>1.11</v>
+      </c>
+      <c r="Z26">
+        <v>4.85</v>
+      </c>
+      <c r="AA26">
+        <v>1.45</v>
+      </c>
+      <c r="AB26">
+        <v>2.41</v>
+      </c>
+      <c r="AC26">
+        <v>2.15</v>
+      </c>
+      <c r="AD26">
+        <v>1.61</v>
+      </c>
+      <c r="AE26">
+        <v>1.22</v>
+      </c>
+      <c r="AF26">
+        <v>1.44</v>
+      </c>
+      <c r="AG26">
         <v>2.53</v>
       </c>
-      <c r="V26">
-        <v>1.42</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.18</v>
-      </c>
-      <c r="Z26">
-        <v>3.84</v>
-      </c>
-      <c r="AA26">
-        <v>1.75</v>
-      </c>
-      <c r="AB26">
-        <v>2.05</v>
-      </c>
-      <c r="AC26">
-        <v>2.74</v>
-      </c>
-      <c r="AD26">
-        <v>1.35</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
-      <c r="AF26">
-        <v>1.64</v>
-      </c>
-      <c r="AG26">
-        <v>2.08</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q27">
-        <v>2.32</v>
+        <v>3.52</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>3.34</v>
+        <v>2.67</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.79</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>4.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA27">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AG27">
-        <v>2.53</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="R35">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
+        <v>1.28</v>
+      </c>
+      <c r="T35">
+        <v>3.3</v>
+      </c>
+      <c r="U35">
+        <v>2.34</v>
+      </c>
+      <c r="V35">
+        <v>1.53</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.14</v>
+      </c>
+      <c r="Z35">
+        <v>4.4</v>
+      </c>
+      <c r="AA35">
+        <v>1.61</v>
+      </c>
+      <c r="AB35">
+        <v>2.25</v>
+      </c>
+      <c r="AC35">
+        <v>2.39</v>
+      </c>
+      <c r="AD35">
+        <v>1.46</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
+        <v>1.5</v>
+      </c>
+      <c r="AG35">
+        <v>2.42</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.26</v>
       </c>
-      <c r="T35">
-        <v>3.34</v>
-      </c>
-      <c r="U35">
-        <v>2.14</v>
-      </c>
-      <c r="V35">
+      <c r="AK35">
         <v>1.66</v>
-      </c>
-      <c r="W35">
-        <v>1.15</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.09</v>
-      </c>
-      <c r="Z35">
-        <v>5.25</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.7</v>
-      </c>
-      <c r="AC35">
-        <v>2.08</v>
-      </c>
-      <c r="AD35">
-        <v>1.72</v>
-      </c>
-      <c r="AE35">
-        <v>1.26</v>
-      </c>
-      <c r="AF35">
-        <v>1.49</v>
-      </c>
-      <c r="AG35">
-        <v>2.4</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.23</v>
-      </c>
-      <c r="AK35">
-        <v>2.26</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W36">
+        <v>1.15</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
         <v>1.09</v>
       </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.14</v>
-      </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AD36">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG36">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O46">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q46">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="R46">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S46">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T46">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U46">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="V46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W46">
         <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z46">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AA46">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB46">
         <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD46">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AG46">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK46">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O47">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="R47">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S47">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T47">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U47">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="V47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W47">
         <v>1.02</v>
       </c>
       <c r="X47">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z47">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AA47">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB47">
         <v>1.36</v>
       </c>
       <c r="AC47">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AG47">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>7.28</v>
+        <v>1.26</v>
       </c>
       <c r="O52">
-        <v>5.49</v>
+        <v>5.95</v>
       </c>
       <c r="P52">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q52">
-        <v>6.1</v>
+        <v>1.64</v>
       </c>
       <c r="R52">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8806,22 +8806,22 @@
         <v>3.5</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V52">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA52">
         <v>1.44</v>
@@ -8830,19 +8830,19 @@
         <v>2.7</v>
       </c>
       <c r="AC52">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD52">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AG52">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK52">
-        <v>1.07</v>
+        <v>3.68</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.26</v>
+        <v>7.28</v>
       </c>
       <c r="O53">
-        <v>5.95</v>
+        <v>5.49</v>
       </c>
       <c r="P53">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="Q53">
-        <v>1.64</v>
+        <v>6.1</v>
       </c>
       <c r="R53">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="S53">
         <v>1.22</v>
@@ -8969,22 +8969,22 @@
         <v>3.5</v>
       </c>
       <c r="U53">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V53">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z53">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
         <v>1.44</v>
@@ -8993,19 +8993,19 @@
         <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD53">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE53">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AG53">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK53">
-        <v>3.68</v>
+        <v>1.07</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="O67">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U67">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="V67">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W67">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA67">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD67">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AE67">
+        <v>1.16</v>
+      </c>
+      <c r="AF67">
+        <v>1.48</v>
+      </c>
+      <c r="AG67">
+        <v>2.47</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.28</v>
       </c>
-      <c r="AF67">
-        <v>1.39</v>
-      </c>
-      <c r="AG67">
-        <v>2.77</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.24</v>
-      </c>
       <c r="AK67">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q68">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="R68">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z68">
-        <v>4.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA68">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB68">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AC68">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AD68">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AG68">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="O76">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P76">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q76">
         <v>2.86</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P82">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q82">
-        <v>4.04</v>
+        <v>3.55</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U82">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V82">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
+        <v>1.17</v>
+      </c>
+      <c r="Z82">
+        <v>4.05</v>
+      </c>
+      <c r="AA82">
+        <v>1.65</v>
+      </c>
+      <c r="AB82">
+        <v>2.11</v>
+      </c>
+      <c r="AC82">
+        <v>2.68</v>
+      </c>
+      <c r="AD82">
+        <v>1.4</v>
+      </c>
+      <c r="AE82">
         <v>1.12</v>
       </c>
-      <c r="Z82">
-        <v>4.8</v>
-      </c>
-      <c r="AA82">
-        <v>1.48</v>
-      </c>
-      <c r="AB82">
-        <v>2.33</v>
-      </c>
-      <c r="AC82">
-        <v>2.25</v>
-      </c>
-      <c r="AD82">
-        <v>1.57</v>
-      </c>
-      <c r="AE82">
-        <v>1.19</v>
-      </c>
       <c r="AF82">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AG82">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,65 +13838,65 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O83">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="Q83">
-        <v>3.55</v>
+        <v>4.04</v>
       </c>
       <c r="R83">
+        <v>2.25</v>
+      </c>
+      <c r="S83">
+        <v>1.25</v>
+      </c>
+      <c r="T83">
+        <v>3.28</v>
+      </c>
+      <c r="U83">
+        <v>2.22</v>
+      </c>
+      <c r="V83">
+        <v>1.58</v>
+      </c>
+      <c r="W83">
+        <v>1.11</v>
+      </c>
+      <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
+        <v>1.12</v>
+      </c>
+      <c r="Z83">
+        <v>4.8</v>
+      </c>
+      <c r="AA83">
+        <v>1.48</v>
+      </c>
+      <c r="AB83">
+        <v>2.33</v>
+      </c>
+      <c r="AC83">
+        <v>2.25</v>
+      </c>
+      <c r="AD83">
+        <v>1.57</v>
+      </c>
+      <c r="AE83">
+        <v>1.19</v>
+      </c>
+      <c r="AF83">
+        <v>1.46</v>
+      </c>
+      <c r="AG83">
         <v>2.18</v>
       </c>
-      <c r="S83">
-        <v>1.29</v>
-      </c>
-      <c r="T83">
-        <v>3.12</v>
-      </c>
-      <c r="U83">
-        <v>2.41</v>
-      </c>
-      <c r="V83">
-        <v>1.47</v>
-      </c>
-      <c r="W83">
-        <v>1.08</v>
-      </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
-      <c r="Y83">
-        <v>1.17</v>
-      </c>
-      <c r="Z83">
-        <v>4.05</v>
-      </c>
-      <c r="AA83">
-        <v>1.65</v>
-      </c>
-      <c r="AB83">
-        <v>2.11</v>
-      </c>
-      <c r="AC83">
-        <v>2.68</v>
-      </c>
-      <c r="AD83">
-        <v>1.4</v>
-      </c>
-      <c r="AE83">
-        <v>1.12</v>
-      </c>
-      <c r="AF83">
-        <v>1.54</v>
-      </c>
-      <c r="AG83">
-        <v>2.29</v>
-      </c>
       <c r="AH83" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
+        <v>1.21</v>
+      </c>
+      <c r="AK83">
         <v>1.22</v>
-      </c>
-      <c r="AK83">
-        <v>1.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O92">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q92">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
+        <v>1.35</v>
+      </c>
+      <c r="T92">
+        <v>2.94</v>
+      </c>
+      <c r="U92">
+        <v>2.65</v>
+      </c>
+      <c r="V92">
         <v>1.42</v>
       </c>
-      <c r="T92">
-        <v>2.77</v>
-      </c>
-      <c r="U92">
-        <v>2.77</v>
-      </c>
-      <c r="V92">
-        <v>1.43</v>
-      </c>
       <c r="W92">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z92">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA92">
+        <v>1.84</v>
+      </c>
+      <c r="AB92">
         <v>1.95</v>
       </c>
-      <c r="AB92">
-        <v>1.85</v>
-      </c>
       <c r="AC92">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF92">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK92">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P93">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="Q93">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U93">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA93">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
+        <v>1.85</v>
+      </c>
+      <c r="AC93">
+        <v>3.2</v>
+      </c>
+      <c r="AD93">
+        <v>1.3</v>
+      </c>
+      <c r="AE93">
+        <v>1.11</v>
+      </c>
+      <c r="AF93">
+        <v>1.79</v>
+      </c>
+      <c r="AG93">
+        <v>2</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.2</v>
+      </c>
+      <c r="AK93">
         <v>1.95</v>
-      </c>
-      <c r="AC93">
-        <v>2.94</v>
-      </c>
-      <c r="AD93">
-        <v>1.31</v>
-      </c>
-      <c r="AE93">
-        <v>1.09</v>
-      </c>
-      <c r="AF93">
-        <v>1.65</v>
-      </c>
-      <c r="AG93">
-        <v>2.11</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.28</v>
-      </c>
-      <c r="AK93">
-        <v>1.59</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q104">
         <v>2.54</v>
@@ -17306,7 +17306,7 @@
         <v>1.44</v>
       </c>
       <c r="AC104">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="AD104">
         <v>1.1</v>
@@ -17315,10 +17315,10 @@
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AG104">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17590,10 +17590,10 @@
         <v>1.64</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P106">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O108">
         <v>2.9</v>
@@ -17958,7 +17958,7 @@
         <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="AD108">
         <v>1.13</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O118">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="Q118">
         <v>2.7</v>
@@ -19748,7 +19748,7 @@
         <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC119">
         <v>2.97</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2763,7 +2763,7 @@
         <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.25</v>
@@ -2775,10 +2775,10 @@
         <v>3.18</v>
       </c>
       <c r="U15">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
         <v>1.09</v>
@@ -2787,7 +2787,7 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
         <v>4.25</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>2.32</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>3.34</v>
+        <v>2.67</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.79</v>
       </c>
       <c r="V26">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>4.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="AD26">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>2.53</v>
+        <v>1.96</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>3.52</v>
+        <v>2.32</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>2.67</v>
+        <v>3.34</v>
       </c>
       <c r="U27">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>3.08</v>
+        <v>4.85</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AB27">
+        <v>2.41</v>
+      </c>
+      <c r="AC27">
+        <v>2.15</v>
+      </c>
+      <c r="AD27">
+        <v>1.61</v>
+      </c>
+      <c r="AE27">
+        <v>1.22</v>
+      </c>
+      <c r="AF27">
+        <v>1.44</v>
+      </c>
+      <c r="AG27">
+        <v>2.53</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.2</v>
+      </c>
+      <c r="AK27">
         <v>1.8</v>
-      </c>
-      <c r="AC27">
-        <v>3.28</v>
-      </c>
-      <c r="AD27">
-        <v>1.25</v>
-      </c>
-      <c r="AE27">
-        <v>1.06</v>
-      </c>
-      <c r="AF27">
-        <v>1.72</v>
-      </c>
-      <c r="AG27">
-        <v>1.96</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.26</v>
-      </c>
-      <c r="AK27">
-        <v>1.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>2.89</v>
       </c>
       <c r="Q29">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5063,7 +5063,7 @@
         <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5078,7 +5078,7 @@
         <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC29">
         <v>3.08</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.67</v>
+        <v>2.13</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W35">
+        <v>1.15</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
         <v>1.09</v>
       </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.14</v>
-      </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA35">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG35">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q36">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="R36">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
+        <v>1.28</v>
+      </c>
+      <c r="T36">
+        <v>3.3</v>
+      </c>
+      <c r="U36">
+        <v>2.34</v>
+      </c>
+      <c r="V36">
+        <v>1.53</v>
+      </c>
+      <c r="W36">
+        <v>1.09</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.14</v>
+      </c>
+      <c r="Z36">
+        <v>4.4</v>
+      </c>
+      <c r="AA36">
+        <v>1.61</v>
+      </c>
+      <c r="AB36">
+        <v>2.25</v>
+      </c>
+      <c r="AC36">
+        <v>2.39</v>
+      </c>
+      <c r="AD36">
+        <v>1.46</v>
+      </c>
+      <c r="AE36">
+        <v>1.15</v>
+      </c>
+      <c r="AF36">
+        <v>1.5</v>
+      </c>
+      <c r="AG36">
+        <v>2.42</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.26</v>
       </c>
-      <c r="T36">
-        <v>3.34</v>
-      </c>
-      <c r="U36">
-        <v>2.14</v>
-      </c>
-      <c r="V36">
+      <c r="AK36">
         <v>1.66</v>
-      </c>
-      <c r="W36">
-        <v>1.15</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.09</v>
-      </c>
-      <c r="Z36">
-        <v>5.25</v>
-      </c>
-      <c r="AA36">
-        <v>1.44</v>
-      </c>
-      <c r="AB36">
-        <v>2.7</v>
-      </c>
-      <c r="AC36">
-        <v>2.08</v>
-      </c>
-      <c r="AD36">
-        <v>1.72</v>
-      </c>
-      <c r="AE36">
-        <v>1.26</v>
-      </c>
-      <c r="AF36">
-        <v>1.49</v>
-      </c>
-      <c r="AG36">
-        <v>2.4</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.23</v>
-      </c>
-      <c r="AK36">
-        <v>2.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.73</v>
+        <v>2.56</v>
       </c>
       <c r="O55">
+        <v>3.28</v>
+      </c>
+      <c r="P55">
+        <v>2.66</v>
+      </c>
+      <c r="Q55">
         <v>3.4</v>
       </c>
-      <c r="P55">
-        <v>4.6</v>
-      </c>
-      <c r="Q55">
-        <v>2.24</v>
-      </c>
       <c r="R55">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="S55">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T55">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U55">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="V55">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="AA55">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AC55">
-        <v>2.8</v>
+        <v>4.59</v>
       </c>
       <c r="AD55">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE55">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AG55">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK55">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="O56">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>2.66</v>
+        <v>3.32</v>
       </c>
       <c r="Q56">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T56">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U56">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V56">
+        <v>1.34</v>
+      </c>
+      <c r="W56">
+        <v>1.03</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
         <v>1.3</v>
       </c>
-      <c r="W56">
-        <v>1.02</v>
-      </c>
-      <c r="X56">
-        <v>1.02</v>
-      </c>
-      <c r="Y56">
-        <v>1.4</v>
-      </c>
       <c r="Z56">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA56">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC56">
-        <v>4.59</v>
+        <v>3.52</v>
       </c>
       <c r="AD56">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG56">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.31</v>
       </c>
       <c r="AK56">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="O57">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q57">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="R57">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="S57">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="U57">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB57">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC57">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD57">
+        <v>1.34</v>
+      </c>
+      <c r="AE57">
+        <v>1.1</v>
+      </c>
+      <c r="AF57">
+        <v>1.74</v>
+      </c>
+      <c r="AG57">
+        <v>1.98</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
         <v>1.25</v>
       </c>
-      <c r="AE57">
-        <v>1.05</v>
-      </c>
-      <c r="AF57">
-        <v>1.75</v>
-      </c>
-      <c r="AG57">
-        <v>1.97</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.33</v>
-      </c>
       <c r="AK57">
-        <v>1.38</v>
+        <v>2.07</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>3.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="R58">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U58">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="V58">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
         <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB58">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC58">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="R67">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T67">
-        <v>3.16</v>
+        <v>4.5</v>
       </c>
       <c r="U67">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="V67">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
+        <v>1.03</v>
+      </c>
+      <c r="Z67">
+        <v>7.4</v>
+      </c>
+      <c r="AA67">
+        <v>1.24</v>
+      </c>
+      <c r="AB67">
+        <v>3.5</v>
+      </c>
+      <c r="AC67">
+        <v>1.72</v>
+      </c>
+      <c r="AD67">
+        <v>2.06</v>
+      </c>
+      <c r="AE67">
+        <v>1.43</v>
+      </c>
+      <c r="AF67">
+        <v>1.38</v>
+      </c>
+      <c r="AG67">
+        <v>2.81</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.14</v>
       </c>
-      <c r="Z67">
-        <v>4.4</v>
-      </c>
-      <c r="AA67">
-        <v>1.6</v>
-      </c>
-      <c r="AB67">
-        <v>2.3</v>
-      </c>
-      <c r="AC67">
-        <v>2.35</v>
-      </c>
-      <c r="AD67">
-        <v>1.47</v>
-      </c>
-      <c r="AE67">
-        <v>1.16</v>
-      </c>
-      <c r="AF67">
-        <v>1.48</v>
-      </c>
-      <c r="AG67">
-        <v>2.47</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.28</v>
-      </c>
       <c r="AK67">
-        <v>1.46</v>
+        <v>2.64</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="O68">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S68">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA68">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB68">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AC68">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD68">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
+        <v>1.16</v>
+      </c>
+      <c r="AF68">
+        <v>1.48</v>
+      </c>
+      <c r="AG68">
+        <v>2.47</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.28</v>
       </c>
-      <c r="AF68">
-        <v>1.39</v>
-      </c>
-      <c r="AG68">
-        <v>2.77</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.24</v>
-      </c>
       <c r="AK68">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.44</v>
+        <v>2.81</v>
       </c>
       <c r="O69">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="Q69">
-        <v>1.85</v>
+        <v>3.34</v>
       </c>
       <c r="R69">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="S69">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U69">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="V69">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="W69">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z69">
-        <v>7.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA69">
+        <v>1.41</v>
+      </c>
+      <c r="AB69">
+        <v>2.52</v>
+      </c>
+      <c r="AC69">
+        <v>2.14</v>
+      </c>
+      <c r="AD69">
+        <v>1.67</v>
+      </c>
+      <c r="AE69">
+        <v>1.28</v>
+      </c>
+      <c r="AF69">
+        <v>1.39</v>
+      </c>
+      <c r="AG69">
+        <v>2.77</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.24</v>
       </c>
-      <c r="AB69">
-        <v>3.5</v>
-      </c>
-      <c r="AC69">
-        <v>1.72</v>
-      </c>
-      <c r="AD69">
-        <v>2.06</v>
-      </c>
-      <c r="AE69">
-        <v>1.43</v>
-      </c>
-      <c r="AF69">
-        <v>1.38</v>
-      </c>
-      <c r="AG69">
-        <v>2.81</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.14</v>
-      </c>
       <c r="AK69">
-        <v>2.64</v>
+        <v>1.39</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,16 +11722,16 @@
         <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
         <v>2.75</v>
       </c>
       <c r="Q70">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="R70">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>1.27</v>
@@ -11755,13 +11755,13 @@
         <v>1.15</v>
       </c>
       <c r="Z70">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA70">
         <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC70">
         <v>2.46</v>
@@ -11773,10 +11773,10 @@
         <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,65 +13675,65 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O82">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="Q82">
-        <v>3.55</v>
+        <v>4.04</v>
       </c>
       <c r="R82">
+        <v>2.25</v>
+      </c>
+      <c r="S82">
+        <v>1.25</v>
+      </c>
+      <c r="T82">
+        <v>3.28</v>
+      </c>
+      <c r="U82">
+        <v>2.22</v>
+      </c>
+      <c r="V82">
+        <v>1.58</v>
+      </c>
+      <c r="W82">
+        <v>1.11</v>
+      </c>
+      <c r="X82">
+        <v>1.01</v>
+      </c>
+      <c r="Y82">
+        <v>1.12</v>
+      </c>
+      <c r="Z82">
+        <v>4.8</v>
+      </c>
+      <c r="AA82">
+        <v>1.48</v>
+      </c>
+      <c r="AB82">
+        <v>2.33</v>
+      </c>
+      <c r="AC82">
+        <v>2.25</v>
+      </c>
+      <c r="AD82">
+        <v>1.57</v>
+      </c>
+      <c r="AE82">
+        <v>1.19</v>
+      </c>
+      <c r="AF82">
+        <v>1.46</v>
+      </c>
+      <c r="AG82">
         <v>2.18</v>
       </c>
-      <c r="S82">
-        <v>1.29</v>
-      </c>
-      <c r="T82">
-        <v>3.12</v>
-      </c>
-      <c r="U82">
-        <v>2.41</v>
-      </c>
-      <c r="V82">
-        <v>1.47</v>
-      </c>
-      <c r="W82">
-        <v>1.08</v>
-      </c>
-      <c r="X82">
-        <v>1.03</v>
-      </c>
-      <c r="Y82">
-        <v>1.17</v>
-      </c>
-      <c r="Z82">
-        <v>4.05</v>
-      </c>
-      <c r="AA82">
-        <v>1.65</v>
-      </c>
-      <c r="AB82">
-        <v>2.11</v>
-      </c>
-      <c r="AC82">
-        <v>2.68</v>
-      </c>
-      <c r="AD82">
-        <v>1.4</v>
-      </c>
-      <c r="AE82">
-        <v>1.12</v>
-      </c>
-      <c r="AF82">
-        <v>1.54</v>
-      </c>
-      <c r="AG82">
-        <v>2.29</v>
-      </c>
       <c r="AH82" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
+        <v>1.21</v>
+      </c>
+      <c r="AK82">
         <v>1.22</v>
-      </c>
-      <c r="AK82">
-        <v>1.31</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P83">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>4.04</v>
+        <v>3.55</v>
       </c>
       <c r="R83">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U83">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V83">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
+        <v>1.17</v>
+      </c>
+      <c r="Z83">
+        <v>4.05</v>
+      </c>
+      <c r="AA83">
+        <v>1.65</v>
+      </c>
+      <c r="AB83">
+        <v>2.11</v>
+      </c>
+      <c r="AC83">
+        <v>2.68</v>
+      </c>
+      <c r="AD83">
+        <v>1.4</v>
+      </c>
+      <c r="AE83">
         <v>1.12</v>
       </c>
-      <c r="Z83">
-        <v>4.8</v>
-      </c>
-      <c r="AA83">
-        <v>1.48</v>
-      </c>
-      <c r="AB83">
-        <v>2.33</v>
-      </c>
-      <c r="AC83">
-        <v>2.25</v>
-      </c>
-      <c r="AD83">
-        <v>1.57</v>
-      </c>
-      <c r="AE83">
-        <v>1.19</v>
-      </c>
       <c r="AF83">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AG83">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V92">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA92">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
+        <v>1.85</v>
+      </c>
+      <c r="AC92">
+        <v>3.2</v>
+      </c>
+      <c r="AD92">
+        <v>1.3</v>
+      </c>
+      <c r="AE92">
+        <v>1.11</v>
+      </c>
+      <c r="AF92">
+        <v>1.79</v>
+      </c>
+      <c r="AG92">
+        <v>2</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.2</v>
+      </c>
+      <c r="AK92">
         <v>1.95</v>
-      </c>
-      <c r="AC92">
-        <v>2.94</v>
-      </c>
-      <c r="AD92">
-        <v>1.31</v>
-      </c>
-      <c r="AE92">
-        <v>1.09</v>
-      </c>
-      <c r="AF92">
-        <v>1.65</v>
-      </c>
-      <c r="AG92">
-        <v>2.11</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.28</v>
-      </c>
-      <c r="AK92">
-        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O93">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q93">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
+        <v>1.35</v>
+      </c>
+      <c r="T93">
+        <v>2.94</v>
+      </c>
+      <c r="U93">
+        <v>2.65</v>
+      </c>
+      <c r="V93">
         <v>1.42</v>
       </c>
-      <c r="T93">
-        <v>2.77</v>
-      </c>
-      <c r="U93">
-        <v>2.77</v>
-      </c>
-      <c r="V93">
-        <v>1.43</v>
-      </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA93">
+        <v>1.84</v>
+      </c>
+      <c r="AB93">
         <v>1.95</v>
       </c>
-      <c r="AB93">
-        <v>1.85</v>
-      </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD93">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF93">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK93">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P103">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -20041,52 +20041,52 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>3.56</v>
+        <v>3.92</v>
       </c>
       <c r="R121">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S121">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T121">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U121">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V121">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W121">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X121">
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z121">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA121">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB121">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC121">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD121">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE121">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF121">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG121">
         <v>2.1</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK121">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O12">
-        <v>6.6</v>
+        <v>7.45</v>
       </c>
       <c r="P12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Q12">
         <v>10.1</v>
       </c>
       <c r="R12">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="S12">
         <v>1.17</v>
@@ -2286,7 +2286,7 @@
         <v>3.95</v>
       </c>
       <c r="U12">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
         <v>1.67</v>
@@ -2298,13 +2298,13 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
         <v>5.67</v>
       </c>
       <c r="AA12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
         <v>2.62</v>
@@ -2319,10 +2319,10 @@
         <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.8</v>
+      </c>
+      <c r="O19">
         <v>2.25</v>
       </c>
-      <c r="O19">
-        <v>3.45</v>
-      </c>
       <c r="P19">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
         <v>2.31</v>
@@ -3445,7 +3445,7 @@
         <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
         <v>2.15</v>
@@ -3457,7 +3457,7 @@
         <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
         <v>1.51</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         <v>2.78</v>
       </c>
       <c r="O21">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="P21">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R21">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T21">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U21">
         <v>2.5</v>
@@ -3762,10 +3762,10 @@
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
         <v>3.82</v>
@@ -3780,7 +3780,7 @@
         <v>2.78</v>
       </c>
       <c r="AD21">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE21">
         <v>1.09</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
         <v>1.4</v>
@@ -4067,25 +4067,25 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R23">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
         <v>3.14</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4094,28 +4094,28 @@
         <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="AA23">
         <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC23">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD23">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4230,40 +4230,40 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U24">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24">
         <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC24">
         <v>2.38</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="U25">
-        <v>2.53</v>
+        <v>2.79</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.28</v>
+      </c>
+      <c r="Z25">
+        <v>3.08</v>
+      </c>
+      <c r="AA25">
+        <v>2</v>
+      </c>
+      <c r="AB25">
+        <v>1.8</v>
+      </c>
+      <c r="AC25">
+        <v>3.28</v>
+      </c>
+      <c r="AD25">
+        <v>1.25</v>
+      </c>
+      <c r="AE25">
         <v>1.06</v>
       </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.18</v>
-      </c>
-      <c r="Z25">
-        <v>3.84</v>
-      </c>
-      <c r="AA25">
-        <v>1.75</v>
-      </c>
-      <c r="AB25">
-        <v>2.05</v>
-      </c>
-      <c r="AC25">
-        <v>2.74</v>
-      </c>
-      <c r="AD25">
-        <v>1.35</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
       <c r="AF25">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG25">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK25">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>3.52</v>
+        <v>2.37</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>2.67</v>
+        <v>3.28</v>
       </c>
       <c r="U26">
-        <v>2.79</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC26">
-        <v>3.28</v>
+        <v>2.19</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.85</v>
+        <v>3.85</v>
       </c>
       <c r="AA27">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O28">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P28">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q28">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="R28">
         <v>1.8</v>
       </c>
       <c r="S28">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="T28">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="U28">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
         <v>1.06</v>
@@ -4915,7 +4915,7 @@
         <v>2.21</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC28">
         <v>4.05</v>
@@ -4924,13 +4924,13 @@
         <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>4.15</v>
       </c>
       <c r="U30">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
         <v>1.7</v>
@@ -5238,7 +5238,7 @@
         <v>6.05</v>
       </c>
       <c r="AA30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB30">
         <v>2.74</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="O32">
         <v>3.75</v>
@@ -5564,13 +5564,13 @@
         <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
         <v>1.72</v>
       </c>
       <c r="AC32">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AD32">
         <v>1.21</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
         <v>2.8</v>
@@ -5872,10 +5872,10 @@
         <v>3.08</v>
       </c>
       <c r="U34">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5896,19 +5896,19 @@
         <v>2.04</v>
       </c>
       <c r="AC34">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE34">
         <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>2.13</v>
+        <v>2.69</v>
       </c>
       <c r="R35">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="S35">
+        <v>1.28</v>
+      </c>
+      <c r="T35">
+        <v>3.3</v>
+      </c>
+      <c r="U35">
+        <v>2.4</v>
+      </c>
+      <c r="V35">
+        <v>1.53</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.14</v>
+      </c>
+      <c r="Z35">
+        <v>4.4</v>
+      </c>
+      <c r="AA35">
+        <v>1.61</v>
+      </c>
+      <c r="AB35">
+        <v>2.27</v>
+      </c>
+      <c r="AC35">
+        <v>2.52</v>
+      </c>
+      <c r="AD35">
+        <v>1.46</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
+        <v>1.5</v>
+      </c>
+      <c r="AG35">
+        <v>2.42</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.26</v>
       </c>
-      <c r="T35">
-        <v>3.34</v>
-      </c>
-      <c r="U35">
-        <v>2.14</v>
-      </c>
-      <c r="V35">
-        <v>1.66</v>
-      </c>
-      <c r="W35">
-        <v>1.15</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.09</v>
-      </c>
-      <c r="Z35">
-        <v>5.25</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.7</v>
-      </c>
-      <c r="AC35">
-        <v>2.08</v>
-      </c>
-      <c r="AD35">
-        <v>1.72</v>
-      </c>
-      <c r="AE35">
-        <v>1.26</v>
-      </c>
-      <c r="AF35">
-        <v>1.49</v>
-      </c>
-      <c r="AG35">
-        <v>2.4</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.23</v>
-      </c>
       <c r="AK35">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>2.18</v>
+      </c>
+      <c r="R36">
+        <v>2.5</v>
+      </c>
+      <c r="S36">
+        <v>1.26</v>
+      </c>
+      <c r="T36">
+        <v>3.34</v>
+      </c>
+      <c r="U36">
+        <v>2.11</v>
+      </c>
+      <c r="V36">
+        <v>1.68</v>
+      </c>
+      <c r="W36">
+        <v>1.15</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.1</v>
+      </c>
+      <c r="Z36">
+        <v>5.75</v>
+      </c>
+      <c r="AA36">
+        <v>1.4</v>
+      </c>
+      <c r="AB36">
+        <v>2.57</v>
+      </c>
+      <c r="AC36">
         <v>2.1</v>
       </c>
-      <c r="O36">
-        <v>3.4</v>
-      </c>
-      <c r="P36">
-        <v>2.8</v>
-      </c>
-      <c r="Q36">
-        <v>2.67</v>
-      </c>
-      <c r="R36">
-        <v>2.25</v>
-      </c>
-      <c r="S36">
-        <v>1.28</v>
-      </c>
-      <c r="T36">
-        <v>3.3</v>
-      </c>
-      <c r="U36">
-        <v>2.34</v>
-      </c>
-      <c r="V36">
-        <v>1.53</v>
-      </c>
-      <c r="W36">
-        <v>1.09</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.14</v>
-      </c>
-      <c r="Z36">
-        <v>4.4</v>
-      </c>
-      <c r="AA36">
-        <v>1.61</v>
-      </c>
-      <c r="AB36">
-        <v>2.25</v>
-      </c>
-      <c r="AC36">
-        <v>2.39</v>
-      </c>
       <c r="AD36">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.66</v>
+        <v>2.17</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="O37">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="P37">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q37">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="R37">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
         <v>1.24</v>
@@ -6361,7 +6361,7 @@
         <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="V37">
         <v>1.62</v>
@@ -6370,34 +6370,34 @@
         <v>1.14</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
         <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD37">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
         <v>1.52</v>
       </c>
       <c r="AG37">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
         <v>1.22</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O38">
         <v>4.4</v>
       </c>
       <c r="P38">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="Q38">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
         <v>1.33</v>
@@ -6524,34 +6524,34 @@
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="V38">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
         <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA38">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
         <v>1.18</v>
@@ -6560,7 +6560,7 @@
         <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="R41">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
         <v>2.24</v>
@@ -7019,7 +7019,7 @@
         <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,13 +7031,13 @@
         <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC41">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AD41">
         <v>1.51</v>
@@ -7049,7 +7049,7 @@
         <v>1.45</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7481,22 +7481,22 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O44">
+        <v>3.8</v>
+      </c>
+      <c r="P44">
         <v>3.5</v>
       </c>
-      <c r="P44">
-        <v>3.4</v>
-      </c>
       <c r="Q44">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R44">
         <v>2.33</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
         <v>3.34</v>
@@ -7517,22 +7517,22 @@
         <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="AA44">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB44">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC44">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD44">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
         <v>1.49</v>
@@ -7554,7 +7554,7 @@
         <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7825,25 +7825,25 @@
         <v>1.62</v>
       </c>
       <c r="T46">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U46">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="V46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
         <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Z46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AA46">
         <v>3</v>
@@ -7852,10 +7852,10 @@
         <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AD46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE46">
         <v>1.02</v>
@@ -7979,10 +7979,10 @@
         <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="R47">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S47">
         <v>1.58</v>
@@ -8003,13 +8003,13 @@
         <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z47">
         <v>2.25</v>
       </c>
       <c r="AA47">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB47">
         <v>1.36</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
         <v>1.37</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="O49">
-        <v>4.44</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="O50">
-        <v>3.76</v>
+        <v>4.35</v>
       </c>
       <c r="P50">
-        <v>2.19</v>
+        <v>4.3</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>3.3</v>
       </c>
       <c r="P51">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="Q51">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
         <v>1.33</v>
@@ -8652,19 +8652,19 @@
         <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AC51">
         <v>2.83</v>
@@ -8673,13 +8673,13 @@
         <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,43 +8785,43 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="O52">
-        <v>5.95</v>
+        <v>6.34</v>
       </c>
       <c r="P52">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q52">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R52">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="U52">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="V52">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z52">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AA52">
         <v>1.44</v>
@@ -8830,19 +8830,19 @@
         <v>2.7</v>
       </c>
       <c r="AC52">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD52">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF52">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK52">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,43 +8948,43 @@
         </is>
       </c>
       <c r="N53">
-        <v>7.28</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O53">
-        <v>5.49</v>
+        <v>5.71</v>
       </c>
       <c r="P53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q53">
-        <v>6.1</v>
+        <v>6.35</v>
       </c>
       <c r="R53">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="U53">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W53">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA53">
         <v>1.44</v>
@@ -8993,19 +8993,19 @@
         <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AD53">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE53">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF53">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK53">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="O54">
         <v>3.1</v>
@@ -9132,7 +9132,7 @@
         <v>2.59</v>
       </c>
       <c r="U54">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="V54">
         <v>1.35</v>
@@ -9144,16 +9144,16 @@
         <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z54">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AA54">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC54">
         <v>3.38</v>
@@ -9162,13 +9162,13 @@
         <v>1.24</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,25 +9277,25 @@
         <v>2.56</v>
       </c>
       <c r="O55">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="P55">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q55">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="R55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T55">
         <v>2.59</v>
       </c>
       <c r="U55">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="V55">
         <v>1.3</v>
@@ -9313,25 +9313,25 @@
         <v>2.88</v>
       </c>
       <c r="AA55">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB55">
         <v>1.57</v>
       </c>
       <c r="AC55">
-        <v>4.59</v>
+        <v>4</v>
       </c>
       <c r="AD55">
         <v>1.17</v>
       </c>
       <c r="AE55">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG55">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O56">
+        <v>3.25</v>
+      </c>
+      <c r="P56">
         <v>3.3</v>
       </c>
-      <c r="P56">
-        <v>3.32</v>
-      </c>
       <c r="Q56">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R56">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T56">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U56">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="V56">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
         <v>1.03</v>
@@ -9470,31 +9470,31 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AA56">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB56">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC56">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE56">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG56">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,52 +9600,52 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q57">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R57">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S57">
         <v>1.35</v>
       </c>
       <c r="T57">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U57">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="V57">
         <v>1.44</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
         <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z57">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA57">
+        <v>1.85</v>
+      </c>
+      <c r="AB57">
         <v>1.95</v>
       </c>
-      <c r="AB57">
-        <v>1.85</v>
-      </c>
       <c r="AC57">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AD57">
         <v>1.34</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="O58">
         <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q58">
         <v>3.7</v>
       </c>
       <c r="R58">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
         <v>1.43</v>
@@ -9784,10 +9784,10 @@
         <v>2.62</v>
       </c>
       <c r="U58">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
         <v>1.03</v>
@@ -9799,22 +9799,22 @@
         <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB58">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC58">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE58">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF58">
         <v>1.75</v>
@@ -9941,13 +9941,13 @@
         <v>2.16</v>
       </c>
       <c r="S59">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="U59">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V59">
         <v>1.47</v>
@@ -9959,31 +9959,31 @@
         <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="AA59">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB59">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC59">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD59">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
         <v>1.65</v>
       </c>
       <c r="AG59">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10267,10 +10267,10 @@
         <v>2.08</v>
       </c>
       <c r="S61">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="U61">
         <v>2.74</v>
@@ -10279,7 +10279,7 @@
         <v>1.37</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10291,10 +10291,10 @@
         <v>3.14</v>
       </c>
       <c r="AA61">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB61">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC61">
         <v>3.14</v>
@@ -10309,7 +10309,7 @@
         <v>1.82</v>
       </c>
       <c r="AG61">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,37 +10415,37 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q62">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="R62">
         <v>2.25</v>
       </c>
       <c r="S62">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U62">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V62">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.19</v>
@@ -10454,7 +10454,7 @@
         <v>3.8</v>
       </c>
       <c r="AA62">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB62">
         <v>2.05</v>
@@ -10463,16 +10463,16 @@
         <v>2.62</v>
       </c>
       <c r="AD62">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
         <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,22 +10578,22 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P63">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q63">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="R63">
         <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
         <v>3.58</v>
@@ -10602,10 +10602,10 @@
         <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W63">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10623,7 +10623,7 @@
         <v>2.51</v>
       </c>
       <c r="AC63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD63">
         <v>1.73</v>
@@ -10651,7 +10651,7 @@
         <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,22 +10741,22 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q64">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="R64">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T64">
         <v>3.82</v>
@@ -10780,25 +10780,25 @@
         <v>5.9</v>
       </c>
       <c r="AA64">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB64">
         <v>2.7</v>
       </c>
       <c r="AC64">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AD64">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE64">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG64">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O65">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="P65">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q65">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R65">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="S65">
         <v>1.17</v>
@@ -10943,10 +10943,10 @@
         <v>6.45</v>
       </c>
       <c r="AA65">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB65">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC65">
         <v>1.81</v>
@@ -10955,13 +10955,13 @@
         <v>1.95</v>
       </c>
       <c r="AE65">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG65">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>4.33</v>
       </c>
       <c r="Q66">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="R66">
         <v>2.4</v>
@@ -11088,7 +11088,7 @@
         <v>3.52</v>
       </c>
       <c r="U66">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
         <v>1.62</v>
@@ -11100,10 +11100,10 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="AA66">
         <v>1.5</v>
@@ -11112,19 +11112,19 @@
         <v>2.5</v>
       </c>
       <c r="AC66">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AD66">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE66">
         <v>1.21</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,16 +11233,16 @@
         <v>1.44</v>
       </c>
       <c r="O67">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P67">
         <v>5</v>
       </c>
       <c r="Q67">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R67">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="S67">
         <v>1.14</v>
@@ -11251,7 +11251,7 @@
         <v>4.5</v>
       </c>
       <c r="U67">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V67">
         <v>1.89</v>
@@ -11269,7 +11269,7 @@
         <v>7.4</v>
       </c>
       <c r="AA67">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB67">
         <v>3.5</v>
@@ -11281,10 +11281,10 @@
         <v>2.06</v>
       </c>
       <c r="AE67">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AF67">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
         <v>2.81</v>
@@ -11303,7 +11303,7 @@
         <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>3</v>
       </c>
       <c r="R68">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S68">
         <v>1.3</v>
@@ -11414,19 +11414,19 @@
         <v>3.16</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
         <v>1.09</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
         <v>4.4</v>
@@ -11435,22 +11435,22 @@
         <v>1.6</v>
       </c>
       <c r="AB68">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC68">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD68">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AE68">
         <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG68">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11556,16 +11556,16 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="O69">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="P69">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q69">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="R69">
         <v>2.31</v>
@@ -11574,31 +11574,31 @@
         <v>1.22</v>
       </c>
       <c r="T69">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U69">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V69">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W69">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X69">
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z69">
         <v>5.45</v>
       </c>
       <c r="AA69">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB69">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC69">
         <v>2.14</v>
@@ -11607,13 +11607,13 @@
         <v>1.67</v>
       </c>
       <c r="AE69">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AF69">
         <v>1.39</v>
       </c>
       <c r="AG69">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11725,10 +11725,10 @@
         <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q70">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R70">
         <v>2.25</v>
@@ -11743,25 +11743,25 @@
         <v>2.33</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>4.3</v>
+        <v>4.47</v>
       </c>
       <c r="AA70">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC70">
         <v>2.46</v>
@@ -11773,10 +11773,10 @@
         <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG70">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="O71">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="P71">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O72">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P72">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O73">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R73">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S73">
         <v>1.43</v>
@@ -12229,7 +12229,7 @@
         <v>2.59</v>
       </c>
       <c r="U73">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="V73">
         <v>1.33</v>
@@ -12247,10 +12247,10 @@
         <v>2.97</v>
       </c>
       <c r="AA73">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB73">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC73">
         <v>3.58</v>
@@ -12262,10 +12262,10 @@
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG73">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="O74">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P74">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R74">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
         <v>1.33</v>
@@ -12410,10 +12410,10 @@
         <v>3.88</v>
       </c>
       <c r="AA74">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB74">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC74">
         <v>2.66</v>
@@ -12425,7 +12425,7 @@
         <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG74">
         <v>1.8</v>
@@ -12444,7 +12444,7 @@
         <v>1.16</v>
       </c>
       <c r="AK74">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R75">
         <v>2.09</v>
@@ -12564,7 +12564,7 @@
         <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
         <v>1.22</v>
@@ -12573,10 +12573,10 @@
         <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC75">
         <v>2.97</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12869,55 +12869,55 @@
         <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S77">
         <v>1.42</v>
       </c>
       <c r="T77">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U77">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="V77">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z77">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AA77">
         <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC77">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AD77">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
         <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q78">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
         <v>1.3</v>
@@ -13044,7 +13044,7 @@
         <v>3.16</v>
       </c>
       <c r="U78">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V78">
         <v>1.5</v>
@@ -13056,16 +13056,16 @@
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA78">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB78">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AC78">
         <v>2.46</v>
@@ -13186,19 +13186,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O79">
         <v>4.8</v>
       </c>
       <c r="P79">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q79">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R79">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="S79">
         <v>1.21</v>
@@ -13207,10 +13207,10 @@
         <v>4.2</v>
       </c>
       <c r="U79">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V79">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W79">
         <v>1.22</v>
@@ -13222,28 +13222,28 @@
         <v>1.07</v>
       </c>
       <c r="Z79">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA79">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB79">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AC79">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AD79">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE79">
         <v>1.33</v>
       </c>
       <c r="AF79">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG79">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.21</v>
       </c>
       <c r="AK79">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,28 +13349,28 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="O80">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="P80">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="Q80">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R80">
         <v>2.04</v>
       </c>
       <c r="S80">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U80">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V80">
         <v>1.32</v>
@@ -13394,10 +13394,10 @@
         <v>1.7</v>
       </c>
       <c r="AC80">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD80">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
         <v>1.04</v>
@@ -14170,13 +14170,13 @@
         <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q85">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="R85">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S85">
         <v>1.55</v>
@@ -14203,7 +14203,7 @@
         <v>2.77</v>
       </c>
       <c r="AA85">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB85">
         <v>1.61</v>
@@ -14215,10 +14215,10 @@
         <v>1.19</v>
       </c>
       <c r="AE85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF85">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG85">
         <v>1.7</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O86">
-        <v>6.5</v>
+        <v>6.28</v>
       </c>
       <c r="P86">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="O87">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P87">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q87">
         <v>5.15</v>
@@ -14508,25 +14508,25 @@
         <v>1.22</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U87">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="V87">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W87">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA87">
         <v>1.5</v>
@@ -14538,16 +14538,16 @@
         <v>2.28</v>
       </c>
       <c r="AD87">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE87">
         <v>1.24</v>
       </c>
       <c r="AF87">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG87">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P88">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Q88">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S88">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
         <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V88">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z88">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB88">
         <v>2.35</v>
       </c>
       <c r="AC88">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AD88">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE88">
         <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG88">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15960,22 +15960,22 @@
         <v>6.5</v>
       </c>
       <c r="O96">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="P96">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q96">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="R96">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="S96">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U96">
         <v>2.06</v>
@@ -15984,37 +15984,37 @@
         <v>1.79</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
         <v>1.07</v>
       </c>
       <c r="Z96">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="AA96">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB96">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AC96">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AD96">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE96">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AF96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16123,19 +16123,19 @@
         <v>1.4</v>
       </c>
       <c r="O97">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P97">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q97">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R97">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T97">
         <v>3.94</v>
@@ -16147,7 +16147,7 @@
         <v>1.73</v>
       </c>
       <c r="W97">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X97">
         <v>1.02</v>
@@ -16165,7 +16165,7 @@
         <v>2.75</v>
       </c>
       <c r="AC97">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD97">
         <v>1.81</v>
@@ -16177,7 +16177,7 @@
         <v>1.59</v>
       </c>
       <c r="AG97">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK97">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16446,34 +16446,34 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O99">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P99">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q99">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="R99">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T99">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U99">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V99">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X99">
         <v>1.03</v>
@@ -16482,19 +16482,19 @@
         <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA99">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AB99">
-        <v>2.24</v>
+        <v>2.09</v>
       </c>
       <c r="AC99">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="AD99">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE99">
         <v>1.14</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK99">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="O100">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P100">
-        <v>6.56</v>
+        <v>6.8</v>
       </c>
       <c r="Q100">
         <v>2.04</v>
@@ -16642,16 +16642,16 @@
         <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z100">
         <v>3.1</v>
       </c>
       <c r="AA100">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
         <v>3.3</v>
@@ -17282,16 +17282,16 @@
         <v>2.25</v>
       </c>
       <c r="U104">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="V104">
         <v>1.22</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X104">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y104">
         <v>1.54</v>
@@ -17315,7 +17315,7 @@
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG104">
         <v>1.53</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O108">
         <v>2.9</v>
@@ -17922,19 +17922,19 @@
         <v>2.7</v>
       </c>
       <c r="Q108">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="R108">
         <v>1.89</v>
       </c>
       <c r="S108">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T108">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U108">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V108">
         <v>1.26</v>
@@ -17946,19 +17946,19 @@
         <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z108">
         <v>2.46</v>
       </c>
       <c r="AA108">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB108">
         <v>1.5</v>
       </c>
       <c r="AC108">
-        <v>4.2</v>
+        <v>4.91</v>
       </c>
       <c r="AD108">
         <v>1.13</v>
@@ -17967,10 +17967,10 @@
         <v>1.01</v>
       </c>
       <c r="AF108">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG108">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK108">
         <v>1.47</v>
@@ -19715,10 +19715,10 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S119">
         <v>1.35</v>
@@ -19727,7 +19727,7 @@
         <v>2.9</v>
       </c>
       <c r="U119">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V119">
         <v>1.41</v>
@@ -19739,7 +19739,7 @@
         <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z119">
         <v>3.42</v>
@@ -19751,7 +19751,7 @@
         <v>1.95</v>
       </c>
       <c r="AC119">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD119">
         <v>1.3</v>
@@ -19760,10 +19760,10 @@
         <v>1.08</v>
       </c>
       <c r="AF119">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG119">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,31 +8948,31 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O53">
-        <v>6.34</v>
+        <v>5.71</v>
       </c>
       <c r="P53">
-        <v>10</v>
+        <v>1.29</v>
       </c>
       <c r="Q53">
-        <v>1.6</v>
+        <v>6.35</v>
       </c>
       <c r="R53">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="S53">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T53">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="U53">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W53">
         <v>1.17</v>
@@ -8981,10 +8981,10 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>5.45</v>
+        <v>5.9</v>
       </c>
       <c r="AA53">
         <v>1.44</v>
@@ -8993,19 +8993,19 @@
         <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AD53">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE53">
         <v>1.28</v>
       </c>
       <c r="AF53">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK53">
-        <v>3.8</v>
+        <v>1.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>8.050000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="O54">
-        <v>5.71</v>
+        <v>6.34</v>
       </c>
       <c r="P54">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="Q54">
-        <v>6.35</v>
+        <v>1.6</v>
       </c>
       <c r="R54">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="S54">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T54">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="U54">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="V54">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W54">
         <v>1.17</v>
@@ -9144,10 +9144,10 @@
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>5.9</v>
+        <v>5.45</v>
       </c>
       <c r="AA54">
         <v>1.44</v>
@@ -9156,19 +9156,19 @@
         <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE54">
         <v>1.28</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG54">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK54">
-        <v>1.05</v>
+        <v>3.8</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,65 +9437,65 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="O56">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P56">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T56">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="U56">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="V56">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA56">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB56">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC56">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AD56">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF56">
+        <v>1.78</v>
+      </c>
+      <c r="AG56">
         <v>1.93</v>
       </c>
-      <c r="AG56">
-        <v>1.73</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q57">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="R57">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U57">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V57">
         <v>1.35</v>
@@ -9630,7 +9630,7 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.28</v>
@@ -9639,10 +9639,10 @@
         <v>3.08</v>
       </c>
       <c r="AA57">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB57">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC57">
         <v>3.38</v>
@@ -9651,13 +9651,13 @@
         <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q58">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="R58">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T58">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U58">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC58">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="AD58">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE58">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>2.13</v>
+        <v>1.47</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.89</v>
+        <v>1.67</v>
       </c>
       <c r="O59">
+        <v>3.5</v>
+      </c>
+      <c r="P59">
+        <v>4.5</v>
+      </c>
+      <c r="Q59">
+        <v>2.22</v>
+      </c>
+      <c r="R59">
+        <v>2.29</v>
+      </c>
+      <c r="S59">
+        <v>1.35</v>
+      </c>
+      <c r="T59">
         <v>3.1</v>
       </c>
-      <c r="P59">
-        <v>2.43</v>
-      </c>
-      <c r="Q59">
-        <v>3.7</v>
-      </c>
-      <c r="R59">
-        <v>2.1</v>
-      </c>
-      <c r="S59">
-        <v>1.43</v>
-      </c>
-      <c r="T59">
-        <v>2.62</v>
-      </c>
       <c r="U59">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="V59">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z59">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB59">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE59">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF59">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="O73">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P73">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="R73">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S73">
         <v>1.21</v>
@@ -12229,59 +12229,59 @@
         <v>3.58</v>
       </c>
       <c r="U73">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V73">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W73">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z73">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA73">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AC73">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD73">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AE73">
+        <v>1.26</v>
+      </c>
+      <c r="AF73">
+        <v>1.39</v>
+      </c>
+      <c r="AG73">
+        <v>2.73</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.19</v>
       </c>
-      <c r="AF73">
-        <v>1.49</v>
-      </c>
-      <c r="AG73">
-        <v>2.42</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.17</v>
-      </c>
       <c r="AK73">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="O74">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P74">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S74">
         <v>1.21</v>
@@ -12392,43 +12392,43 @@
         <v>3.58</v>
       </c>
       <c r="U74">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="V74">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z74">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA74">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AB74">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AC74">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AD74">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AE74">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF74">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AG74">
-        <v>2.73</v>
+        <v>2.42</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>1.69</v>
+        <v>2.01</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="O78">
+        <v>2.8</v>
+      </c>
+      <c r="P78">
+        <v>3.75</v>
+      </c>
+      <c r="Q78">
         <v>2.85</v>
-      </c>
-      <c r="P78">
-        <v>3.5</v>
-      </c>
-      <c r="Q78">
-        <v>2.86</v>
       </c>
       <c r="R78">
         <v>1.77</v>
@@ -13044,7 +13044,7 @@
         <v>2.1</v>
       </c>
       <c r="U78">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="V78">
         <v>1.18</v>
@@ -13062,10 +13062,10 @@
         <v>2.19</v>
       </c>
       <c r="AA78">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AB78">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC78">
         <v>5.45</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
         <v>1.63</v>
@@ -17916,10 +17916,10 @@
         <v>1.64</v>
       </c>
       <c r="O108">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="P108">
-        <v>5.71</v>
+        <v>5.88</v>
       </c>
       <c r="Q108">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U27">
+        <v>2.18</v>
+      </c>
+      <c r="V27">
+        <v>1.59</v>
+      </c>
+      <c r="W27">
+        <v>1.12</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>1.12</v>
+      </c>
+      <c r="Z27">
+        <v>4.75</v>
+      </c>
+      <c r="AA27">
+        <v>1.5</v>
+      </c>
+      <c r="AB27">
         <v>2.5</v>
       </c>
-      <c r="V27">
-        <v>1.43</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.03</v>
-      </c>
-      <c r="Y27">
-        <v>1.18</v>
-      </c>
-      <c r="Z27">
-        <v>3.86</v>
-      </c>
-      <c r="AA27">
-        <v>1.75</v>
-      </c>
-      <c r="AB27">
-        <v>2.05</v>
-      </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>2.19</v>
       </c>
       <c r="AD27">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q28">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="R28">
+        <v>2.13</v>
+      </c>
+      <c r="S28">
+        <v>1.3</v>
+      </c>
+      <c r="T28">
+        <v>3.2</v>
+      </c>
+      <c r="U28">
         <v>2.5</v>
       </c>
-      <c r="S28">
-        <v>1.25</v>
-      </c>
-      <c r="T28">
-        <v>3.28</v>
-      </c>
-      <c r="U28">
-        <v>2.18</v>
-      </c>
       <c r="V28">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>4.75</v>
+        <v>3.86</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="AD28">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O47">
+        <v>2.8</v>
+      </c>
+      <c r="P47">
+        <v>2.6</v>
+      </c>
+      <c r="Q47">
+        <v>3.5</v>
+      </c>
+      <c r="R47">
+        <v>1.83</v>
+      </c>
+      <c r="S47">
+        <v>1.58</v>
+      </c>
+      <c r="T47">
+        <v>2.22</v>
+      </c>
+      <c r="U47">
+        <v>3.85</v>
+      </c>
+      <c r="V47">
+        <v>1.18</v>
+      </c>
+      <c r="W47">
+        <v>1.02</v>
+      </c>
+      <c r="X47">
+        <v>1.06</v>
+      </c>
+      <c r="Y47">
+        <v>1.6</v>
+      </c>
+      <c r="Z47">
+        <v>2.25</v>
+      </c>
+      <c r="AA47">
         <v>2.75</v>
-      </c>
-      <c r="P47">
-        <v>3</v>
-      </c>
-      <c r="Q47">
-        <v>3.34</v>
-      </c>
-      <c r="R47">
-        <v>1.79</v>
-      </c>
-      <c r="S47">
-        <v>1.62</v>
-      </c>
-      <c r="T47">
-        <v>2.18</v>
-      </c>
-      <c r="U47">
-        <v>3.94</v>
-      </c>
-      <c r="V47">
-        <v>1.2</v>
-      </c>
-      <c r="W47">
-        <v>1.03</v>
-      </c>
-      <c r="X47">
-        <v>1.08</v>
-      </c>
-      <c r="Y47">
-        <v>1.62</v>
-      </c>
-      <c r="Z47">
-        <v>2.16</v>
-      </c>
-      <c r="AA47">
-        <v>3</v>
       </c>
       <c r="AB47">
         <v>1.36</v>
       </c>
       <c r="AC47">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AD47">
         <v>1.07</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AG47">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O48">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P48">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="R48">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S48">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T48">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U48">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="V48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y48">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z48">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AA48">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB48">
         <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD48">
         <v>1.07</v>
       </c>
       <c r="AE48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF48">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AG48">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
+        <v>2.9</v>
+      </c>
+      <c r="O84">
         <v>3.3</v>
       </c>
-      <c r="O84">
-        <v>3.6</v>
-      </c>
       <c r="P84">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>4.01</v>
+        <v>3.55</v>
       </c>
       <c r="R84">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T84">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>5.04</v>
+        <v>4.05</v>
       </c>
       <c r="AA84">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB84">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC84">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD84">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF84">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG84">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q85">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="R85">
+        <v>2.25</v>
+      </c>
+      <c r="S85">
+        <v>1.25</v>
+      </c>
+      <c r="T85">
+        <v>3.28</v>
+      </c>
+      <c r="U85">
         <v>2.2</v>
       </c>
-      <c r="S85">
-        <v>1.28</v>
-      </c>
-      <c r="T85">
-        <v>3.12</v>
-      </c>
-      <c r="U85">
-        <v>2.3</v>
-      </c>
       <c r="V85">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z85">
-        <v>4.05</v>
+        <v>5.04</v>
       </c>
       <c r="AA85">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB85">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC85">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD85">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE85">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF85">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG85">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -2277,7 +2277,7 @@
         <v>10.1</v>
       </c>
       <c r="R12">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="S12">
         <v>1.17</v>
@@ -2304,7 +2304,7 @@
         <v>5.67</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB12">
         <v>2.62</v>
@@ -2322,7 +2322,7 @@
         <v>2.03</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AK12">
         <v>1.02</v>
@@ -2467,7 +2467,7 @@
         <v>2.52</v>
       </c>
       <c r="AA13">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AB13">
         <v>1.52</v>
@@ -2932,13 +2932,13 @@
         <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U16">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
         <v>1.49</v>
@@ -2953,13 +2953,13 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB16">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AC16">
         <v>2.46</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
+        <v>3.5</v>
+      </c>
+      <c r="P20">
+        <v>2.61</v>
+      </c>
+      <c r="Q20">
+        <v>2.66</v>
+      </c>
+      <c r="R20">
         <v>2.25</v>
-      </c>
-      <c r="P20">
-        <v>3.1</v>
-      </c>
-      <c r="Q20">
-        <v>2.81</v>
-      </c>
-      <c r="R20">
-        <v>2.23</v>
       </c>
       <c r="S20">
         <v>1.29</v>
@@ -3590,10 +3590,10 @@
         <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.11</v>
@@ -3602,7 +3602,7 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
         <v>4.2</v>
@@ -3611,7 +3611,7 @@
         <v>1.64</v>
       </c>
       <c r="AB20">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
         <v>2.49</v>
@@ -3620,7 +3620,7 @@
         <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
         <v>1.51</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q22">
         <v>3.32</v>
@@ -3916,10 +3916,10 @@
         <v>3.02</v>
       </c>
       <c r="U22">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3931,16 +3931,16 @@
         <v>1.19</v>
       </c>
       <c r="Z22">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD22">
         <v>1.39</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
         <v>2.77</v>
@@ -4236,7 +4236,7 @@
         <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
         <v>3.14</v>
@@ -4251,7 +4251,7 @@
         <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.14</v>
@@ -4272,13 +4272,13 @@
         <v>1.47</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG24">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4393,13 +4393,13 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="R25">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
         <v>3.04</v>
@@ -4408,37 +4408,37 @@
         <v>2.25</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA25">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC25">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE25">
         <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
         <v>2.2</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S26">
         <v>1.38</v>
@@ -4574,7 +4574,7 @@
         <v>1.35</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4589,22 +4589,22 @@
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC26">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
         <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="R27">
+        <v>2.13</v>
+      </c>
+      <c r="S27">
+        <v>1.31</v>
+      </c>
+      <c r="T27">
+        <v>2.97</v>
+      </c>
+      <c r="U27">
         <v>2.5</v>
       </c>
-      <c r="S27">
-        <v>1.25</v>
-      </c>
-      <c r="T27">
-        <v>3.28</v>
-      </c>
-      <c r="U27">
-        <v>2.18</v>
-      </c>
       <c r="V27">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="AD27">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AE27">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AG27">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
+        <v>2.18</v>
+      </c>
+      <c r="V28">
+        <v>1.59</v>
+      </c>
+      <c r="W28">
+        <v>1.12</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.12</v>
+      </c>
+      <c r="Z28">
+        <v>4.75</v>
+      </c>
+      <c r="AA28">
+        <v>1.5</v>
+      </c>
+      <c r="AB28">
         <v>2.5</v>
       </c>
-      <c r="V28">
-        <v>1.43</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.03</v>
-      </c>
-      <c r="Y28">
-        <v>1.18</v>
-      </c>
-      <c r="Z28">
-        <v>3.86</v>
-      </c>
-      <c r="AA28">
-        <v>1.75</v>
-      </c>
-      <c r="AB28">
-        <v>2.05</v>
-      </c>
       <c r="AC28">
-        <v>2.74</v>
+        <v>2.19</v>
       </c>
       <c r="AD28">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>2.7</v>
       </c>
       <c r="P29">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q29">
         <v>2.9</v>
@@ -5069,16 +5069,16 @@
         <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="AA29">
         <v>2.23</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
         <v>4</v>
@@ -5090,7 +5090,7 @@
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
         <v>1.75</v>
@@ -5226,7 +5226,7 @@
         <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
         <v>1.55</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
         <v>1.51</v>
@@ -5579,10 +5579,10 @@
         <v>1.26</v>
       </c>
       <c r="AF32">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5857,13 +5857,13 @@
         <v>3.75</v>
       </c>
       <c r="P34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q34">
         <v>6.55</v>
       </c>
       <c r="R34">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S34">
         <v>1.44</v>
@@ -5896,7 +5896,7 @@
         <v>1.72</v>
       </c>
       <c r="AC34">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AD34">
         <v>1.21</v>
@@ -6177,34 +6177,34 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q36">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="R36">
         <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
         <v>3.08</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6222,10 +6222,10 @@
         <v>2.04</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE36">
         <v>1.11</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6352,13 +6352,13 @@
         <v>2.18</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U37">
         <v>2.11</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>6.31</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AC37">
         <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG37">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q38">
         <v>2.69</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
         <v>1.28</v>
@@ -6524,7 +6524,7 @@
         <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V38">
         <v>1.53</v>
@@ -6548,7 +6548,7 @@
         <v>2.27</v>
       </c>
       <c r="AC38">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="AD38">
         <v>1.46</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="O39">
         <v>4.2</v>
@@ -6675,13 +6675,13 @@
         <v>1.67</v>
       </c>
       <c r="Q39">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R39">
         <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.5</v>
@@ -6699,13 +6699,13 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
         <v>4.85</v>
       </c>
       <c r="AA39">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
         <v>2.39</v>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q40">
         <v>2.02</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
         <v>3.3</v>
@@ -6859,25 +6859,25 @@
         <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
         <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
         <v>1.18</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O41">
         <v>4</v>
@@ -7010,19 +7010,19 @@
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="U41">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V41">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W41">
         <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
         <v>1.2</v>
@@ -7034,13 +7034,13 @@
         <v>1.6</v>
       </c>
       <c r="AB41">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC41">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AD41">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
         <v>1.16</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK41">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O42">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="Q42">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="R42">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
         <v>1.23</v>
@@ -7176,7 +7176,7 @@
         <v>3.52</v>
       </c>
       <c r="U42">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V42">
         <v>1.64</v>
@@ -7191,7 +7191,7 @@
         <v>1.09</v>
       </c>
       <c r="Z42">
-        <v>5.4</v>
+        <v>5.73</v>
       </c>
       <c r="AA42">
         <v>1.5</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
         <v>1.51</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -7333,10 +7333,10 @@
         <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="U43">
         <v>2.24</v>
@@ -7357,25 +7357,25 @@
         <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB43">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD43">
         <v>1.51</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF43">
         <v>1.45</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7810,13 +7810,13 @@
         <v>1.8</v>
       </c>
       <c r="O46">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P46">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="R46">
         <v>2.33</v>
@@ -7840,31 +7840,31 @@
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB46">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="AC46">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD46">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE46">
         <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O47">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P47">
         <v>2.6</v>
@@ -7985,10 +7985,10 @@
         <v>1.83</v>
       </c>
       <c r="S47">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="T47">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="U47">
         <v>3.85</v>
@@ -8027,7 +8027,7 @@
         <v>2.21</v>
       </c>
       <c r="AG47">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,28 +8133,28 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O48">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P48">
         <v>3</v>
       </c>
       <c r="Q48">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="R48">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S48">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T48">
         <v>2.18</v>
       </c>
       <c r="U48">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="V48">
         <v>1.2</v>
@@ -8163,19 +8163,19 @@
         <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y48">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z48">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AA48">
         <v>3</v>
       </c>
       <c r="AB48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC48">
         <v>5.95</v>
@@ -8184,7 +8184,7 @@
         <v>1.07</v>
       </c>
       <c r="AE48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
         <v>2.3</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="O50">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>4.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q50">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="R50">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="S50">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="U50">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="V50">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>6.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AC50">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AD50">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AE50">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
         <v>1.41</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,58 +8622,58 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>3.91</v>
       </c>
       <c r="P51">
-        <v>2.15</v>
+        <v>3.99</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="R51">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="S51">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T51">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U51">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z51">
-        <v>5.05</v>
+        <v>6.25</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AC51">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AD51">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AE51">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF51">
         <v>1.41</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>3.15</v>
       </c>
       <c r="P52">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="Q52">
         <v>2.45</v>
@@ -8815,7 +8815,7 @@
         <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
         <v>1.25</v>
@@ -8824,22 +8824,22 @@
         <v>3.7</v>
       </c>
       <c r="AA52">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB52">
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG52">
         <v>2.05</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>8.050000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="O53">
-        <v>5.71</v>
+        <v>5.35</v>
       </c>
       <c r="P53">
-        <v>1.29</v>
+        <v>6.9</v>
       </c>
       <c r="Q53">
-        <v>6.35</v>
+        <v>1.68</v>
       </c>
       <c r="R53">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="S53">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="U53">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="V53">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>5.9</v>
+        <v>5.15</v>
       </c>
       <c r="AA53">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB53">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC53">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD53">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE53">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK53">
-        <v>1.05</v>
+        <v>3.09</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O54">
-        <v>6.34</v>
+        <v>5.71</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>1.27</v>
       </c>
       <c r="Q54">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="R54">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="S54">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T54">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="U54">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W54">
         <v>1.17</v>
@@ -9144,31 +9144,31 @@
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>5.45</v>
+        <v>6.05</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD54">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE54">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF54">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
-        <v>3.8</v>
+        <v>1.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,16 +9274,16 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P55">
         <v>2.3</v>
       </c>
       <c r="Q55">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="R55">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         <v>2.59</v>
       </c>
       <c r="U55">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V55">
         <v>1.35</v>
@@ -9307,7 +9307,7 @@
         <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z55">
         <v>3</v>
@@ -9316,7 +9316,7 @@
         <v>2.05</v>
       </c>
       <c r="AB55">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC55">
         <v>3.38</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="O56">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R56">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S56">
         <v>1.41</v>
       </c>
       <c r="T56">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U56">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="V56">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
         <v>1.03</v>
@@ -9473,13 +9473,13 @@
         <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA56">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC56">
         <v>3.38</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
         <v>1.68</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="O57">
         <v>3.1</v>
       </c>
       <c r="P57">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q57">
         <v>3.7</v>
       </c>
       <c r="R57">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S57">
         <v>1.43</v>
@@ -9633,7 +9633,7 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z57">
         <v>3.08</v>
@@ -9651,10 +9651,10 @@
         <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG57">
         <v>1.97</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.56</v>
+        <v>1.55</v>
       </c>
       <c r="O58">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R58">
+        <v>2.29</v>
+      </c>
+      <c r="S58">
+        <v>1.35</v>
+      </c>
+      <c r="T58">
+        <v>3.1</v>
+      </c>
+      <c r="U58">
+        <v>2.59</v>
+      </c>
+      <c r="V58">
+        <v>1.44</v>
+      </c>
+      <c r="W58">
+        <v>1.08</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="Y58">
+        <v>1.21</v>
+      </c>
+      <c r="Z58">
+        <v>3.62</v>
+      </c>
+      <c r="AA58">
+        <v>1.78</v>
+      </c>
+      <c r="AB58">
         <v>2</v>
       </c>
-      <c r="S58">
-        <v>1.5</v>
-      </c>
-      <c r="T58">
-        <v>2.59</v>
-      </c>
-      <c r="U58">
-        <v>3.22</v>
-      </c>
-      <c r="V58">
-        <v>1.3</v>
-      </c>
-      <c r="W58">
-        <v>1.02</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.4</v>
-      </c>
-      <c r="Z58">
-        <v>2.88</v>
-      </c>
-      <c r="AA58">
-        <v>2.3</v>
-      </c>
-      <c r="AB58">
-        <v>1.57</v>
-      </c>
       <c r="AC58">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="AD58">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AG58">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q59">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="R59">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U59">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z59">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA59">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB59">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="AD59">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE59">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG59">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK59">
-        <v>2.13</v>
+        <v>1.47</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10101,7 +10101,7 @@
         <v>2.33</v>
       </c>
       <c r="R60">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S60">
         <v>1.33</v>
@@ -10113,7 +10113,7 @@
         <v>2.5</v>
       </c>
       <c r="V60">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10125,28 +10125,28 @@
         <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AA60">
         <v>1.77</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC60">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD60">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE60">
         <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG60">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>2.7</v>
       </c>
       <c r="U62">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="V62">
         <v>1.37</v>
@@ -10448,7 +10448,7 @@
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z62">
         <v>3.14</v>
@@ -10469,7 +10469,7 @@
         <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG62">
         <v>1.91</v>
@@ -10584,19 +10584,19 @@
         <v>3.75</v>
       </c>
       <c r="P63">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R63">
         <v>2.25</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T63">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U63">
         <v>2.56</v>
@@ -10605,7 +10605,7 @@
         <v>1.48</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X63">
         <v>1.04</v>
@@ -10632,10 +10632,10 @@
         <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG63">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.18</v>
       </c>
       <c r="AK63">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,16 +10741,16 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q64">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="R64">
         <v>2.5</v>
@@ -10780,25 +10780,25 @@
         <v>5.1</v>
       </c>
       <c r="AA64">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB64">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="AC64">
         <v>2.15</v>
       </c>
       <c r="AD64">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE64">
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG64">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK64">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="Q66">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R66">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="S66">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T66">
-        <v>3.82</v>
+        <v>4.75</v>
       </c>
       <c r="U66">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="W66">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z66">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AB66">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AC66">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AD66">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AE66">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AF66">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG66">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="O67">
+        <v>3.85</v>
+      </c>
+      <c r="P67">
+        <v>4.25</v>
+      </c>
+      <c r="Q67">
+        <v>1.97</v>
+      </c>
+      <c r="R67">
+        <v>2.4</v>
+      </c>
+      <c r="S67">
+        <v>1.23</v>
+      </c>
+      <c r="T67">
+        <v>3.52</v>
+      </c>
+      <c r="U67">
+        <v>2.2</v>
+      </c>
+      <c r="V67">
+        <v>1.62</v>
+      </c>
+      <c r="W67">
+        <v>1.13</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.11</v>
+      </c>
+      <c r="Z67">
         <v>4.95</v>
       </c>
-      <c r="P67">
-        <v>5.75</v>
-      </c>
-      <c r="Q67">
-        <v>1.77</v>
-      </c>
-      <c r="R67">
-        <v>2.9</v>
-      </c>
-      <c r="S67">
-        <v>1.17</v>
-      </c>
-      <c r="T67">
-        <v>4.15</v>
-      </c>
-      <c r="U67">
-        <v>1.9</v>
-      </c>
-      <c r="V67">
-        <v>1.83</v>
-      </c>
-      <c r="W67">
-        <v>1.22</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.05</v>
-      </c>
-      <c r="Z67">
-        <v>6.45</v>
-      </c>
       <c r="AA67">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="AC67">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="AD67">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AE67">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="O68">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="P68">
-        <v>4.33</v>
+        <v>5.58</v>
       </c>
       <c r="Q68">
+        <v>1.87</v>
+      </c>
+      <c r="R68">
+        <v>2.95</v>
+      </c>
+      <c r="S68">
+        <v>1.14</v>
+      </c>
+      <c r="T68">
+        <v>4.45</v>
+      </c>
+      <c r="U68">
+        <v>1.75</v>
+      </c>
+      <c r="V68">
+        <v>1.89</v>
+      </c>
+      <c r="W68">
+        <v>1.23</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.03</v>
+      </c>
+      <c r="Z68">
+        <v>7.4</v>
+      </c>
+      <c r="AA68">
+        <v>1.24</v>
+      </c>
+      <c r="AB68">
+        <v>3.34</v>
+      </c>
+      <c r="AC68">
+        <v>1.72</v>
+      </c>
+      <c r="AD68">
         <v>2.06</v>
       </c>
-      <c r="R68">
-        <v>2.4</v>
-      </c>
-      <c r="S68">
-        <v>1.23</v>
-      </c>
-      <c r="T68">
-        <v>3.52</v>
-      </c>
-      <c r="U68">
-        <v>2.2</v>
-      </c>
-      <c r="V68">
-        <v>1.62</v>
-      </c>
-      <c r="W68">
-        <v>1.13</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
+      <c r="AE68">
+        <v>1.42</v>
+      </c>
+      <c r="AF68">
+        <v>1.36</v>
+      </c>
+      <c r="AG68">
+        <v>2.81</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.14</v>
       </c>
-      <c r="Z68">
-        <v>5.23</v>
-      </c>
-      <c r="AA68">
-        <v>1.5</v>
-      </c>
-      <c r="AB68">
-        <v>2.5</v>
-      </c>
-      <c r="AC68">
-        <v>2.17</v>
-      </c>
-      <c r="AD68">
-        <v>1.61</v>
-      </c>
-      <c r="AE68">
-        <v>1.21</v>
-      </c>
-      <c r="AF68">
-        <v>1.5</v>
-      </c>
-      <c r="AG68">
-        <v>2.38</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.19</v>
-      </c>
       <c r="AK68">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O69">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="Q69">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R69">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="U69">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="V69">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AA69">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="AC69">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AD69">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AE69">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG69">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>2.61</v>
+        <v>1.46</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q70">
         <v>3</v>
       </c>
       <c r="R70">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T70">
-        <v>3.16</v>
+        <v>3.9</v>
       </c>
       <c r="U70">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="V70">
+        <v>1.67</v>
+      </c>
+      <c r="W70">
+        <v>1.17</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.12</v>
+      </c>
+      <c r="Z70">
+        <v>5.65</v>
+      </c>
+      <c r="AA70">
         <v>1.5</v>
       </c>
-      <c r="W70">
-        <v>1.09</v>
-      </c>
-      <c r="X70">
-        <v>1.04</v>
-      </c>
-      <c r="Y70">
-        <v>1.2</v>
-      </c>
-      <c r="Z70">
-        <v>4.4</v>
-      </c>
-      <c r="AA70">
-        <v>1.6</v>
-      </c>
       <c r="AB70">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AC70">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AD70">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AE70">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF70">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK70">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P71">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q71">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R71">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U71">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V71">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W71">
         <v>1.15</v>
@@ -11915,31 +11915,31 @@
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>5.45</v>
+        <v>5.95</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AD71">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF71">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.24</v>
       </c>
       <c r="AK71">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12051,7 +12051,7 @@
         <v>3.65</v>
       </c>
       <c r="P72">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
         <v>2.7</v>
@@ -12075,7 +12075,7 @@
         <v>1.13</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
         <v>1.2</v>
@@ -12084,10 +12084,10 @@
         <v>4.47</v>
       </c>
       <c r="AA72">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB72">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC72">
         <v>2.46</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O73">
         <v>3.75</v>
@@ -12217,7 +12217,7 @@
         <v>3.1</v>
       </c>
       <c r="Q73">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R73">
         <v>2.38</v>
@@ -12229,16 +12229,16 @@
         <v>3.58</v>
       </c>
       <c r="U73">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V73">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W73">
         <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
         <v>1.09</v>
@@ -12247,16 +12247,16 @@
         <v>5.25</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB73">
         <v>2.56</v>
       </c>
       <c r="AC73">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD73">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE73">
         <v>1.26</v>
@@ -12374,13 +12374,13 @@
         <v>1.66</v>
       </c>
       <c r="O74">
-        <v>4.05</v>
+        <v>3.63</v>
       </c>
       <c r="P74">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="Q74">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R74">
         <v>2.39</v>
@@ -12413,7 +12413,7 @@
         <v>1.51</v>
       </c>
       <c r="AB74">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="AC74">
         <v>2.25</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="O75">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="Q75">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="S75">
         <v>1.43</v>
@@ -12576,7 +12576,7 @@
         <v>2.1</v>
       </c>
       <c r="AB75">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC75">
         <v>3.58</v>
@@ -12591,7 +12591,7 @@
         <v>1.83</v>
       </c>
       <c r="AG75">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>4.05</v>
       </c>
       <c r="P76">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="Q76">
         <v>1.83</v>
@@ -12727,7 +12727,7 @@
         <v>1.06</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.18</v>
@@ -12742,16 +12742,16 @@
         <v>2.07</v>
       </c>
       <c r="AC76">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD76">
         <v>1.37</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG76">
         <v>1.8</v>
@@ -12872,7 +12872,7 @@
         <v>3</v>
       </c>
       <c r="R77">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
         <v>1.33</v>
@@ -12890,28 +12890,28 @@
         <v>1.04</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z77">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AB77">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC77">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
         <v>1.63</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P79">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q79">
         <v>2.45</v>
@@ -13201,10 +13201,10 @@
         <v>2.19</v>
       </c>
       <c r="S79">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="U79">
         <v>2.89</v>
@@ -13219,28 +13219,28 @@
         <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z79">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA79">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB79">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC79">
-        <v>3.24</v>
+        <v>3.76</v>
       </c>
       <c r="AD79">
         <v>1.26</v>
       </c>
       <c r="AE79">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG79">
         <v>1.86</v>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q80">
         <v>2.85</v>
@@ -13364,13 +13364,13 @@
         <v>2.3</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T80">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U80">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="V80">
         <v>1.5</v>
@@ -13379,7 +13379,7 @@
         <v>1.09</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
         <v>1.21</v>
@@ -13388,7 +13388,7 @@
         <v>3.8</v>
       </c>
       <c r="AA80">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB80">
         <v>2.11</v>
@@ -13422,7 +13422,7 @@
         <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O81">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="P81">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q81">
         <v>1.92</v>
       </c>
       <c r="R81">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="S81">
         <v>1.21</v>
@@ -13533,10 +13533,10 @@
         <v>4.2</v>
       </c>
       <c r="U81">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V81">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W81">
         <v>1.22</v>
@@ -13548,28 +13548,28 @@
         <v>1.07</v>
       </c>
       <c r="Z81">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA81">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB81">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AC81">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD81">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE81">
         <v>1.33</v>
       </c>
       <c r="AF81">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG81">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,10 +13678,10 @@
         <v>2.35</v>
       </c>
       <c r="O82">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P82">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q82">
         <v>3</v>
@@ -13690,10 +13690,10 @@
         <v>2.04</v>
       </c>
       <c r="S82">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T82">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U82">
         <v>3</v>
@@ -13714,16 +13714,16 @@
         <v>2.97</v>
       </c>
       <c r="AA82">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB82">
         <v>1.7</v>
       </c>
       <c r="AC82">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE82">
         <v>1.04</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P84">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q84">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="R84">
+        <v>2.25</v>
+      </c>
+      <c r="S84">
+        <v>1.25</v>
+      </c>
+      <c r="T84">
+        <v>3.28</v>
+      </c>
+      <c r="U84">
         <v>2.2</v>
       </c>
-      <c r="S84">
-        <v>1.28</v>
-      </c>
-      <c r="T84">
-        <v>3.12</v>
-      </c>
-      <c r="U84">
-        <v>2.3</v>
-      </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>4.05</v>
+        <v>5.04</v>
       </c>
       <c r="AA84">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC84">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD84">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE84">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF84">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG84">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
+        <v>2.9</v>
+      </c>
+      <c r="O85">
         <v>3.3</v>
       </c>
-      <c r="O85">
-        <v>3.6</v>
-      </c>
       <c r="P85">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>4.01</v>
+        <v>3.55</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T85">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V85">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z85">
-        <v>5.04</v>
+        <v>4.05</v>
       </c>
       <c r="AA85">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB85">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC85">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AD85">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE85">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF85">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG85">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="N87">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P87">
         <v>1.79</v>
@@ -14523,16 +14523,16 @@
         <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z87">
         <v>2.77</v>
       </c>
       <c r="AA87">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AB87">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AC87">
         <v>4.1</v>
@@ -14541,13 +14541,13 @@
         <v>1.19</v>
       </c>
       <c r="AE87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF87">
         <v>2</v>
       </c>
       <c r="AG87">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>9.6</v>
+        <v>8.99</v>
       </c>
       <c r="O88">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="P88">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O89">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P89">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q89">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="R89">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U89">
         <v>2.26</v>
@@ -14849,19 +14849,19 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB89">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AC89">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD89">
         <v>1.65</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
         <v>1.18</v>
@@ -14979,16 +14979,16 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O90">
         <v>3.85</v>
       </c>
       <c r="P90">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q90">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R90">
         <v>2.36</v>
@@ -15012,16 +15012,16 @@
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
         <v>4.4</v>
       </c>
       <c r="AA90">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AB90">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AC90">
         <v>2.39</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16286,16 +16286,16 @@
         <v>6.5</v>
       </c>
       <c r="O98">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P98">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q98">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="R98">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="S98">
         <v>1.22</v>
@@ -16304,10 +16304,10 @@
         <v>4.2</v>
       </c>
       <c r="U98">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V98">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W98">
         <v>1.21</v>
@@ -16322,13 +16322,13 @@
         <v>7</v>
       </c>
       <c r="AA98">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB98">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="AC98">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AD98">
         <v>1.85</v>
@@ -16337,10 +16337,10 @@
         <v>1.36</v>
       </c>
       <c r="AF98">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG98">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,31 +16446,31 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="P99">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="Q99">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="S99">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U99">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V99">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W99">
         <v>1.17</v>
@@ -16482,13 +16482,13 @@
         <v>1.1</v>
       </c>
       <c r="Z99">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB99">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AC99">
         <v>2.17</v>
@@ -16503,7 +16503,7 @@
         <v>1.58</v>
       </c>
       <c r="AG99">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O101">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="P101">
         <v>13</v>
       </c>
       <c r="Q101">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="R101">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S101">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T101">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U101">
         <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
         <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA101">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB101">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AC101">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AD101">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
         <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AG101">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK101">
-        <v>4.76</v>
+        <v>4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,10 +16938,10 @@
         <v>1.41</v>
       </c>
       <c r="O102">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P102">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q102">
         <v>2.04</v>
@@ -16968,19 +16968,19 @@
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA102">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD102">
         <v>1.28</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O106">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P106">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q106">
         <v>2.54</v>
@@ -17608,13 +17608,13 @@
         <v>2.25</v>
       </c>
       <c r="U106">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V106">
         <v>1.22</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
         <v>1.11</v>
@@ -17629,13 +17629,13 @@
         <v>2.52</v>
       </c>
       <c r="AB106">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC106">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AD106">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE106">
         <v>1.04</v>
@@ -17644,7 +17644,7 @@
         <v>2.28</v>
       </c>
       <c r="AG106">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK106">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O110">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q110">
         <v>3.44</v>
@@ -18254,10 +18254,10 @@
         <v>1.89</v>
       </c>
       <c r="S110">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T110">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="U110">
         <v>3.6</v>
@@ -18278,7 +18278,7 @@
         <v>2.46</v>
       </c>
       <c r="AA110">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AB110">
         <v>1.5</v>
@@ -18290,7 +18290,7 @@
         <v>1.13</v>
       </c>
       <c r="AE110">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
         <v>1.95</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK110">
         <v>1.47</v>
@@ -19555,7 +19555,7 @@
         <v>2</v>
       </c>
       <c r="R118">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S118">
         <v>1.35</v>
@@ -19576,7 +19576,7 @@
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
         <v>3.42</v>
@@ -19588,7 +19588,7 @@
         <v>1.95</v>
       </c>
       <c r="AC118">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD118">
         <v>1.3</v>
@@ -19600,7 +19600,7 @@
         <v>1.9</v>
       </c>
       <c r="AG118">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -976,13 +976,13 @@
         <v>2.21</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
         <v>3.08</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -991,13 +991,13 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA4">
         <v>1.75</v>
@@ -1006,19 +1006,19 @@
         <v>2.07</v>
       </c>
       <c r="AC4">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE4">
         <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.85</v>
+        <v>4.06</v>
       </c>
       <c r="R5">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U5">
         <v>2.2</v>
@@ -1169,35 +1169,35 @@
         <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE5">
+        <v>1.17</v>
+      </c>
+      <c r="AF5">
+        <v>1.6</v>
+      </c>
+      <c r="AG5">
+        <v>2.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.16</v>
       </c>
-      <c r="AF5">
-        <v>1.59</v>
-      </c>
-      <c r="AG5">
-        <v>2.19</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>2.15</v>
-      </c>
       <c r="AK5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="R22">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG22">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="O44">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="P44">
         <v>1.3</v>
@@ -7505,7 +7505,7 @@
         <v>1.95</v>
       </c>
       <c r="V44">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="W44">
         <v>1.17</v>
@@ -7526,13 +7526,13 @@
         <v>2.92</v>
       </c>
       <c r="AC44">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD44">
         <v>1.8</v>
       </c>
       <c r="AE44">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF44">
         <v>1.66</v>
@@ -7554,7 +7554,7 @@
         <v>1.14</v>
       </c>
       <c r="AK44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="Q45">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R45">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="V45">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>4.95</v>
+        <v>5.45</v>
       </c>
       <c r="AA45">
         <v>1.47</v>
       </c>
       <c r="AB45">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AC45">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AD45">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O46">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P46">
         <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
         <v>3.34</v>
@@ -7846,10 +7846,10 @@
         <v>4.65</v>
       </c>
       <c r="AA46">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AC46">
         <v>2.35</v>
@@ -7858,7 +7858,7 @@
         <v>1.59</v>
       </c>
       <c r="AE46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
         <v>1.5</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P47">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="R47">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S47">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="T47">
         <v>2.13</v>
       </c>
       <c r="U47">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="V47">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W47">
         <v>1.02</v>
       </c>
       <c r="X47">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y47">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z47">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AA47">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC47">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD47">
         <v>1.07</v>
       </c>
       <c r="AE47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AG47">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK47">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O48">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P48">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q48">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="R48">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="S48">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T48">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="U48">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="V48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z48">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AA48">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB48">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AD48">
         <v>1.07</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF48">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AG48">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W50">
         <v>1.12</v>
@@ -8625,22 +8625,22 @@
         <v>1.57</v>
       </c>
       <c r="O51">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="P51">
-        <v>3.99</v>
+        <v>4.33</v>
       </c>
       <c r="Q51">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R51">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S51">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T51">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U51">
         <v>1.99</v>
@@ -8667,7 +8667,7 @@
         <v>2.75</v>
       </c>
       <c r="AC51">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD51">
         <v>1.77</v>
@@ -8695,7 +8695,7 @@
         <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O53">
         <v>5.35</v>
@@ -8960,7 +8960,7 @@
         <v>1.68</v>
       </c>
       <c r="R53">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="S53">
         <v>1.19</v>
@@ -8990,7 +8990,7 @@
         <v>1.47</v>
       </c>
       <c r="AB53">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC53">
         <v>2.1</v>
@@ -9021,7 +9021,7 @@
         <v>1.12</v>
       </c>
       <c r="AK53">
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>8.050000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="O54">
-        <v>5.71</v>
+        <v>5.6</v>
       </c>
       <c r="P54">
         <v>1.27</v>
@@ -9156,10 +9156,10 @@
         <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD54">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE54">
         <v>1.33</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q58">
-        <v>2.23</v>
+        <v>3.22</v>
       </c>
       <c r="R58">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AB58">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC58">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="AD58">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE58">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q59">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="R59">
+        <v>2.29</v>
+      </c>
+      <c r="S59">
+        <v>1.35</v>
+      </c>
+      <c r="T59">
+        <v>3.1</v>
+      </c>
+      <c r="U59">
+        <v>2.59</v>
+      </c>
+      <c r="V59">
+        <v>1.44</v>
+      </c>
+      <c r="W59">
+        <v>1.08</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="Y59">
+        <v>1.21</v>
+      </c>
+      <c r="Z59">
+        <v>3.62</v>
+      </c>
+      <c r="AA59">
+        <v>1.78</v>
+      </c>
+      <c r="AB59">
         <v>2</v>
       </c>
-      <c r="S59">
-        <v>1.44</v>
-      </c>
-      <c r="T59">
-        <v>2.59</v>
-      </c>
-      <c r="U59">
-        <v>3.22</v>
-      </c>
-      <c r="V59">
-        <v>1.3</v>
-      </c>
-      <c r="W59">
-        <v>1.02</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.4</v>
-      </c>
-      <c r="Z59">
-        <v>2.88</v>
-      </c>
-      <c r="AA59">
-        <v>2.3</v>
-      </c>
-      <c r="AB59">
-        <v>1.57</v>
-      </c>
       <c r="AC59">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="AD59">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF59">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK59">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12051,10 +12051,10 @@
         <v>3.65</v>
       </c>
       <c r="P72">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q72">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R72">
         <v>2.25</v>
@@ -12069,10 +12069,10 @@
         <v>2.33</v>
       </c>
       <c r="V72">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
         <v>1.03</v>
@@ -12081,19 +12081,19 @@
         <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="AA72">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB72">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC72">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD72">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE72">
         <v>1.14</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="O73">
         <v>3.75</v>
@@ -12259,7 +12259,7 @@
         <v>1.68</v>
       </c>
       <c r="AE73">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF73">
         <v>1.39</v>
@@ -12371,25 +12371,25 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O74">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="R74">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
         <v>1.21</v>
       </c>
       <c r="T74">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U74">
         <v>2.2</v>
@@ -12404,25 +12404,25 @@
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>5.1</v>
+        <v>5.04</v>
       </c>
       <c r="AA74">
         <v>1.51</v>
       </c>
       <c r="AB74">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AC74">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD74">
         <v>1.57</v>
       </c>
       <c r="AE74">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
         <v>1.49</v>
@@ -12444,7 +12444,7 @@
         <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O83">
         <v>3.2</v>
@@ -13847,10 +13847,10 @@
         <v>2.4</v>
       </c>
       <c r="Q83">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="R83">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.36</v>
@@ -13877,7 +13877,7 @@
         <v>3.34</v>
       </c>
       <c r="AA83">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB83">
         <v>1.9</v>
@@ -13886,10 +13886,10 @@
         <v>2.97</v>
       </c>
       <c r="AD83">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
         <v>1.62</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q84">
-        <v>4.01</v>
+        <v>3.45</v>
       </c>
       <c r="R84">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T84">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U84">
+        <v>2.41</v>
+      </c>
+      <c r="V84">
+        <v>1.47</v>
+      </c>
+      <c r="W84">
+        <v>1.08</v>
+      </c>
+      <c r="X84">
+        <v>1.03</v>
+      </c>
+      <c r="Y84">
+        <v>1.22</v>
+      </c>
+      <c r="Z84">
+        <v>4.2</v>
+      </c>
+      <c r="AA84">
+        <v>1.54</v>
+      </c>
+      <c r="AB84">
         <v>2.2</v>
       </c>
-      <c r="V84">
-        <v>1.58</v>
-      </c>
-      <c r="W84">
-        <v>1.11</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.15</v>
-      </c>
-      <c r="Z84">
-        <v>5.04</v>
-      </c>
-      <c r="AA84">
-        <v>1.5</v>
-      </c>
-      <c r="AB84">
-        <v>1.98</v>
-      </c>
       <c r="AC84">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD84">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AG84">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q85">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="R85">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U85">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V85">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z85">
-        <v>4.05</v>
+        <v>5.04</v>
       </c>
       <c r="AA85">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AB85">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AC85">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG85">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14333,7 +14333,7 @@
         <v>3.5</v>
       </c>
       <c r="P86">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q86">
         <v>4.84</v>
@@ -14348,7 +14348,7 @@
         <v>2.96</v>
       </c>
       <c r="U86">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V86">
         <v>1.43</v>
@@ -14357,10 +14357,10 @@
         <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z86">
         <v>3.74</v>
@@ -14372,10 +14372,10 @@
         <v>2.07</v>
       </c>
       <c r="AC86">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AD86">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE86">
         <v>1.1</v>
@@ -14384,7 +14384,7 @@
         <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>8.99</v>
       </c>
       <c r="O88">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="P88">
         <v>1.25</v>
@@ -15637,7 +15637,7 @@
         <v>3.6</v>
       </c>
       <c r="P94">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q94">
         <v>2.25</v>
@@ -15670,7 +15670,7 @@
         <v>3.3</v>
       </c>
       <c r="AA94">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB94">
         <v>1.85</v>
@@ -15833,7 +15833,7 @@
         <v>3.44</v>
       </c>
       <c r="AA95">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB95">
         <v>1.93</v>
@@ -15851,7 +15851,7 @@
         <v>1.65</v>
       </c>
       <c r="AG95">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="O96">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="P96">
         <v>1.61</v>
       </c>
       <c r="Q96">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="R96">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S96">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T96">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U96">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="V96">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W96">
         <v>1.14</v>
@@ -15996,7 +15996,7 @@
         <v>5.25</v>
       </c>
       <c r="AA96">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB96">
         <v>2.6</v>
@@ -16008,10 +16008,10 @@
         <v>1.69</v>
       </c>
       <c r="AE96">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF96">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG96">
         <v>2.45</v>
@@ -16030,7 +16030,7 @@
         <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17756,10 +17756,10 @@
         <v>3.25</v>
       </c>
       <c r="P107">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q107">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R107">
         <v>2.2</v>
@@ -17789,10 +17789,10 @@
         <v>3.5</v>
       </c>
       <c r="AA107">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AB107">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
         <v>2.92</v>
@@ -18076,19 +18076,19 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="O109">
         <v>3.4</v>
       </c>
       <c r="P109">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q109">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
         <v>1.35</v>
@@ -18097,10 +18097,10 @@
         <v>3.26</v>
       </c>
       <c r="U109">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V109">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W109">
         <v>1.08</v>
@@ -18115,13 +18115,13 @@
         <v>4.04</v>
       </c>
       <c r="AA109">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB109">
         <v>2.05</v>
       </c>
       <c r="AC109">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AD109">
         <v>1.4</v>
@@ -18133,7 +18133,7 @@
         <v>1.6</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK109">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19217,16 +19217,16 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q116">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R116">
         <v>2.1</v>
@@ -19235,7 +19235,7 @@
         <v>1.4</v>
       </c>
       <c r="T116">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="U116">
         <v>2.75</v>
@@ -19256,10 +19256,10 @@
         <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB116">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC116">
         <v>3.28</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,10 +19389,10 @@
         <v>2.08</v>
       </c>
       <c r="Q117">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="R117">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S117">
         <v>1.44</v>
@@ -19401,10 +19401,10 @@
         <v>2.5</v>
       </c>
       <c r="U117">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V117">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W117">
         <v>1.04</v>
@@ -19416,22 +19416,22 @@
         <v>1.35</v>
       </c>
       <c r="Z117">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="AA117">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB117">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC117">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="AD117">
         <v>1.21</v>
       </c>
       <c r="AE117">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
         <v>1.87</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19890,7 +19890,7 @@
         <v>3.6</v>
       </c>
       <c r="U120">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V120">
         <v>1.55</v>
@@ -19899,10 +19899,10 @@
         <v>1.13</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z120">
         <v>4.45</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="U27">
+        <v>2.18</v>
+      </c>
+      <c r="V27">
+        <v>1.59</v>
+      </c>
+      <c r="W27">
+        <v>1.12</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>1.12</v>
+      </c>
+      <c r="Z27">
+        <v>4.75</v>
+      </c>
+      <c r="AA27">
+        <v>1.5</v>
+      </c>
+      <c r="AB27">
         <v>2.5</v>
       </c>
-      <c r="V27">
-        <v>1.43</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.04</v>
-      </c>
-      <c r="Y27">
-        <v>1.18</v>
-      </c>
-      <c r="Z27">
-        <v>3.85</v>
-      </c>
-      <c r="AA27">
-        <v>1.75</v>
-      </c>
-      <c r="AB27">
-        <v>2</v>
-      </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>2.19</v>
       </c>
       <c r="AD27">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q28">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="R28">
+        <v>2.13</v>
+      </c>
+      <c r="S28">
+        <v>1.31</v>
+      </c>
+      <c r="T28">
+        <v>2.97</v>
+      </c>
+      <c r="U28">
         <v>2.5</v>
       </c>
-      <c r="S28">
-        <v>1.25</v>
-      </c>
-      <c r="T28">
-        <v>3.28</v>
-      </c>
-      <c r="U28">
-        <v>2.18</v>
-      </c>
       <c r="V28">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="AD28">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
+        <v>1.1</v>
+      </c>
+      <c r="AF28">
+        <v>1.64</v>
+      </c>
+      <c r="AG28">
+        <v>2.08</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.21</v>
       </c>
-      <c r="AF28">
-        <v>1.44</v>
-      </c>
-      <c r="AG28">
-        <v>2.5</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.2</v>
-      </c>
       <c r="AK28">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
+        <v>1.09</v>
+      </c>
+      <c r="X37">
+        <v>1.03</v>
+      </c>
+      <c r="Y37">
+        <v>1.14</v>
+      </c>
+      <c r="Z37">
+        <v>4.4</v>
+      </c>
+      <c r="AA37">
+        <v>1.61</v>
+      </c>
+      <c r="AB37">
+        <v>2.27</v>
+      </c>
+      <c r="AC37">
+        <v>2.39</v>
+      </c>
+      <c r="AD37">
+        <v>1.46</v>
+      </c>
+      <c r="AE37">
         <v>1.15</v>
       </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.13</v>
-      </c>
-      <c r="Z37">
-        <v>6.31</v>
-      </c>
-      <c r="AA37">
-        <v>1.43</v>
-      </c>
-      <c r="AB37">
-        <v>2.61</v>
-      </c>
-      <c r="AC37">
-        <v>2.1</v>
-      </c>
-      <c r="AD37">
-        <v>1.76</v>
-      </c>
-      <c r="AE37">
-        <v>1.28</v>
-      </c>
       <c r="AF37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <v>2.18</v>
       </c>
-      <c r="O38">
-        <v>3.6</v>
-      </c>
-      <c r="P38">
-        <v>3</v>
-      </c>
-      <c r="Q38">
-        <v>2.69</v>
-      </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
+        <v>1.2</v>
+      </c>
+      <c r="T38">
+        <v>3.42</v>
+      </c>
+      <c r="U38">
+        <v>2.11</v>
+      </c>
+      <c r="V38">
+        <v>1.68</v>
+      </c>
+      <c r="W38">
+        <v>1.15</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.13</v>
+      </c>
+      <c r="Z38">
+        <v>6.31</v>
+      </c>
+      <c r="AA38">
+        <v>1.43</v>
+      </c>
+      <c r="AB38">
+        <v>2.61</v>
+      </c>
+      <c r="AC38">
+        <v>2.1</v>
+      </c>
+      <c r="AD38">
+        <v>1.76</v>
+      </c>
+      <c r="AE38">
         <v>1.28</v>
       </c>
-      <c r="T38">
-        <v>3.3</v>
-      </c>
-      <c r="U38">
-        <v>2.34</v>
-      </c>
-      <c r="V38">
-        <v>1.53</v>
-      </c>
-      <c r="W38">
-        <v>1.09</v>
-      </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.14</v>
-      </c>
-      <c r="Z38">
-        <v>4.4</v>
-      </c>
-      <c r="AA38">
-        <v>1.61</v>
-      </c>
-      <c r="AB38">
-        <v>2.27</v>
-      </c>
-      <c r="AC38">
-        <v>2.39</v>
-      </c>
-      <c r="AD38">
-        <v>1.46</v>
-      </c>
-      <c r="AE38">
-        <v>1.15</v>
-      </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.65</v>
+        <v>2.17</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.36</v>
+        <v>7.4</v>
       </c>
       <c r="O53">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="P53">
-        <v>6.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q53">
-        <v>1.68</v>
+        <v>6.4</v>
       </c>
       <c r="R53">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="S53">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T53">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="V53">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z53">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA53">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB53">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="AC53">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AD53">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AE53">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK53">
-        <v>2.79</v>
+        <v>1.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>7.4</v>
+        <v>1.36</v>
       </c>
       <c r="O54">
-        <v>5.6</v>
+        <v>5.35</v>
       </c>
       <c r="P54">
-        <v>1.27</v>
+        <v>6.9</v>
       </c>
       <c r="Q54">
-        <v>6.4</v>
+        <v>1.68</v>
       </c>
       <c r="R54">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="S54">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="U54">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V54">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA54">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB54">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="AC54">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AE54">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK54">
-        <v>1.05</v>
+        <v>2.79</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="O57">
+        <v>3.7</v>
+      </c>
+      <c r="P57">
+        <v>4.5</v>
+      </c>
+      <c r="Q57">
+        <v>2.23</v>
+      </c>
+      <c r="R57">
+        <v>2.29</v>
+      </c>
+      <c r="S57">
+        <v>1.35</v>
+      </c>
+      <c r="T57">
         <v>3.1</v>
       </c>
-      <c r="P57">
-        <v>2.37</v>
-      </c>
-      <c r="Q57">
-        <v>3.7</v>
-      </c>
-      <c r="R57">
-        <v>1.99</v>
-      </c>
-      <c r="S57">
-        <v>1.43</v>
-      </c>
-      <c r="T57">
-        <v>2.62</v>
-      </c>
       <c r="U57">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V57">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z57">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA57">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AB57">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC57">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AD57">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="O59">
+        <v>3.1</v>
+      </c>
+      <c r="P59">
+        <v>2.37</v>
+      </c>
+      <c r="Q59">
         <v>3.7</v>
       </c>
-      <c r="P59">
-        <v>4.5</v>
-      </c>
-      <c r="Q59">
-        <v>2.23</v>
-      </c>
       <c r="R59">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="S59">
+        <v>1.43</v>
+      </c>
+      <c r="T59">
+        <v>2.62</v>
+      </c>
+      <c r="U59">
+        <v>2.8</v>
+      </c>
+      <c r="V59">
         <v>1.35</v>
       </c>
-      <c r="T59">
-        <v>3.1</v>
-      </c>
-      <c r="U59">
-        <v>2.59</v>
-      </c>
-      <c r="V59">
-        <v>1.44</v>
-      </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z59">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA59">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AB59">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AC59">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="AD59">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="O69">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="P69">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="Q69">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T69">
-        <v>3.16</v>
+        <v>4.1</v>
       </c>
       <c r="U69">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="V69">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="W69">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>4.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA69">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB69">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AD69">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AE69">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AF69">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AG69">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="P70">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q70">
         <v>3</v>
       </c>
       <c r="R70">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>3.16</v>
       </c>
       <c r="U70">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="AC70">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="AD70">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE70">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF70">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="O71">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="Q71">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="V71">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>5.95</v>
+        <v>5.65</v>
       </c>
       <c r="AA71">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC71">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD71">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE71">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG71">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.24</v>
       </c>
       <c r="AK71">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
         <v>2.8</v>
@@ -13032,28 +13032,28 @@
         <v>3.75</v>
       </c>
       <c r="Q78">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="R78">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S78">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T78">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U78">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="V78">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W78">
         <v>1.03</v>
       </c>
       <c r="X78">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y78">
         <v>1.6</v>
@@ -13065,7 +13065,7 @@
         <v>2.74</v>
       </c>
       <c r="AB78">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC78">
         <v>5.45</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK78">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O84">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P84">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q84">
-        <v>3.45</v>
+        <v>4.01</v>
       </c>
       <c r="R84">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U84">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="V84">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>4.2</v>
+        <v>5.04</v>
       </c>
       <c r="AA84">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB84">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC84">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD84">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE84">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AF84">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AG84">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>4.01</v>
+        <v>3.45</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T85">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U85">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V85">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>5.04</v>
+        <v>4.2</v>
       </c>
       <c r="AA85">
+        <v>1.54</v>
+      </c>
+      <c r="AB85">
+        <v>2.2</v>
+      </c>
+      <c r="AC85">
+        <v>2.33</v>
+      </c>
+      <c r="AD85">
         <v>1.48</v>
       </c>
-      <c r="AB85">
-        <v>2.33</v>
-      </c>
-      <c r="AC85">
-        <v>2.25</v>
-      </c>
-      <c r="AD85">
-        <v>1.6</v>
-      </c>
       <c r="AE85">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF85">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AG85">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="O106">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="P106">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q106">
         <v>2.54</v>
@@ -17602,7 +17602,7 @@
         <v>1.86</v>
       </c>
       <c r="S106">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="T106">
         <v>2.25</v>
@@ -17614,10 +17614,10 @@
         <v>1.22</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y106">
         <v>1.54</v>
@@ -17632,16 +17632,16 @@
         <v>1.41</v>
       </c>
       <c r="AC106">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD106">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE106">
         <v>1.04</v>
       </c>
       <c r="AF106">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AG106">
         <v>1.55</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AK106">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17756,28 +17756,28 @@
         <v>3.25</v>
       </c>
       <c r="P107">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q107">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="R107">
         <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T107">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U107">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V107">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -17789,10 +17789,10 @@
         <v>3.5</v>
       </c>
       <c r="AA107">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC107">
         <v>2.92</v>
@@ -17916,10 +17916,10 @@
         <v>1.64</v>
       </c>
       <c r="O108">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="P108">
-        <v>5.88</v>
+        <v>4.75</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O110">
         <v>3</v>
       </c>
       <c r="P110">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q110">
         <v>3.44</v>
@@ -18257,13 +18257,13 @@
         <v>1.51</v>
       </c>
       <c r="T110">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U110">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V110">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W110">
         <v>1</v>
@@ -18272,16 +18272,16 @@
         <v>1.05</v>
       </c>
       <c r="Y110">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z110">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="AA110">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB110">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC110">
         <v>4.91</v>
@@ -18290,13 +18290,13 @@
         <v>1.13</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF110">
         <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -19217,25 +19217,25 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O116">
+        <v>3.2</v>
+      </c>
+      <c r="P116">
         <v>3.3</v>
-      </c>
-      <c r="P116">
-        <v>3.4</v>
       </c>
       <c r="Q116">
         <v>2.55</v>
       </c>
       <c r="R116">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S116">
         <v>1.4</v>
       </c>
       <c r="T116">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="U116">
         <v>2.75</v>
@@ -19256,7 +19256,7 @@
         <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB116">
         <v>1.8</v>
@@ -19268,13 +19268,13 @@
         <v>1.25</v>
       </c>
       <c r="AE116">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF116">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG116">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="O117">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P117">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q117">
         <v>4.3</v>
@@ -19567,31 +19567,31 @@
         <v>2.5</v>
       </c>
       <c r="V118">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z118">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA118">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB118">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC118">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD118">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE118">
         <v>1.08</v>
@@ -19600,7 +19600,7 @@
         <v>1.9</v>
       </c>
       <c r="AG118">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL118">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU120"/>
+  <dimension ref="A1:AU119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>7.45</v>
+        <v>7.55</v>
       </c>
       <c r="P12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Q12">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="R12">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="U12">
         <v>2.04</v>
@@ -2301,7 +2301,7 @@
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AA12">
         <v>1.38</v>
@@ -2316,13 +2316,13 @@
         <v>1.68</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG12">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="AK12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="R13">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W13">
         <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y13">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AA13">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AB13">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AC13">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,55 +2917,55 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="O16">
+        <v>3.55</v>
+      </c>
+      <c r="P16">
         <v>3.65</v>
       </c>
-      <c r="P16">
-        <v>3.75</v>
-      </c>
       <c r="Q16">
+        <v>2.38</v>
+      </c>
+      <c r="R16">
+        <v>2.2</v>
+      </c>
+      <c r="S16">
+        <v>1.25</v>
+      </c>
+      <c r="T16">
+        <v>3.5</v>
+      </c>
+      <c r="U16">
         <v>2.3</v>
       </c>
-      <c r="R16">
-        <v>2.25</v>
-      </c>
-      <c r="S16">
-        <v>1.29</v>
-      </c>
-      <c r="T16">
-        <v>3.4</v>
-      </c>
-      <c r="U16">
-        <v>2.29</v>
-      </c>
       <c r="V16">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
         <v>2.46</v>
       </c>
       <c r="AD16">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE16">
         <v>1.14</v>
@@ -2974,7 +2974,7 @@
         <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
         <v>1.83</v>
@@ -3572,22 +3572,22 @@
         <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.29</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
         <v>2.33</v>
@@ -3596,28 +3596,28 @@
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB20">
         <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
         <v>2.47</v>
@@ -3922,16 +3922,16 @@
         <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AA22">
         <v>1.72</v>
@@ -3940,19 +3940,19 @@
         <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="R23">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S23">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="T23">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U23">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="V23">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y23">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z23">
         <v>2.6</v>
       </c>
       <c r="AA23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB23">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC23">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD23">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="P24">
-        <v>9</v>
+        <v>7.65</v>
       </c>
       <c r="Q24">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="S24">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
         <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA24">
+        <v>1.46</v>
+      </c>
+      <c r="AB24">
+        <v>2.38</v>
+      </c>
+      <c r="AC24">
+        <v>2.23</v>
+      </c>
+      <c r="AD24">
         <v>1.57</v>
       </c>
-      <c r="AB24">
-        <v>2.23</v>
-      </c>
-      <c r="AC24">
-        <v>2.35</v>
-      </c>
-      <c r="AD24">
-        <v>1.47</v>
-      </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.1</v>
       </c>
       <c r="AK24">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,56 +4393,56 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB25">
+        <v>2.26</v>
+      </c>
+      <c r="AC25">
+        <v>2.3</v>
+      </c>
+      <c r="AD25">
+        <v>1.53</v>
+      </c>
+      <c r="AE25">
+        <v>1.18</v>
+      </c>
+      <c r="AF25">
+        <v>1.58</v>
+      </c>
+      <c r="AG25">
         <v>2.19</v>
       </c>
-      <c r="AC25">
-        <v>2.35</v>
-      </c>
-      <c r="AD25">
-        <v>1.47</v>
-      </c>
-      <c r="AE25">
-        <v>1.16</v>
-      </c>
-      <c r="AF25">
-        <v>1.62</v>
-      </c>
-      <c r="AG25">
-        <v>2.2</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R26">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
+        <v>1.25</v>
+      </c>
+      <c r="Z26">
+        <v>3.28</v>
+      </c>
+      <c r="AA26">
+        <v>1.9</v>
+      </c>
+      <c r="AB26">
+        <v>1.9</v>
+      </c>
+      <c r="AC26">
+        <v>3.05</v>
+      </c>
+      <c r="AD26">
         <v>1.28</v>
       </c>
-      <c r="Z26">
-        <v>3.08</v>
-      </c>
-      <c r="AA26">
-        <v>2</v>
-      </c>
-      <c r="AB26">
-        <v>1.77</v>
-      </c>
-      <c r="AC26">
-        <v>3.2</v>
-      </c>
-      <c r="AD26">
-        <v>1.26</v>
-      </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG26">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V27">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z27">
-        <v>4.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AC27">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
+        <v>2.18</v>
+      </c>
+      <c r="V28">
+        <v>1.64</v>
+      </c>
+      <c r="W28">
+        <v>1.14</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.12</v>
+      </c>
+      <c r="Z28">
+        <v>4.75</v>
+      </c>
+      <c r="AA28">
+        <v>1.5</v>
+      </c>
+      <c r="AB28">
+        <v>2.38</v>
+      </c>
+      <c r="AC28">
+        <v>2.19</v>
+      </c>
+      <c r="AD28">
+        <v>1.61</v>
+      </c>
+      <c r="AE28">
+        <v>1.21</v>
+      </c>
+      <c r="AF28">
+        <v>1.43</v>
+      </c>
+      <c r="AG28">
         <v>2.5</v>
-      </c>
-      <c r="V28">
-        <v>1.43</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.04</v>
-      </c>
-      <c r="Y28">
-        <v>1.18</v>
-      </c>
-      <c r="Z28">
-        <v>3.85</v>
-      </c>
-      <c r="AA28">
-        <v>1.75</v>
-      </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>2.74</v>
-      </c>
-      <c r="AD28">
-        <v>1.35</v>
-      </c>
-      <c r="AE28">
-        <v>1.1</v>
-      </c>
-      <c r="AF28">
-        <v>1.64</v>
-      </c>
-      <c r="AG28">
-        <v>2.08</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,34 +5036,34 @@
         </is>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="P29">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="Q29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.06</v>
@@ -5072,28 +5072,28 @@
         <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AA29">
         <v>2.23</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>2.89</v>
+        <v>3.37</v>
       </c>
       <c r="Q30">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="R30">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5220,7 +5220,7 @@
         <v>2.85</v>
       </c>
       <c r="U30">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="V30">
         <v>1.4</v>
@@ -5253,10 +5253,10 @@
         <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG30">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="R31">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S31">
         <v>1.49</v>
@@ -5383,7 +5383,7 @@
         <v>2.34</v>
       </c>
       <c r="U31">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="V31">
         <v>1.28</v>
@@ -5401,7 +5401,7 @@
         <v>2.62</v>
       </c>
       <c r="AA31">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AB31">
         <v>1.57</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
         <v>1.51</v>
@@ -5531,28 +5531,28 @@
         <v>5.8</v>
       </c>
       <c r="P32">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R32">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="S32">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T32">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U32">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V32">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5564,10 +5564,10 @@
         <v>6.05</v>
       </c>
       <c r="AA32">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB32">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AC32">
         <v>1.99</v>
@@ -5579,7 +5579,7 @@
         <v>1.26</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG32">
         <v>2.1</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="O39">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="P39">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q39">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S39">
         <v>1.25</v>
@@ -6690,7 +6690,7 @@
         <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
         <v>1.14</v>
@@ -6705,10 +6705,10 @@
         <v>4.85</v>
       </c>
       <c r="AA39">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AB39">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AC39">
         <v>2.3</v>
@@ -6720,7 +6720,7 @@
         <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
         <v>2.33</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U43">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7357,7 +7357,7 @@
         <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
         <v>2.33</v>
@@ -7369,13 +7369,13 @@
         <v>1.51</v>
       </c>
       <c r="AE43">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
         <v>1.45</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,46 +7807,46 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O46">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
         <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S46">
         <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="U46">
         <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB46">
         <v>2.4</v>
@@ -7858,13 +7858,13 @@
         <v>1.59</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG46">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P47">
         <v>2.95</v>
       </c>
       <c r="Q47">
-        <v>3.27</v>
+        <v>3.46</v>
       </c>
       <c r="R47">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="S47">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="T47">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U47">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="V47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W47">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y47">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z47">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AA47">
         <v>3</v>
       </c>
       <c r="AB47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC47">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AD47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P48">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q48">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="R48">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="S48">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="T48">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="U48">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="V48">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W48">
         <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y48">
         <v>1.6</v>
       </c>
       <c r="Z48">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA48">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB48">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC48">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD48">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF48">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AG48">
         <v>1.6</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK48">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
       </c>
       <c r="R50">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,10 +8480,10 @@
         <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="V50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
         <v>1.12</v>
@@ -8492,22 +8492,22 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA50">
         <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD50">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
         <v>1.21</v>
@@ -8532,7 +8532,7 @@
         <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O51">
         <v>4</v>
       </c>
       <c r="P51">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q51">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R51">
         <v>2.51</v>
       </c>
       <c r="S51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U51">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="V51">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W51">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8661,19 +8661,19 @@
         <v>6.25</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB51">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AC51">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AD51">
         <v>1.77</v>
       </c>
       <c r="AE51">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF51">
         <v>1.41</v>
@@ -8797,7 +8797,7 @@
         <v>2.45</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
         <v>1.33</v>
@@ -8806,22 +8806,22 @@
         <v>2.98</v>
       </c>
       <c r="U52">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AA52">
         <v>1.79</v>
@@ -8830,13 +8830,13 @@
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
         <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
         <v>1.68</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>7.4</v>
+        <v>1.36</v>
       </c>
       <c r="O53">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="P53">
-        <v>1.27</v>
+        <v>7.25</v>
       </c>
       <c r="Q53">
-        <v>6.4</v>
+        <v>1.68</v>
       </c>
       <c r="R53">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="S53">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U53">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V53">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA53">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB53">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AC53">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD53">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AE53">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK53">
-        <v>1.05</v>
+        <v>3.09</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.36</v>
+        <v>7.25</v>
       </c>
       <c r="O54">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="P54">
-        <v>6.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q54">
-        <v>1.68</v>
+        <v>5.8</v>
       </c>
       <c r="R54">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA54">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB54">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AC54">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD54">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE54">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="AK54">
-        <v>2.79</v>
+        <v>1.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q57">
-        <v>2.23</v>
+        <v>3.22</v>
       </c>
       <c r="R57">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U57">
-        <v>2.59</v>
+        <v>3.22</v>
       </c>
       <c r="V57">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z57">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA57">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AB57">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC57">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="AD57">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG57">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U58">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AB58">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC58">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AD58">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG58">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="O59">
+        <v>3.7</v>
+      </c>
+      <c r="P59">
+        <v>4.5</v>
+      </c>
+      <c r="Q59">
+        <v>2.23</v>
+      </c>
+      <c r="R59">
+        <v>2.29</v>
+      </c>
+      <c r="S59">
+        <v>1.35</v>
+      </c>
+      <c r="T59">
         <v>3.1</v>
       </c>
-      <c r="P59">
-        <v>2.37</v>
-      </c>
-      <c r="Q59">
-        <v>3.7</v>
-      </c>
-      <c r="R59">
-        <v>1.99</v>
-      </c>
-      <c r="S59">
-        <v>1.43</v>
-      </c>
-      <c r="T59">
-        <v>2.62</v>
-      </c>
       <c r="U59">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V59">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z59">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA59">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AB59">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AC59">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF59">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK59">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="O64">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
         <v>2.12</v>
@@ -10780,41 +10780,41 @@
         <v>5.1</v>
       </c>
       <c r="AA64">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB64">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AC64">
         <v>2.15</v>
       </c>
       <c r="AD64">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE64">
+        <v>1.29</v>
+      </c>
+      <c r="AF64">
+        <v>1.5</v>
+      </c>
+      <c r="AG64">
+        <v>2.65</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.25</v>
       </c>
-      <c r="AF64">
-        <v>1.43</v>
-      </c>
-      <c r="AG64">
-        <v>2.63</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.26</v>
-      </c>
       <c r="AK64">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,55 +11067,55 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P66">
-        <v>5.5</v>
+        <v>6.07</v>
       </c>
       <c r="Q66">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R66">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="S66">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T66">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="U66">
         <v>1.87</v>
       </c>
       <c r="V66">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W66">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z66">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="AA66">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB66">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AC66">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AD66">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE66">
         <v>1.4</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK66">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O67">
         <v>3.85</v>
       </c>
       <c r="P67">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q67">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S67">
         <v>1.23</v>
@@ -11251,7 +11251,7 @@
         <v>3.52</v>
       </c>
       <c r="U67">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V67">
         <v>1.62</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
         <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AC67">
         <v>2.26</v>
       </c>
       <c r="AD67">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE67">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
         <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         <v>1.43</v>
       </c>
       <c r="O68">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P68">
-        <v>5.58</v>
+        <v>5</v>
       </c>
       <c r="Q68">
         <v>1.87</v>
@@ -11414,7 +11414,7 @@
         <v>4.45</v>
       </c>
       <c r="U68">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V68">
         <v>1.89</v>
@@ -11426,10 +11426,10 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA68">
         <v>1.24</v>
@@ -11438,13 +11438,13 @@
         <v>3.34</v>
       </c>
       <c r="AC68">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD68">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE68">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AF68">
         <v>1.36</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK68">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="O69">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R69">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="S69">
+        <v>1.3</v>
+      </c>
+      <c r="T69">
+        <v>3.16</v>
+      </c>
+      <c r="U69">
+        <v>2.32</v>
+      </c>
+      <c r="V69">
+        <v>1.53</v>
+      </c>
+      <c r="W69">
+        <v>1.09</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
         <v>1.2</v>
       </c>
-      <c r="T69">
-        <v>4.1</v>
-      </c>
-      <c r="U69">
-        <v>2.06</v>
-      </c>
-      <c r="V69">
-        <v>1.7</v>
-      </c>
-      <c r="W69">
-        <v>1.15</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.07</v>
-      </c>
       <c r="Z69">
-        <v>5.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AD69">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AE69">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AF69">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG69">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AK69">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O70">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="Q70">
         <v>3</v>
       </c>
       <c r="R70">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="V70">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W70">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z70">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB70">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="AC70">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD70">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AE70">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AF70">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AK70">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="O71">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P71">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q71">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
         <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="V71">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD71">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="O73">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P73">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q73">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="R73">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S73">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U73">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V73">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="W73">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA73">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB73">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AC73">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="AD73">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AE73">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF73">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK73">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="O74">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P74">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="Q74">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="R74">
         <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T74">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U74">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V74">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z74">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AA74">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB74">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AC74">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AD74">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF74">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AG74">
-        <v>2.42</v>
+        <v>2.73</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P75">
         <v>3.35</v>
@@ -12549,22 +12549,22 @@
         <v>1.97</v>
       </c>
       <c r="S75">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T75">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U75">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
         <v>1.3</v>
@@ -12576,13 +12576,13 @@
         <v>2.1</v>
       </c>
       <c r="AB75">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC75">
         <v>3.58</v>
       </c>
       <c r="AD75">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE75">
         <v>1.03</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK75">
         <v>1.67</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O79">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
         <v>3.9</v>
@@ -13225,10 +13225,10 @@
         <v>3.05</v>
       </c>
       <c r="AA79">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB79">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC79">
         <v>3.76</v>
@@ -13240,10 +13240,10 @@
         <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG79">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O81">
         <v>4.85</v>
@@ -13524,22 +13524,22 @@
         <v>1.92</v>
       </c>
       <c r="R81">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S81">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U81">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="V81">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W81">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13548,13 +13548,13 @@
         <v>1.07</v>
       </c>
       <c r="Z81">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA81">
         <v>1.35</v>
       </c>
       <c r="AB81">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC81">
         <v>2.02</v>
@@ -13563,7 +13563,7 @@
         <v>1.92</v>
       </c>
       <c r="AE81">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF81">
         <v>1.48</v>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="O87">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="P87">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q87">
         <v>5</v>
@@ -14511,7 +14511,7 @@
         <v>2.43</v>
       </c>
       <c r="U87">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V87">
         <v>1.31</v>
@@ -14520,34 +14520,34 @@
         <v>1.03</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y87">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z87">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="AA87">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB87">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AC87">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD87">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE87">
         <v>1.01</v>
       </c>
       <c r="AF87">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG87">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="AK87">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,10 +14653,10 @@
         </is>
       </c>
       <c r="N88">
-        <v>8.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O88">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P88">
         <v>1.25</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O90">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q90">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R90">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S90">
         <v>1.25</v>
@@ -15006,31 +15006,31 @@
         <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z90">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA90">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB90">
         <v>2.24</v>
       </c>
       <c r="AC90">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AD90">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE90">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF90">
         <v>1.52</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
         <v>1.87</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,68 +15464,68 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="O94">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P94">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q94">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="R94">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
+        <v>1.35</v>
+      </c>
+      <c r="T94">
+        <v>2.94</v>
+      </c>
+      <c r="U94">
+        <v>2.65</v>
+      </c>
+      <c r="V94">
         <v>1.42</v>
       </c>
-      <c r="T94">
-        <v>2.77</v>
-      </c>
-      <c r="U94">
-        <v>2.77</v>
-      </c>
-      <c r="V94">
-        <v>1.43</v>
-      </c>
       <c r="W94">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA94">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC94">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD94">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE94">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF94">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK94">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G95">
@@ -15790,68 +15790,68 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N95">
-        <v>2.29</v>
+        <v>4.25</v>
       </c>
       <c r="O95">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="P95">
-        <v>2.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q95">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="R95">
+        <v>2.44</v>
+      </c>
+      <c r="S95">
+        <v>1.2</v>
+      </c>
+      <c r="T95">
+        <v>3.8</v>
+      </c>
+      <c r="U95">
+        <v>2.19</v>
+      </c>
+      <c r="V95">
+        <v>1.67</v>
+      </c>
+      <c r="W95">
+        <v>1.14</v>
+      </c>
+      <c r="X95">
+        <v>1.02</v>
+      </c>
+      <c r="Y95">
+        <v>1.09</v>
+      </c>
+      <c r="Z95">
+        <v>5.25</v>
+      </c>
+      <c r="AA95">
+        <v>1.42</v>
+      </c>
+      <c r="AB95">
+        <v>2.6</v>
+      </c>
+      <c r="AC95">
         <v>2.15</v>
       </c>
-      <c r="S95">
-        <v>1.35</v>
-      </c>
-      <c r="T95">
-        <v>2.94</v>
-      </c>
-      <c r="U95">
-        <v>2.65</v>
-      </c>
-      <c r="V95">
-        <v>1.42</v>
-      </c>
-      <c r="W95">
-        <v>1.06</v>
-      </c>
-      <c r="X95">
-        <v>1</v>
-      </c>
-      <c r="Y95">
-        <v>1.23</v>
-      </c>
-      <c r="Z95">
-        <v>3.44</v>
-      </c>
-      <c r="AA95">
-        <v>1.84</v>
-      </c>
-      <c r="AB95">
-        <v>1.93</v>
-      </c>
-      <c r="AC95">
-        <v>2.94</v>
-      </c>
       <c r="AD95">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="AE95">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AF95">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG95">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P96">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q96">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R96">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S96">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T96">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U96">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V96">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W96">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y96">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z96">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD96">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE96">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG96">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK96">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="O98">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="P98">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="Q98">
-        <v>5.8</v>
+        <v>1.83</v>
       </c>
       <c r="R98">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S98">
         <v>1.22</v>
       </c>
       <c r="T98">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U98">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V98">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W98">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AA98">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB98">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AC98">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AD98">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE98">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF98">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AG98">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.13</v>
+        <v>2.96</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="O99">
-        <v>5.05</v>
+        <v>3.05</v>
       </c>
       <c r="P99">
-        <v>6.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q99">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="R99">
-        <v>2.65</v>
+        <v>1.92</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="T99">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="U99">
+        <v>3.6</v>
+      </c>
+      <c r="V99">
+        <v>1.25</v>
+      </c>
+      <c r="W99">
+        <v>1.03</v>
+      </c>
+      <c r="X99">
+        <v>1.05</v>
+      </c>
+      <c r="Y99">
+        <v>1.43</v>
+      </c>
+      <c r="Z99">
+        <v>2.46</v>
+      </c>
+      <c r="AA99">
+        <v>2.37</v>
+      </c>
+      <c r="AB99">
+        <v>1.5</v>
+      </c>
+      <c r="AC99">
+        <v>4.45</v>
+      </c>
+      <c r="AD99">
+        <v>1.14</v>
+      </c>
+      <c r="AE99">
+        <v>1.01</v>
+      </c>
+      <c r="AF99">
         <v>2.15</v>
       </c>
-      <c r="V99">
-        <v>1.73</v>
-      </c>
-      <c r="W99">
-        <v>1.17</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.1</v>
-      </c>
-      <c r="Z99">
-        <v>5.75</v>
-      </c>
-      <c r="AA99">
-        <v>1.39</v>
-      </c>
-      <c r="AB99">
-        <v>2.72</v>
-      </c>
-      <c r="AC99">
-        <v>2.17</v>
-      </c>
-      <c r="AD99">
-        <v>1.81</v>
-      </c>
-      <c r="AE99">
-        <v>1.27</v>
-      </c>
-      <c r="AF99">
-        <v>1.58</v>
-      </c>
       <c r="AG99">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>2.96</v>
+        <v>1.84</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.78</v>
+        <v>1.19</v>
       </c>
       <c r="O100">
-        <v>3.24</v>
+        <v>6.15</v>
       </c>
       <c r="P100">
-        <v>4.38</v>
+        <v>13</v>
       </c>
       <c r="Q100">
+        <v>1.62</v>
+      </c>
+      <c r="R100">
+        <v>2.51</v>
+      </c>
+      <c r="S100">
+        <v>1.25</v>
+      </c>
+      <c r="T100">
+        <v>3.6</v>
+      </c>
+      <c r="U100">
+        <v>2.4</v>
+      </c>
+      <c r="V100">
+        <v>1.44</v>
+      </c>
+      <c r="W100">
+        <v>1.11</v>
+      </c>
+      <c r="X100">
+        <v>1.03</v>
+      </c>
+      <c r="Y100">
+        <v>1.19</v>
+      </c>
+      <c r="Z100">
+        <v>3.68</v>
+      </c>
+      <c r="AA100">
+        <v>1.65</v>
+      </c>
+      <c r="AB100">
+        <v>2.24</v>
+      </c>
+      <c r="AC100">
         <v>2.5</v>
       </c>
-      <c r="R100">
-        <v>2</v>
-      </c>
-      <c r="S100">
+      <c r="AD100">
         <v>1.45</v>
       </c>
-      <c r="T100">
-        <v>2.55</v>
-      </c>
-      <c r="U100">
-        <v>3.6</v>
-      </c>
-      <c r="V100">
-        <v>1.25</v>
-      </c>
-      <c r="W100">
-        <v>1.03</v>
-      </c>
-      <c r="X100">
-        <v>1.04</v>
-      </c>
-      <c r="Y100">
-        <v>1.42</v>
-      </c>
-      <c r="Z100">
-        <v>2.49</v>
-      </c>
-      <c r="AA100">
-        <v>2.36</v>
-      </c>
-      <c r="AB100">
-        <v>1.52</v>
-      </c>
-      <c r="AC100">
-        <v>4.4</v>
-      </c>
-      <c r="AD100">
+      <c r="AE100">
         <v>1.14</v>
       </c>
-      <c r="AE100">
-        <v>1.01</v>
-      </c>
       <c r="AF100">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="AG100">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK100">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.46</v>
+      </c>
+      <c r="O101">
+        <v>4.2</v>
+      </c>
+      <c r="P101">
+        <v>6.56</v>
+      </c>
+      <c r="Q101">
+        <v>2.04</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>1.47</v>
+      </c>
+      <c r="T101">
+        <v>2.41</v>
+      </c>
+      <c r="U101">
+        <v>3.2</v>
+      </c>
+      <c r="V101">
+        <v>1.3</v>
+      </c>
+      <c r="W101">
+        <v>1.07</v>
+      </c>
+      <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.36</v>
+      </c>
+      <c r="Z101">
+        <v>3.1</v>
+      </c>
+      <c r="AA101">
+        <v>2.2</v>
+      </c>
+      <c r="AB101">
+        <v>1.65</v>
+      </c>
+      <c r="AC101">
+        <v>4.05</v>
+      </c>
+      <c r="AD101">
+        <v>1.28</v>
+      </c>
+      <c r="AE101">
+        <v>1.08</v>
+      </c>
+      <c r="AF101">
+        <v>2.15</v>
+      </c>
+      <c r="AG101">
+        <v>1.52</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
         <v>1.19</v>
       </c>
-      <c r="O101">
-        <v>6.15</v>
-      </c>
-      <c r="P101">
-        <v>13</v>
-      </c>
-      <c r="Q101">
-        <v>1.62</v>
-      </c>
-      <c r="R101">
-        <v>2.51</v>
-      </c>
-      <c r="S101">
-        <v>1.25</v>
-      </c>
-      <c r="T101">
-        <v>3.6</v>
-      </c>
-      <c r="U101">
-        <v>2.4</v>
-      </c>
-      <c r="V101">
-        <v>1.44</v>
-      </c>
-      <c r="W101">
-        <v>1.11</v>
-      </c>
-      <c r="X101">
-        <v>1.03</v>
-      </c>
-      <c r="Y101">
-        <v>1.19</v>
-      </c>
-      <c r="Z101">
-        <v>3.68</v>
-      </c>
-      <c r="AA101">
-        <v>1.65</v>
-      </c>
-      <c r="AB101">
-        <v>2.24</v>
-      </c>
-      <c r="AC101">
-        <v>2.5</v>
-      </c>
-      <c r="AD101">
-        <v>1.45</v>
-      </c>
-      <c r="AE101">
-        <v>1.14</v>
-      </c>
-      <c r="AF101">
-        <v>2.46</v>
-      </c>
-      <c r="AG101">
-        <v>1.48</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.07</v>
-      </c>
       <c r="AK101">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="O102">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="P102">
-        <v>7</v>
+        <v>3.83</v>
       </c>
       <c r="Q102">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-04 17:00:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.73</v>
+        <v>2.21</v>
       </c>
       <c r="O103">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P103">
-        <v>3.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="O104">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P104">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S104">
         <v>0</v>
@@ -17282,10 +17282,10 @@
         <v>0</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W104">
         <v>0</v>
@@ -17294,31 +17294,31 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE104">
         <v>0</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,65 +17424,65 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="O105">
-        <v>3.45</v>
+        <v>2.71</v>
       </c>
       <c r="P105">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q105">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R105">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U105">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="V105">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y105">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="Z105">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="AA105">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="AB105">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="AC105">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
+        <v>2.31</v>
+      </c>
+      <c r="AG105">
         <v>1.55</v>
       </c>
-      <c r="AG105">
-        <v>2.25</v>
-      </c>
       <c r="AH105" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AK105">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.88</v>
+        <v>2.96</v>
       </c>
       <c r="O106">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>4.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q106">
-        <v>2.54</v>
+        <v>3.66</v>
       </c>
       <c r="R106">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="U106">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="V106">
+        <v>1.44</v>
+      </c>
+      <c r="W106">
+        <v>1.1</v>
+      </c>
+      <c r="X106">
+        <v>1.01</v>
+      </c>
+      <c r="Y106">
         <v>1.22</v>
       </c>
-      <c r="W106">
-        <v>1.03</v>
-      </c>
-      <c r="X106">
-        <v>1.09</v>
-      </c>
-      <c r="Y106">
-        <v>1.54</v>
-      </c>
       <c r="Z106">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AC106">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD106">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AE106">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
-        <v>2.31</v>
+        <v>1.64</v>
       </c>
       <c r="AG106">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.96</v>
+        <v>1.64</v>
       </c>
       <c r="O107">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P107">
-        <v>2.09</v>
+        <v>4.75</v>
       </c>
       <c r="Q107">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T107">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U107">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+      <c r="Z107">
+        <v>0</v>
+      </c>
+      <c r="AA107">
+        <v>2.7</v>
+      </c>
+      <c r="AB107">
         <v>1.44</v>
       </c>
-      <c r="W107">
-        <v>1.1</v>
-      </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
-        <v>1.22</v>
-      </c>
-      <c r="Z107">
-        <v>3.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.8</v>
-      </c>
-      <c r="AB107">
-        <v>1.9</v>
-      </c>
       <c r="AC107">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.64</v>
+        <v>2.56</v>
       </c>
       <c r="O108">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>4.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA108">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB108">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="O109">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q109">
-        <v>2.84</v>
+        <v>3.44</v>
       </c>
       <c r="R109">
+        <v>1.89</v>
+      </c>
+      <c r="S109">
+        <v>1.51</v>
+      </c>
+      <c r="T109">
+        <v>2.44</v>
+      </c>
+      <c r="U109">
+        <v>3.25</v>
+      </c>
+      <c r="V109">
+        <v>1.25</v>
+      </c>
+      <c r="W109">
+        <v>1</v>
+      </c>
+      <c r="X109">
+        <v>1.05</v>
+      </c>
+      <c r="Y109">
+        <v>1.43</v>
+      </c>
+      <c r="Z109">
+        <v>2.9</v>
+      </c>
+      <c r="AA109">
         <v>2.2</v>
       </c>
-      <c r="S109">
+      <c r="AB109">
+        <v>1.51</v>
+      </c>
+      <c r="AC109">
+        <v>4.91</v>
+      </c>
+      <c r="AD109">
+        <v>1.13</v>
+      </c>
+      <c r="AE109">
+        <v>1.01</v>
+      </c>
+      <c r="AF109">
+        <v>1.95</v>
+      </c>
+      <c r="AG109">
+        <v>1.73</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.35</v>
       </c>
-      <c r="T109">
-        <v>3.26</v>
-      </c>
-      <c r="U109">
-        <v>2.63</v>
-      </c>
-      <c r="V109">
+      <c r="AK109">
         <v>1.47</v>
-      </c>
-      <c r="W109">
-        <v>1.08</v>
-      </c>
-      <c r="X109">
-        <v>1.02</v>
-      </c>
-      <c r="Y109">
-        <v>1.23</v>
-      </c>
-      <c r="Z109">
-        <v>4.04</v>
-      </c>
-      <c r="AA109">
-        <v>1.77</v>
-      </c>
-      <c r="AB109">
-        <v>2.05</v>
-      </c>
-      <c r="AC109">
-        <v>2.76</v>
-      </c>
-      <c r="AD109">
-        <v>1.4</v>
-      </c>
-      <c r="AE109">
-        <v>1.15</v>
-      </c>
-      <c r="AF109">
-        <v>1.6</v>
-      </c>
-      <c r="AG109">
-        <v>2.2</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.24</v>
-      </c>
-      <c r="AK109">
-        <v>1.39</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S110">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T110">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V110">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z110">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB110">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113">
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-04 21:00:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="O115">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P116">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q116">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="R116">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S116">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T116">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U116">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="V116">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
+        <v>1.35</v>
+      </c>
+      <c r="Z116">
+        <v>2.84</v>
+      </c>
+      <c r="AA116">
+        <v>2.13</v>
+      </c>
+      <c r="AB116">
+        <v>1.67</v>
+      </c>
+      <c r="AC116">
+        <v>3.74</v>
+      </c>
+      <c r="AD116">
+        <v>1.21</v>
+      </c>
+      <c r="AE116">
+        <v>1.04</v>
+      </c>
+      <c r="AF116">
+        <v>1.87</v>
+      </c>
+      <c r="AG116">
+        <v>1.82</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
         <v>1.29</v>
       </c>
-      <c r="Z116">
-        <v>3.2</v>
-      </c>
-      <c r="AA116">
-        <v>1.94</v>
-      </c>
-      <c r="AB116">
-        <v>1.8</v>
-      </c>
-      <c r="AC116">
-        <v>3.28</v>
-      </c>
-      <c r="AD116">
+      <c r="AK116">
         <v>1.25</v>
-      </c>
-      <c r="AE116">
-        <v>1.06</v>
-      </c>
-      <c r="AF116">
-        <v>1.78</v>
-      </c>
-      <c r="AG116">
-        <v>1.91</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.25</v>
-      </c>
-      <c r="AK116">
-        <v>1.67</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q117">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="R117">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T117">
+        <v>2.9</v>
+      </c>
+      <c r="U117">
         <v>2.5</v>
       </c>
-      <c r="U117">
-        <v>3.02</v>
-      </c>
       <c r="V117">
+        <v>1.42</v>
+      </c>
+      <c r="W117">
+        <v>1.06</v>
+      </c>
+      <c r="X117">
+        <v>1.01</v>
+      </c>
+      <c r="Y117">
+        <v>1.22</v>
+      </c>
+      <c r="Z117">
+        <v>3.5</v>
+      </c>
+      <c r="AA117">
+        <v>1.89</v>
+      </c>
+      <c r="AB117">
+        <v>1.98</v>
+      </c>
+      <c r="AC117">
+        <v>2.92</v>
+      </c>
+      <c r="AD117">
         <v>1.31</v>
       </c>
-      <c r="W117">
-        <v>1.04</v>
-      </c>
-      <c r="X117">
-        <v>1.03</v>
-      </c>
-      <c r="Y117">
-        <v>1.35</v>
-      </c>
-      <c r="Z117">
-        <v>2.84</v>
-      </c>
-      <c r="AA117">
-        <v>2.13</v>
-      </c>
-      <c r="AB117">
-        <v>1.67</v>
-      </c>
-      <c r="AC117">
-        <v>3.74</v>
-      </c>
-      <c r="AD117">
+      <c r="AE117">
+        <v>1.08</v>
+      </c>
+      <c r="AF117">
+        <v>1.9</v>
+      </c>
+      <c r="AG117">
+        <v>1.83</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
         <v>1.21</v>
       </c>
-      <c r="AE117">
-        <v>1.04</v>
-      </c>
-      <c r="AF117">
-        <v>1.87</v>
-      </c>
-      <c r="AG117">
-        <v>1.82</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.29</v>
-      </c>
       <c r="AK117">
-        <v>1.25</v>
+        <v>2.43</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G118">
@@ -19552,55 +19552,55 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R118">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S118">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T118">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U118">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W118">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z118">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA118">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB118">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC118">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD118">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE118">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF118">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG118">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK118">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-04 21:30:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G119">
@@ -19715,55 +19715,55 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19809,169 +19809,6 @@
         <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>3.68</v>
-      </c>
-      <c r="R120">
-        <v>2.35</v>
-      </c>
-      <c r="S120">
-        <v>1.25</v>
-      </c>
-      <c r="T120">
-        <v>3.6</v>
-      </c>
-      <c r="U120">
-        <v>2.26</v>
-      </c>
-      <c r="V120">
-        <v>1.55</v>
-      </c>
-      <c r="W120">
-        <v>1.13</v>
-      </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.11</v>
-      </c>
-      <c r="Z120">
-        <v>4.45</v>
-      </c>
-      <c r="AA120">
-        <v>1.56</v>
-      </c>
-      <c r="AB120">
-        <v>2.25</v>
-      </c>
-      <c r="AC120">
-        <v>2.35</v>
-      </c>
-      <c r="AD120">
-        <v>1.47</v>
-      </c>
-      <c r="AE120">
-        <v>1.16</v>
-      </c>
-      <c r="AF120">
-        <v>1.49</v>
-      </c>
-      <c r="AG120">
-        <v>2.28</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.2</v>
-      </c>
-      <c r="AK120">
-        <v>1.26</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q37">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="R37">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>4.88</v>
       </c>
       <c r="AA37">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q38">
+        <v>2.02</v>
+      </c>
+      <c r="R38">
+        <v>2.39</v>
+      </c>
+      <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>3.42</v>
+      </c>
+      <c r="U38">
+        <v>2.11</v>
+      </c>
+      <c r="V38">
+        <v>1.68</v>
+      </c>
+      <c r="W38">
+        <v>1.15</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.1</v>
+      </c>
+      <c r="Z38">
+        <v>5.75</v>
+      </c>
+      <c r="AA38">
+        <v>1.39</v>
+      </c>
+      <c r="AB38">
         <v>2.7</v>
       </c>
-      <c r="R38">
-        <v>2.24</v>
-      </c>
-      <c r="S38">
-        <v>1.28</v>
-      </c>
-      <c r="T38">
-        <v>3.3</v>
-      </c>
-      <c r="U38">
-        <v>2.34</v>
-      </c>
-      <c r="V38">
-        <v>1.53</v>
-      </c>
-      <c r="W38">
-        <v>1.09</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.14</v>
-      </c>
-      <c r="Z38">
-        <v>4.88</v>
-      </c>
-      <c r="AA38">
-        <v>1.61</v>
-      </c>
-      <c r="AB38">
-        <v>2.27</v>
-      </c>
       <c r="AC38">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7161,13 +7161,13 @@
         <v>4</v>
       </c>
       <c r="P42">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="Q42">
         <v>1.95</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S42">
         <v>1.25</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA42">
         <v>1.6</v>
@@ -7209,7 +7209,7 @@
         <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG42">
         <v>2.15</v>
@@ -7321,10 +7321,10 @@
         <v>2.3</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q43">
         <v>2.89</v>
@@ -7354,7 +7354,7 @@
         <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>5.71</v>
+        <v>5.77</v>
       </c>
       <c r="AA43">
         <v>1.5</v>
@@ -7366,7 +7366,7 @@
         <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE43">
         <v>1.23</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G48">
@@ -8139,58 +8139,58 @@
         <v>2.75</v>
       </c>
       <c r="P48">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q48">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="R48">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="S48">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="T48">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U48">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="V48">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y48">
         <v>1.6</v>
       </c>
       <c r="Z48">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AA48">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB48">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD48">
         <v>1.08</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF48">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AG48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK48">
         <v>1.4</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G49">
@@ -8302,58 +8302,58 @@
         <v>2.75</v>
       </c>
       <c r="P49">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q49">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="R49">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="S49">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="T49">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U49">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="V49">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y49">
         <v>1.6</v>
       </c>
       <c r="Z49">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AA49">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB49">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC49">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD49">
         <v>1.08</v>
       </c>
       <c r="AE49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AG49">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
         <v>1.4</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.36</v>
+        <v>7.25</v>
       </c>
       <c r="O54">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P54">
-        <v>7.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q54">
-        <v>1.68</v>
+        <v>5.8</v>
       </c>
       <c r="R54">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA54">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB54">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AC54">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD54">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE54">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="AK54">
-        <v>3.09</v>
+        <v>1.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>1.36</v>
+      </c>
+      <c r="O55">
+        <v>5.25</v>
+      </c>
+      <c r="P55">
         <v>7.25</v>
       </c>
-      <c r="O55">
-        <v>5.3</v>
-      </c>
-      <c r="P55">
-        <v>1.27</v>
-      </c>
       <c r="Q55">
-        <v>5.8</v>
+        <v>1.68</v>
       </c>
       <c r="R55">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U55">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V55">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W55">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA55">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AB55">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD55">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE55">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF55">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG55">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK55">
-        <v>1.05</v>
+        <v>3.09</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
+        <v>2.2</v>
+      </c>
+      <c r="S58">
+        <v>1.3</v>
+      </c>
+      <c r="T58">
+        <v>3.2</v>
+      </c>
+      <c r="U58">
+        <v>2.53</v>
+      </c>
+      <c r="V58">
+        <v>1.44</v>
+      </c>
+      <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="Y58">
+        <v>1.21</v>
+      </c>
+      <c r="Z58">
+        <v>3.9</v>
+      </c>
+      <c r="AA58">
+        <v>1.7</v>
+      </c>
+      <c r="AB58">
+        <v>1.95</v>
+      </c>
+      <c r="AC58">
+        <v>3.17</v>
+      </c>
+      <c r="AD58">
+        <v>1.36</v>
+      </c>
+      <c r="AE58">
+        <v>1.12</v>
+      </c>
+      <c r="AF58">
+        <v>1.66</v>
+      </c>
+      <c r="AG58">
+        <v>1.95</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.2</v>
+      </c>
+      <c r="AK58">
         <v>2.1</v>
-      </c>
-      <c r="S58">
-        <v>1.36</v>
-      </c>
-      <c r="T58">
-        <v>2.62</v>
-      </c>
-      <c r="U58">
-        <v>2.8</v>
-      </c>
-      <c r="V58">
-        <v>1.35</v>
-      </c>
-      <c r="W58">
-        <v>1.05</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.28</v>
-      </c>
-      <c r="Z58">
-        <v>3.08</v>
-      </c>
-      <c r="AA58">
-        <v>2.03</v>
-      </c>
-      <c r="AB58">
-        <v>1.69</v>
-      </c>
-      <c r="AC58">
-        <v>4.25</v>
-      </c>
-      <c r="AD58">
-        <v>1.24</v>
-      </c>
-      <c r="AE58">
-        <v>1.05</v>
-      </c>
-      <c r="AF58">
-        <v>1.77</v>
-      </c>
-      <c r="AG58">
-        <v>1.75</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.52</v>
-      </c>
-      <c r="AK58">
-        <v>1.35</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q59">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U59">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
+        <v>1.05</v>
+      </c>
+      <c r="X59">
         <v>1.02</v>
       </c>
-      <c r="X59">
-        <v>1.09</v>
-      </c>
       <c r="Y59">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA59">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB59">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AC59">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AD59">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AK59">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P60">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q60">
-        <v>2.27</v>
+        <v>3.44</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S60">
+        <v>1.44</v>
+      </c>
+      <c r="T60">
+        <v>2.59</v>
+      </c>
+      <c r="U60">
+        <v>3.2</v>
+      </c>
+      <c r="V60">
         <v>1.3</v>
       </c>
-      <c r="T60">
-        <v>3.2</v>
-      </c>
-      <c r="U60">
-        <v>2.53</v>
-      </c>
-      <c r="V60">
-        <v>1.44</v>
-      </c>
       <c r="W60">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y60">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z60">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB60">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC60">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD60">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE60">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK60">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q70">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="U70">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="V70">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z70">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB70">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC70">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD70">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF70">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AK70">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="O71">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P71">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q71">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S71">
         <v>1.2</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="V71">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
         <v>1.18</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD71">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="O72">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P72">
+        <v>2.45</v>
+      </c>
+      <c r="Q72">
+        <v>2.95</v>
+      </c>
+      <c r="R72">
+        <v>2.17</v>
+      </c>
+      <c r="S72">
+        <v>1.3</v>
+      </c>
+      <c r="T72">
+        <v>3.16</v>
+      </c>
+      <c r="U72">
+        <v>2.32</v>
+      </c>
+      <c r="V72">
+        <v>1.53</v>
+      </c>
+      <c r="W72">
+        <v>1.09</v>
+      </c>
+      <c r="X72">
+        <v>1.01</v>
+      </c>
+      <c r="Y72">
+        <v>1.2</v>
+      </c>
+      <c r="Z72">
+        <v>4.4</v>
+      </c>
+      <c r="AA72">
+        <v>1.6</v>
+      </c>
+      <c r="AB72">
+        <v>2.3</v>
+      </c>
+      <c r="AC72">
+        <v>2.43</v>
+      </c>
+      <c r="AD72">
+        <v>1.53</v>
+      </c>
+      <c r="AE72">
+        <v>1.21</v>
+      </c>
+      <c r="AF72">
+        <v>1.45</v>
+      </c>
+      <c r="AG72">
         <v>2.5</v>
       </c>
-      <c r="Q72">
-        <v>2.75</v>
-      </c>
-      <c r="R72">
-        <v>2.36</v>
-      </c>
-      <c r="S72">
-        <v>1.2</v>
-      </c>
-      <c r="T72">
-        <v>3.9</v>
-      </c>
-      <c r="U72">
-        <v>1.95</v>
-      </c>
-      <c r="V72">
-        <v>1.77</v>
-      </c>
-      <c r="W72">
-        <v>1.18</v>
-      </c>
-      <c r="X72">
-        <v>1.03</v>
-      </c>
-      <c r="Y72">
-        <v>1.07</v>
-      </c>
-      <c r="Z72">
-        <v>5.95</v>
-      </c>
-      <c r="AA72">
-        <v>1.44</v>
-      </c>
-      <c r="AB72">
-        <v>2.7</v>
-      </c>
-      <c r="AC72">
-        <v>2.05</v>
-      </c>
-      <c r="AD72">
-        <v>1.76</v>
-      </c>
-      <c r="AE72">
-        <v>1.26</v>
-      </c>
-      <c r="AF72">
-        <v>1.36</v>
-      </c>
-      <c r="AG72">
-        <v>2.8</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O79">
         <v>2.8</v>
@@ -13201,13 +13201,13 @@
         <v>1.79</v>
       </c>
       <c r="S79">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T79">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U79">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V79">
         <v>1.2</v>
@@ -13228,7 +13228,7 @@
         <v>2.74</v>
       </c>
       <c r="AB79">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC79">
         <v>5.45</v>
@@ -18737,16 +18737,16 @@
         <v>1.91</v>
       </c>
       <c r="Q113">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="R113">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="S113">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T113">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U113">
         <v>3.02</v>
@@ -18758,34 +18758,34 @@
         <v>1.04</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z113">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AA113">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB113">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC113">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="AD113">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
         <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG113">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="O27">
         <v>3.5</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
         <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V28">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.17</v>
+      </c>
+      <c r="Z28">
+        <v>3.98</v>
+      </c>
+      <c r="AA28">
+        <v>1.7</v>
+      </c>
+      <c r="AB28">
+        <v>2.1</v>
+      </c>
+      <c r="AC28">
+        <v>2.88</v>
+      </c>
+      <c r="AD28">
+        <v>1.4</v>
+      </c>
+      <c r="AE28">
         <v>1.13</v>
       </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.12</v>
-      </c>
-      <c r="Z28">
-        <v>4.75</v>
-      </c>
-      <c r="AA28">
-        <v>1.5</v>
-      </c>
-      <c r="AB28">
-        <v>2.38</v>
-      </c>
-      <c r="AC28">
-        <v>2.22</v>
-      </c>
-      <c r="AD28">
+      <c r="AF28">
         <v>1.61</v>
       </c>
-      <c r="AE28">
-        <v>1.21</v>
-      </c>
-      <c r="AF28">
-        <v>1.43</v>
-      </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>3.44</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S58">
+        <v>1.44</v>
+      </c>
+      <c r="T58">
+        <v>2.59</v>
+      </c>
+      <c r="U58">
+        <v>3.2</v>
+      </c>
+      <c r="V58">
         <v>1.3</v>
       </c>
-      <c r="T58">
-        <v>3.2</v>
-      </c>
-      <c r="U58">
-        <v>2.53</v>
-      </c>
-      <c r="V58">
-        <v>1.44</v>
-      </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y58">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC58">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="AD58">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,80 +10089,80 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O60">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q60">
-        <v>3.44</v>
+        <v>2.27</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S60">
+        <v>1.3</v>
+      </c>
+      <c r="T60">
+        <v>3.2</v>
+      </c>
+      <c r="U60">
+        <v>2.53</v>
+      </c>
+      <c r="V60">
         <v>1.44</v>
       </c>
-      <c r="T60">
-        <v>2.59</v>
-      </c>
-      <c r="U60">
-        <v>3.2</v>
-      </c>
-      <c r="V60">
-        <v>1.3</v>
-      </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z60">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA60">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC60">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD60">
+        <v>1.36</v>
+      </c>
+      <c r="AE60">
+        <v>1.12</v>
+      </c>
+      <c r="AF60">
+        <v>1.66</v>
+      </c>
+      <c r="AG60">
+        <v>1.95</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.2</v>
       </c>
-      <c r="AE60">
-        <v>1.06</v>
-      </c>
-      <c r="AF60">
-        <v>1.91</v>
-      </c>
-      <c r="AG60">
-        <v>1.73</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.33</v>
-      </c>
       <c r="AK60">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="O70">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P70">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R70">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S70">
         <v>1.2</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U70">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="V70">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W70">
         <v>1.18</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AC70">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD70">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE70">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF70">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AK70">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P71">
+        <v>2.45</v>
+      </c>
+      <c r="Q71">
+        <v>2.95</v>
+      </c>
+      <c r="R71">
+        <v>2.17</v>
+      </c>
+      <c r="S71">
+        <v>1.3</v>
+      </c>
+      <c r="T71">
+        <v>3.16</v>
+      </c>
+      <c r="U71">
+        <v>2.32</v>
+      </c>
+      <c r="V71">
+        <v>1.53</v>
+      </c>
+      <c r="W71">
+        <v>1.09</v>
+      </c>
+      <c r="X71">
+        <v>1.01</v>
+      </c>
+      <c r="Y71">
+        <v>1.2</v>
+      </c>
+      <c r="Z71">
+        <v>4.4</v>
+      </c>
+      <c r="AA71">
+        <v>1.6</v>
+      </c>
+      <c r="AB71">
+        <v>2.3</v>
+      </c>
+      <c r="AC71">
+        <v>2.43</v>
+      </c>
+      <c r="AD71">
+        <v>1.53</v>
+      </c>
+      <c r="AE71">
+        <v>1.21</v>
+      </c>
+      <c r="AF71">
+        <v>1.45</v>
+      </c>
+      <c r="AG71">
         <v>2.5</v>
       </c>
-      <c r="Q71">
-        <v>2.75</v>
-      </c>
-      <c r="R71">
-        <v>2.36</v>
-      </c>
-      <c r="S71">
-        <v>1.2</v>
-      </c>
-      <c r="T71">
-        <v>3.9</v>
-      </c>
-      <c r="U71">
-        <v>1.95</v>
-      </c>
-      <c r="V71">
-        <v>1.77</v>
-      </c>
-      <c r="W71">
-        <v>1.18</v>
-      </c>
-      <c r="X71">
-        <v>1.03</v>
-      </c>
-      <c r="Y71">
-        <v>1.07</v>
-      </c>
-      <c r="Z71">
-        <v>5.95</v>
-      </c>
-      <c r="AA71">
-        <v>1.44</v>
-      </c>
-      <c r="AB71">
-        <v>2.7</v>
-      </c>
-      <c r="AC71">
-        <v>2.05</v>
-      </c>
-      <c r="AD71">
-        <v>1.76</v>
-      </c>
-      <c r="AE71">
-        <v>1.26</v>
-      </c>
-      <c r="AF71">
-        <v>1.36</v>
-      </c>
-      <c r="AG71">
-        <v>2.8</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AK71">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O72">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P72">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q72">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R72">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="V72">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W72">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA72">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AC72">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD72">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF72">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AG72">
         <v>2.5</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AK72">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL72">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O13">
-        <v>7.55</v>
+        <v>6.9</v>
       </c>
       <c r="P13">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Q13">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="S13">
         <v>1.18</v>
@@ -2449,7 +2449,7 @@
         <v>3.88</v>
       </c>
       <c r="U13">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="V13">
         <v>1.67</v>
@@ -2461,7 +2461,7 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
         <v>5.5</v>
@@ -2482,7 +2482,7 @@
         <v>1.27</v>
       </c>
       <c r="AF13">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AG13">
         <v>1.75</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AK13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
         <v>2.86</v>
@@ -2630,10 +2630,10 @@
         <v>2.44</v>
       </c>
       <c r="AA14">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AB14">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC14">
         <v>5.25</v>
@@ -2645,7 +2645,7 @@
         <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AG14">
         <v>1.65</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
         <v>1.25</v>
@@ -3104,10 +3104,10 @@
         <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3116,28 +3116,28 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC17">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O20">
         <v>3.4</v>
@@ -3581,7 +3581,7 @@
         <v>2.84</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.29</v>
@@ -3596,16 +3596,16 @@
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
         <v>1.62</v>
@@ -3617,7 +3617,7 @@
         <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O22">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="Q22">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R22">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
         <v>2.47</v>
@@ -3925,25 +3925,25 @@
         <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.95</v>
+        <v>4.07</v>
       </c>
       <c r="AA22">
         <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC22">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD22">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
         <v>1.16</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
         <v>3</v>
       </c>
       <c r="P23">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S23">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T23">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U23">
         <v>3.42</v>
@@ -4097,10 +4097,10 @@
         <v>2.6</v>
       </c>
       <c r="AA23">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AB23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC23">
         <v>4.5</v>
@@ -4131,7 +4131,7 @@
         <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,16 +4224,16 @@
         <v>1.26</v>
       </c>
       <c r="O24">
-        <v>5.15</v>
+        <v>4.8</v>
       </c>
       <c r="P24">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R24">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4260,10 +4260,10 @@
         <v>5.4</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC24">
         <v>2.21</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK24">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S25">
         <v>1.25</v>
@@ -4411,10 +4411,10 @@
         <v>1.56</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.13</v>
@@ -4426,22 +4426,22 @@
         <v>1.53</v>
       </c>
       <c r="AB25">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD25">
         <v>1.53</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
         <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="O26">
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q26">
         <v>3.25</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S26">
         <v>1.36</v>
@@ -4568,13 +4568,13 @@
         <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4589,7 +4589,7 @@
         <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC26">
         <v>2.97</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q27">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S27">
         <v>1.24</v>
@@ -4734,13 +4734,13 @@
         <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
         <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.12</v>
@@ -4752,13 +4752,13 @@
         <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC27">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
         <v>1.21</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
         <v>1.65</v>
@@ -4885,25 +4885,25 @@
         <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="S28">
         <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U28">
         <v>2.47</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
         <v>1.17</v>
@@ -4912,22 +4912,22 @@
         <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
         <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
         <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
         <v>2.15</v>
@@ -5036,37 +5036,37 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O29">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>2.98</v>
+        <v>2.42</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="R29">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y29">
         <v>1.4</v>
@@ -5075,25 +5075,25 @@
         <v>2.75</v>
       </c>
       <c r="AA29">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB29">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK29">
         <v>1.44</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>3.37</v>
+        <v>2.71</v>
       </c>
       <c r="Q30">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
         <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
+        <v>1.85</v>
+      </c>
+      <c r="AB30">
         <v>1.9</v>
       </c>
-      <c r="AB30">
-        <v>1.88</v>
-      </c>
       <c r="AC30">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q31">
         <v>3.19</v>
@@ -5395,16 +5395,16 @@
         <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z31">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AA31">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB31">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC31">
         <v>3.92</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="O32">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="P32">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q32">
         <v>1.7</v>
       </c>
       <c r="R32">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="S32">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T32">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U32">
         <v>1.95</v>
@@ -5552,7 +5552,7 @@
         <v>1.77</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5561,13 +5561,13 @@
         <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AA32">
         <v>1.38</v>
       </c>
       <c r="AB32">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC32">
         <v>1.99</v>
@@ -5576,13 +5576,13 @@
         <v>1.73</v>
       </c>
       <c r="AE32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF32">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q37">
+        <v>2.02</v>
+      </c>
+      <c r="R37">
+        <v>2.39</v>
+      </c>
+      <c r="S37">
+        <v>1.25</v>
+      </c>
+      <c r="T37">
+        <v>3.42</v>
+      </c>
+      <c r="U37">
+        <v>2.11</v>
+      </c>
+      <c r="V37">
+        <v>1.68</v>
+      </c>
+      <c r="W37">
+        <v>1.15</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.1</v>
+      </c>
+      <c r="Z37">
+        <v>5.75</v>
+      </c>
+      <c r="AA37">
+        <v>1.39</v>
+      </c>
+      <c r="AB37">
         <v>2.7</v>
       </c>
-      <c r="R37">
-        <v>2.24</v>
-      </c>
-      <c r="S37">
-        <v>1.28</v>
-      </c>
-      <c r="T37">
-        <v>3.3</v>
-      </c>
-      <c r="U37">
-        <v>2.34</v>
-      </c>
-      <c r="V37">
-        <v>1.53</v>
-      </c>
-      <c r="W37">
-        <v>1.09</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.14</v>
-      </c>
-      <c r="Z37">
-        <v>4.88</v>
-      </c>
-      <c r="AA37">
-        <v>1.61</v>
-      </c>
-      <c r="AB37">
-        <v>2.27</v>
-      </c>
       <c r="AC37">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG37">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q38">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="R38">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="V38">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>5.75</v>
+        <v>4.88</v>
       </c>
       <c r="AA38">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AD38">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="O39">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="P39">
         <v>1.65</v>
       </c>
       <c r="Q39">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="R39">
         <v>2.43</v>
@@ -6684,31 +6684,31 @@
         <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U39">
         <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W39">
         <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>4.85</v>
+        <v>5.48</v>
       </c>
       <c r="AA39">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
         <v>2.3</v>
@@ -6720,10 +6720,10 @@
         <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P44">
         <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="R44">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T44">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
         <v>2.25</v>
@@ -7520,10 +7520,10 @@
         <v>4.5</v>
       </c>
       <c r="AA44">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC44">
         <v>2.38</v>
@@ -7538,7 +7538,7 @@
         <v>1.45</v>
       </c>
       <c r="AG44">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O47">
         <v>3.6</v>
       </c>
       <c r="P47">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="Q47">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R47">
         <v>2.33</v>
@@ -7988,16 +7988,16 @@
         <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="U47">
         <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8009,16 +8009,16 @@
         <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AC47">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AD47">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8027,7 +8027,7 @@
         <v>1.48</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P48">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q48">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="R48">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S48">
         <v>1.65</v>
       </c>
       <c r="T48">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U48">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="V48">
         <v>1.18</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X48">
         <v>1.1</v>
@@ -8178,7 +8178,7 @@
         <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AD48">
         <v>1.08</v>
@@ -8187,7 +8187,7 @@
         <v>1.01</v>
       </c>
       <c r="AF48">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AG48">
         <v>1.57</v>
@@ -8206,7 +8206,7 @@
         <v>1.37</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,40 +8299,40 @@
         <v>2.5</v>
       </c>
       <c r="O49">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P49">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R49">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S49">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T49">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U49">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="V49">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
         <v>1.08</v>
       </c>
       <c r="Y49">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z49">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AA49">
         <v>2.62</v>
@@ -8341,19 +8341,19 @@
         <v>1.44</v>
       </c>
       <c r="AC49">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD49">
         <v>1.08</v>
       </c>
       <c r="AE49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG49">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O51">
         <v>4</v>
       </c>
       <c r="P51">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R51">
         <v>2.51</v>
@@ -8640,16 +8640,16 @@
         <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U51">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="V51">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,22 +8658,22 @@
         <v>1.06</v>
       </c>
       <c r="Z51">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AA51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB51">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AC51">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AD51">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
         <v>1.41</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK51">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="O52">
         <v>3.5</v>
@@ -8794,10 +8794,10 @@
         <v>2.1</v>
       </c>
       <c r="Q52">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8818,22 +8818,22 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z52">
         <v>5.25</v>
       </c>
       <c r="AA52">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AC52">
         <v>2.2</v>
       </c>
       <c r="AD52">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE52">
         <v>1.21</v>
@@ -8858,7 +8858,7 @@
         <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,31 +8951,31 @@
         <v>2.26</v>
       </c>
       <c r="O53">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="P53">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="Q53">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T53">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U53">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -8984,10 +8984,10 @@
         <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="AA53">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
         <v>2</v>
@@ -8996,16 +8996,16 @@
         <v>2.95</v>
       </c>
       <c r="AD53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
         <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
+        <v>1.37</v>
+      </c>
+      <c r="O54">
+        <v>5</v>
+      </c>
+      <c r="P54">
         <v>7.25</v>
       </c>
-      <c r="O54">
-        <v>5.3</v>
-      </c>
-      <c r="P54">
-        <v>1.27</v>
-      </c>
       <c r="Q54">
-        <v>5.8</v>
+        <v>1.68</v>
       </c>
       <c r="R54">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="S54">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U54">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="V54">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="AA54">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AC54">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>3.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK54">
-        <v>1.05</v>
+        <v>3.18</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="O55">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="P55">
-        <v>7.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q55">
-        <v>1.68</v>
+        <v>5.75</v>
       </c>
       <c r="R55">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="S55">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T55">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="U55">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V55">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>5.15</v>
+        <v>6.1</v>
       </c>
       <c r="AA55">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB55">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AC55">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AD55">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AE55">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AF55">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>3.09</v>
+        <v>1.07</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>3.44</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
+        <v>1.3</v>
+      </c>
+      <c r="T58">
+        <v>3.2</v>
+      </c>
+      <c r="U58">
+        <v>2.53</v>
+      </c>
+      <c r="V58">
         <v>1.44</v>
       </c>
-      <c r="T58">
-        <v>2.59</v>
-      </c>
-      <c r="U58">
-        <v>3.2</v>
-      </c>
-      <c r="V58">
-        <v>1.3</v>
-      </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA58">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AB58">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC58">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD58">
+        <v>1.36</v>
+      </c>
+      <c r="AE58">
+        <v>1.12</v>
+      </c>
+      <c r="AF58">
+        <v>1.66</v>
+      </c>
+      <c r="AG58">
+        <v>1.95</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.2</v>
       </c>
-      <c r="AE58">
-        <v>1.06</v>
-      </c>
-      <c r="AF58">
-        <v>1.91</v>
-      </c>
-      <c r="AG58">
-        <v>1.73</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.33</v>
-      </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q59">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R59">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U59">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V59">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y59">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z59">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA59">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AB59">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AC59">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG59">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q60">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U60">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W60">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB60">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AC60">
-        <v>3.17</v>
+        <v>4.25</v>
       </c>
       <c r="AD60">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE60">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AK60">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10907,16 +10907,16 @@
         <v>1.85</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P65">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q65">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="R65">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S65">
         <v>1.23</v>
@@ -10925,7 +10925,7 @@
         <v>3.58</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V65">
         <v>1.69</v>
@@ -10943,25 +10943,25 @@
         <v>5.1</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB65">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AC65">
         <v>2.15</v>
       </c>
       <c r="AD65">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE65">
         <v>1.29</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK65">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O67">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P67">
-        <v>6.07</v>
+        <v>5.25</v>
       </c>
       <c r="Q67">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R67">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="S67">
         <v>1.15</v>
@@ -11251,10 +11251,10 @@
         <v>4.8</v>
       </c>
       <c r="U67">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V67">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W67">
         <v>1.23</v>
@@ -11266,28 +11266,28 @@
         <v>1.04</v>
       </c>
       <c r="Z67">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="AA67">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB67">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AC67">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AD67">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AE67">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF67">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG67">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.12</v>
       </c>
       <c r="AK67">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O68">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P68">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Q68">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R68">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S68">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
         <v>2.15</v>
@@ -11426,31 +11426,31 @@
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="AA68">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB68">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AC68">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AD68">
         <v>1.62</v>
       </c>
       <c r="AE68">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF68">
         <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11574,16 +11574,16 @@
         <v>1.14</v>
       </c>
       <c r="T69">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U69">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="V69">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="W69">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,7 +11592,7 @@
         <v>1.05</v>
       </c>
       <c r="Z69">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA69">
         <v>1.24</v>
@@ -11601,19 +11601,19 @@
         <v>3.34</v>
       </c>
       <c r="AC69">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD69">
         <v>2.1</v>
       </c>
       <c r="AE69">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF69">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG69">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.15</v>
       </c>
       <c r="AK69">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.75</v>
+      </c>
+      <c r="O70">
+        <v>3.5</v>
+      </c>
+      <c r="P70">
+        <v>2.15</v>
+      </c>
+      <c r="Q70">
+        <v>3</v>
+      </c>
+      <c r="R70">
         <v>2.29</v>
       </c>
-      <c r="O70">
-        <v>3.65</v>
-      </c>
-      <c r="P70">
-        <v>2.5</v>
-      </c>
-      <c r="Q70">
-        <v>2.75</v>
-      </c>
-      <c r="R70">
-        <v>2.36</v>
-      </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="U70">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="V70">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z70">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA70">
         <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AC70">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AD70">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF70">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG70">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
         <v>2.45</v>
       </c>
       <c r="Q71">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T71">
-        <v>3.16</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="V71">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W71">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>4.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA71">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB71">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AD71">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AK71">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P72">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q72">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R72">
+        <v>2.27</v>
+      </c>
+      <c r="S72">
+        <v>1.3</v>
+      </c>
+      <c r="T72">
+        <v>3.16</v>
+      </c>
+      <c r="U72">
         <v>2.32</v>
       </c>
-      <c r="S72">
+      <c r="V72">
+        <v>1.57</v>
+      </c>
+      <c r="W72">
+        <v>1.11</v>
+      </c>
+      <c r="X72">
+        <v>1.03</v>
+      </c>
+      <c r="Y72">
         <v>1.2</v>
       </c>
-      <c r="T72">
-        <v>4</v>
-      </c>
-      <c r="U72">
-        <v>2.07</v>
-      </c>
-      <c r="V72">
-        <v>1.65</v>
-      </c>
-      <c r="W72">
-        <v>1.18</v>
-      </c>
-      <c r="X72">
-        <v>1.02</v>
-      </c>
-      <c r="Y72">
-        <v>1.14</v>
-      </c>
       <c r="Z72">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AA72">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB72">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="AC72">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AD72">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AE72">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AF72">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG72">
         <v>2.5</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12380,13 +12380,13 @@
         <v>3.15</v>
       </c>
       <c r="Q74">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="R74">
         <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T74">
         <v>3.58</v>
@@ -12395,10 +12395,10 @@
         <v>2.1</v>
       </c>
       <c r="V74">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X74">
         <v>1.02</v>
@@ -12410,13 +12410,13 @@
         <v>5.25</v>
       </c>
       <c r="AA74">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB74">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AC74">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD74">
         <v>1.68</v>
@@ -12425,10 +12425,10 @@
         <v>1.26</v>
       </c>
       <c r="AF74">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q75">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R75">
         <v>2.5</v>
@@ -12561,31 +12561,31 @@
         <v>1.56</v>
       </c>
       <c r="W75">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z75">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA75">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC75">
         <v>2.34</v>
       </c>
       <c r="AD75">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE75">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
         <v>1.5</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O76">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q76">
         <v>2.76</v>
@@ -12712,22 +12712,22 @@
         <v>1.97</v>
       </c>
       <c r="S76">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T76">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="U76">
         <v>3</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
         <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
@@ -12739,13 +12739,13 @@
         <v>2.1</v>
       </c>
       <c r="AB76">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC76">
         <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE76">
         <v>1.03</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK76">
         <v>1.67</v>
@@ -13349,28 +13349,28 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="O80">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P80">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q80">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R80">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S80">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T80">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U80">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V80">
         <v>1.36</v>
@@ -13382,47 +13382,47 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA80">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB80">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC80">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="AD80">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
         <v>1.06</v>
       </c>
       <c r="AF80">
+        <v>1.85</v>
+      </c>
+      <c r="AG80">
+        <v>1.79</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
+        <v>1.34</v>
+      </c>
+      <c r="AK80">
         <v>1.8</v>
-      </c>
-      <c r="AG80">
-        <v>1.8</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.22</v>
-      </c>
-      <c r="AK80">
-        <v>1.9</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O82">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P82">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q82">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R82">
         <v>2.7</v>
@@ -13693,7 +13693,7 @@
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U82">
         <v>1.91</v>
@@ -13702,7 +13702,7 @@
         <v>1.83</v>
       </c>
       <c r="W82">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13711,28 +13711,28 @@
         <v>1.07</v>
       </c>
       <c r="Z82">
-        <v>5.9</v>
+        <v>6.05</v>
       </c>
       <c r="AA82">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AC82">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD82">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AE82">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AF82">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O88">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q88">
         <v>5</v>
@@ -14671,43 +14671,43 @@
         <v>1.55</v>
       </c>
       <c r="T88">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="U88">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V88">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W88">
         <v>1.03</v>
       </c>
       <c r="X88">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y88">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z88">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AA88">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB88">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC88">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG88">
         <v>1.7</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
         <v>1.18</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="O89">
         <v>6</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P91">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q91">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="R91">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S91">
         <v>1.25</v>
@@ -15163,22 +15163,22 @@
         <v>3.6</v>
       </c>
       <c r="U91">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="V91">
         <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA91">
         <v>1.52</v>
@@ -15187,13 +15187,13 @@
         <v>2.24</v>
       </c>
       <c r="AC91">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="AD91">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE91">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF91">
         <v>1.52</v>
@@ -15215,7 +15215,7 @@
         <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O100">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q100">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="R100">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S100">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="T100">
         <v>2.31</v>
       </c>
       <c r="U100">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="V100">
         <v>1.25</v>
       </c>
       <c r="W100">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X100">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y100">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z100">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AA100">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB100">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC100">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AD100">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE100">
         <v>1.01</v>
       </c>
       <c r="AF100">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG100">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O102">
         <v>4.2</v>
@@ -16950,37 +16950,37 @@
         <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="T102">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="W102">
         <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y102">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z102">
         <v>3.1</v>
       </c>
       <c r="AA102">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AB102">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD102">
         <v>1.28</v>
@@ -16992,7 +16992,7 @@
         <v>2.15</v>
       </c>
       <c r="AG102">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>3.85</v>
+        <v>4.66</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AD4">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.92</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
+        <v>1.06</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.22</v>
+      </c>
+      <c r="Z5">
+        <v>4.1</v>
+      </c>
+      <c r="AA5">
+        <v>1.73</v>
+      </c>
+      <c r="AB5">
+        <v>2.03</v>
+      </c>
+      <c r="AC5">
+        <v>2.88</v>
+      </c>
+      <c r="AD5">
+        <v>1.4</v>
+      </c>
+      <c r="AE5">
         <v>1.11</v>
       </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.14</v>
-      </c>
-      <c r="Z5">
-        <v>4.4</v>
-      </c>
-      <c r="AA5">
-        <v>1.57</v>
-      </c>
-      <c r="AB5">
-        <v>2.3</v>
-      </c>
-      <c r="AC5">
-        <v>2.45</v>
-      </c>
-      <c r="AD5">
-        <v>1.5</v>
-      </c>
-      <c r="AE5">
-        <v>1.17</v>
-      </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="AK5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>3.08</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>1.93</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>4.58</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,10 +3901,10 @@
         <v>3.46</v>
       </c>
       <c r="P22">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
         <v>2.15</v>
@@ -3922,34 +3922,34 @@
         <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="AA22">
         <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
         <v>1.16</v>
       </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG22">
         <v>2.2</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4064,58 +4064,58 @@
         <v>3</v>
       </c>
       <c r="P23">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R23">
         <v>1.82</v>
       </c>
       <c r="S23">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="U23">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
         <v>1.07</v>
       </c>
       <c r="Y23">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z23">
         <v>2.6</v>
       </c>
       <c r="AA23">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AB23">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC23">
         <v>4.5</v>
       </c>
       <c r="AD23">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG23">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V27">
+        <v>1.44</v>
+      </c>
+      <c r="W27">
+        <v>1.06</v>
+      </c>
+      <c r="X27">
+        <v>1.04</v>
+      </c>
+      <c r="Y27">
+        <v>1.17</v>
+      </c>
+      <c r="Z27">
+        <v>3.98</v>
+      </c>
+      <c r="AA27">
+        <v>1.72</v>
+      </c>
+      <c r="AB27">
+        <v>2.07</v>
+      </c>
+      <c r="AC27">
+        <v>2.88</v>
+      </c>
+      <c r="AD27">
+        <v>1.36</v>
+      </c>
+      <c r="AE27">
+        <v>1.13</v>
+      </c>
+      <c r="AF27">
         <v>1.62</v>
       </c>
-      <c r="W27">
-        <v>1.13</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.12</v>
-      </c>
-      <c r="Z27">
-        <v>4.75</v>
-      </c>
-      <c r="AA27">
-        <v>1.5</v>
-      </c>
-      <c r="AB27">
-        <v>2.5</v>
-      </c>
-      <c r="AC27">
-        <v>2.19</v>
-      </c>
-      <c r="AD27">
-        <v>1.59</v>
-      </c>
-      <c r="AE27">
-        <v>1.21</v>
-      </c>
-      <c r="AF27">
-        <v>1.43</v>
-      </c>
       <c r="AG27">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R28">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA28">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AB28">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5854,22 +5854,22 @@
         <v>5.66</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
         <v>1.5</v>
       </c>
       <c r="Q34">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="R34">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S34">
         <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="U34">
         <v>3.05</v>
@@ -5890,16 +5890,16 @@
         <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB34">
         <v>1.67</v>
       </c>
       <c r="AC34">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
         <v>1.12</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>2.2</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q36">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T36">
         <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V36">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6210,25 +6210,25 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA36">
         <v>1.65</v>
       </c>
       <c r="AB36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD36">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
         <v>1.55</v>
@@ -6250,7 +6250,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q37">
         <v>2.02</v>
@@ -6361,43 +6361,43 @@
         <v>3.42</v>
       </c>
       <c r="U37">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
         <v>1.15</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA37">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
         <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD37">
         <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
         <v>1.44</v>
       </c>
       <c r="AG37">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R38">
         <v>2.24</v>
@@ -6536,16 +6536,16 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.88</v>
+        <v>4.4</v>
       </c>
       <c r="AA38">
         <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC38">
         <v>2.55</v>
@@ -6554,7 +6554,7 @@
         <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
         <v>1.5</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O40">
         <v>4.4</v>
       </c>
       <c r="P40">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>2.02</v>
       </c>
       <c r="R40">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
         <v>1.33</v>
@@ -6850,7 +6850,7 @@
         <v>3.3</v>
       </c>
       <c r="U40">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
         <v>1.53</v>
@@ -6859,28 +6859,28 @@
         <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB40">
         <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
         <v>1.76</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="Q42">
-        <v>1.95</v>
+        <v>2.89</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T42">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="U42">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V42">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="Z42">
-        <v>4.7</v>
+        <v>5.35</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB42">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC42">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AD42">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="Q43">
-        <v>2.89</v>
+        <v>1.93</v>
       </c>
       <c r="R43">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="U43">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>5.77</v>
+        <v>4.8</v>
       </c>
       <c r="AA43">
+        <v>1.6</v>
+      </c>
+      <c r="AB43">
+        <v>2.38</v>
+      </c>
+      <c r="AC43">
+        <v>2.39</v>
+      </c>
+      <c r="AD43">
         <v>1.5</v>
       </c>
-      <c r="AB43">
-        <v>2.6</v>
-      </c>
-      <c r="AC43">
+      <c r="AE43">
+        <v>1.17</v>
+      </c>
+      <c r="AF43">
+        <v>1.62</v>
+      </c>
+      <c r="AG43">
         <v>2.2</v>
       </c>
-      <c r="AD43">
-        <v>1.68</v>
-      </c>
-      <c r="AE43">
-        <v>1.23</v>
-      </c>
-      <c r="AF43">
-        <v>1.38</v>
-      </c>
-      <c r="AG43">
-        <v>2.81</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="N45">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O45">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="P45">
         <v>1.27</v>
@@ -7656,22 +7656,22 @@
         <v>7.5</v>
       </c>
       <c r="R45">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T45">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="U45">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="V45">
         <v>1.71</v>
       </c>
       <c r="W45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7689,19 +7689,19 @@
         <v>3.04</v>
       </c>
       <c r="AC45">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD45">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE45">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
         <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
+        <v>1.13</v>
+      </c>
+      <c r="AK45">
         <v>1.05</v>
-      </c>
-      <c r="AK45">
-        <v>1.06</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,16 +7810,16 @@
         <v>2.1</v>
       </c>
       <c r="O46">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="Q46">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="R46">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S46">
         <v>1.21</v>
@@ -7834,7 +7834,7 @@
         <v>1.65</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,10 +7843,10 @@
         <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>5.77</v>
+        <v>5.45</v>
       </c>
       <c r="AA46">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB46">
         <v>2.54</v>
@@ -7861,10 +7861,10 @@
         <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="P47">
-        <v>3.84</v>
+        <v>3.33</v>
       </c>
       <c r="Q47">
         <v>2.34</v>
       </c>
       <c r="R47">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S47">
         <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="U47">
         <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8012,13 +8012,13 @@
         <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD47">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8027,7 +8027,7 @@
         <v>1.48</v>
       </c>
       <c r="AG47">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
         <v>1.93</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O48">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P48">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="R48">
         <v>1.74</v>
       </c>
       <c r="S48">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="T48">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U48">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V48">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W48">
         <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y48">
+        <v>1.62</v>
+      </c>
+      <c r="Z48">
+        <v>2.29</v>
+      </c>
+      <c r="AA48">
+        <v>2.62</v>
+      </c>
+      <c r="AB48">
+        <v>1.44</v>
+      </c>
+      <c r="AC48">
+        <v>5.45</v>
+      </c>
+      <c r="AD48">
+        <v>1.09</v>
+      </c>
+      <c r="AE48">
+        <v>1.04</v>
+      </c>
+      <c r="AF48">
+        <v>2.15</v>
+      </c>
+      <c r="AG48">
         <v>1.6</v>
       </c>
-      <c r="Z48">
-        <v>2.19</v>
-      </c>
-      <c r="AA48">
-        <v>3</v>
-      </c>
-      <c r="AB48">
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.36</v>
       </c>
-      <c r="AC48">
-        <v>6.5</v>
-      </c>
-      <c r="AD48">
-        <v>1.08</v>
-      </c>
-      <c r="AE48">
-        <v>1.01</v>
-      </c>
-      <c r="AF48">
-        <v>2.23</v>
-      </c>
-      <c r="AG48">
-        <v>1.57</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.37</v>
-      </c>
       <c r="AK48">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="O49">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P49">
+        <v>2.63</v>
+      </c>
+      <c r="Q49">
+        <v>3.46</v>
+      </c>
+      <c r="R49">
+        <v>1.85</v>
+      </c>
+      <c r="S49">
+        <v>1.63</v>
+      </c>
+      <c r="T49">
+        <v>2.1</v>
+      </c>
+      <c r="U49">
+        <v>3.88</v>
+      </c>
+      <c r="V49">
+        <v>1.22</v>
+      </c>
+      <c r="W49">
+        <v>1.02</v>
+      </c>
+      <c r="X49">
+        <v>1.1</v>
+      </c>
+      <c r="Y49">
+        <v>1.6</v>
+      </c>
+      <c r="Z49">
+        <v>2.25</v>
+      </c>
+      <c r="AA49">
         <v>3</v>
       </c>
-      <c r="Q49">
-        <v>3.3</v>
-      </c>
-      <c r="R49">
-        <v>1.83</v>
-      </c>
-      <c r="S49">
-        <v>1.6</v>
-      </c>
-      <c r="T49">
-        <v>2.15</v>
-      </c>
-      <c r="U49">
-        <v>3.8</v>
-      </c>
-      <c r="V49">
-        <v>1.2</v>
-      </c>
-      <c r="W49">
+      <c r="AB49">
+        <v>1.36</v>
+      </c>
+      <c r="AC49">
+        <v>7</v>
+      </c>
+      <c r="AD49">
+        <v>1.07</v>
+      </c>
+      <c r="AE49">
         <v>1.01</v>
       </c>
-      <c r="X49">
-        <v>1.08</v>
-      </c>
-      <c r="Y49">
-        <v>1.62</v>
-      </c>
-      <c r="Z49">
-        <v>2.29</v>
-      </c>
-      <c r="AA49">
-        <v>2.62</v>
-      </c>
-      <c r="AB49">
-        <v>1.44</v>
-      </c>
-      <c r="AC49">
-        <v>5.45</v>
-      </c>
-      <c r="AD49">
-        <v>1.08</v>
-      </c>
-      <c r="AE49">
-        <v>1.02</v>
-      </c>
       <c r="AF49">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG49">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK49">
         <v>1.39</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.37</v>
+        <v>7.5</v>
       </c>
       <c r="O54">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P54">
-        <v>7.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q54">
-        <v>1.68</v>
+        <v>5.75</v>
       </c>
       <c r="R54">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U54">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="V54">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>5.75</v>
+        <v>6.31</v>
       </c>
       <c r="AA54">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB54">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AC54">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AD54">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE54">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK54">
-        <v>3.18</v>
+        <v>1.07</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>7.5</v>
+        <v>1.37</v>
       </c>
       <c r="O55">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="P55">
-        <v>1.27</v>
+        <v>7.25</v>
       </c>
       <c r="Q55">
-        <v>5.75</v>
+        <v>1.67</v>
       </c>
       <c r="R55">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="S55">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V55">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W55">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
+        <v>1.1</v>
+      </c>
+      <c r="Z55">
+        <v>5.2</v>
+      </c>
+      <c r="AA55">
+        <v>1.44</v>
+      </c>
+      <c r="AB55">
+        <v>2.7</v>
+      </c>
+      <c r="AC55">
+        <v>2.1</v>
+      </c>
+      <c r="AD55">
+        <v>1.68</v>
+      </c>
+      <c r="AE55">
+        <v>1.28</v>
+      </c>
+      <c r="AF55">
+        <v>1.67</v>
+      </c>
+      <c r="AG55">
+        <v>1.98</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.06</v>
       </c>
-      <c r="Z55">
-        <v>6.1</v>
-      </c>
-      <c r="AA55">
-        <v>1.33</v>
-      </c>
-      <c r="AB55">
-        <v>2.83</v>
-      </c>
-      <c r="AC55">
-        <v>1.94</v>
-      </c>
-      <c r="AD55">
-        <v>1.81</v>
-      </c>
-      <c r="AE55">
-        <v>1.34</v>
-      </c>
-      <c r="AF55">
-        <v>1.62</v>
-      </c>
-      <c r="AG55">
-        <v>2.18</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.13</v>
-      </c>
       <c r="AK55">
-        <v>1.07</v>
+        <v>2.79</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,40 +9437,40 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O56">
         <v>3.05</v>
       </c>
       <c r="P56">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="R56">
         <v>2</v>
       </c>
       <c r="S56">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T56">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U56">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V56">
         <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z56">
         <v>2.94</v>
@@ -9479,7 +9479,7 @@
         <v>2.05</v>
       </c>
       <c r="AB56">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC56">
         <v>3.38</v>
@@ -9510,7 +9510,7 @@
         <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P57">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q57">
         <v>2.77</v>
       </c>
       <c r="R57">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="U57">
         <v>2.89</v>
@@ -9627,22 +9627,22 @@
         <v>1.36</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA57">
         <v>2.1</v>
       </c>
       <c r="AB57">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC57">
         <v>3.38</v>
@@ -9673,7 +9673,7 @@
         <v>1.28</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q58">
-        <v>2.27</v>
+        <v>3.23</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U58">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="AA58">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB58">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AC58">
-        <v>3.17</v>
+        <v>3.82</v>
       </c>
       <c r="AD58">
+        <v>1.24</v>
+      </c>
+      <c r="AE58">
+        <v>1.05</v>
+      </c>
+      <c r="AF58">
+        <v>1.77</v>
+      </c>
+      <c r="AG58">
+        <v>1.97</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.36</v>
       </c>
-      <c r="AE58">
-        <v>1.12</v>
-      </c>
-      <c r="AF58">
-        <v>1.66</v>
-      </c>
-      <c r="AG58">
-        <v>1.95</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.2</v>
-      </c>
       <c r="AK58">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P59">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q59">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="R59">
         <v>2</v>
@@ -9968,7 +9968,7 @@
         <v>2.3</v>
       </c>
       <c r="AB59">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
         <v>4.33</v>
@@ -9977,7 +9977,7 @@
         <v>1.2</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
         <v>1.91</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="O60">
+        <v>3.92</v>
+      </c>
+      <c r="P60">
+        <v>4.25</v>
+      </c>
+      <c r="Q60">
+        <v>2.29</v>
+      </c>
+      <c r="R60">
+        <v>2.2</v>
+      </c>
+      <c r="S60">
+        <v>1.37</v>
+      </c>
+      <c r="T60">
         <v>3.1</v>
       </c>
-      <c r="P60">
-        <v>2.37</v>
-      </c>
-      <c r="Q60">
-        <v>3.6</v>
-      </c>
-      <c r="R60">
-        <v>2.1</v>
-      </c>
-      <c r="S60">
-        <v>1.36</v>
-      </c>
-      <c r="T60">
-        <v>2.62</v>
-      </c>
       <c r="U60">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V60">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y60">
         <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>3.08</v>
+        <v>3.63</v>
       </c>
       <c r="AA60">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AB60">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AC60">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD60">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE60">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AG60">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>1.35</v>
+        <v>2.09</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="O61">
         <v>3.7</v>
@@ -10264,52 +10264,52 @@
         <v>2.38</v>
       </c>
       <c r="R61">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="U61">
         <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>3.83</v>
+        <v>4.04</v>
       </c>
       <c r="AA61">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB61">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC61">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="AD61">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
         <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10587,19 +10587,19 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="R63">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T63">
         <v>2.7</v>
       </c>
       <c r="U63">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="V63">
         <v>1.37</v>
@@ -10617,25 +10617,25 @@
         <v>3.14</v>
       </c>
       <c r="AA63">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB63">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC63">
         <v>3.14</v>
       </c>
       <c r="AD63">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE63">
         <v>1.07</v>
       </c>
       <c r="AF63">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG63">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10744,58 +10744,58 @@
         <v>1.59</v>
       </c>
       <c r="O64">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="Q64">
         <v>1.99</v>
       </c>
       <c r="R64">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S64">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U64">
         <v>2.4</v>
       </c>
       <c r="V64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W64">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA64">
         <v>1.73</v>
       </c>
       <c r="AB64">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD64">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE64">
         <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG64">
         <v>2</v>
@@ -11106,10 +11106,10 @@
         <v>2.46</v>
       </c>
       <c r="AA66">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="AB66">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC66">
         <v>4.65</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="O67">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P67">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="Q67">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="R67">
-        <v>2.72</v>
+        <v>2.43</v>
       </c>
       <c r="S67">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="U67">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="W67">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>6.85</v>
+        <v>5.31</v>
       </c>
       <c r="AA67">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AB67">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="AC67">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="AD67">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AE67">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK67">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="O68">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P68">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Q68">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="R68">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="S68">
+        <v>1.14</v>
+      </c>
+      <c r="T68">
+        <v>4.5</v>
+      </c>
+      <c r="U68">
+        <v>1.77</v>
+      </c>
+      <c r="V68">
+        <v>2.02</v>
+      </c>
+      <c r="W68">
         <v>1.25</v>
       </c>
-      <c r="T68">
-        <v>3.55</v>
-      </c>
-      <c r="U68">
-        <v>2.15</v>
-      </c>
-      <c r="V68">
-        <v>1.62</v>
-      </c>
-      <c r="W68">
-        <v>1.13</v>
-      </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>5.31</v>
+        <v>8.5</v>
       </c>
       <c r="AA68">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AB68">
-        <v>2.58</v>
+        <v>3.34</v>
       </c>
       <c r="AC68">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="AD68">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AE68">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG68">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK68">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="S69">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U69">
+        <v>1.95</v>
+      </c>
+      <c r="V69">
         <v>1.77</v>
       </c>
-      <c r="V69">
-        <v>2.02</v>
-      </c>
       <c r="W69">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z69">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA69">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AB69">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AD69">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AE69">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AF69">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AG69">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK69">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q70">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R70">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S70">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="U70">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="V70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA70">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AC70">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AD70">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF70">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
+        <v>2.75</v>
+      </c>
+      <c r="O71">
+        <v>3.5</v>
+      </c>
+      <c r="P71">
         <v>2.15</v>
       </c>
-      <c r="O71">
-        <v>3.7</v>
-      </c>
-      <c r="P71">
-        <v>2.45</v>
-      </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S71">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T71">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="U71">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="V71">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="W71">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z71">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA71">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AC71">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AD71">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF71">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AG71">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="O72">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="P72">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q72">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="R72">
-        <v>2.27</v>
+        <v>2.72</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="T72">
-        <v>3.16</v>
+        <v>4.8</v>
       </c>
       <c r="U72">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="V72">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z72">
-        <v>4.75</v>
+        <v>6.85</v>
       </c>
       <c r="AA72">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB72">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AC72">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD72">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AE72">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AF72">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK72">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12214,13 +12214,13 @@
         <v>3.4</v>
       </c>
       <c r="P73">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q73">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
         <v>1.27</v>
@@ -12229,10 +12229,10 @@
         <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V73">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
         <v>1.12</v>
@@ -12244,7 +12244,7 @@
         <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA73">
         <v>1.6</v>
@@ -12253,10 +12253,10 @@
         <v>2.19</v>
       </c>
       <c r="AC73">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD73">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE73">
         <v>1.19</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="O74">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="Q74">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T74">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V74">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z74">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA74">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC74">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AD74">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE74">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
+        <v>1.95</v>
+      </c>
+      <c r="O75">
+        <v>3.75</v>
+      </c>
+      <c r="P75">
+        <v>3.15</v>
+      </c>
+      <c r="Q75">
+        <v>2.47</v>
+      </c>
+      <c r="R75">
+        <v>2.38</v>
+      </c>
+      <c r="S75">
+        <v>1.21</v>
+      </c>
+      <c r="T75">
+        <v>3.58</v>
+      </c>
+      <c r="U75">
+        <v>2.1</v>
+      </c>
+      <c r="V75">
+        <v>1.65</v>
+      </c>
+      <c r="W75">
+        <v>1.14</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.09</v>
+      </c>
+      <c r="Z75">
+        <v>5.25</v>
+      </c>
+      <c r="AA75">
+        <v>1.45</v>
+      </c>
+      <c r="AB75">
+        <v>2.56</v>
+      </c>
+      <c r="AC75">
+        <v>2.15</v>
+      </c>
+      <c r="AD75">
         <v>1.68</v>
       </c>
-      <c r="O75">
-        <v>3.7</v>
-      </c>
-      <c r="P75">
-        <v>4.03</v>
-      </c>
-      <c r="Q75">
-        <v>2.25</v>
-      </c>
-      <c r="R75">
-        <v>2.5</v>
-      </c>
-      <c r="S75">
-        <v>1.22</v>
-      </c>
-      <c r="T75">
-        <v>3.5</v>
-      </c>
-      <c r="U75">
-        <v>2.26</v>
-      </c>
-      <c r="V75">
-        <v>1.56</v>
-      </c>
-      <c r="W75">
-        <v>1.1</v>
-      </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.11</v>
-      </c>
-      <c r="Z75">
-        <v>4.8</v>
-      </c>
-      <c r="AA75">
-        <v>1.57</v>
-      </c>
-      <c r="AB75">
-        <v>2.35</v>
-      </c>
-      <c r="AC75">
-        <v>2.34</v>
-      </c>
-      <c r="AD75">
-        <v>1.53</v>
-      </c>
       <c r="AE75">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF75">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG75">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12860,37 +12860,37 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O77">
         <v>4.2</v>
       </c>
       <c r="P77">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Q77">
         <v>1.83</v>
       </c>
       <c r="R77">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T77">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="U77">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.18</v>
@@ -12899,25 +12899,25 @@
         <v>3.88</v>
       </c>
       <c r="AA77">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC77">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="AD77">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE77">
         <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG77">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q78">
         <v>3.25</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S78">
         <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U78">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V78">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z78">
-        <v>4.01</v>
+        <v>4.15</v>
       </c>
       <c r="AA78">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AB78">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC78">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD78">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
         <v>1.39</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q81">
         <v>2.85</v>
@@ -13527,16 +13527,16 @@
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U81">
         <v>2.39</v>
       </c>
       <c r="V81">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W81">
         <v>1.12</v>
@@ -13545,19 +13545,19 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z81">
         <v>3.8</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB81">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
@@ -13566,10 +13566,10 @@
         <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG81">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.27</v>
       </c>
       <c r="AK81">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O83">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
         <v>2.55</v>
@@ -13850,22 +13850,22 @@
         <v>3</v>
       </c>
       <c r="R83">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="S83">
+        <v>1.39</v>
+      </c>
+      <c r="T83">
+        <v>2.66</v>
+      </c>
+      <c r="U83">
+        <v>3.1</v>
+      </c>
+      <c r="V83">
         <v>1.35</v>
       </c>
-      <c r="T83">
-        <v>2.18</v>
-      </c>
-      <c r="U83">
-        <v>2.35</v>
-      </c>
-      <c r="V83">
-        <v>1.29</v>
-      </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13874,7 +13874,7 @@
         <v>1.35</v>
       </c>
       <c r="Z83">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AA83">
         <v>2.07</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O84">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P84">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q84">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R84">
         <v>2.07</v>
@@ -14019,13 +14019,13 @@
         <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U84">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V84">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
         <v>1.06</v>
@@ -14037,28 +14037,28 @@
         <v>1.27</v>
       </c>
       <c r="Z84">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="AA84">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB84">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC84">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="AD84">
         <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF84">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R85">
+        <v>2.2</v>
+      </c>
+      <c r="S85">
+        <v>1.28</v>
+      </c>
+      <c r="T85">
+        <v>3.12</v>
+      </c>
+      <c r="U85">
+        <v>2.41</v>
+      </c>
+      <c r="V85">
+        <v>1.47</v>
+      </c>
+      <c r="W85">
+        <v>1.08</v>
+      </c>
+      <c r="X85">
+        <v>1.03</v>
+      </c>
+      <c r="Y85">
+        <v>1.17</v>
+      </c>
+      <c r="Z85">
+        <v>4.05</v>
+      </c>
+      <c r="AA85">
+        <v>1.54</v>
+      </c>
+      <c r="AB85">
+        <v>2.2</v>
+      </c>
+      <c r="AC85">
         <v>2.33</v>
       </c>
-      <c r="S85">
-        <v>1.25</v>
-      </c>
-      <c r="T85">
-        <v>3.28</v>
-      </c>
-      <c r="U85">
-        <v>2.22</v>
-      </c>
-      <c r="V85">
-        <v>1.58</v>
-      </c>
-      <c r="W85">
-        <v>1.11</v>
-      </c>
-      <c r="X85">
-        <v>1.01</v>
-      </c>
-      <c r="Y85">
+      <c r="AD85">
+        <v>1.48</v>
+      </c>
+      <c r="AE85">
         <v>1.12</v>
       </c>
-      <c r="Z85">
-        <v>5.04</v>
-      </c>
-      <c r="AA85">
-        <v>1.52</v>
-      </c>
-      <c r="AB85">
-        <v>2.17</v>
-      </c>
-      <c r="AC85">
-        <v>2.28</v>
-      </c>
-      <c r="AD85">
-        <v>1.57</v>
-      </c>
-      <c r="AE85">
-        <v>1.19</v>
-      </c>
       <c r="AF85">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.9</v>
+        <v>3.43</v>
       </c>
       <c r="O86">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q86">
-        <v>3.4</v>
+        <v>4.01</v>
       </c>
       <c r="R86">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U86">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="V86">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z86">
-        <v>4.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA86">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB86">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC86">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD86">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG86">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,13 +14493,13 @@
         <v>3.9</v>
       </c>
       <c r="O87">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
         <v>1.7</v>
       </c>
       <c r="Q87">
-        <v>4.2</v>
+        <v>4.88</v>
       </c>
       <c r="R87">
         <v>2.28</v>
@@ -14508,31 +14508,31 @@
         <v>1.32</v>
       </c>
       <c r="T87">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="U87">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V87">
         <v>1.46</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
         <v>1</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z87">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="AA87">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB87">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC87">
         <v>2.74</v>
@@ -14544,7 +14544,7 @@
         <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG87">
         <v>2</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>8.94</v>
+        <v>9.07</v>
       </c>
       <c r="O89">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="P89">
         <v>1.25</v>
@@ -14979,34 +14979,34 @@
         </is>
       </c>
       <c r="N90">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O90">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P90">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q90">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S90">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="U90">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V90">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W90">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
         <v>1.02</v>
@@ -15021,22 +15021,22 @@
         <v>1.42</v>
       </c>
       <c r="AB90">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="AC90">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD90">
         <v>1.65</v>
       </c>
       <c r="AE90">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF90">
         <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="O93">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA93">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB93">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O94">
         <v>3.4</v>
       </c>
       <c r="P94">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q94">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="R94">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S94">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T94">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U94">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="V94">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W94">
         <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y94">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z94">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AA94">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC94">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF94">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG94">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK94">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.35</v>
+        <v>4.23</v>
       </c>
       <c r="O96">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="P96">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q96">
         <v>4</v>
       </c>
       <c r="R96">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S96">
         <v>1.22</v>
@@ -15993,28 +15993,28 @@
         <v>1.09</v>
       </c>
       <c r="Z96">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA96">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB96">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AC96">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="AD96">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE96">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF96">
         <v>1.48</v>
       </c>
       <c r="AG96">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O98">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="P98">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="Q98">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="R98">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S98">
         <v>1.21</v>
@@ -16304,10 +16304,10 @@
         <v>4.2</v>
       </c>
       <c r="U98">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V98">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W98">
         <v>1.21</v>
@@ -16316,13 +16316,13 @@
         <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z98">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AA98">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB98">
         <v>2.82</v>
@@ -16334,13 +16334,13 @@
         <v>1.85</v>
       </c>
       <c r="AE98">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF98">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG98">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16446,34 +16446,34 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O99">
         <v>5</v>
       </c>
       <c r="P99">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="Q99">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R99">
         <v>2.65</v>
       </c>
       <c r="S99">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T99">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U99">
         <v>2</v>
       </c>
       <c r="V99">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W99">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16488,22 +16488,22 @@
         <v>1.4</v>
       </c>
       <c r="AB99">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AC99">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD99">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AE99">
         <v>1.28</v>
       </c>
       <c r="AF99">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG99">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16775,19 +16775,19 @@
         <v>1.2</v>
       </c>
       <c r="O101">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="P101">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q101">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R101">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T101">
         <v>3.6</v>
@@ -16796,40 +16796,40 @@
         <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>3.73</v>
+        <v>4.1</v>
       </c>
       <c r="AA101">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB101">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC101">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD101">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE101">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF101">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AG101">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AK101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16956,7 +16956,7 @@
         <v>2.8</v>
       </c>
       <c r="U102">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="V102">
         <v>1.41</v>
@@ -16965,25 +16965,25 @@
         <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA102">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AB102">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AC102">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD102">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE102">
         <v>1.08</v>
@@ -16992,7 +16992,7 @@
         <v>2.15</v>
       </c>
       <c r="AG102">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,31 +17107,31 @@
         <v>3.7</v>
       </c>
       <c r="Q103">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R103">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="S103">
         <v>1.2</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U103">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V103">
         <v>1.64</v>
       </c>
       <c r="W103">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z103">
         <v>5.3</v>
@@ -17140,13 +17140,13 @@
         <v>1.41</v>
       </c>
       <c r="AB103">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC103">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD103">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE103">
         <v>1.24</v>
@@ -17171,7 +17171,7 @@
         <v>1.18</v>
       </c>
       <c r="AK103">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O104">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P105">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q105">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="R105">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="V105">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z105">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="AA105">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB105">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC105">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG105">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
         <v>1.58</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O106">
         <v>3</v>
       </c>
       <c r="P106">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="Q106">
         <v>2.55</v>
@@ -17602,10 +17602,10 @@
         <v>1.86</v>
       </c>
       <c r="S106">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T106">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U106">
         <v>3.6</v>
@@ -17614,28 +17614,28 @@
         <v>1.22</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X106">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y106">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z106">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AA106">
         <v>2.52</v>
       </c>
       <c r="AB106">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AC106">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AD106">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE106">
         <v>1.04</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK106">
         <v>1.88</v>
@@ -17750,25 +17750,25 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O107">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="Q107">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="R107">
         <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T107">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="U107">
         <v>2.63</v>
@@ -17780,7 +17780,7 @@
         <v>1.1</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
         <v>1.22</v>
@@ -17789,25 +17789,25 @@
         <v>3.5</v>
       </c>
       <c r="AA107">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB107">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC107">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="AD107">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
         <v>1.08</v>
       </c>
       <c r="AF107">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG107">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18076,16 +18076,16 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="O109">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="P109">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q109">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="R109">
         <v>2.15</v>
@@ -18094,28 +18094,28 @@
         <v>1.35</v>
       </c>
       <c r="T109">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U109">
         <v>2.5</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z109">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AA109">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
         <v>2.05</v>
@@ -18127,10 +18127,10 @@
         <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
         <v>2.2</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18245,10 +18245,10 @@
         <v>3</v>
       </c>
       <c r="P110">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q110">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R110">
         <v>1.89</v>
@@ -18257,46 +18257,46 @@
         <v>1.51</v>
       </c>
       <c r="T110">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U110">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V110">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W110">
         <v>1</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z110">
         <v>2.9</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AB110">
         <v>1.51</v>
       </c>
       <c r="AC110">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="AD110">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE110">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG110">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18405,10 +18405,10 @@
         <v>2.2</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P111">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -18441,7 +18441,7 @@
         <v>2.7</v>
       </c>
       <c r="AA111">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AB111">
         <v>1.59</v>
@@ -18565,46 +18565,46 @@
         </is>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O112">
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q112">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="R112">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S112">
         <v>1.4</v>
       </c>
       <c r="T112">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U112">
         <v>2.75</v>
       </c>
       <c r="V112">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
         <v>3.2</v>
       </c>
       <c r="AA112">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB112">
         <v>1.8</v>
@@ -18616,10 +18616,10 @@
         <v>1.25</v>
       </c>
       <c r="AE112">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG112">
         <v>1.91</v>
@@ -18638,7 +18638,7 @@
         <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O113">
         <v>3.1</v>
@@ -18737,10 +18737,10 @@
         <v>1.91</v>
       </c>
       <c r="Q113">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="R113">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S113">
         <v>1.45</v>
@@ -18767,7 +18767,7 @@
         <v>2.86</v>
       </c>
       <c r="AA113">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB113">
         <v>1.68</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18903,13 +18903,13 @@
         <v>2</v>
       </c>
       <c r="R114">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S114">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T114">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U114">
         <v>2.5</v>
@@ -18924,7 +18924,7 @@
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z114">
         <v>3.5</v>
@@ -18933,7 +18933,7 @@
         <v>1.89</v>
       </c>
       <c r="AB114">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC114">
         <v>2.92</v>
@@ -18948,7 +18948,7 @@
         <v>1.9</v>
       </c>
       <c r="AG114">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AK114">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19235,46 +19235,46 @@
         <v>1.25</v>
       </c>
       <c r="T116">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="U116">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="V116">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W116">
+        <v>1.11</v>
+      </c>
+      <c r="X116">
+        <v>1.02</v>
+      </c>
+      <c r="Y116">
         <v>1.13</v>
       </c>
-      <c r="X116">
-        <v>1.03</v>
-      </c>
-      <c r="Y116">
-        <v>1.14</v>
-      </c>
       <c r="Z116">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA116">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB116">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC116">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD116">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE116">
         <v>1.16</v>
       </c>
       <c r="AF116">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AG116">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK116">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AL116">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R27">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S27">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q28">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S28">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="U28">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="V28">
+        <v>1.44</v>
+      </c>
+      <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.17</v>
+      </c>
+      <c r="Z28">
+        <v>3.98</v>
+      </c>
+      <c r="AA28">
+        <v>1.72</v>
+      </c>
+      <c r="AB28">
+        <v>2.07</v>
+      </c>
+      <c r="AC28">
+        <v>2.88</v>
+      </c>
+      <c r="AD28">
+        <v>1.36</v>
+      </c>
+      <c r="AE28">
+        <v>1.13</v>
+      </c>
+      <c r="AF28">
         <v>1.62</v>
       </c>
-      <c r="W28">
-        <v>1.13</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.12</v>
-      </c>
-      <c r="Z28">
-        <v>4.75</v>
-      </c>
-      <c r="AA28">
-        <v>1.5</v>
-      </c>
-      <c r="AB28">
-        <v>2.5</v>
-      </c>
-      <c r="AC28">
-        <v>2.19</v>
-      </c>
-      <c r="AD28">
-        <v>1.59</v>
-      </c>
-      <c r="AE28">
-        <v>1.21</v>
-      </c>
-      <c r="AF28">
-        <v>1.43</v>
-      </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6832,19 +6832,19 @@
         <v>1.48</v>
       </c>
       <c r="O40">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q40">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
         <v>3.3</v>
@@ -6853,10 +6853,10 @@
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6868,7 +6868,7 @@
         <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB40">
         <v>2.15</v>
@@ -6880,10 +6880,10 @@
         <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG40">
         <v>2</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK40">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O48">
         <v>2.75</v>
       </c>
       <c r="P48">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="Q48">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="R48">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="S48">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="T48">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U48">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V48">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W48">
         <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z48">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AA48">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB48">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC48">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="AD48">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF48">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK48">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O49">
         <v>2.75</v>
       </c>
       <c r="P49">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="Q49">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="R49">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="S49">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="T49">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U49">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V49">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W49">
         <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y49">
+        <v>1.62</v>
+      </c>
+      <c r="Z49">
+        <v>2.29</v>
+      </c>
+      <c r="AA49">
+        <v>2.62</v>
+      </c>
+      <c r="AB49">
+        <v>1.44</v>
+      </c>
+      <c r="AC49">
+        <v>5.45</v>
+      </c>
+      <c r="AD49">
+        <v>1.09</v>
+      </c>
+      <c r="AE49">
+        <v>1.04</v>
+      </c>
+      <c r="AF49">
+        <v>2.15</v>
+      </c>
+      <c r="AG49">
         <v>1.6</v>
       </c>
-      <c r="Z49">
-        <v>2.25</v>
-      </c>
-      <c r="AA49">
-        <v>3</v>
-      </c>
-      <c r="AB49">
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.36</v>
       </c>
-      <c r="AC49">
-        <v>7</v>
-      </c>
-      <c r="AD49">
-        <v>1.07</v>
-      </c>
-      <c r="AE49">
-        <v>1.01</v>
-      </c>
-      <c r="AF49">
-        <v>2.25</v>
-      </c>
-      <c r="AG49">
-        <v>1.57</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.35</v>
-      </c>
       <c r="AK49">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
         <v>2.45</v>
       </c>
       <c r="Q69">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="R69">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S69">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>3.9</v>
+        <v>3.16</v>
       </c>
       <c r="U69">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="V69">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
         <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="AA69">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC69">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD69">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AE69">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AG69">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P70">
         <v>2.45</v>
       </c>
       <c r="Q70">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R70">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T70">
-        <v>3.16</v>
+        <v>3.9</v>
       </c>
       <c r="U70">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="V70">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X70">
         <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z70">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AB70">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="AC70">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD70">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="AE70">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AF70">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK70">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
+        <v>1.4</v>
+      </c>
+      <c r="O71">
+        <v>4.6</v>
+      </c>
+      <c r="P71">
+        <v>5.25</v>
+      </c>
+      <c r="Q71">
+        <v>1.83</v>
+      </c>
+      <c r="R71">
+        <v>2.72</v>
+      </c>
+      <c r="S71">
+        <v>1.15</v>
+      </c>
+      <c r="T71">
+        <v>4.8</v>
+      </c>
+      <c r="U71">
+        <v>1.85</v>
+      </c>
+      <c r="V71">
+        <v>1.89</v>
+      </c>
+      <c r="W71">
+        <v>1.23</v>
+      </c>
+      <c r="X71">
+        <v>1.01</v>
+      </c>
+      <c r="Y71">
+        <v>1.04</v>
+      </c>
+      <c r="Z71">
+        <v>6.85</v>
+      </c>
+      <c r="AA71">
+        <v>1.25</v>
+      </c>
+      <c r="AB71">
+        <v>3.2</v>
+      </c>
+      <c r="AC71">
+        <v>1.74</v>
+      </c>
+      <c r="AD71">
+        <v>2.04</v>
+      </c>
+      <c r="AE71">
+        <v>1.42</v>
+      </c>
+      <c r="AF71">
+        <v>1.42</v>
+      </c>
+      <c r="AG71">
+        <v>2.62</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.12</v>
+      </c>
+      <c r="AK71">
         <v>2.75</v>
-      </c>
-      <c r="O71">
-        <v>3.5</v>
-      </c>
-      <c r="P71">
-        <v>2.15</v>
-      </c>
-      <c r="Q71">
-        <v>3</v>
-      </c>
-      <c r="R71">
-        <v>2.29</v>
-      </c>
-      <c r="S71">
-        <v>1.23</v>
-      </c>
-      <c r="T71">
-        <v>3.52</v>
-      </c>
-      <c r="U71">
-        <v>2.19</v>
-      </c>
-      <c r="V71">
-        <v>1.62</v>
-      </c>
-      <c r="W71">
-        <v>1.12</v>
-      </c>
-      <c r="X71">
-        <v>1.02</v>
-      </c>
-      <c r="Y71">
-        <v>1.13</v>
-      </c>
-      <c r="Z71">
-        <v>5.25</v>
-      </c>
-      <c r="AA71">
-        <v>1.44</v>
-      </c>
-      <c r="AB71">
-        <v>2.43</v>
-      </c>
-      <c r="AC71">
-        <v>2.26</v>
-      </c>
-      <c r="AD71">
-        <v>1.63</v>
-      </c>
-      <c r="AE71">
-        <v>1.21</v>
-      </c>
-      <c r="AF71">
-        <v>1.41</v>
-      </c>
-      <c r="AG71">
-        <v>2.5</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.25</v>
-      </c>
-      <c r="AK71">
-        <v>1.39</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="O72">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
+        <v>2.15</v>
+      </c>
+      <c r="Q72">
+        <v>3</v>
+      </c>
+      <c r="R72">
+        <v>2.29</v>
+      </c>
+      <c r="S72">
+        <v>1.23</v>
+      </c>
+      <c r="T72">
+        <v>3.52</v>
+      </c>
+      <c r="U72">
+        <v>2.19</v>
+      </c>
+      <c r="V72">
+        <v>1.62</v>
+      </c>
+      <c r="W72">
+        <v>1.12</v>
+      </c>
+      <c r="X72">
+        <v>1.02</v>
+      </c>
+      <c r="Y72">
+        <v>1.13</v>
+      </c>
+      <c r="Z72">
         <v>5.25</v>
       </c>
-      <c r="Q72">
-        <v>1.83</v>
-      </c>
-      <c r="R72">
-        <v>2.72</v>
-      </c>
-      <c r="S72">
-        <v>1.15</v>
-      </c>
-      <c r="T72">
-        <v>4.8</v>
-      </c>
-      <c r="U72">
-        <v>1.85</v>
-      </c>
-      <c r="V72">
-        <v>1.89</v>
-      </c>
-      <c r="W72">
-        <v>1.23</v>
-      </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.04</v>
-      </c>
-      <c r="Z72">
-        <v>6.85</v>
-      </c>
       <c r="AA72">
+        <v>1.44</v>
+      </c>
+      <c r="AB72">
+        <v>2.43</v>
+      </c>
+      <c r="AC72">
+        <v>2.26</v>
+      </c>
+      <c r="AD72">
+        <v>1.63</v>
+      </c>
+      <c r="AE72">
+        <v>1.21</v>
+      </c>
+      <c r="AF72">
+        <v>1.41</v>
+      </c>
+      <c r="AG72">
+        <v>2.5</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.25</v>
       </c>
-      <c r="AB72">
-        <v>3.2</v>
-      </c>
-      <c r="AC72">
-        <v>1.74</v>
-      </c>
-      <c r="AD72">
-        <v>2.04</v>
-      </c>
-      <c r="AE72">
-        <v>1.42</v>
-      </c>
-      <c r="AF72">
-        <v>1.42</v>
-      </c>
-      <c r="AG72">
-        <v>2.62</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.12</v>
-      </c>
       <c r="AK72">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
+        <v>1.95</v>
+      </c>
+      <c r="O74">
+        <v>3.75</v>
+      </c>
+      <c r="P74">
+        <v>3.15</v>
+      </c>
+      <c r="Q74">
+        <v>2.47</v>
+      </c>
+      <c r="R74">
+        <v>2.38</v>
+      </c>
+      <c r="S74">
+        <v>1.21</v>
+      </c>
+      <c r="T74">
+        <v>3.58</v>
+      </c>
+      <c r="U74">
+        <v>2.1</v>
+      </c>
+      <c r="V74">
+        <v>1.65</v>
+      </c>
+      <c r="W74">
+        <v>1.14</v>
+      </c>
+      <c r="X74">
+        <v>1.02</v>
+      </c>
+      <c r="Y74">
+        <v>1.09</v>
+      </c>
+      <c r="Z74">
+        <v>5.25</v>
+      </c>
+      <c r="AA74">
+        <v>1.45</v>
+      </c>
+      <c r="AB74">
+        <v>2.56</v>
+      </c>
+      <c r="AC74">
+        <v>2.15</v>
+      </c>
+      <c r="AD74">
         <v>1.68</v>
       </c>
-      <c r="O74">
-        <v>3.7</v>
-      </c>
-      <c r="P74">
-        <v>4.03</v>
-      </c>
-      <c r="Q74">
-        <v>2.25</v>
-      </c>
-      <c r="R74">
-        <v>2.5</v>
-      </c>
-      <c r="S74">
-        <v>1.22</v>
-      </c>
-      <c r="T74">
-        <v>3.5</v>
-      </c>
-      <c r="U74">
-        <v>2.26</v>
-      </c>
-      <c r="V74">
-        <v>1.56</v>
-      </c>
-      <c r="W74">
-        <v>1.1</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>1.11</v>
-      </c>
-      <c r="Z74">
-        <v>4.8</v>
-      </c>
-      <c r="AA74">
-        <v>1.57</v>
-      </c>
-      <c r="AB74">
-        <v>2.35</v>
-      </c>
-      <c r="AC74">
-        <v>2.34</v>
-      </c>
-      <c r="AD74">
-        <v>1.53</v>
-      </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF74">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="O75">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="Q75">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T75">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U75">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V75">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W75">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z75">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA75">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC75">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AD75">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE75">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG75">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13518,7 +13518,7 @@
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q81">
         <v>2.85</v>
@@ -13527,19 +13527,19 @@
         <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T81">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U81">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V81">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W81">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13548,7 +13548,7 @@
         <v>1.18</v>
       </c>
       <c r="Z81">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA81">
         <v>1.62</v>
@@ -13563,13 +13563,13 @@
         <v>1.43</v>
       </c>
       <c r="AE81">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
         <v>1.57</v>
       </c>
       <c r="AG81">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.27</v>
       </c>
       <c r="AK81">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.9</v>
+        <v>3.43</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q85">
-        <v>3.64</v>
+        <v>4.01</v>
       </c>
       <c r="R85">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U85">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="V85">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z85">
-        <v>4.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA85">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB85">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC85">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD85">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE85">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG85">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q86">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="R86">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T86">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U86">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z86">
-        <v>5.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA86">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB86">
+        <v>2.2</v>
+      </c>
+      <c r="AC86">
         <v>2.33</v>
       </c>
-      <c r="AC86">
-        <v>2.28</v>
-      </c>
       <c r="AD86">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE86">
+        <v>1.12</v>
+      </c>
+      <c r="AF86">
+        <v>1.53</v>
+      </c>
+      <c r="AG86">
+        <v>2.29</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.22</v>
       </c>
-      <c r="AF86">
-        <v>1.45</v>
-      </c>
-      <c r="AG86">
-        <v>2.63</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.21</v>
-      </c>
       <c r="AK86">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="O98">
         <v>5.2</v>
@@ -16292,25 +16292,25 @@
         <v>1.41</v>
       </c>
       <c r="Q98">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="R98">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="S98">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T98">
         <v>4.2</v>
       </c>
       <c r="U98">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="V98">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W98">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X98">
         <v>1.04</v>
@@ -16319,28 +16319,28 @@
         <v>1.07</v>
       </c>
       <c r="Z98">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="AA98">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB98">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="AC98">
+        <v>1.94</v>
+      </c>
+      <c r="AD98">
         <v>1.93</v>
-      </c>
-      <c r="AD98">
-        <v>1.85</v>
       </c>
       <c r="AE98">
         <v>1.35</v>
       </c>
       <c r="AF98">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG98">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,31 +16446,31 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O99">
         <v>5</v>
       </c>
       <c r="P99">
-        <v>6.95</v>
+        <v>7.55</v>
       </c>
       <c r="Q99">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S99">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U99">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V99">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W99">
         <v>1.18</v>
@@ -16479,28 +16479,28 @@
         <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z99">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA99">
         <v>1.4</v>
       </c>
       <c r="AB99">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC99">
         <v>2.06</v>
       </c>
       <c r="AD99">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AE99">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF99">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG99">
         <v>2.3</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK99">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O104">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P104">
         <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA104">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB104">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O105">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
         <v>2.9</v>
       </c>
       <c r="Q105">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB105">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AC105">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O113">
         <v>3.1</v>
       </c>
       <c r="P113">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q113">
         <v>4.7</v>
@@ -18749,7 +18749,7 @@
         <v>2.47</v>
       </c>
       <c r="U113">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="V113">
         <v>1.31</v>
@@ -18761,25 +18761,25 @@
         <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z113">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AA113">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB113">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC113">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="AD113">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF113">
         <v>1.88</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU116"/>
+  <dimension ref="A1:AU115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O2">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="S4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.66</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="AK4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="R5">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="AA5">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
         <v>4</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="U8">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z8">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AA8">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC8">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AD8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kelantan</t>
+          <t>Kelantan Red Warrior</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>7.5</v>
+        <v>1.37</v>
       </c>
       <c r="O54">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="P54">
-        <v>1.27</v>
+        <v>7.25</v>
       </c>
       <c r="Q54">
-        <v>5.75</v>
+        <v>1.67</v>
       </c>
       <c r="R54">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="S54">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U54">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="V54">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W54">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>6.31</v>
+        <v>5.2</v>
       </c>
       <c r="AA54">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE54">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK54">
-        <v>1.07</v>
+        <v>2.79</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.37</v>
+        <v>7.5</v>
       </c>
       <c r="O55">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P55">
-        <v>7.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q55">
-        <v>1.67</v>
+        <v>5.75</v>
       </c>
       <c r="R55">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="S55">
+        <v>1.17</v>
+      </c>
+      <c r="T55">
+        <v>4.5</v>
+      </c>
+      <c r="U55">
+        <v>1.94</v>
+      </c>
+      <c r="V55">
+        <v>1.74</v>
+      </c>
+      <c r="W55">
         <v>1.2</v>
       </c>
-      <c r="T55">
-        <v>3.8</v>
-      </c>
-      <c r="U55">
-        <v>2.07</v>
-      </c>
-      <c r="V55">
-        <v>1.7</v>
-      </c>
-      <c r="W55">
-        <v>1.14</v>
-      </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>5.2</v>
+        <v>6.31</v>
       </c>
       <c r="AA55">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB55">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC55">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AD55">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE55">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF55">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>2.79</v>
+        <v>1.07</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>3.92</v>
       </c>
       <c r="P58">
-        <v>2.3</v>
+        <v>4.25</v>
       </c>
       <c r="Q58">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="R58">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U58">
+        <v>2.59</v>
+      </c>
+      <c r="V58">
+        <v>1.44</v>
+      </c>
+      <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="Y58">
+        <v>1.28</v>
+      </c>
+      <c r="Z58">
+        <v>3.63</v>
+      </c>
+      <c r="AA58">
+        <v>1.89</v>
+      </c>
+      <c r="AB58">
+        <v>1.94</v>
+      </c>
+      <c r="AC58">
         <v>2.8</v>
       </c>
-      <c r="V58">
-        <v>1.35</v>
-      </c>
-      <c r="W58">
-        <v>1.03</v>
-      </c>
-      <c r="X58">
-        <v>1.04</v>
-      </c>
-      <c r="Y58">
-        <v>1.35</v>
-      </c>
-      <c r="Z58">
-        <v>3.18</v>
-      </c>
-      <c r="AA58">
-        <v>2.03</v>
-      </c>
-      <c r="AB58">
-        <v>1.69</v>
-      </c>
-      <c r="AC58">
-        <v>3.82</v>
-      </c>
       <c r="AD58">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE58">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AG58">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>2.09</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O59">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q59">
-        <v>3.46</v>
+        <v>3.23</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T59">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U59">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X59">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="AA59">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB59">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC59">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD59">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,80 +10089,80 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.6</v>
+      </c>
+      <c r="O60">
+        <v>2.95</v>
+      </c>
+      <c r="P60">
+        <v>2.41</v>
+      </c>
+      <c r="Q60">
+        <v>3.46</v>
+      </c>
+      <c r="R60">
+        <v>2</v>
+      </c>
+      <c r="S60">
+        <v>1.44</v>
+      </c>
+      <c r="T60">
+        <v>2.59</v>
+      </c>
+      <c r="U60">
+        <v>3.2</v>
+      </c>
+      <c r="V60">
+        <v>1.3</v>
+      </c>
+      <c r="W60">
+        <v>1.02</v>
+      </c>
+      <c r="X60">
+        <v>1.09</v>
+      </c>
+      <c r="Y60">
+        <v>1.4</v>
+      </c>
+      <c r="Z60">
+        <v>2.88</v>
+      </c>
+      <c r="AA60">
+        <v>2.3</v>
+      </c>
+      <c r="AB60">
+        <v>1.57</v>
+      </c>
+      <c r="AC60">
+        <v>4.33</v>
+      </c>
+      <c r="AD60">
+        <v>1.2</v>
+      </c>
+      <c r="AE60">
+        <v>1.02</v>
+      </c>
+      <c r="AF60">
+        <v>1.91</v>
+      </c>
+      <c r="AG60">
         <v>1.73</v>
       </c>
-      <c r="O60">
-        <v>3.92</v>
-      </c>
-      <c r="P60">
-        <v>4.25</v>
-      </c>
-      <c r="Q60">
-        <v>2.29</v>
-      </c>
-      <c r="R60">
-        <v>2.2</v>
-      </c>
-      <c r="S60">
-        <v>1.37</v>
-      </c>
-      <c r="T60">
-        <v>3.1</v>
-      </c>
-      <c r="U60">
-        <v>2.59</v>
-      </c>
-      <c r="V60">
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.44</v>
       </c>
-      <c r="W60">
-        <v>1.07</v>
-      </c>
-      <c r="X60">
-        <v>1</v>
-      </c>
-      <c r="Y60">
-        <v>1.28</v>
-      </c>
-      <c r="Z60">
-        <v>3.63</v>
-      </c>
-      <c r="AA60">
-        <v>1.89</v>
-      </c>
-      <c r="AB60">
-        <v>1.94</v>
-      </c>
-      <c r="AC60">
-        <v>2.8</v>
-      </c>
-      <c r="AD60">
-        <v>1.36</v>
-      </c>
-      <c r="AE60">
-        <v>1.1</v>
-      </c>
-      <c r="AF60">
-        <v>1.66</v>
-      </c>
-      <c r="AG60">
-        <v>2</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.2</v>
-      </c>
       <c r="AK60">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="P69">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q69">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="R69">
-        <v>2.27</v>
+        <v>2.72</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="T69">
-        <v>3.16</v>
+        <v>4.8</v>
       </c>
       <c r="U69">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="V69">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="W69">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z69">
-        <v>4.75</v>
+        <v>6.85</v>
       </c>
       <c r="AA69">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB69">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AC69">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="AD69">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AE69">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AF69">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG69">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK69">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="O70">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
         <v>2.45</v>
       </c>
       <c r="Q70">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="R70">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S70">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.9</v>
+        <v>3.16</v>
       </c>
       <c r="U70">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="V70">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="W70">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
         <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="AA70">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC70">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD70">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AF70">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AG70">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="O71">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
+        <v>2.15</v>
+      </c>
+      <c r="Q71">
+        <v>3</v>
+      </c>
+      <c r="R71">
+        <v>2.29</v>
+      </c>
+      <c r="S71">
+        <v>1.23</v>
+      </c>
+      <c r="T71">
+        <v>3.52</v>
+      </c>
+      <c r="U71">
+        <v>2.19</v>
+      </c>
+      <c r="V71">
+        <v>1.62</v>
+      </c>
+      <c r="W71">
+        <v>1.12</v>
+      </c>
+      <c r="X71">
+        <v>1.02</v>
+      </c>
+      <c r="Y71">
+        <v>1.13</v>
+      </c>
+      <c r="Z71">
         <v>5.25</v>
       </c>
-      <c r="Q71">
-        <v>1.83</v>
-      </c>
-      <c r="R71">
-        <v>2.72</v>
-      </c>
-      <c r="S71">
-        <v>1.15</v>
-      </c>
-      <c r="T71">
-        <v>4.8</v>
-      </c>
-      <c r="U71">
-        <v>1.85</v>
-      </c>
-      <c r="V71">
-        <v>1.89</v>
-      </c>
-      <c r="W71">
-        <v>1.23</v>
-      </c>
-      <c r="X71">
-        <v>1.01</v>
-      </c>
-      <c r="Y71">
-        <v>1.04</v>
-      </c>
-      <c r="Z71">
-        <v>6.85</v>
-      </c>
       <c r="AA71">
+        <v>1.44</v>
+      </c>
+      <c r="AB71">
+        <v>2.43</v>
+      </c>
+      <c r="AC71">
+        <v>2.26</v>
+      </c>
+      <c r="AD71">
+        <v>1.63</v>
+      </c>
+      <c r="AE71">
+        <v>1.21</v>
+      </c>
+      <c r="AF71">
+        <v>1.41</v>
+      </c>
+      <c r="AG71">
+        <v>2.5</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
         <v>1.25</v>
       </c>
-      <c r="AB71">
-        <v>3.2</v>
-      </c>
-      <c r="AC71">
-        <v>1.74</v>
-      </c>
-      <c r="AD71">
-        <v>2.04</v>
-      </c>
-      <c r="AE71">
-        <v>1.42</v>
-      </c>
-      <c r="AF71">
-        <v>1.42</v>
-      </c>
-      <c r="AG71">
-        <v>2.62</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.12</v>
-      </c>
       <c r="AK71">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q72">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R72">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S72">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T72">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="U72">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="V72">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="W72">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z72">
-        <v>5.25</v>
+        <v>5.95</v>
       </c>
       <c r="AA72">
+        <v>1.36</v>
+      </c>
+      <c r="AB72">
+        <v>2.7</v>
+      </c>
+      <c r="AC72">
+        <v>1.9</v>
+      </c>
+      <c r="AD72">
+        <v>1.78</v>
+      </c>
+      <c r="AE72">
+        <v>1.26</v>
+      </c>
+      <c r="AF72">
+        <v>1.35</v>
+      </c>
+      <c r="AG72">
+        <v>2.8</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.44</v>
       </c>
-      <c r="AB72">
-        <v>2.43</v>
-      </c>
-      <c r="AC72">
-        <v>2.26</v>
-      </c>
-      <c r="AD72">
-        <v>1.63</v>
-      </c>
-      <c r="AE72">
-        <v>1.21</v>
-      </c>
-      <c r="AF72">
-        <v>1.41</v>
-      </c>
-      <c r="AG72">
-        <v>2.5</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.25</v>
-      </c>
       <c r="AK72">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="O74">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>3.15</v>
+        <v>4.03</v>
       </c>
       <c r="Q74">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T74">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V74">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z74">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA74">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC74">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AD74">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE74">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
+        <v>1.95</v>
+      </c>
+      <c r="O75">
+        <v>3.75</v>
+      </c>
+      <c r="P75">
+        <v>3.15</v>
+      </c>
+      <c r="Q75">
+        <v>2.47</v>
+      </c>
+      <c r="R75">
+        <v>2.38</v>
+      </c>
+      <c r="S75">
+        <v>1.21</v>
+      </c>
+      <c r="T75">
+        <v>3.58</v>
+      </c>
+      <c r="U75">
+        <v>2.1</v>
+      </c>
+      <c r="V75">
+        <v>1.65</v>
+      </c>
+      <c r="W75">
+        <v>1.14</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.09</v>
+      </c>
+      <c r="Z75">
+        <v>5.25</v>
+      </c>
+      <c r="AA75">
+        <v>1.45</v>
+      </c>
+      <c r="AB75">
+        <v>2.56</v>
+      </c>
+      <c r="AC75">
+        <v>2.15</v>
+      </c>
+      <c r="AD75">
         <v>1.68</v>
       </c>
-      <c r="O75">
-        <v>3.7</v>
-      </c>
-      <c r="P75">
-        <v>4.03</v>
-      </c>
-      <c r="Q75">
-        <v>2.25</v>
-      </c>
-      <c r="R75">
-        <v>2.5</v>
-      </c>
-      <c r="S75">
-        <v>1.22</v>
-      </c>
-      <c r="T75">
-        <v>3.5</v>
-      </c>
-      <c r="U75">
-        <v>2.26</v>
-      </c>
-      <c r="V75">
-        <v>1.56</v>
-      </c>
-      <c r="W75">
-        <v>1.1</v>
-      </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.11</v>
-      </c>
-      <c r="Z75">
-        <v>4.8</v>
-      </c>
-      <c r="AA75">
-        <v>1.57</v>
-      </c>
-      <c r="AB75">
-        <v>2.35</v>
-      </c>
-      <c r="AC75">
-        <v>2.34</v>
-      </c>
-      <c r="AD75">
-        <v>1.53</v>
-      </c>
       <c r="AE75">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF75">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG75">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q85">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T85">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U85">
-        <v>2.22</v>
+        <v>2.41</v>
       </c>
       <c r="V85">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA85">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB85">
+        <v>2.2</v>
+      </c>
+      <c r="AC85">
         <v>2.33</v>
       </c>
-      <c r="AC85">
-        <v>2.28</v>
-      </c>
       <c r="AD85">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE85">
+        <v>1.12</v>
+      </c>
+      <c r="AF85">
+        <v>1.53</v>
+      </c>
+      <c r="AG85">
+        <v>2.29</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.22</v>
       </c>
-      <c r="AF85">
-        <v>1.45</v>
-      </c>
-      <c r="AG85">
-        <v>2.63</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.21</v>
-      </c>
       <c r="AK85">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.9</v>
+        <v>3.43</v>
       </c>
       <c r="O86">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q86">
-        <v>3.64</v>
+        <v>4.01</v>
       </c>
       <c r="R86">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U86">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="V86">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z86">
-        <v>4.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA86">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB86">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC86">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD86">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG86">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,68 +15301,68 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,84 +15464,84 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N93">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q93">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="R93">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="T93">
-        <v>4.6</v>
+        <v>2.89</v>
       </c>
       <c r="U93">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="V93">
-        <v>1.81</v>
+        <v>1.43</v>
       </c>
       <c r="W93">
+        <v>1.06</v>
+      </c>
+      <c r="X93">
+        <v>1.04</v>
+      </c>
+      <c r="Y93">
         <v>1.24</v>
       </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.05</v>
-      </c>
       <c r="Z93">
-        <v>6.7</v>
+        <v>3.69</v>
       </c>
       <c r="AA93">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AB93">
-        <v>3.08</v>
+        <v>1.9</v>
       </c>
       <c r="AC93">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
+        <v>1.3</v>
+      </c>
+      <c r="AE93">
+        <v>1.13</v>
+      </c>
+      <c r="AF93">
+        <v>1.75</v>
+      </c>
+      <c r="AG93">
+        <v>1.97</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.26</v>
+      </c>
+      <c r="AK93">
         <v>1.93</v>
-      </c>
-      <c r="AE93">
-        <v>1.37</v>
-      </c>
-      <c r="AF93">
-        <v>1.32</v>
-      </c>
-      <c r="AG93">
-        <v>3.05</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.17</v>
-      </c>
-      <c r="AK93">
-        <v>1.92</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P94">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="Q94">
-        <v>2.41</v>
+        <v>2.85</v>
       </c>
       <c r="R94">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T94">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U94">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V94">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W94">
         <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z94">
-        <v>3.69</v>
+        <v>3.44</v>
       </c>
       <c r="AA94">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB94">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC94">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD94">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE94">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF94">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG94">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK94">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G95">
@@ -15790,68 +15790,68 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N95">
-        <v>2.29</v>
+        <v>4.23</v>
       </c>
       <c r="O95">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P95">
-        <v>2.92</v>
+        <v>1.62</v>
       </c>
       <c r="Q95">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S95">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>2.94</v>
+        <v>3.66</v>
       </c>
       <c r="U95">
-        <v>2.65</v>
+        <v>2.14</v>
       </c>
       <c r="V95">
+        <v>1.66</v>
+      </c>
+      <c r="W95">
+        <v>1.14</v>
+      </c>
+      <c r="X95">
+        <v>1.02</v>
+      </c>
+      <c r="Y95">
+        <v>1.09</v>
+      </c>
+      <c r="Z95">
+        <v>5.25</v>
+      </c>
+      <c r="AA95">
         <v>1.42</v>
       </c>
-      <c r="W95">
-        <v>1.06</v>
-      </c>
-      <c r="X95">
-        <v>1</v>
-      </c>
-      <c r="Y95">
+      <c r="AB95">
+        <v>2.51</v>
+      </c>
+      <c r="AC95">
+        <v>2.21</v>
+      </c>
+      <c r="AD95">
+        <v>1.69</v>
+      </c>
+      <c r="AE95">
         <v>1.23</v>
       </c>
-      <c r="Z95">
-        <v>3.44</v>
-      </c>
-      <c r="AA95">
-        <v>1.84</v>
-      </c>
-      <c r="AB95">
-        <v>1.93</v>
-      </c>
-      <c r="AC95">
-        <v>2.94</v>
-      </c>
-      <c r="AD95">
-        <v>1.31</v>
-      </c>
-      <c r="AE95">
-        <v>1.09</v>
-      </c>
       <c r="AF95">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AG95">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.23</v>
+        <v>2.19</v>
       </c>
       <c r="O96">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
+        <v>3.24</v>
+      </c>
+      <c r="Q96">
+        <v>3.02</v>
+      </c>
+      <c r="R96">
+        <v>2.05</v>
+      </c>
+      <c r="S96">
+        <v>1.4</v>
+      </c>
+      <c r="T96">
+        <v>2.7</v>
+      </c>
+      <c r="U96">
+        <v>3</v>
+      </c>
+      <c r="V96">
+        <v>1.35</v>
+      </c>
+      <c r="W96">
+        <v>1.07</v>
+      </c>
+      <c r="X96">
+        <v>1.07</v>
+      </c>
+      <c r="Y96">
+        <v>1.36</v>
+      </c>
+      <c r="Z96">
+        <v>2.9</v>
+      </c>
+      <c r="AA96">
+        <v>2.15</v>
+      </c>
+      <c r="AB96">
         <v>1.62</v>
       </c>
-      <c r="Q96">
-        <v>4</v>
-      </c>
-      <c r="R96">
-        <v>2.45</v>
-      </c>
-      <c r="S96">
+      <c r="AC96">
+        <v>3.8</v>
+      </c>
+      <c r="AD96">
         <v>1.22</v>
       </c>
-      <c r="T96">
-        <v>3.66</v>
-      </c>
-      <c r="U96">
-        <v>2.14</v>
-      </c>
-      <c r="V96">
-        <v>1.66</v>
-      </c>
-      <c r="W96">
-        <v>1.14</v>
-      </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.09</v>
-      </c>
-      <c r="Z96">
-        <v>5.25</v>
-      </c>
-      <c r="AA96">
-        <v>1.42</v>
-      </c>
-      <c r="AB96">
-        <v>2.51</v>
-      </c>
-      <c r="AC96">
-        <v>2.21</v>
-      </c>
-      <c r="AD96">
-        <v>1.69</v>
-      </c>
       <c r="AE96">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AG96">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK96">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.19</v>
+        <v>6.3</v>
       </c>
       <c r="O97">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="P97">
-        <v>3.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q97">
-        <v>3.02</v>
+        <v>6.05</v>
       </c>
       <c r="R97">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="S97">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="T97">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="U97">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="V97">
+        <v>1.75</v>
+      </c>
+      <c r="W97">
+        <v>1.2</v>
+      </c>
+      <c r="X97">
+        <v>1.04</v>
+      </c>
+      <c r="Y97">
+        <v>1.07</v>
+      </c>
+      <c r="Z97">
+        <v>6.15</v>
+      </c>
+      <c r="AA97">
         <v>1.35</v>
       </c>
-      <c r="W97">
-        <v>1.07</v>
-      </c>
-      <c r="X97">
-        <v>1.07</v>
-      </c>
-      <c r="Y97">
-        <v>1.36</v>
-      </c>
-      <c r="Z97">
-        <v>2.9</v>
-      </c>
-      <c r="AA97">
-        <v>2.15</v>
-      </c>
       <c r="AB97">
-        <v>1.62</v>
+        <v>2.94</v>
       </c>
       <c r="AC97">
-        <v>3.8</v>
+        <v>1.94</v>
       </c>
       <c r="AD97">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="AE97">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="AF97">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AK97">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>6.3</v>
+        <v>1.28</v>
       </c>
       <c r="O98">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>1.41</v>
+        <v>7.55</v>
       </c>
       <c r="Q98">
-        <v>6.05</v>
+        <v>1.83</v>
       </c>
       <c r="R98">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="S98">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T98">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U98">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="V98">
         <v>1.75</v>
       </c>
       <c r="W98">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z98">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AA98">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AB98">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="AC98">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AD98">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AE98">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF98">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG98">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>1.12</v>
+        <v>2.75</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-09-04 16:00:00</t>
+          <t>2026-09-04 16:05:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,81 +16446,81 @@
         </is>
       </c>
       <c r="N99">
+        <v>1.91</v>
+      </c>
+      <c r="O99">
+        <v>3</v>
+      </c>
+      <c r="P99">
+        <v>3.9</v>
+      </c>
+      <c r="Q99">
+        <v>2.56</v>
+      </c>
+      <c r="R99">
+        <v>1.9</v>
+      </c>
+      <c r="S99">
+        <v>1.54</v>
+      </c>
+      <c r="T99">
+        <v>2.31</v>
+      </c>
+      <c r="U99">
+        <v>3.34</v>
+      </c>
+      <c r="V99">
+        <v>1.25</v>
+      </c>
+      <c r="W99">
+        <v>1.01</v>
+      </c>
+      <c r="X99">
+        <v>1.06</v>
+      </c>
+      <c r="Y99">
+        <v>1.47</v>
+      </c>
+      <c r="Z99">
+        <v>2.42</v>
+      </c>
+      <c r="AA99">
+        <v>2.5</v>
+      </c>
+      <c r="AB99">
+        <v>1.49</v>
+      </c>
+      <c r="AC99">
+        <v>4.55</v>
+      </c>
+      <c r="AD99">
+        <v>1.13</v>
+      </c>
+      <c r="AE99">
+        <v>1.01</v>
+      </c>
+      <c r="AF99">
+        <v>2.14</v>
+      </c>
+      <c r="AG99">
+        <v>1.62</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.28</v>
       </c>
-      <c r="O99">
-        <v>5</v>
-      </c>
-      <c r="P99">
-        <v>7.55</v>
-      </c>
-      <c r="Q99">
-        <v>1.83</v>
-      </c>
-      <c r="R99">
-        <v>2.7</v>
-      </c>
-      <c r="S99">
-        <v>1.2</v>
-      </c>
-      <c r="T99">
-        <v>4.05</v>
-      </c>
-      <c r="U99">
-        <v>2.07</v>
-      </c>
-      <c r="V99">
+      <c r="AK99">
         <v>1.75</v>
       </c>
-      <c r="W99">
-        <v>1.18</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.08</v>
-      </c>
-      <c r="Z99">
-        <v>6.5</v>
-      </c>
-      <c r="AA99">
-        <v>1.4</v>
-      </c>
-      <c r="AB99">
-        <v>2.62</v>
-      </c>
-      <c r="AC99">
-        <v>2.06</v>
-      </c>
-      <c r="AD99">
-        <v>1.73</v>
-      </c>
-      <c r="AE99">
-        <v>1.3</v>
-      </c>
-      <c r="AF99">
-        <v>1.56</v>
-      </c>
-      <c r="AG99">
-        <v>2.3</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.06</v>
-      </c>
-      <c r="AK99">
-        <v>2.75</v>
-      </c>
       <c r="AL99">
         <v>0</v>
       </c>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-09-04 16:05:00</t>
+          <t>2026-09-04 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="O100">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="P100">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="Q100">
+        <v>1.53</v>
+      </c>
+      <c r="R100">
         <v>2.56</v>
       </c>
-      <c r="R100">
-        <v>1.9</v>
-      </c>
       <c r="S100">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>2.31</v>
+        <v>3.6</v>
       </c>
       <c r="U100">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="V100">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="W100">
+        <v>1.09</v>
+      </c>
+      <c r="X100">
         <v>1.01</v>
       </c>
-      <c r="X100">
-        <v>1.06</v>
-      </c>
       <c r="Y100">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA100">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB100">
-        <v>1.49</v>
+        <v>2.13</v>
       </c>
       <c r="AC100">
-        <v>4.55</v>
+        <v>2.47</v>
       </c>
       <c r="AD100">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AE100">
+        <v>1.15</v>
+      </c>
+      <c r="AF100">
+        <v>2.65</v>
+      </c>
+      <c r="AG100">
+        <v>1.5</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.01</v>
       </c>
-      <c r="AF100">
-        <v>2.14</v>
-      </c>
-      <c r="AG100">
-        <v>1.62</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.28</v>
-      </c>
       <c r="AK100">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,65 +16772,65 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O101">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="P101">
-        <v>16</v>
+        <v>6.56</v>
       </c>
       <c r="Q101">
+        <v>2.04</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>1.38</v>
+      </c>
+      <c r="T101">
+        <v>2.8</v>
+      </c>
+      <c r="U101">
+        <v>3.2</v>
+      </c>
+      <c r="V101">
+        <v>1.41</v>
+      </c>
+      <c r="W101">
+        <v>1.07</v>
+      </c>
+      <c r="X101">
+        <v>1.03</v>
+      </c>
+      <c r="Y101">
+        <v>1.3</v>
+      </c>
+      <c r="Z101">
+        <v>2.7</v>
+      </c>
+      <c r="AA101">
+        <v>2.25</v>
+      </c>
+      <c r="AB101">
+        <v>1.59</v>
+      </c>
+      <c r="AC101">
+        <v>4.05</v>
+      </c>
+      <c r="AD101">
+        <v>1.16</v>
+      </c>
+      <c r="AE101">
+        <v>1.08</v>
+      </c>
+      <c r="AF101">
+        <v>2.15</v>
+      </c>
+      <c r="AG101">
         <v>1.53</v>
       </c>
-      <c r="R101">
-        <v>2.56</v>
-      </c>
-      <c r="S101">
-        <v>1.32</v>
-      </c>
-      <c r="T101">
-        <v>3.6</v>
-      </c>
-      <c r="U101">
-        <v>2.4</v>
-      </c>
-      <c r="V101">
-        <v>1.48</v>
-      </c>
-      <c r="W101">
-        <v>1.09</v>
-      </c>
-      <c r="X101">
-        <v>1.01</v>
-      </c>
-      <c r="Y101">
-        <v>1.2</v>
-      </c>
-      <c r="Z101">
-        <v>4.1</v>
-      </c>
-      <c r="AA101">
-        <v>1.61</v>
-      </c>
-      <c r="AB101">
-        <v>2.13</v>
-      </c>
-      <c r="AC101">
-        <v>2.47</v>
-      </c>
-      <c r="AD101">
-        <v>1.46</v>
-      </c>
-      <c r="AE101">
-        <v>1.15</v>
-      </c>
-      <c r="AF101">
-        <v>2.65</v>
-      </c>
-      <c r="AG101">
-        <v>1.5</v>
-      </c>
       <c r="AH101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-04 16:15:00</t>
+          <t>2026-09-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O102">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P102">
-        <v>6.56</v>
+        <v>3.7</v>
       </c>
       <c r="Q102">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T102">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="U102">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="V102">
+        <v>1.64</v>
+      </c>
+      <c r="W102">
+        <v>1.18</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.09</v>
+      </c>
+      <c r="Z102">
+        <v>5.3</v>
+      </c>
+      <c r="AA102">
         <v>1.41</v>
       </c>
-      <c r="W102">
-        <v>1.07</v>
-      </c>
-      <c r="X102">
-        <v>1.03</v>
-      </c>
-      <c r="Y102">
-        <v>1.3</v>
-      </c>
-      <c r="Z102">
-        <v>2.7</v>
-      </c>
-      <c r="AA102">
-        <v>2.25</v>
-      </c>
       <c r="AB102">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC102">
-        <v>4.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD102">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF102">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AG102">
-        <v>1.53</v>
+        <v>2.56</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK102">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-04 17:00:00</t>
+          <t>2026-09-04 18:15:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O103">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q103">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="R103">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="S103">
+        <v>1.33</v>
+      </c>
+      <c r="T103">
+        <v>2.91</v>
+      </c>
+      <c r="U103">
+        <v>2.56</v>
+      </c>
+      <c r="V103">
+        <v>1.42</v>
+      </c>
+      <c r="W103">
+        <v>1.11</v>
+      </c>
+      <c r="X103">
+        <v>1.01</v>
+      </c>
+      <c r="Y103">
         <v>1.2</v>
       </c>
-      <c r="T103">
-        <v>3.7</v>
-      </c>
-      <c r="U103">
-        <v>2.05</v>
-      </c>
-      <c r="V103">
-        <v>1.64</v>
-      </c>
-      <c r="W103">
-        <v>1.18</v>
-      </c>
-      <c r="X103">
-        <v>1.02</v>
-      </c>
-      <c r="Y103">
-        <v>1.09</v>
-      </c>
       <c r="Z103">
-        <v>5.3</v>
+        <v>3.68</v>
       </c>
       <c r="AA103">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AB103">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="AC103">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="AD103">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AE103">
+        <v>1.1</v>
+      </c>
+      <c r="AF103">
+        <v>1.61</v>
+      </c>
+      <c r="AG103">
+        <v>2.16</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
         <v>1.24</v>
       </c>
-      <c r="AF103">
-        <v>1.44</v>
-      </c>
-      <c r="AG103">
-        <v>2.56</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.18</v>
-      </c>
       <c r="AK103">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-04 18:15:00</t>
+          <t>2026-09-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O104">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
         <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB104">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P105">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA105">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AB105">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-04 19:00:00</t>
+          <t>2026-09-04 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="O106">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="Q106">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="R106">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="T106">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="U106">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="V106">
+        <v>1.44</v>
+      </c>
+      <c r="W106">
+        <v>1.06</v>
+      </c>
+      <c r="X106">
+        <v>1.02</v>
+      </c>
+      <c r="Y106">
         <v>1.22</v>
       </c>
-      <c r="W106">
-        <v>1.01</v>
-      </c>
-      <c r="X106">
-        <v>1.11</v>
-      </c>
-      <c r="Y106">
-        <v>1.53</v>
-      </c>
       <c r="Z106">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="AB106">
-        <v>1.46</v>
+        <v>1.92</v>
       </c>
       <c r="AC106">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD106">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AE106">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
-        <v>2.31</v>
+        <v>1.63</v>
       </c>
       <c r="AG106">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-04 19:30:00</t>
+          <t>2026-09-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.53</v>
+        <v>1.64</v>
       </c>
       <c r="O107">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P107">
-        <v>2.06</v>
+        <v>4.75</v>
       </c>
       <c r="Q107">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S107">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T107">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U107">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+      <c r="Z107">
+        <v>0</v>
+      </c>
+      <c r="AA107">
+        <v>2.7</v>
+      </c>
+      <c r="AB107">
         <v>1.44</v>
       </c>
-      <c r="W107">
-        <v>1.1</v>
-      </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.22</v>
-      </c>
-      <c r="Z107">
-        <v>3.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.79</v>
-      </c>
-      <c r="AB107">
-        <v>1.92</v>
-      </c>
       <c r="AC107">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.64</v>
+        <v>2.58</v>
       </c>
       <c r="O108">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="P108">
-        <v>4.75</v>
+        <v>2.54</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA108">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB108">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-09-04 20:00:00</t>
+          <t>2026-09-04 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="O109">
-        <v>3.86</v>
+        <v>2.9</v>
       </c>
       <c r="P109">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="Q109">
-        <v>3.18</v>
+        <v>3.39</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
+        <v>1.52</v>
+      </c>
+      <c r="T109">
+        <v>2.48</v>
+      </c>
+      <c r="U109">
+        <v>3.42</v>
+      </c>
+      <c r="V109">
+        <v>1.25</v>
+      </c>
+      <c r="W109">
+        <v>1.03</v>
+      </c>
+      <c r="X109">
+        <v>1.06</v>
+      </c>
+      <c r="Y109">
+        <v>1.43</v>
+      </c>
+      <c r="Z109">
+        <v>2.8</v>
+      </c>
+      <c r="AA109">
+        <v>2.28</v>
+      </c>
+      <c r="AB109">
+        <v>1.5</v>
+      </c>
+      <c r="AC109">
+        <v>4.86</v>
+      </c>
+      <c r="AD109">
+        <v>1.13</v>
+      </c>
+      <c r="AE109">
+        <v>1.02</v>
+      </c>
+      <c r="AF109">
+        <v>2.02</v>
+      </c>
+      <c r="AG109">
+        <v>1.7</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
         <v>1.35</v>
       </c>
-      <c r="T109">
-        <v>3.27</v>
-      </c>
-      <c r="U109">
-        <v>2.5</v>
-      </c>
-      <c r="V109">
+      <c r="AK109">
         <v>1.47</v>
-      </c>
-      <c r="W109">
-        <v>1.08</v>
-      </c>
-      <c r="X109">
-        <v>1.03</v>
-      </c>
-      <c r="Y109">
-        <v>1.22</v>
-      </c>
-      <c r="Z109">
-        <v>4</v>
-      </c>
-      <c r="AA109">
-        <v>1.75</v>
-      </c>
-      <c r="AB109">
-        <v>2.05</v>
-      </c>
-      <c r="AC109">
-        <v>2.88</v>
-      </c>
-      <c r="AD109">
-        <v>1.4</v>
-      </c>
-      <c r="AE109">
-        <v>1.14</v>
-      </c>
-      <c r="AF109">
-        <v>1.62</v>
-      </c>
-      <c r="AG109">
-        <v>2.2</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.29</v>
-      </c>
-      <c r="AK109">
-        <v>1.45</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,81 +18239,81 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O110">
+        <v>2.9</v>
+      </c>
+      <c r="P110">
+        <v>3.2</v>
+      </c>
+      <c r="Q110">
         <v>3</v>
       </c>
-      <c r="P110">
-        <v>2.55</v>
-      </c>
-      <c r="Q110">
-        <v>3.4</v>
-      </c>
       <c r="R110">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S110">
+        <v>1.46</v>
+      </c>
+      <c r="T110">
+        <v>2.44</v>
+      </c>
+      <c r="U110">
+        <v>3.18</v>
+      </c>
+      <c r="V110">
+        <v>1.28</v>
+      </c>
+      <c r="W110">
+        <v>1.03</v>
+      </c>
+      <c r="X110">
+        <v>1.03</v>
+      </c>
+      <c r="Y110">
+        <v>1.36</v>
+      </c>
+      <c r="Z110">
+        <v>2.7</v>
+      </c>
+      <c r="AA110">
+        <v>2.18</v>
+      </c>
+      <c r="AB110">
+        <v>1.59</v>
+      </c>
+      <c r="AC110">
+        <v>3.98</v>
+      </c>
+      <c r="AD110">
+        <v>1.17</v>
+      </c>
+      <c r="AE110">
+        <v>1.02</v>
+      </c>
+      <c r="AF110">
+        <v>1.88</v>
+      </c>
+      <c r="AG110">
+        <v>1.81</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>1.28</v>
+      </c>
+      <c r="AK110">
         <v>1.51</v>
       </c>
-      <c r="T110">
-        <v>2.45</v>
-      </c>
-      <c r="U110">
-        <v>3.42</v>
-      </c>
-      <c r="V110">
-        <v>1.26</v>
-      </c>
-      <c r="W110">
-        <v>1</v>
-      </c>
-      <c r="X110">
-        <v>1.06</v>
-      </c>
-      <c r="Y110">
-        <v>1.48</v>
-      </c>
-      <c r="Z110">
-        <v>2.9</v>
-      </c>
-      <c r="AA110">
-        <v>2.47</v>
-      </c>
-      <c r="AB110">
-        <v>1.51</v>
-      </c>
-      <c r="AC110">
-        <v>4.97</v>
-      </c>
-      <c r="AD110">
-        <v>1.14</v>
-      </c>
-      <c r="AE110">
-        <v>1.04</v>
-      </c>
-      <c r="AF110">
-        <v>2.02</v>
-      </c>
-      <c r="AG110">
-        <v>1.7</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.35</v>
-      </c>
-      <c r="AK110">
-        <v>1.47</v>
-      </c>
       <c r="AL110">
         <v>0</v>
       </c>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-09-04 20:30:00</t>
+          <t>2026-09-04 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O111">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
+        <v>3.5</v>
+      </c>
+      <c r="Q111">
+        <v>2.47</v>
+      </c>
+      <c r="R111">
+        <v>2.03</v>
+      </c>
+      <c r="S111">
+        <v>1.4</v>
+      </c>
+      <c r="T111">
+        <v>2.95</v>
+      </c>
+      <c r="U111">
+        <v>2.75</v>
+      </c>
+      <c r="V111">
+        <v>1.4</v>
+      </c>
+      <c r="W111">
+        <v>1.06</v>
+      </c>
+      <c r="X111">
+        <v>1.04</v>
+      </c>
+      <c r="Y111">
+        <v>1.3</v>
+      </c>
+      <c r="Z111">
         <v>3.2</v>
       </c>
-      <c r="Q111">
-        <v>3</v>
-      </c>
-      <c r="R111">
-        <v>1.92</v>
-      </c>
-      <c r="S111">
-        <v>1.46</v>
-      </c>
-      <c r="T111">
-        <v>2.44</v>
-      </c>
-      <c r="U111">
-        <v>3.18</v>
-      </c>
-      <c r="V111">
-        <v>1.28</v>
-      </c>
-      <c r="W111">
-        <v>1.03</v>
-      </c>
-      <c r="X111">
-        <v>1.03</v>
-      </c>
-      <c r="Y111">
-        <v>1.36</v>
-      </c>
-      <c r="Z111">
-        <v>2.7</v>
-      </c>
       <c r="AA111">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AB111">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AC111">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="AD111">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF111">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AG111">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
+        <v>3.9</v>
+      </c>
+      <c r="O112">
+        <v>3.1</v>
+      </c>
+      <c r="P112">
+        <v>1.94</v>
+      </c>
+      <c r="Q112">
+        <v>4.7</v>
+      </c>
+      <c r="R112">
         <v>1.95</v>
       </c>
-      <c r="O112">
-        <v>3.2</v>
-      </c>
-      <c r="P112">
-        <v>3.5</v>
-      </c>
-      <c r="Q112">
+      <c r="S112">
+        <v>1.45</v>
+      </c>
+      <c r="T112">
         <v>2.47</v>
       </c>
-      <c r="R112">
-        <v>2.03</v>
-      </c>
-      <c r="S112">
-        <v>1.4</v>
-      </c>
-      <c r="T112">
-        <v>2.95</v>
-      </c>
       <c r="U112">
-        <v>2.75</v>
+        <v>3.19</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X112">
         <v>1.04</v>
       </c>
       <c r="Y112">
+        <v>1.33</v>
+      </c>
+      <c r="Z112">
+        <v>2.83</v>
+      </c>
+      <c r="AA112">
+        <v>2.11</v>
+      </c>
+      <c r="AB112">
+        <v>1.65</v>
+      </c>
+      <c r="AC112">
+        <v>3.58</v>
+      </c>
+      <c r="AD112">
+        <v>1.21</v>
+      </c>
+      <c r="AE112">
+        <v>1.08</v>
+      </c>
+      <c r="AF112">
+        <v>1.88</v>
+      </c>
+      <c r="AG112">
+        <v>1.81</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
         <v>1.3</v>
       </c>
-      <c r="Z112">
-        <v>3.2</v>
-      </c>
-      <c r="AA112">
-        <v>2.02</v>
-      </c>
-      <c r="AB112">
-        <v>1.8</v>
-      </c>
-      <c r="AC112">
-        <v>3.28</v>
-      </c>
-      <c r="AD112">
-        <v>1.25</v>
-      </c>
-      <c r="AE112">
-        <v>1.09</v>
-      </c>
-      <c r="AF112">
-        <v>1.79</v>
-      </c>
-      <c r="AG112">
-        <v>1.91</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.25</v>
-      </c>
       <c r="AK112">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="R113">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="S113">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T113">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="U113">
-        <v>3.19</v>
+        <v>2.5</v>
       </c>
       <c r="V113">
+        <v>1.42</v>
+      </c>
+      <c r="W113">
+        <v>1.06</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.22</v>
+      </c>
+      <c r="Z113">
+        <v>3.8</v>
+      </c>
+      <c r="AA113">
+        <v>1.89</v>
+      </c>
+      <c r="AB113">
+        <v>1.9</v>
+      </c>
+      <c r="AC113">
+        <v>2.92</v>
+      </c>
+      <c r="AD113">
         <v>1.31</v>
-      </c>
-      <c r="W113">
-        <v>1.04</v>
-      </c>
-      <c r="X113">
-        <v>1.04</v>
-      </c>
-      <c r="Y113">
-        <v>1.33</v>
-      </c>
-      <c r="Z113">
-        <v>2.83</v>
-      </c>
-      <c r="AA113">
-        <v>2.11</v>
-      </c>
-      <c r="AB113">
-        <v>1.65</v>
-      </c>
-      <c r="AC113">
-        <v>3.58</v>
-      </c>
-      <c r="AD113">
-        <v>1.21</v>
       </c>
       <c r="AE113">
         <v>1.08</v>
       </c>
       <c r="AF113">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG113">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G114">
@@ -18900,55 +18900,55 @@
         <v>0</v>
       </c>
       <c r="Q114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R114">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S114">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T114">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U114">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V114">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W114">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y114">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z114">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC114">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD114">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF114">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG114">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK114">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-04 21:30:00</t>
+          <t>2026-09-04 22:30:00</t>
         </is>
       </c>
     </row>
@@ -19007,7 +19007,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G115">
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19157,169 +19157,6 @@
         <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
-        <is>
-          <t>2026-09-04 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>3.8</v>
-      </c>
-      <c r="R116">
-        <v>2.35</v>
-      </c>
-      <c r="S116">
-        <v>1.25</v>
-      </c>
-      <c r="T116">
-        <v>3.6</v>
-      </c>
-      <c r="U116">
-        <v>2.32</v>
-      </c>
-      <c r="V116">
-        <v>1.55</v>
-      </c>
-      <c r="W116">
-        <v>1.11</v>
-      </c>
-      <c r="X116">
-        <v>1.02</v>
-      </c>
-      <c r="Y116">
-        <v>1.13</v>
-      </c>
-      <c r="Z116">
-        <v>4.55</v>
-      </c>
-      <c r="AA116">
-        <v>1.54</v>
-      </c>
-      <c r="AB116">
-        <v>2.29</v>
-      </c>
-      <c r="AC116">
-        <v>2.33</v>
-      </c>
-      <c r="AD116">
-        <v>1.48</v>
-      </c>
-      <c r="AE116">
-        <v>1.16</v>
-      </c>
-      <c r="AF116">
-        <v>1.36</v>
-      </c>
-      <c r="AG116">
-        <v>2.15</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.2</v>
-      </c>
-      <c r="AK116">
-        <v>1.26</v>
-      </c>
-      <c r="AL116">
-        <v>0</v>
-      </c>
-      <c r="AM116">
-        <v>-1</v>
-      </c>
-      <c r="AN116">
-        <v>-1</v>
-      </c>
-      <c r="AO116">
-        <v>-1</v>
-      </c>
-      <c r="AP116">
-        <v>-1</v>
-      </c>
-      <c r="AQ116">
-        <v>0</v>
-      </c>
-      <c r="AR116">
-        <v>0</v>
-      </c>
-      <c r="AS116">
-        <v>0</v>
-      </c>
-      <c r="AT116">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
         <is>
           <t>2026-09-04 23:00:00</t>
         </is>

--- a/jogos_2026-09-04.xlsx
+++ b/jogos_2026-09-04.xlsx
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -831,31 +831,31 @@
         <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AA3">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="R4">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.89</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.39</v>
+        <v>2.19</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.66</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="AC5">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="AK5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
-        <v>5.08</v>
+        <v>4.76</v>
       </c>
       <c r="R7">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="S7">
         <v>1.33</v>
@@ -1471,43 +1471,43 @@
         <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
         <v>1.04</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC7">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD7">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="P13">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Q13">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="R13">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="S13">
         <v>1.18</v>
       </c>
       <c r="T13">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U13">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="V13">
         <v>1.67</v>
@@ -2464,7 +2464,7 @@
         <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA13">
         <v>1.38</v>
@@ -2473,16 +2473,16 @@
         <v>2.62</v>
       </c>
       <c r="AC13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD13">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF13">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG13">
         <v>1.75</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
         <v>2.8</v>
@@ -2600,34 +2600,34 @@
         <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R14">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U14">
         <v>3.42</v>
       </c>
       <c r="V14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AA14">
         <v>2.5</v>
@@ -2636,35 +2636,35 @@
         <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>5.25</v>
+        <v>4.45</v>
       </c>
       <c r="AD14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
         <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG14">
+        <v>1.66</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.2</v>
+      </c>
+      <c r="AK14">
         <v>1.65</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.29</v>
-      </c>
-      <c r="AK14">
-        <v>1.57</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3092,22 +3092,22 @@
         <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3116,22 +3116,22 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB17">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
         <v>1.53</v>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q18">
-        <v>4.16</v>
+        <v>3.88</v>
       </c>
       <c r="R18">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S18">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="U18">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AA18">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB18">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC18">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG18">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
         <v>1.29</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
         <v>1.5</v>
@@ -3602,22 +3602,22 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
         <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O22">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="P22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R22">
         <v>2.15</v>
@@ -3916,34 +3916,34 @@
         <v>3.08</v>
       </c>
       <c r="U22">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB22">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC22">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
         <v>1.16</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>2.15</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P23">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
         <v>2.94</v>
@@ -4076,7 +4076,7 @@
         <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="U23">
         <v>3.25</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="O24">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="R24">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
         <v>1.11</v>
       </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.13</v>
-      </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA24">
         <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC24">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AD24">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,28 +4393,28 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R25">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
         <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.13</v>
@@ -4432,16 +4432,16 @@
         <v>2.35</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="Q26">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
+        <v>2.33</v>
+      </c>
+      <c r="S26">
+        <v>1.3</v>
+      </c>
+      <c r="T26">
+        <v>3.14</v>
+      </c>
+      <c r="U26">
+        <v>2.47</v>
+      </c>
+      <c r="V26">
+        <v>1.49</v>
+      </c>
+      <c r="W26">
+        <v>1.08</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.17</v>
+      </c>
+      <c r="Z26">
+        <v>3.98</v>
+      </c>
+      <c r="AA26">
+        <v>1.7</v>
+      </c>
+      <c r="AB26">
         <v>2.04</v>
       </c>
-      <c r="S26">
+      <c r="AC26">
+        <v>2.88</v>
+      </c>
+      <c r="AD26">
         <v>1.36</v>
       </c>
-      <c r="T26">
-        <v>2.9</v>
-      </c>
-      <c r="U26">
-        <v>2.67</v>
-      </c>
-      <c r="V26">
-        <v>1.38</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.25</v>
-      </c>
-      <c r="Z26">
-        <v>3.28</v>
-      </c>
-      <c r="AA26">
-        <v>1.9</v>
-      </c>
-      <c r="AB26">
-        <v>1.84</v>
-      </c>
-      <c r="AC26">
-        <v>2.97</v>
-      </c>
-      <c r="AD26">
-        <v>1.3</v>
-      </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC27">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AD27">
+        <v>1.71</v>
+      </c>
+      <c r="AE27">
+        <v>1.27</v>
+      </c>
+      <c r="AF27">
+        <v>1.36</v>
+      </c>
+      <c r="AG27">
+        <v>2.7</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.22</v>
+      </c>
+      <c r="AK27">
         <v>1.59</v>
-      </c>
-      <c r="AE27">
-        <v>1.21</v>
-      </c>
-      <c r="AF27">
-        <v>1.43</v>
-      </c>
-      <c r="AG27">
-        <v>2.5</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.19</v>
-      </c>
-      <c r="AK27">
-        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.78</v>
+        <v>2.64</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="U28">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
+        <v>1.84</v>
+      </c>
+      <c r="AC28">
+        <v>3</v>
+      </c>
+      <c r="AD28">
+        <v>1.3</v>
+      </c>
+      <c r="AE28">
+        <v>1.07</v>
+      </c>
+      <c r="AF28">
+        <v>1.65</v>
+      </c>
+      <c r="AG28">
         <v>2.07</v>
       </c>
-      <c r="AC28">
-        <v>2.88</v>
-      </c>
-      <c r="AD28">
-        <v>1.36</v>
-      </c>
-      <c r="AE28">
-        <v>1.13</v>
-      </c>
-      <c r="AF28">
-        <v>1.62</v>
-      </c>
-      <c r="AG28">
-        <v>2.15</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P29">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="R29">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="S29">
         <v>1.44</v>
@@ -5066,16 +5066,16 @@
         <v>1.01</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
         <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="AA29">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB29">
         <v>1.57</v>
@@ -5084,13 +5084,13 @@
         <v>4.15</v>
       </c>
       <c r="AD29">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG29">
         <v>1.78</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U30">
         <v>2.67</v>
@@ -5226,10 +5226,10 @@
         <v>1.41</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
         <v>1.22</v>
@@ -5244,19 +5244,19 @@
         <v>1.9</v>
       </c>
       <c r="AC30">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P31">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S31">
         <v>1.49</v>
@@ -5386,28 +5386,28 @@
         <v>3.4</v>
       </c>
       <c r="V31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
         <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z31">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AA31">
         <v>2.45</v>
       </c>
       <c r="AB31">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC31">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
         <v>1.18</v>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="O32">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P32">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>1.7</v>
       </c>
       <c r="R32">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="S32">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U32">
         <v>1.95</v>
@@ -5552,37 +5552,37 @@
         <v>1.77</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>6.1</v>
+        <v>5.88</v>
       </c>
       <c r="AA32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB32">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC32">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD32">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE32">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF32">
         <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O33">
         <v>4</v>
       </c>
       <c r="P33">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q33">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="R33">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="S33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="U33">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
         <v>1.14</v>
       </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.1</v>
-      </c>
       <c r="Z33">
-        <v>5.15</v>
+        <v>4.45</v>
       </c>
       <c r="AA33">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AB33">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="AC33">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="AD33">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>5.66</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q34">
         <v>6.45</v>
@@ -5890,7 +5890,7 @@
         <v>2.78</v>
       </c>
       <c r="AA34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB34">
         <v>1.67</v>
@@ -5899,16 +5899,16 @@
         <v>3.72</v>
       </c>
       <c r="AD34">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q35">
         <v>2.27</v>
@@ -6032,7 +6032,7 @@
         <v>1.31</v>
       </c>
       <c r="T35">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
         <v>2.42</v>
@@ -6047,10 +6047,10 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA35">
         <v>1.8</v>
@@ -6068,7 +6068,7 @@
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG35">
         <v>2</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O36">
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -6198,7 +6198,7 @@
         <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="V36">
         <v>1.47</v>
@@ -6213,22 +6213,22 @@
         <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC36">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
         <v>1.55</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK36">
         <v>1.55</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q37">
         <v>2.02</v>
@@ -6355,19 +6355,19 @@
         <v>2.39</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T37">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="U37">
         <v>2.1</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.01</v>
@@ -6376,28 +6376,28 @@
         <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AC37">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
         <v>1.44</v>
       </c>
       <c r="AG37">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O38">
         <v>3.68</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q38">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
         <v>1.28</v>
@@ -6527,7 +6527,7 @@
         <v>2.34</v>
       </c>
       <c r="V38">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W38">
         <v>1.09</v>
@@ -6536,13 +6536,13 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB38">
         <v>2.25</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,58 +6666,58 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O39">
+        <v>4.33</v>
+      </c>
+      <c r="P39">
+        <v>1.61</v>
+      </c>
+      <c r="Q39">
         <v>4.2</v>
       </c>
-      <c r="P39">
-        <v>1.65</v>
-      </c>
-      <c r="Q39">
-        <v>4.25</v>
-      </c>
       <c r="R39">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U39">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>5.48</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF39">
         <v>1.52</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,16 +6832,16 @@
         <v>1.48</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P40">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q40">
         <v>1.91</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
         <v>1.29</v>
@@ -6853,7 +6853,7 @@
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
         <v>1.1</v>
@@ -6874,19 +6874,19 @@
         <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
         <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
         <v>2.4</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O41">
         <v>5.2</v>
       </c>
       <c r="P41">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q44">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U44">
         <v>2.25</v>
       </c>
       <c r="V44">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
         <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.5</v>
+        <v>4.99</v>
       </c>
       <c r="AA44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB44">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC44">
         <v>2.38</v>
       </c>
       <c r="AD44">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O47">
-        <v>3.73</v>
+        <v>3.88</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>3.95</v>
       </c>
       <c r="Q47">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="R47">
         <v>2.34</v>
@@ -7991,13 +7991,13 @@
         <v>3.45</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8018,10 +8018,10 @@
         <v>2.38</v>
       </c>
       <c r="AD47">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
         <v>1.48</v>
@@ -8043,7 +8043,7 @@
         <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="O48">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="P48">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q48">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S48">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="T48">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U48">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="V48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
         <v>1.1</v>
       </c>
       <c r="Y48">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Z48">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AA48">
         <v>3</v>
       </c>
       <c r="AB48">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC48">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AD48">
         <v>1.07</v>
       </c>
       <c r="AE48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG48">
         <v>1.57</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK48">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,13 +8299,13 @@
         <v>2.45</v>
       </c>
       <c r="O49">
+        <v>2.7</v>
+      </c>
+      <c r="P49">
         <v>2.75</v>
       </c>
-      <c r="P49">
-        <v>3.1</v>
-      </c>
       <c r="Q49">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R49">
         <v>1.74</v>
@@ -8323,7 +8323,7 @@
         <v>1.19</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
         <v>1.08</v>
@@ -8344,7 +8344,7 @@
         <v>5.45</v>
       </c>
       <c r="AD49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE49">
         <v>1.04</v>
@@ -8369,7 +8369,7 @@
         <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,61 +8462,61 @@
         <v>3.01</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P50">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q50">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="R50">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S50">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T50">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="U50">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="V50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
         <v>1.65</v>
       </c>
       <c r="AC50">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AD50">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG50">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
         <v>4</v>
       </c>
       <c r="P51">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="Q51">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R51">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
         <v>1.2</v>
@@ -8643,10 +8643,10 @@
         <v>4.1</v>
       </c>
       <c r="U51">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="V51">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W51">
         <v>1.15</v>
@@ -8658,28 +8658,28 @@
         <v>1.06</v>
       </c>
       <c r="Z51">
-        <v>6.2</v>
+        <v>6.23</v>
       </c>
       <c r="AA51">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AC51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD51">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE51">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK51">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O52">
         <v>3.5</v>
@@ -8794,10 +8794,10 @@
         <v>2.1</v>
       </c>
       <c r="Q52">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8809,34 +8809,34 @@
         <v>2.16</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA52">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AC52">
         <v>2.2</v>
       </c>
       <c r="AD52">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
         <v>1.41</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="AK52">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,28 +8951,28 @@
         <v>2.26</v>
       </c>
       <c r="O53">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
         <v>3.5</v>
       </c>
       <c r="Q53">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
         <v>1.05</v>
@@ -8984,7 +8984,7 @@
         <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA53">
         <v>1.8</v>
@@ -8996,7 +8996,7 @@
         <v>2.95</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE53">
         <v>1.14</v>
@@ -9021,7 +9021,7 @@
         <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O54">
         <v>5</v>
       </c>
       <c r="P54">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="Q54">
         <v>1.67</v>
@@ -9129,25 +9129,25 @@
         <v>1.2</v>
       </c>
       <c r="T54">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="U54">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V54">
         <v>1.7</v>
       </c>
       <c r="W54">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>5.2</v>
+        <v>5.54</v>
       </c>
       <c r="AA54">
         <v>1.44</v>
@@ -9162,7 +9162,7 @@
         <v>1.68</v>
       </c>
       <c r="AE54">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF54">
         <v>1.67</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK54">
         <v>2.79</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>7.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O55">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P55">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q55">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="R55">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="S55">
         <v>1.17</v>
@@ -9295,43 +9295,43 @@
         <v>4.5</v>
       </c>
       <c r="U55">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V55">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W55">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>6.31</v>
+        <v>6.56</v>
       </c>
       <c r="AA55">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB55">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC55">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AD55">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF55">
         <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O56">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q56">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="R56">
         <v>2</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="U56">
         <v>2.94</v>
@@ -9470,10 +9470,10 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z56">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="AA56">
         <v>2.05</v>
@@ -9485,16 +9485,16 @@
         <v>3.38</v>
       </c>
       <c r="AD56">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
         <v>1.05</v>
       </c>
       <c r="AF56">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG56">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O57">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="Q57">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="R57">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T57">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U57">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y57">
         <v>1.28</v>
       </c>
       <c r="Z57">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA57">
         <v>2.1</v>
       </c>
       <c r="AB57">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC57">
-        <v>3.38</v>
+        <v>3.97</v>
       </c>
       <c r="AD57">
         <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF57">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG57">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,65 +9763,65 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.73</v>
+        <v>2.51</v>
       </c>
       <c r="O58">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="P58">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q58">
-        <v>2.29</v>
+        <v>3.4</v>
       </c>
       <c r="R58">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U58">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
         <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>3.63</v>
+        <v>3.23</v>
       </c>
       <c r="AA58">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB58">
+        <v>1.7</v>
+      </c>
+      <c r="AC58">
+        <v>3.75</v>
+      </c>
+      <c r="AD58">
+        <v>1.25</v>
+      </c>
+      <c r="AE58">
+        <v>1.05</v>
+      </c>
+      <c r="AF58">
+        <v>1.77</v>
+      </c>
+      <c r="AG58">
         <v>1.94</v>
       </c>
-      <c r="AC58">
-        <v>2.8</v>
-      </c>
-      <c r="AD58">
-        <v>1.36</v>
-      </c>
-      <c r="AE58">
-        <v>1.1</v>
-      </c>
-      <c r="AF58">
-        <v>1.66</v>
-      </c>
-      <c r="AG58">
-        <v>2</v>
-      </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="AK58">
-        <v>2.09</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,65 +9926,65 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P59">
+        <v>2.66</v>
+      </c>
+      <c r="Q59">
+        <v>3.5</v>
+      </c>
+      <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
+        <v>1.44</v>
+      </c>
+      <c r="T59">
+        <v>2.59</v>
+      </c>
+      <c r="U59">
+        <v>3.2</v>
+      </c>
+      <c r="V59">
+        <v>1.3</v>
+      </c>
+      <c r="W59">
+        <v>1.02</v>
+      </c>
+      <c r="X59">
+        <v>1.09</v>
+      </c>
+      <c r="Y59">
+        <v>1.44</v>
+      </c>
+      <c r="Z59">
+        <v>2.85</v>
+      </c>
+      <c r="AA59">
         <v>2.3</v>
       </c>
-      <c r="Q59">
-        <v>3.23</v>
-      </c>
-      <c r="R59">
-        <v>2.1</v>
-      </c>
-      <c r="S59">
-        <v>1.43</v>
-      </c>
-      <c r="T59">
-        <v>2.62</v>
-      </c>
-      <c r="U59">
-        <v>2.8</v>
-      </c>
-      <c r="V59">
-        <v>1.35</v>
-      </c>
-      <c r="W59">
+      <c r="AB59">
+        <v>1.58</v>
+      </c>
+      <c r="AC59">
+        <v>4.33</v>
+      </c>
+      <c r="AD59">
+        <v>1.2</v>
+      </c>
+      <c r="AE59">
         <v>1.03</v>
       </c>
-      <c r="X59">
-        <v>1.04</v>
-      </c>
-      <c r="Y59">
-        <v>1.35</v>
-      </c>
-      <c r="Z59">
-        <v>3.18</v>
-      </c>
-      <c r="AA59">
-        <v>2.03</v>
-      </c>
-      <c r="AB59">
-        <v>1.69</v>
-      </c>
-      <c r="AC59">
-        <v>3.82</v>
-      </c>
-      <c r="AD59">
-        <v>1.24</v>
-      </c>
-      <c r="AE59">
-        <v>1.05</v>
-      </c>
       <c r="AF59">
+        <v>1.88</v>
+      </c>
+      <c r="AG59">
         <v>1.77</v>
       </c>
-      <c r="AG59">
-        <v>1.97</v>
-      </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK59">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,65 +10089,65 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="O60">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="P60">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="Q60">
-        <v>3.46</v>
+        <v>2.46</v>
       </c>
       <c r="R60">
+        <v>2.2</v>
+      </c>
+      <c r="S60">
+        <v>1.33</v>
+      </c>
+      <c r="T60">
+        <v>3.04</v>
+      </c>
+      <c r="U60">
+        <v>2.86</v>
+      </c>
+      <c r="V60">
+        <v>1.41</v>
+      </c>
+      <c r="W60">
+        <v>1.07</v>
+      </c>
+      <c r="X60">
+        <v>1.01</v>
+      </c>
+      <c r="Y60">
+        <v>1.29</v>
+      </c>
+      <c r="Z60">
+        <v>3.6</v>
+      </c>
+      <c r="AA60">
+        <v>1.93</v>
+      </c>
+      <c r="AB60">
+        <v>1.93</v>
+      </c>
+      <c r="AC60">
+        <v>2.8</v>
+      </c>
+      <c r="AD60">
+        <v>1.38</v>
+      </c>
+      <c r="AE60">
+        <v>1.08</v>
+      </c>
+      <c r="AF60">
+        <v>1.66</v>
+      </c>
+      <c r="AG60">
         <v>2</v>
       </c>
-      <c r="S60">
-        <v>1.44</v>
-      </c>
-      <c r="T60">
-        <v>2.59</v>
-      </c>
-      <c r="U60">
-        <v>3.2</v>
-      </c>
-      <c r="V60">
-        <v>1.3</v>
-      </c>
-      <c r="W60">
-        <v>1.02</v>
-      </c>
-      <c r="X60">
-        <v>1.09</v>
-      </c>
-      <c r="Y60">
-        <v>1.4</v>
-      </c>
-      <c r="Z60">
-        <v>2.88</v>
-      </c>
-      <c r="AA60">
-        <v>2.3</v>
-      </c>
-      <c r="AB60">
-        <v>1.57</v>
-      </c>
-      <c r="AC60">
-        <v>4.33</v>
-      </c>
-      <c r="AD60">
-        <v>1.2</v>
-      </c>
-      <c r="AE60">
-        <v>1.02</v>
-      </c>
-      <c r="AF60">
-        <v>1.91</v>
-      </c>
-      <c r="AG60">
-        <v>1.73</v>
-      </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK60">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O61">
         <v>3.7</v>
@@ -10261,55 +10261,55 @@
         <v>4</v>
       </c>
       <c r="Q61">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="R61">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T61">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U61">
         <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="AA61">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB61">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC61">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG61">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.51</v>
+        <v>2.97</v>
       </c>
       <c r="Q62">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S62">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T62">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U62">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V62">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z62">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA62">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB62">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC62">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD62">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE62">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG62">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
         <v>1.56</v>
@@ -10587,19 +10587,19 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="R63">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S63">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
         <v>2.7</v>
       </c>
       <c r="U63">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="V63">
         <v>1.37</v>
@@ -10611,13 +10611,13 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z63">
         <v>3.14</v>
       </c>
       <c r="AA63">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB63">
         <v>1.83</v>
@@ -10626,16 +10626,16 @@
         <v>3.14</v>
       </c>
       <c r="AD63">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE63">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10747,58 +10747,58 @@
         <v>3.8</v>
       </c>
       <c r="P64">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q64">
         <v>1.99</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U64">
         <v>2.4</v>
       </c>
       <c r="V64">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>3.84</v>
+        <v>4.16</v>
       </c>
       <c r="AA64">
         <v>1.73</v>
       </c>
       <c r="AB64">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC64">
         <v>2.88</v>
       </c>
       <c r="AD64">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF64">
         <v>1.7</v>
       </c>
       <c r="AG64">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R65">
         <v>2.36</v>
       </c>
       <c r="S65">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U65">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="V65">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W65">
         <v>1.16</v>
@@ -10940,7 +10940,7 @@
         <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>5.1</v>
+        <v>6.01</v>
       </c>
       <c r="AA65">
         <v>1.42</v>
@@ -10949,19 +10949,19 @@
         <v>2.51</v>
       </c>
       <c r="AC65">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD65">
         <v>1.72</v>
       </c>
       <c r="AE65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11079,22 +11079,22 @@
         <v>3.38</v>
       </c>
       <c r="R66">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="S66">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T66">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="U66">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="V66">
         <v>1.22</v>
       </c>
       <c r="W66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
         <v>1.06</v>
@@ -11106,7 +11106,7 @@
         <v>2.46</v>
       </c>
       <c r="AA66">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AB66">
         <v>1.48</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
         <v>1.39</v>
@@ -11233,13 +11233,13 @@
         <v>1.51</v>
       </c>
       <c r="O67">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P67">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q67">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="R67">
         <v>2.43</v>
@@ -11257,37 +11257,37 @@
         <v>1.62</v>
       </c>
       <c r="W67">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.31</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB67">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AC67">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD67">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE67">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF67">
         <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,7 +11402,7 @@
         <v>5</v>
       </c>
       <c r="Q68">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R68">
         <v>2.95</v>
@@ -11414,22 +11414,22 @@
         <v>4.5</v>
       </c>
       <c r="U68">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V68">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="W68">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z68">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA68">
         <v>1.24</v>
@@ -11438,19 +11438,19 @@
         <v>3.34</v>
       </c>
       <c r="AC68">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE68">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF68">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG68">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK68">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="O69">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P69">
-        <v>5.25</v>
+        <v>2.61</v>
       </c>
       <c r="Q69">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="S69">
+        <v>1.19</v>
+      </c>
+      <c r="T69">
+        <v>3.9</v>
+      </c>
+      <c r="U69">
+        <v>1.95</v>
+      </c>
+      <c r="V69">
+        <v>1.77</v>
+      </c>
+      <c r="W69">
         <v>1.15</v>
       </c>
-      <c r="T69">
-        <v>4.8</v>
-      </c>
-      <c r="U69">
-        <v>1.85</v>
-      </c>
-      <c r="V69">
-        <v>1.89</v>
-      </c>
-      <c r="W69">
-        <v>1.23</v>
-      </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z69">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA69">
+        <v>1.42</v>
+      </c>
+      <c r="AB69">
+        <v>2.9</v>
+      </c>
+      <c r="AC69">
+        <v>2</v>
+      </c>
+      <c r="AD69">
+        <v>1.73</v>
+      </c>
+      <c r="AE69">
         <v>1.25</v>
       </c>
-      <c r="AB69">
-        <v>3.2</v>
-      </c>
-      <c r="AC69">
-        <v>1.74</v>
-      </c>
-      <c r="AD69">
-        <v>2.04</v>
-      </c>
-      <c r="AE69">
-        <v>1.42</v>
-      </c>
       <c r="AF69">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AG69">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AK69">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,52 +11719,52 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
         <v>3.35</v>
       </c>
       <c r="P70">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q70">
         <v>2.95</v>
       </c>
       <c r="R70">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U70">
         <v>2.32</v>
       </c>
       <c r="V70">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
         <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB70">
         <v>2.27</v>
       </c>
       <c r="AC70">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD70">
         <v>1.47</v>
@@ -11773,7 +11773,7 @@
         <v>1.16</v>
       </c>
       <c r="AF70">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG70">
         <v>2.5</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P71">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q71">
         <v>3</v>
       </c>
       <c r="R71">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S71">
         <v>1.23</v>
@@ -11915,25 +11915,25 @@
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z71">
-        <v>5.25</v>
+        <v>5.61</v>
       </c>
       <c r="AA71">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC71">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AD71">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF71">
         <v>1.41</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="O72">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P72">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="Q72">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="R72">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="S72">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="T72">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="U72">
+        <v>1.77</v>
+      </c>
+      <c r="V72">
         <v>1.95</v>
       </c>
-      <c r="V72">
-        <v>1.77</v>
-      </c>
       <c r="W72">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z72">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="AA72">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB72">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AC72">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD72">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AE72">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AF72">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12211,31 +12211,31 @@
         <v>2.15</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q73">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S73">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
         <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.03</v>
@@ -12244,13 +12244,13 @@
         <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="AA73">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB73">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC73">
         <v>2.55</v>
@@ -12259,7 +12259,7 @@
         <v>1.5</v>
       </c>
       <c r="AE73">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
         <v>1.5</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,43 +12371,43 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="O74">
+        <v>3.65</v>
+      </c>
+      <c r="P74">
         <v>3.7</v>
       </c>
-      <c r="P74">
-        <v>4.03</v>
-      </c>
       <c r="Q74">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="R74">
         <v>2.5</v>
       </c>
       <c r="S74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U74">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="V74">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W74">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z74">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA74">
         <v>1.57</v>
@@ -12419,16 +12419,16 @@
         <v>2.34</v>
       </c>
       <c r="AD74">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
         <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK74">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12537,31 +12537,31 @@
         <v>1.95</v>
       </c>
       <c r="O75">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q75">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="S75">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U75">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V75">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W75">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X75">
         <v>1.02</v>
@@ -12573,19 +12573,19 @@
         <v>5.25</v>
       </c>
       <c r="AA75">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB75">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AC75">
         <v>2.15</v>
       </c>
       <c r="AD75">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE75">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF75">
         <v>1.36</v>
@@ -12607,7 +12607,7 @@
         <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O76">
         <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q76">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R76">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S76">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U76">
         <v>3</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W76">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z76">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA76">
         <v>2.1</v>
       </c>
       <c r="AB76">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC76">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD76">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF76">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK76">
         <v>1.67</v>
@@ -12863,7 +12863,7 @@
         <v>1.4</v>
       </c>
       <c r="O77">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P77">
         <v>7.5</v>
@@ -12872,25 +12872,25 @@
         <v>1.83</v>
       </c>
       <c r="R77">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V77">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
         <v>1.18</v>
@@ -12902,13 +12902,13 @@
         <v>1.7</v>
       </c>
       <c r="AB77">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC77">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="AD77">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE77">
         <v>1.11</v>
@@ -12917,7 +12917,7 @@
         <v>1.9</v>
       </c>
       <c r="AG77">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O78">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
         <v>2.25</v>
       </c>
       <c r="Q78">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R78">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T78">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U78">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
         <v>1.19</v>
       </c>
       <c r="Z78">
-        <v>4.15</v>
+        <v>3.78</v>
       </c>
       <c r="AA78">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB78">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AC78">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AD78">
+        <v>1.36</v>
+      </c>
+      <c r="AE78">
+        <v>1.07</v>
+      </c>
+      <c r="AF78">
+        <v>1.59</v>
+      </c>
+      <c r="AG78">
+        <v>2.19</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.22</v>
+      </c>
+      <c r="AK78">
         <v>1.4</v>
-      </c>
-      <c r="AE78">
-        <v>1.11</v>
-      </c>
-      <c r="AF78">
-        <v>1.65</v>
-      </c>
-      <c r="AG78">
-        <v>2.21</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.28</v>
-      </c>
-      <c r="AK78">
-        <v>1.39</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="O80">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P80">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="Q80">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S80">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T80">
         <v>2.53</v>
       </c>
       <c r="U80">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
         <v>1.04</v>
@@ -13382,28 +13382,28 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA80">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB80">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC80">
         <v>3.81</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE80">
         <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG80">
         <v>1.79</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK80">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P81">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="Q81">
         <v>2.85</v>
@@ -13536,7 +13536,7 @@
         <v>2.3</v>
       </c>
       <c r="V81">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W81">
         <v>1.13</v>
@@ -13566,10 +13566,10 @@
         <v>1.13</v>
       </c>
       <c r="AF81">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG81">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O82">
+        <v>4.9</v>
+      </c>
+      <c r="P82">
+        <v>5</v>
+      </c>
+      <c r="Q82">
+        <v>1.83</v>
+      </c>
+      <c r="R82">
+        <v>2.75</v>
+      </c>
+      <c r="S82">
+        <v>1.14</v>
+      </c>
+      <c r="T82">
         <v>4.8</v>
-      </c>
-      <c r="P82">
-        <v>4.8</v>
-      </c>
-      <c r="Q82">
-        <v>1.91</v>
-      </c>
-      <c r="R82">
-        <v>2.7</v>
-      </c>
-      <c r="S82">
-        <v>1.2</v>
-      </c>
-      <c r="T82">
-        <v>4.35</v>
       </c>
       <c r="U82">
         <v>1.91</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AA82">
         <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="AC82">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AD82">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE82">
         <v>1.37</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG82">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,13 +13844,13 @@
         <v>3.25</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q83">
         <v>3</v>
       </c>
       <c r="R83">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
         <v>1.39</v>
@@ -13859,13 +13859,13 @@
         <v>2.66</v>
       </c>
       <c r="U83">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13877,10 +13877,10 @@
         <v>2.5</v>
       </c>
       <c r="AA83">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB83">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AC83">
         <v>3.5</v>
@@ -13892,10 +13892,10 @@
         <v>1.04</v>
       </c>
       <c r="AF83">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG83">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">